--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
-    <sheet name="定制" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,39 +32,7 @@
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="F3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1 神圣套</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>admin</author>
-  </authors>
-  <commentList>
-    <comment ref="F3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -92,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>ID</t>
   </si>
@@ -100,6 +67,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Cycle</t>
+  </si>
+  <si>
     <t>Part</t>
   </si>
   <si>
@@ -109,7 +79,10 @@
     <t>Level</t>
   </si>
   <si>
-    <t>品质</t>
+    <t>StartQuality</t>
+  </si>
+  <si>
+    <t>EndQuality</t>
   </si>
   <si>
     <t>词条</t>
@@ -121,9 +94,6 @@
     <t>Id</t>
   </si>
   <si>
-    <t>Quality</t>
-  </si>
-  <si>
     <t>RuneId</t>
   </si>
   <si>
@@ -136,25 +106,82 @@
     <t>string</t>
   </si>
   <si>
+    <t>神圣狂斩</t>
+  </si>
+  <si>
+    <t>神圣破魂</t>
+  </si>
+  <si>
+    <t>神圣血刃</t>
+  </si>
+  <si>
+    <t>神圣屠龙</t>
+  </si>
+  <si>
+    <t>神圣倚天</t>
+  </si>
+  <si>
+    <t>神圣天命</t>
+  </si>
+  <si>
+    <t>传奇狂斩</t>
+  </si>
+  <si>
+    <t>传奇破魂</t>
+  </si>
+  <si>
+    <t>传奇血刃</t>
+  </si>
+  <si>
+    <t>传奇屠龙</t>
+  </si>
+  <si>
+    <t>传奇倚天</t>
+  </si>
+  <si>
+    <t>传奇天命</t>
+  </si>
+  <si>
+    <t>不朽狂斩</t>
+  </si>
+  <si>
+    <t>不朽破魂</t>
+  </si>
+  <si>
+    <t>不朽血刃</t>
+  </si>
+  <si>
+    <t>不朽屠龙</t>
+  </si>
+  <si>
+    <t>不朽倚天</t>
+  </si>
+  <si>
+    <t>不朽天命</t>
+  </si>
+  <si>
+    <t>永恒狂斩</t>
+  </si>
+  <si>
+    <t>永恒破魂</t>
+  </si>
+  <si>
+    <t>永恒血刃</t>
+  </si>
+  <si>
+    <t>永恒屠龙</t>
+  </si>
+  <si>
+    <t>永恒倚天</t>
+  </si>
+  <si>
+    <t>永恒天命</t>
+  </si>
+  <si>
     <t>神圣怒斩</t>
   </si>
   <si>
     <t>神圣噬魂</t>
-  </si>
-  <si>
-    <t>神圣血饮</t>
-  </si>
-  <si>
-    <t>神圣屠龙</t>
-  </si>
-  <si>
-    <t>神圣倚天</t>
-  </si>
-  <si>
-    <t>神圣命运</t>
-  </si>
-  <si>
-    <t>#</t>
   </si>
 </sst>
 </file>
@@ -1124,28 +1151,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:L53"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" style="1" customWidth="1"/>
-    <col min="8" max="10" width="12.25" customWidth="1"/>
-    <col min="11" max="16371" width="9" style="2"/>
+    <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.125" style="1" customWidth="1"/>
+    <col min="9" max="12" width="12.25" customWidth="1"/>
+    <col min="13" max="16373" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:2">
+    <row r="1" s="1" customFormat="1" ht="13" spans="1:2">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:2">
+    <row r="2" s="1" customFormat="1" ht="13" spans="1:2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1172,12 +1199,18 @@
       <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
+      <c r="K3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>1</v>
@@ -1192,632 +1225,1027 @@
         <v>4</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
+      <c r="L4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="13.5" spans="1:12">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>13</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>15</v>
       </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K6">
+        <v>-1</v>
+      </c>
+      <c r="L6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C7">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
         <v>16</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>1</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K7">
+        <v>-1</v>
+      </c>
+      <c r="L7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
         <v>17</v>
       </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>1</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K8">
+        <v>-1</v>
+      </c>
+      <c r="L8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
         <v>18</v>
       </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K9">
+        <v>-1</v>
+      </c>
+      <c r="L9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
         <v>19</v>
       </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="27" customHeight="1" spans="3:10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>-1</v>
+      </c>
+      <c r="L10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="27" customHeight="1" spans="3:12">
       <c r="C11">
         <v>6</v>
       </c>
       <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11">
+        <v>-1</v>
+      </c>
+      <c r="L11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" ht="27" customHeight="1" spans="7:7">
+      <c r="G12" s="1"/>
+    </row>
+    <row r="13" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>1007</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>6</v>
+      </c>
+      <c r="K13">
+        <v>-1</v>
+      </c>
+      <c r="L13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C14">
+        <v>8</v>
+      </c>
+      <c r="D14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14">
+        <v>1008</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>6</v>
+      </c>
+      <c r="K14">
+        <v>-1</v>
+      </c>
+      <c r="L14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>1009</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+      <c r="K15">
+        <v>-1</v>
+      </c>
+      <c r="L15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C16">
+        <v>10</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>1010</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>6</v>
+      </c>
+      <c r="K16">
+        <v>-1</v>
+      </c>
+      <c r="L16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C17">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>1011</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>6</v>
+      </c>
+      <c r="K17">
+        <v>-1</v>
+      </c>
+      <c r="L17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="F18">
+        <v>1012</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18">
+        <v>6</v>
+      </c>
+      <c r="K18">
+        <v>-1</v>
+      </c>
+      <c r="L18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="27" customHeight="1" spans="7:7">
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C20">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <v>1013</v>
+      </c>
+      <c r="G20" s="1">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20">
+        <v>7</v>
+      </c>
+      <c r="K20">
+        <v>-1</v>
+      </c>
+      <c r="L20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C21">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
+      <c r="F21">
+        <v>1014</v>
+      </c>
+      <c r="G21" s="1">
+        <v>3</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>7</v>
+      </c>
+      <c r="K21">
+        <v>-1</v>
+      </c>
+      <c r="L21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C22">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
+      <c r="F22">
+        <v>1015</v>
+      </c>
+      <c r="G22" s="1">
+        <v>3</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>7</v>
+      </c>
+      <c r="K22">
+        <v>-1</v>
+      </c>
+      <c r="L22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C23">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <v>1016</v>
+      </c>
+      <c r="G23" s="1">
+        <v>3</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>7</v>
+      </c>
+      <c r="K23">
+        <v>-1</v>
+      </c>
+      <c r="L23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C24">
+        <v>17</v>
+      </c>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>1017</v>
+      </c>
+      <c r="G24" s="1">
+        <v>3</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>1</v>
+      </c>
+      <c r="J24">
+        <v>7</v>
+      </c>
+      <c r="K24">
+        <v>-1</v>
+      </c>
+      <c r="L24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C25">
+        <v>18</v>
+      </c>
+      <c r="D25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
+      </c>
+      <c r="F25">
+        <v>1018</v>
+      </c>
+      <c r="G25" s="1">
+        <v>3</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25">
+        <v>7</v>
+      </c>
+      <c r="K25">
+        <v>-1</v>
+      </c>
+      <c r="L25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" ht="27" customHeight="1" spans="7:7">
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C27">
         <v>19</v>
       </c>
-      <c r="E11">
+      <c r="D27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>1019</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27">
+        <v>8</v>
+      </c>
+      <c r="K27">
+        <v>-1</v>
+      </c>
+      <c r="L27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C28">
         <v>20</v>
       </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>-1</v>
-      </c>
-      <c r="I11">
-        <v>-1</v>
-      </c>
-      <c r="J11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="3:3">
-      <c r="C12"/>
-    </row>
-    <row r="13" spans="3:3">
-      <c r="C13"/>
-    </row>
-    <row r="14" spans="3:6">
-      <c r="C14"/>
-      <c r="F14"/>
-    </row>
-    <row r="15" spans="3:6">
-      <c r="C15"/>
-      <c r="F15"/>
-    </row>
-    <row r="16" spans="6:6">
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="6:6">
-      <c r="F17"/>
+      <c r="D28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28">
+        <v>4</v>
+      </c>
+      <c r="F28">
+        <v>1020</v>
+      </c>
+      <c r="G28" s="1">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>8</v>
+      </c>
+      <c r="K28">
+        <v>-1</v>
+      </c>
+      <c r="L28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C29">
+        <v>21</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>1021</v>
+      </c>
+      <c r="G29" s="1">
+        <v>4</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>8</v>
+      </c>
+      <c r="K29">
+        <v>-1</v>
+      </c>
+      <c r="L29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C30">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s">
+        <v>36</v>
+      </c>
+      <c r="E30">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>1022</v>
+      </c>
+      <c r="G30" s="1">
+        <v>4</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>8</v>
+      </c>
+      <c r="K30">
+        <v>-1</v>
+      </c>
+      <c r="L30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C31">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>37</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>1023</v>
+      </c>
+      <c r="G31" s="1">
+        <v>4</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>1</v>
+      </c>
+      <c r="J31">
+        <v>8</v>
+      </c>
+      <c r="K31">
+        <v>-1</v>
+      </c>
+      <c r="L31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="27" customHeight="1" spans="3:12">
+      <c r="C32">
+        <v>24</v>
+      </c>
+      <c r="D32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>1024</v>
+      </c>
+      <c r="G32" s="1">
+        <v>4</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>8</v>
+      </c>
+      <c r="K32">
+        <v>-1</v>
+      </c>
+      <c r="L32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="48" spans="3:12">
+      <c r="C48">
+        <v>1000001</v>
+      </c>
+      <c r="D48" t="s">
+        <v>39</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>15</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>14</v>
+      </c>
+      <c r="L48">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="49" spans="3:12">
+      <c r="C49">
+        <v>1000002</v>
+      </c>
+      <c r="D49" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>15</v>
+      </c>
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>1</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49">
+        <v>15</v>
+      </c>
+      <c r="L49">
+        <v>10024</v>
+      </c>
+    </row>
+    <row r="50" spans="3:12">
+      <c r="C50">
+        <v>1000003</v>
+      </c>
+      <c r="D50" t="s">
+        <v>39</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>15</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>1</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50">
+        <v>16</v>
+      </c>
+      <c r="L50">
+        <v>10038</v>
+      </c>
+    </row>
+    <row r="51" spans="3:12">
+      <c r="C51">
+        <v>1000004</v>
+      </c>
+      <c r="D51" t="s">
+        <v>40</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>16</v>
+      </c>
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>14</v>
+      </c>
+      <c r="L51">
+        <v>10010</v>
+      </c>
+    </row>
+    <row r="52" spans="3:12">
+      <c r="C52">
+        <v>1000005</v>
+      </c>
+      <c r="D52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>16</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52">
+        <v>15</v>
+      </c>
+      <c r="L52">
+        <v>10024</v>
+      </c>
+    </row>
+    <row r="53" spans="3:12">
+      <c r="C53">
+        <v>1000006</v>
+      </c>
+      <c r="D53" t="s">
+        <v>40</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>16</v>
+      </c>
+      <c r="G53" s="1">
+        <v>1</v>
+      </c>
+      <c r="H53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>16</v>
+      </c>
+      <c r="L53">
+        <v>10038</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 D4 E4 F4 G4 D5 E5 F5 G5 C3:C5" errorStyle="warning">
-      <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:XFB19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2"/>
-    <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.125" style="1" customWidth="1"/>
-    <col min="8" max="10" width="12.25" customWidth="1"/>
-    <col min="11" max="16371" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:2">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:2">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:10">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:10">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:10">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C6">
-        <v>1000001</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6" s="1">
-        <v>14</v>
-      </c>
-      <c r="J6">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C7">
-        <v>1000002</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7">
-        <v>15</v>
-      </c>
-      <c r="J7">
-        <v>10024</v>
-      </c>
-    </row>
-    <row r="8" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C8">
-        <v>1000003</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>5</v>
-      </c>
-      <c r="I8">
-        <v>16</v>
-      </c>
-      <c r="J8">
-        <v>10038</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C9">
-        <v>1000004</v>
-      </c>
-      <c r="D9" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9">
-        <v>16</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="I9" s="1">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>10010</v>
-      </c>
-    </row>
-    <row r="10" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C10">
-        <v>1000005</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10">
-        <v>16</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>5</v>
-      </c>
-      <c r="I10">
-        <v>15</v>
-      </c>
-      <c r="J10">
-        <v>10024</v>
-      </c>
-    </row>
-    <row r="11" customFormat="1" ht="27" customHeight="1" spans="3:10">
-      <c r="C11">
-        <v>1000006</v>
-      </c>
-      <c r="D11" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11">
-        <v>16</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>5</v>
-      </c>
-      <c r="I11">
-        <v>16</v>
-      </c>
-      <c r="J11">
-        <v>10038</v>
-      </c>
-    </row>
-    <row r="12" customFormat="1" ht="27" customHeight="1" spans="6:6">
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" customFormat="1" ht="27" customHeight="1" spans="6:6">
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" s="2" customFormat="1" spans="3:16382">
-      <c r="C14"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="XER14"/>
-      <c r="XES14"/>
-      <c r="XET14"/>
-      <c r="XEU14"/>
-      <c r="XEV14"/>
-      <c r="XEW14"/>
-      <c r="XEX14"/>
-      <c r="XEY14"/>
-      <c r="XEZ14"/>
-      <c r="XFA14"/>
-      <c r="XFB14"/>
-    </row>
-    <row r="15" s="2" customFormat="1" spans="3:16382">
-      <c r="C15"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15"/>
-      <c r="I15"/>
-      <c r="J15"/>
-      <c r="XER15"/>
-      <c r="XES15"/>
-      <c r="XET15"/>
-      <c r="XEU15"/>
-      <c r="XEV15"/>
-      <c r="XEW15"/>
-      <c r="XEX15"/>
-      <c r="XEY15"/>
-      <c r="XEZ15"/>
-      <c r="XFA15"/>
-      <c r="XFB15"/>
-    </row>
-    <row r="16" s="2" customFormat="1" spans="3:16382">
-      <c r="C16"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16"/>
-      <c r="G16" s="1"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="XER16"/>
-      <c r="XES16"/>
-      <c r="XET16"/>
-      <c r="XEU16"/>
-      <c r="XEV16"/>
-      <c r="XEW16"/>
-      <c r="XEX16"/>
-      <c r="XEY16"/>
-      <c r="XEZ16"/>
-      <c r="XFA16"/>
-      <c r="XFB16"/>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="3:16382">
-      <c r="C17"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17"/>
-      <c r="G17" s="1"/>
-      <c r="H17"/>
-      <c r="I17"/>
-      <c r="J17"/>
-      <c r="XER17"/>
-      <c r="XES17"/>
-      <c r="XET17"/>
-      <c r="XEU17"/>
-      <c r="XEV17"/>
-      <c r="XEW17"/>
-      <c r="XEX17"/>
-      <c r="XEY17"/>
-      <c r="XEZ17"/>
-      <c r="XFA17"/>
-      <c r="XFB17"/>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="3:16382">
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18"/>
-      <c r="G18" s="1"/>
-      <c r="H18"/>
-      <c r="I18"/>
-      <c r="J18"/>
-      <c r="XER18"/>
-      <c r="XES18"/>
-      <c r="XET18"/>
-      <c r="XEU18"/>
-      <c r="XEV18"/>
-      <c r="XEW18"/>
-      <c r="XEX18"/>
-      <c r="XEY18"/>
-      <c r="XEZ18"/>
-      <c r="XFA18"/>
-      <c r="XFB18"/>
-    </row>
-    <row r="19" s="2" customFormat="1" spans="3:16382">
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19"/>
-      <c r="G19" s="1"/>
-      <c r="H19"/>
-      <c r="I19"/>
-      <c r="J19"/>
-      <c r="XER19"/>
-      <c r="XES19"/>
-      <c r="XET19"/>
-      <c r="XEU19"/>
-      <c r="XEV19"/>
-      <c r="XEW19"/>
-      <c r="XEX19"/>
-      <c r="XEY19"/>
-      <c r="XEZ19"/>
-      <c r="XFA19"/>
-      <c r="XFB19"/>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 E3 F3 G3 D4 E4 F4 G4 D5 E5 F5 G5 C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="111">
   <si>
     <t>#</t>
   </si>
@@ -44,6 +44,9 @@
     <t>Role</t>
   </si>
   <si>
+    <t>RequireId</t>
+  </si>
+  <si>
     <t>TalentId</t>
   </si>
   <si>
@@ -80,7 +83,7 @@
     <t>萌新之刃</t>
   </si>
   <si>
-    <t>1,2</t>
+    <t>40000001,40000002</t>
   </si>
   <si>
     <t>100,10</t>
@@ -95,12 +98,18 @@
     <t>小试牛刀</t>
   </si>
   <si>
+    <t>40000001,40000003</t>
+  </si>
+  <si>
     <t>防御加成</t>
   </si>
   <si>
     <t>初露锋芒</t>
   </si>
   <si>
+    <t>40000002,40000003</t>
+  </si>
+  <si>
     <t>血量加成</t>
   </si>
   <si>
@@ -126,6 +135,9 @@
   </si>
   <si>
     <t>天下无敌</t>
+  </si>
+  <si>
+    <t>PreId</t>
   </si>
   <si>
     <t>八荒短刀</t>
@@ -998,6 +1010,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1317,35 +1330,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="12" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.1666666666667" style="2" customWidth="1"/>
-    <col min="14" max="16371" width="9" style="2"/>
-    <col min="16372" max="16384" width="9" style="1"/>
+    <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.9166666666667" style="1" customWidth="1"/>
+    <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
+    <col min="15" max="16372" width="9" style="2"/>
+    <col min="16373" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1378,12 +1392,15 @@
       <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1404,7 +1421,7 @@
         <v>7</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>9</v>
@@ -1412,47 +1429,53 @@
       <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -1461,33 +1484,36 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>1001</v>
       </c>
-      <c r="H6" s="1">
-        <v>10</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="I6" s="1">
+        <v>10</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="1">
         <v>4</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -1496,33 +1522,36 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>1002</v>
       </c>
-      <c r="H7" s="1">
-        <v>10</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="I7" s="1">
+        <v>10</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="1">
         <v>4</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>19</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -1531,33 +1560,36 @@
         <v>0</v>
       </c>
       <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>1003</v>
       </c>
-      <c r="H8" s="1">
-        <v>10</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="1">
+      <c r="I8" s="1">
+        <v>10</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8" s="1">
         <v>4</v>
       </c>
-      <c r="L8" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>19</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -1569,30 +1601,33 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>10</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>10</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="1">
         <v>4</v>
       </c>
-      <c r="L9" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M9" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>19</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -1604,30 +1639,33 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>10</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>10</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10" s="1">
         <v>4</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M10" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>19</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -1639,27 +1677,30 @@
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>10</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>10</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11" s="1">
         <v>5</v>
       </c>
-      <c r="L11" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -1671,27 +1712,30 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>10</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>10</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12" s="1">
         <v>5</v>
       </c>
-      <c r="L12" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M12" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -1703,27 +1747,30 @@
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>10</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>10</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13" s="1">
         <v>5</v>
       </c>
-      <c r="L13" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M13" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1">
         <v>0</v>
@@ -1735,19 +1782,22 @@
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>10</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="1">
+        <v>0</v>
+      </c>
+      <c r="I14" s="1">
+        <v>10</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14" s="1">
         <v>5</v>
       </c>
-      <c r="L14" s="1" t="s">
-        <v>18</v>
+      <c r="M14" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
@@ -1768,15 +1818,15 @@
     <row r="30" s="1" customFormat="1" customHeight="1"/>
     <row r="31" s="1" customFormat="1" customHeight="1"/>
     <row r="32" s="1" customFormat="1" customHeight="1"/>
-    <row r="34" customHeight="1" spans="13:13">
-      <c r="M34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="13:13">
-      <c r="M35" s="1"/>
+    <row r="34" customHeight="1" spans="14:14">
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" customHeight="1" spans="14:14">
+      <c r="N35" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:K5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -1794,29 +1844,29 @@
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="12" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.1666666666667" style="2" customWidth="1"/>
-    <col min="14" max="16371" width="9" style="2"/>
-    <col min="16372" max="16384" width="9" style="1"/>
+    <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="7" max="10" width="12.25" style="1" customWidth="1"/>
+    <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
+    <col min="15" max="16372" width="9" style="2"/>
+    <col min="16373" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1829,7 +1879,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>5</v>
@@ -1849,12 +1899,15 @@
       <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1863,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>5</v>
@@ -1875,7 +1928,7 @@
         <v>7</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>9</v>
@@ -1883,47 +1936,53 @@
       <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1932,33 +1991,36 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>1004</v>
       </c>
-      <c r="H6" s="1">
-        <v>10</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="I6" s="1">
+        <v>10</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="1">
         <v>4</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M6" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
+        <v>19</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -1967,25 +2029,28 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>1007</v>
       </c>
-      <c r="H7" s="1">
-        <v>10</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="I7" s="1">
+        <v>10</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="1">
         <v>4</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>35</v>
+        <v>19</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1"/>
@@ -1999,545 +2064,590 @@
     <row r="16" s="1" customFormat="1" customHeight="1"/>
     <row r="17" s="1" customFormat="1" customHeight="1"/>
     <row r="18" s="1" customFormat="1" customHeight="1"/>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:17">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C19" s="1">
         <v>1101</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
       </c>
       <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
         <v>10011</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>1004</v>
       </c>
-      <c r="H19" s="1">
-        <v>10</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="I19" s="1">
+        <v>10</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="1">
         <v>5</v>
       </c>
-      <c r="L19" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M19" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C20" s="1">
         <v>1102</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
         <v>10021</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>1004</v>
       </c>
-      <c r="H20" s="1">
-        <v>10</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="I20" s="1">
+        <v>10</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="1">
         <v>5</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M20" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C21" s="1">
         <v>1103</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
       </c>
       <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
         <v>10031</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>1004</v>
       </c>
-      <c r="H21" s="1">
-        <v>10</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="I21" s="1">
+        <v>10</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="1">
         <v>5</v>
       </c>
-      <c r="L21" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M21" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C22" s="1">
         <v>1104</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
       </c>
       <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
         <v>10041</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>1004</v>
       </c>
-      <c r="H22" s="1">
-        <v>10</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="I22" s="1">
+        <v>10</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="1">
         <v>5</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M22" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C23" s="1">
         <v>1105</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
       </c>
       <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
         <v>10051</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>1004</v>
       </c>
-      <c r="H23" s="1">
-        <v>10</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="I23" s="1">
+        <v>10</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="1">
         <v>5</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M23" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C24" s="1">
         <v>1106</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
       </c>
       <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
         <v>10061</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>1004</v>
       </c>
-      <c r="H24" s="1">
-        <v>10</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="1">
+      <c r="I24" s="1">
+        <v>10</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="L24" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M24" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C25" s="1">
         <v>1107</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
       </c>
       <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
         <v>10071</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>1004</v>
       </c>
-      <c r="H25" s="1">
-        <v>10</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="1">
+      <c r="I25" s="1">
+        <v>10</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q25" s="4"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="R25" s="4"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C26" s="1">
         <v>1108</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
         <v>10012</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>1004</v>
       </c>
-      <c r="H26" s="1">
-        <v>10</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="1">
+      <c r="I26" s="1">
+        <v>10</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="1">
         <v>6</v>
       </c>
-      <c r="L26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q26" s="4"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R26" s="4"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C27" s="1">
         <v>1109</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
         <v>10022</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <v>1004</v>
       </c>
-      <c r="H27" s="1">
-        <v>10</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="1">
+      <c r="I27" s="1">
+        <v>10</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="1">
         <v>6</v>
       </c>
-      <c r="L27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q27" s="4"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R27" s="4"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C28" s="1">
         <v>1110</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
         <v>10032</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <v>1004</v>
       </c>
-      <c r="H28" s="1">
-        <v>10</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="1">
+      <c r="I28" s="1">
+        <v>10</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="1">
         <v>6</v>
       </c>
-      <c r="L28" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="N28" s="4"/>
-      <c r="O28" s="1"/>
-      <c r="Q28" s="4"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="O28" s="4"/>
+      <c r="P28" s="1"/>
+      <c r="R28" s="4"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C29" s="1">
         <v>1111</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
         <v>10042</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>1004</v>
       </c>
-      <c r="H29" s="1">
-        <v>10</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K29" s="1">
+      <c r="I29" s="1">
+        <v>10</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" s="1">
         <v>6</v>
       </c>
-      <c r="L29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N29" s="4"/>
-      <c r="O29" s="1"/>
-      <c r="Q29" s="4"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M29" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="O29" s="4"/>
+      <c r="P29" s="1"/>
+      <c r="R29" s="4"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C30" s="1">
         <v>1112</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
         <v>10072</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <v>1004</v>
       </c>
-      <c r="H30" s="1">
-        <v>10</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" s="1">
+      <c r="I30" s="1">
+        <v>10</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L30" s="1">
         <v>6</v>
       </c>
-      <c r="L30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="N30" s="4"/>
-      <c r="O30" s="1"/>
-      <c r="Q30" s="4"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O30" s="4"/>
+      <c r="P30" s="1"/>
+      <c r="R30" s="4"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C31" s="1">
         <v>1113</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
         <v>10023</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <v>1004</v>
       </c>
-      <c r="H31" s="1">
-        <v>10</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" s="1">
+      <c r="I31" s="1">
+        <v>10</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" s="1">
         <v>6</v>
       </c>
-      <c r="L31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="N31" s="4"/>
-      <c r="O31" s="1"/>
-      <c r="Q31" s="4"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:17">
+      <c r="M31" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="O31" s="4"/>
+      <c r="P31" s="1"/>
+      <c r="R31" s="4"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C32" s="1">
         <v>1114</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
         <v>10073</v>
       </c>
-      <c r="G32" s="1">
+      <c r="H32" s="1">
         <v>1004</v>
       </c>
-      <c r="H32" s="1">
-        <v>10</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" s="1">
+      <c r="I32" s="1">
+        <v>10</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="1">
         <v>7</v>
       </c>
-      <c r="L32" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="N32" s="4"/>
-      <c r="O32" s="1"/>
-      <c r="Q32" s="4"/>
-    </row>
-    <row r="33" customHeight="1" spans="3:18 16372:16384">
+      <c r="M32" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O32" s="4"/>
+      <c r="P32" s="1"/>
+      <c r="R32" s="4"/>
+    </row>
+    <row r="33" customHeight="1" spans="3:19 16373:16384">
       <c r="C33" s="1">
         <v>1115</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
         <v>10024</v>
       </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <v>1004</v>
       </c>
-      <c r="H33" s="1">
-        <v>10</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" s="1">
+      <c r="I33" s="1">
+        <v>10</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" s="1">
         <v>7</v>
       </c>
-      <c r="L33" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="N33" s="1"/>
+      <c r="M33" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="R33" s="1"/>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:18 16372:16384">
+      <c r="Q33" s="1"/>
+      <c r="S33" s="1"/>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
       <c r="C34" s="1">
         <v>1116</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="1"/>
+      <c r="G34" s="1">
         <v>10034</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <v>1004</v>
       </c>
-      <c r="H34" s="1">
-        <v>10</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K34" s="1">
+      <c r="I34" s="1">
+        <v>10</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" s="1">
         <v>7</v>
       </c>
-      <c r="L34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M34" s="1"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="1"/>
+      <c r="M34" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="N34" s="1"/>
+      <c r="O34" s="4"/>
       <c r="P34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="XER34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="S34" s="1"/>
       <c r="XES34" s="1"/>
       <c r="XET34" s="1"/>
       <c r="XEU34" s="1"/>
@@ -2551,7 +2661,7 @@
       <c r="XFC34" s="1"/>
       <c r="XFD34" s="1"/>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:18 16372:16384">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
       <c r="C35" s="1"/>
       <c r="D35" s="2"/>
       <c r="E35" s="1"/>
@@ -2563,11 +2673,11 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="4"/>
       <c r="P35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="XER35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="S35" s="1"/>
       <c r="XES35" s="1"/>
       <c r="XET35" s="1"/>
       <c r="XEU35" s="1"/>
@@ -2581,13 +2691,13 @@
       <c r="XFC35" s="1"/>
       <c r="XFD35" s="1"/>
     </row>
-    <row r="36" customHeight="1" spans="3:18 16372:16384">
-      <c r="N36" s="1"/>
+    <row r="36" customHeight="1" spans="3:19 16373:16384">
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
-      <c r="R36" s="1"/>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:18 16372:16384">
+      <c r="Q36" s="1"/>
+      <c r="S36" s="1"/>
+    </row>
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -2598,11 +2708,11 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="O37" s="4"/>
       <c r="P37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="XER37" s="1"/>
+      <c r="Q37" s="1"/>
+      <c r="S37" s="1"/>
       <c r="XES37" s="1"/>
       <c r="XET37" s="1"/>
       <c r="XEU37" s="1"/>
@@ -2616,42 +2726,42 @@
       <c r="XFC37" s="1"/>
       <c r="XFD37" s="1"/>
     </row>
-    <row r="38" customHeight="1" spans="3:18 16372:16384">
-      <c r="N38" s="4"/>
-      <c r="O38" s="1"/>
+    <row r="38" customHeight="1" spans="3:19 16373:16384">
+      <c r="O38" s="4"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="R38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:18 16372:16384">
-      <c r="P39" s="1"/>
-      <c r="R39" s="1"/>
-    </row>
-    <row r="40" customHeight="1" spans="3:18 16372:16384">
-      <c r="P40" s="1"/>
-      <c r="R40" s="1"/>
-    </row>
-    <row r="41" customHeight="1" spans="3:18 16372:16384">
-      <c r="N41" s="1"/>
-      <c r="P41" s="1"/>
+      <c r="S38" s="1"/>
+    </row>
+    <row r="39" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q39" s="1"/>
+      <c r="S39" s="1"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q40" s="1"/>
+      <c r="S40" s="1"/>
+    </row>
+    <row r="41" customHeight="1" spans="3:19 16373:16384">
+      <c r="O41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="3:18 16372:16384">
-      <c r="P42" s="1"/>
-      <c r="R42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="3:18 16372:16384">
-      <c r="P43" s="1"/>
-      <c r="R43" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="3:18 16372:16384">
-      <c r="P44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="3:18 16372:16384">
-      <c r="P45" s="1"/>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:18 16372:16384">
+      <c r="S41" s="1"/>
+    </row>
+    <row r="42" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q42" s="1"/>
+      <c r="S42" s="1"/>
+    </row>
+    <row r="43" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q43" s="1"/>
+      <c r="S43" s="1"/>
+    </row>
+    <row r="44" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q45" s="1"/>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -2662,7 +2772,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
-      <c r="XER48" s="1"/>
+      <c r="M48" s="1"/>
       <c r="XES48" s="1"/>
       <c r="XET48" s="1"/>
       <c r="XEU48" s="1"/>
@@ -2676,7 +2786,7 @@
       <c r="XFC48" s="1"/>
       <c r="XFD48" s="1"/>
     </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -2687,7 +2797,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
-      <c r="XER49" s="1"/>
+      <c r="M49" s="1"/>
       <c r="XES49" s="1"/>
       <c r="XET49" s="1"/>
       <c r="XEU49" s="1"/>
@@ -2701,7 +2811,7 @@
       <c r="XFC49" s="1"/>
       <c r="XFD49" s="1"/>
     </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -2712,7 +2822,7 @@
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
-      <c r="XER50" s="1"/>
+      <c r="M50" s="1"/>
       <c r="XES50" s="1"/>
       <c r="XET50" s="1"/>
       <c r="XEU50" s="1"/>
@@ -2726,7 +2836,7 @@
       <c r="XFC50" s="1"/>
       <c r="XFD50" s="1"/>
     </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -2737,7 +2847,7 @@
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
-      <c r="XER51" s="1"/>
+      <c r="M51" s="1"/>
       <c r="XES51" s="1"/>
       <c r="XET51" s="1"/>
       <c r="XEU51" s="1"/>
@@ -2751,7 +2861,7 @@
       <c r="XFC51" s="1"/>
       <c r="XFD51" s="1"/>
     </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -2762,7 +2872,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
-      <c r="XER52" s="1"/>
+      <c r="M52" s="1"/>
       <c r="XES52" s="1"/>
       <c r="XET52" s="1"/>
       <c r="XEU52" s="1"/>
@@ -2776,7 +2886,7 @@
       <c r="XFC52" s="1"/>
       <c r="XFD52" s="1"/>
     </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -2787,7 +2897,7 @@
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
-      <c r="XER53" s="1"/>
+      <c r="M53" s="1"/>
       <c r="XES53" s="1"/>
       <c r="XET53" s="1"/>
       <c r="XEU53" s="1"/>
@@ -2803,7 +2913,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:K5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2821,29 +2931,29 @@
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="12" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.1666666666667" style="2" customWidth="1"/>
-    <col min="14" max="16371" width="9" style="2"/>
-    <col min="16372" max="16384" width="9" style="1"/>
+    <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="7" max="10" width="12.25" style="1" customWidth="1"/>
+    <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
+    <col min="15" max="16372" width="9" style="2"/>
+    <col min="16373" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -2856,7 +2966,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>5</v>
@@ -2876,12 +2986,15 @@
       <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -2890,7 +3003,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>5</v>
@@ -2902,7 +3015,7 @@
         <v>7</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>9</v>
@@ -2910,47 +3023,53 @@
       <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+      <c r="M5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C6" s="1">
         <v>2001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -2959,25 +3078,27 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>1005</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="I6" s="1"/>
+      <c r="J6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="1">
         <v>4</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M6" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="XER6" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="XES6" s="1"/>
       <c r="XET6" s="1"/>
       <c r="XEU6" s="1"/>
@@ -2991,12 +3112,12 @@
       <c r="XFC6" s="1"/>
       <c r="XFD6" s="1"/>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C7" s="1">
         <v>2002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -3005,25 +3126,27 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>1008</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="I7" s="1"/>
+      <c r="J7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="1">
         <v>4</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="M7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="XER7" s="1"/>
+        <v>19</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="XES7" s="1"/>
       <c r="XET7" s="1"/>
       <c r="XEU7" s="1"/>
@@ -3037,7 +3160,7 @@
       <c r="XFC7" s="1"/>
       <c r="XFD7" s="1"/>
     </row>
-    <row r="9" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="9" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -3048,7 +3171,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
-      <c r="XER9" s="1"/>
+      <c r="M9" s="1"/>
       <c r="XES9" s="1"/>
       <c r="XET9" s="1"/>
       <c r="XEU9" s="1"/>
@@ -3062,7 +3185,7 @@
       <c r="XFC9" s="1"/>
       <c r="XFD9" s="1"/>
     </row>
-    <row r="10" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="10" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -3073,7 +3196,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
-      <c r="XER10" s="1"/>
+      <c r="M10" s="1"/>
       <c r="XES10" s="1"/>
       <c r="XET10" s="1"/>
       <c r="XEU10" s="1"/>
@@ -3087,7 +3210,7 @@
       <c r="XFC10" s="1"/>
       <c r="XFD10" s="1"/>
     </row>
-    <row r="11" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="11" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -3098,7 +3221,7 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
-      <c r="XER11" s="1"/>
+      <c r="M11" s="1"/>
       <c r="XES11" s="1"/>
       <c r="XET11" s="1"/>
       <c r="XEU11" s="1"/>
@@ -3112,7 +3235,7 @@
       <c r="XFC11" s="1"/>
       <c r="XFD11" s="1"/>
     </row>
-    <row r="12" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="12" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -3123,7 +3246,7 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
-      <c r="XER12" s="1"/>
+      <c r="M12" s="1"/>
       <c r="XES12" s="1"/>
       <c r="XET12" s="1"/>
       <c r="XEU12" s="1"/>
@@ -3137,7 +3260,7 @@
       <c r="XFC12" s="1"/>
       <c r="XFD12" s="1"/>
     </row>
-    <row r="13" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="13" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -3148,7 +3271,7 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="XER13" s="1"/>
+      <c r="M13" s="1"/>
       <c r="XES13" s="1"/>
       <c r="XET13" s="1"/>
       <c r="XEU13" s="1"/>
@@ -3162,7 +3285,7 @@
       <c r="XFC13" s="1"/>
       <c r="XFD13" s="1"/>
     </row>
-    <row r="14" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="14" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -3173,7 +3296,7 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
-      <c r="XER14" s="1"/>
+      <c r="M14" s="1"/>
       <c r="XES14" s="1"/>
       <c r="XET14" s="1"/>
       <c r="XEU14" s="1"/>
@@ -3187,7 +3310,7 @@
       <c r="XFC14" s="1"/>
       <c r="XFD14" s="1"/>
     </row>
-    <row r="15" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="15" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -3198,7 +3321,7 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="XER15" s="1"/>
+      <c r="M15" s="1"/>
       <c r="XES15" s="1"/>
       <c r="XET15" s="1"/>
       <c r="XEU15" s="1"/>
@@ -3212,7 +3335,7 @@
       <c r="XFC15" s="1"/>
       <c r="XFD15" s="1"/>
     </row>
-    <row r="16" customFormat="1" customHeight="1" spans="1:13 16372:16384">
+    <row r="16" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -3223,7 +3346,7 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
-      <c r="XER16" s="1"/>
+      <c r="M16" s="1"/>
       <c r="XES16" s="1"/>
       <c r="XET16" s="1"/>
       <c r="XEU16" s="1"/>
@@ -3237,7 +3360,7 @@
       <c r="XFC16" s="1"/>
       <c r="XFD16" s="1"/>
     </row>
-    <row r="17" customFormat="1" customHeight="1" spans="3:17 16372:16384">
+    <row r="17" customFormat="1" customHeight="1" spans="3:18 16373:16384">
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -3248,7 +3371,7 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
-      <c r="XER17" s="1"/>
+      <c r="M17" s="1"/>
       <c r="XES17" s="1"/>
       <c r="XET17" s="1"/>
       <c r="XEU17" s="1"/>
@@ -3262,7 +3385,7 @@
       <c r="XFC17" s="1"/>
       <c r="XFD17" s="1"/>
     </row>
-    <row r="18" customFormat="1" customHeight="1" spans="3:17 16372:16384">
+    <row r="18" customFormat="1" customHeight="1" spans="3:18 16373:16384">
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -3273,7 +3396,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
-      <c r="XER18" s="1"/>
+      <c r="M18" s="1"/>
       <c r="XES18" s="1"/>
       <c r="XET18" s="1"/>
       <c r="XEU18" s="1"/>
@@ -3287,38 +3410,40 @@
       <c r="XFC18" s="1"/>
       <c r="XFD18" s="1"/>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:17 16372:16384">
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
       <c r="C19" s="1">
         <v>2101</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
       </c>
       <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
         <v>20011</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>1005</v>
       </c>
-      <c r="H19" s="1">
-        <v>10</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="I19" s="1">
+        <v>10</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="1">
         <v>5</v>
       </c>
-      <c r="L19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="XER19" s="1"/>
+      <c r="M19" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="XES19" s="1"/>
       <c r="XET19" s="1"/>
       <c r="XEU19" s="1"/>
@@ -3332,376 +3457,405 @@
       <c r="XFC19" s="1"/>
       <c r="XFD19" s="1"/>
     </row>
-    <row r="20" customHeight="1" spans="3:17 16372:16384">
+    <row r="20" customHeight="1" spans="3:18 16373:16384">
       <c r="C20" s="1">
         <v>2102</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
       </c>
       <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
         <v>20021</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>1005</v>
       </c>
-      <c r="H20" s="1">
-        <v>10</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="I20" s="1">
+        <v>10</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="1">
         <v>5</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M20" s="1"/>
+      <c r="M20" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="N20" s="1"/>
-      <c r="O20" s="4"/>
+      <c r="O20" s="1"/>
       <c r="P20" s="4"/>
-      <c r="Q20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="3:17 16372:16384">
+      <c r="Q20" s="4"/>
+      <c r="R20" s="1"/>
+    </row>
+    <row r="21" customHeight="1" spans="3:18 16373:16384">
       <c r="C21" s="1">
         <v>2103</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
       <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
         <v>20031</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>1005</v>
       </c>
-      <c r="H21" s="1">
-        <v>10</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="I21" s="1">
+        <v>10</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="1">
         <v>5</v>
       </c>
-      <c r="L21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M21" s="1"/>
+      <c r="M21" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="N21" s="1"/>
-      <c r="O21" s="4"/>
+      <c r="O21" s="1"/>
       <c r="P21" s="4"/>
-      <c r="Q21" s="1"/>
-    </row>
-    <row r="22" customHeight="1" spans="3:17 16372:16384">
+      <c r="Q21" s="4"/>
+      <c r="R21" s="1"/>
+    </row>
+    <row r="22" customHeight="1" spans="3:18 16373:16384">
       <c r="C22" s="1">
         <v>2104</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
       </c>
       <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
         <v>20041</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>1005</v>
       </c>
-      <c r="H22" s="1">
-        <v>10</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="I22" s="1">
+        <v>10</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="1">
         <v>5</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="M22" s="1"/>
+      <c r="M22" s="4" t="s">
+        <v>47</v>
+      </c>
       <c r="N22" s="1"/>
-      <c r="O22" s="4"/>
+      <c r="O22" s="1"/>
       <c r="P22" s="4"/>
-      <c r="Q22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="3:17 16372:16384">
+      <c r="Q22" s="4"/>
+      <c r="R22" s="1"/>
+    </row>
+    <row r="23" customHeight="1" spans="3:18 16373:16384">
       <c r="C23" s="1">
         <v>2105</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
       </c>
       <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
         <v>20051</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>1005</v>
       </c>
-      <c r="H23" s="1">
-        <v>10</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="I23" s="1">
+        <v>10</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="1">
         <v>5</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M23" s="1"/>
+      <c r="M23" s="4" t="s">
+        <v>49</v>
+      </c>
       <c r="N23" s="1"/>
-      <c r="O23" s="4"/>
+      <c r="O23" s="1"/>
       <c r="P23" s="4"/>
-      <c r="Q23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="3:17 16372:16384">
+      <c r="Q23" s="4"/>
+      <c r="R23" s="1"/>
+    </row>
+    <row r="24" customHeight="1" spans="3:18 16373:16384">
       <c r="C24" s="1">
         <v>2106</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
       </c>
       <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
         <v>20061</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>1005</v>
       </c>
-      <c r="H24" s="1">
-        <v>10</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="1">
+      <c r="I24" s="1">
+        <v>10</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="L24" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M24" s="1"/>
+      <c r="M24" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="N24" s="1"/>
-      <c r="O24" s="4"/>
+      <c r="O24" s="1"/>
       <c r="P24" s="4"/>
-      <c r="Q24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="3:17 16372:16384">
+      <c r="Q24" s="4"/>
+      <c r="R24" s="1"/>
+    </row>
+    <row r="25" customHeight="1" spans="3:18 16373:16384">
       <c r="C25" s="1">
         <v>2107</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
       </c>
       <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
         <v>20071</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>1005</v>
       </c>
-      <c r="H25" s="1">
-        <v>10</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="1">
+      <c r="I25" s="1">
+        <v>10</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M25" s="1"/>
+      <c r="M25" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="N25" s="1"/>
-      <c r="O25" s="4"/>
+      <c r="O25" s="1"/>
       <c r="P25" s="4"/>
-      <c r="Q25" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="3:17 16372:16384">
+      <c r="Q25" s="4"/>
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" customHeight="1" spans="3:18 16373:16384">
       <c r="C26" s="1">
         <v>2108</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
       </c>
       <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
         <v>20012</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>1005</v>
       </c>
-      <c r="H26" s="1">
-        <v>10</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="1">
+      <c r="I26" s="1">
+        <v>10</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="1">
         <v>6</v>
       </c>
-      <c r="L26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="M26" s="1"/>
+      <c r="M26" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="N26" s="1"/>
-      <c r="O26" s="4"/>
+      <c r="O26" s="1"/>
       <c r="P26" s="4"/>
-      <c r="Q26" s="1"/>
-    </row>
-    <row r="27" customHeight="1" spans="3:17 16372:16384">
+      <c r="Q26" s="4"/>
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" customHeight="1" spans="3:18 16373:16384">
       <c r="C27" s="1">
         <v>2109</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
       <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
         <v>20022</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <v>1005</v>
       </c>
-      <c r="H27" s="1">
-        <v>10</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="1">
+      <c r="I27" s="1">
+        <v>10</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="1">
         <v>6</v>
       </c>
-      <c r="L27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M27" s="1"/>
+      <c r="M27" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
-      <c r="P27" s="4"/>
-      <c r="Q27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="3:17 16372:16384">
+      <c r="P27" s="1"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="1"/>
+    </row>
+    <row r="28" customHeight="1" spans="3:18 16373:16384">
       <c r="C28" s="1">
         <v>2110</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
       <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
         <v>20032</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <v>1005</v>
       </c>
-      <c r="H28" s="1">
-        <v>10</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="1">
+      <c r="I28" s="1">
+        <v>10</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="1">
         <v>6</v>
       </c>
-      <c r="L28" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M28" s="1"/>
+      <c r="M28" s="4" t="s">
+        <v>59</v>
+      </c>
       <c r="N28" s="1"/>
-      <c r="O28" s="4"/>
+      <c r="O28" s="1"/>
       <c r="P28" s="4"/>
-      <c r="Q28" s="1"/>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:17 16372:16384">
+      <c r="Q28" s="4"/>
+      <c r="R28" s="1"/>
+    </row>
+    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
       <c r="C29" s="1">
         <v>2111</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
       <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
         <v>20072</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>1005</v>
       </c>
-      <c r="H29" s="1">
-        <v>10</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K29" s="1">
+      <c r="I29" s="1">
+        <v>10</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" s="1">
         <v>6</v>
       </c>
-      <c r="L29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="M29" s="1"/>
+      <c r="M29" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="1"/>
-      <c r="XER29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="1"/>
       <c r="XES29" s="1"/>
       <c r="XET29" s="1"/>
       <c r="XEU29" s="1"/>
@@ -3715,43 +3869,45 @@
       <c r="XFC29" s="1"/>
       <c r="XFD29" s="1"/>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:17 16372:16384">
+    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
       <c r="C30" s="1">
         <v>2112</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
         <v>20023</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <v>1005</v>
       </c>
-      <c r="H30" s="1">
-        <v>10</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" s="1">
+      <c r="I30" s="1">
+        <v>10</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L30" s="1">
         <v>6</v>
       </c>
-      <c r="L30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M30" s="1"/>
+      <c r="M30" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="N30" s="1"/>
-      <c r="O30" s="4"/>
+      <c r="O30" s="1"/>
       <c r="P30" s="4"/>
-      <c r="Q30" s="1"/>
-      <c r="XER30" s="1"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="1"/>
       <c r="XES30" s="1"/>
       <c r="XET30" s="1"/>
       <c r="XEU30" s="1"/>
@@ -3765,43 +3921,45 @@
       <c r="XFC30" s="1"/>
       <c r="XFD30" s="1"/>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:17 16372:16384">
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
       <c r="C31" s="1">
         <v>2113</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
         <v>20033</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <v>1005</v>
       </c>
-      <c r="H31" s="1">
-        <v>10</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" s="1">
+      <c r="I31" s="1">
+        <v>10</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" s="1">
         <v>6</v>
       </c>
-      <c r="L31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="M31" s="1"/>
+      <c r="M31" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="1"/>
-      <c r="XER31" s="1"/>
+      <c r="P31" s="1"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="1"/>
       <c r="XES31" s="1"/>
       <c r="XET31" s="1"/>
       <c r="XEU31" s="1"/>
@@ -3815,43 +3973,45 @@
       <c r="XFC31" s="1"/>
       <c r="XFD31" s="1"/>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:17 16372:16384">
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
       <c r="C32" s="1">
         <v>2114</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
         <v>20043</v>
       </c>
-      <c r="G32" s="1">
+      <c r="H32" s="1">
         <v>1005</v>
       </c>
-      <c r="H32" s="1">
-        <v>10</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" s="1">
+      <c r="I32" s="1">
+        <v>10</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="1">
         <v>7</v>
       </c>
-      <c r="L32" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="M32" s="1"/>
+      <c r="M32" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
-      <c r="XER32" s="1"/>
+      <c r="R32" s="1"/>
       <c r="XES32" s="1"/>
       <c r="XET32" s="1"/>
       <c r="XEU32" s="1"/>
@@ -3865,115 +4025,118 @@
       <c r="XFC32" s="1"/>
       <c r="XFD32" s="1"/>
     </row>
-    <row r="33" customHeight="1" spans="3:17">
+    <row r="33" customHeight="1" spans="3:18">
       <c r="C33" s="1">
         <v>2115</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
         <v>20024</v>
       </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <v>1005</v>
       </c>
-      <c r="H33" s="1">
-        <v>10</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" s="1">
+      <c r="I33" s="1">
+        <v>10</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" s="1">
         <v>7</v>
       </c>
-      <c r="L33" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="M33" s="1"/>
+      <c r="M33" s="4" t="s">
+        <v>69</v>
+      </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="3:17">
+      <c r="P33" s="1"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="3:18">
       <c r="C34" s="1">
         <v>2116</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F34" s="1">
+        <v>91</v>
+      </c>
+      <c r="G34" s="1">
         <v>20034</v>
       </c>
-      <c r="G34" s="1">
+      <c r="H34" s="1">
         <v>1005</v>
       </c>
-      <c r="H34" s="1">
-        <v>10</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K34" s="1">
+      <c r="I34" s="1">
+        <v>10</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L34" s="1">
         <v>7</v>
       </c>
-      <c r="L34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M34" s="1"/>
+      <c r="M34" s="4" t="s">
+        <v>71</v>
+      </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="3:17">
-      <c r="M35" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" customHeight="1" spans="3:18">
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="3:17">
-      <c r="M36" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="1"/>
+    </row>
+    <row r="36" customHeight="1" spans="3:18">
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="3:17">
-      <c r="M37" s="1"/>
+      <c r="R36" s="1"/>
+    </row>
+    <row r="37" customHeight="1" spans="3:18">
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="3:17">
-      <c r="M38" s="1"/>
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" customHeight="1" spans="3:18">
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:17">
-      <c r="M39" s="1"/>
+      <c r="P38" s="1"/>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="1"/>
+    </row>
+    <row r="39" customHeight="1" spans="3:18">
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="1"/>
+      <c r="P39" s="1"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:K5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -3991,29 +4154,29 @@
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="12.125" style="1" customWidth="1"/>
-    <col min="6" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="12" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="18.1666666666667" style="2" customWidth="1"/>
-    <col min="14" max="16371" width="9" style="2"/>
-    <col min="16372" max="16384" width="9" style="1"/>
+    <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
+    <col min="7" max="10" width="12.25" style="1" customWidth="1"/>
+    <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
+    <col min="15" max="16372" width="9" style="2"/>
+    <col min="16373" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="M1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="M2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -4026,7 +4189,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>5</v>
@@ -4046,12 +4209,15 @@
       <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -4060,7 +4226,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>5</v>
@@ -4072,7 +4238,7 @@
         <v>7</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>9</v>
@@ -4080,47 +4246,53 @@
       <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C6" s="1">
         <v>3001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -4129,33 +4301,34 @@
         <v>0</v>
       </c>
       <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
         <v>1006</v>
       </c>
-      <c r="H6" s="1">
-        <v>10</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1">
+      <c r="I6" s="1">
+        <v>10</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="1">
         <v>4</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M6" s="1"/>
+      <c r="N6" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C7" s="1">
         <v>3002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -4164,555 +4337,601 @@
         <v>0</v>
       </c>
       <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>1009</v>
       </c>
-      <c r="H7" s="1">
-        <v>10</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="I7" s="1">
+        <v>10</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" s="1">
         <v>4</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="M9"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="M10"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="M11"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="M12"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="M13"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="M14"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="M15"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:13">
-      <c r="M16"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="M17"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="M18"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N9"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N10"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N11"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N12"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N13"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N14"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N15"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N16"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N17"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N18"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C19" s="1">
         <v>3101</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
       </c>
       <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
         <v>30011</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>1006</v>
       </c>
-      <c r="H19" s="1">
-        <v>10</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="1">
+      <c r="I19" s="1">
+        <v>10</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L19" s="1">
         <v>5</v>
       </c>
-      <c r="L19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="M19" s="2"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M19" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C20" s="1">
         <v>3102</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
       </c>
       <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
         <v>30021</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>1006</v>
       </c>
-      <c r="H20" s="1">
-        <v>10</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="1">
+      <c r="I20" s="1">
+        <v>10</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L20" s="1">
         <v>5</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M20" s="2"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="N20" s="2"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C21" s="1">
         <v>3103</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
       </c>
       <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
         <v>30031</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>1006</v>
       </c>
-      <c r="H21" s="1">
-        <v>10</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="I21" s="1">
+        <v>10</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L21" s="1">
         <v>5</v>
       </c>
-      <c r="L21" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M21" s="2"/>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N21" s="2"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C22" s="1">
         <v>3104</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
       </c>
       <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
         <v>30041</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>1006</v>
       </c>
-      <c r="H22" s="1">
-        <v>10</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="I22" s="1">
+        <v>10</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L22" s="1">
         <v>5</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="M22" s="2"/>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="N22" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C23" s="1">
         <v>3105</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
       </c>
       <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
         <v>30051</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>1006</v>
       </c>
-      <c r="H23" s="1">
-        <v>10</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="1">
+      <c r="I23" s="1">
+        <v>10</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L23" s="1">
         <v>5</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M23" s="2"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M23" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="N23" s="2"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="1">
         <v>3106</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
       </c>
       <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
         <v>30061</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>1006</v>
       </c>
-      <c r="H24" s="1">
-        <v>10</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="1">
+      <c r="I24" s="1">
+        <v>10</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="L24" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M24" s="2"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M24" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C25" s="1">
         <v>3107</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
       </c>
       <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
         <v>30071</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>1006</v>
       </c>
-      <c r="H25" s="1">
-        <v>10</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="1">
+      <c r="I25" s="1">
+        <v>10</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="M25" s="2"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="1">
         <v>3108</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
       </c>
       <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
         <v>30012</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>1006</v>
       </c>
-      <c r="H26" s="1">
-        <v>10</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="1">
+      <c r="I26" s="1">
+        <v>10</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L26" s="1">
         <v>6</v>
       </c>
-      <c r="L26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="M26" s="2"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M26" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="2"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="1">
         <v>3109</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
       </c>
       <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
         <v>30022</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <v>1006</v>
       </c>
-      <c r="H27" s="1">
-        <v>10</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="1">
+      <c r="I27" s="1">
+        <v>10</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L27" s="1">
         <v>6</v>
       </c>
-      <c r="L27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M27" s="2"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="2"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C28" s="1">
         <v>3110</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
       </c>
       <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
         <v>30032</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <v>1006</v>
       </c>
-      <c r="H28" s="1">
-        <v>10</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="1">
+      <c r="I28" s="1">
+        <v>10</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L28" s="1">
         <v>6</v>
       </c>
-      <c r="L28" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="M28" s="2"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N28" s="2"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C29" s="1">
         <v>3111</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
       </c>
       <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
         <v>30033</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>1006</v>
       </c>
-      <c r="H29" s="1">
-        <v>10</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K29" s="1">
+      <c r="I29" s="1">
+        <v>10</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L29" s="1">
         <v>6</v>
       </c>
-      <c r="L29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="M29" s="2"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M29" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="N29" s="2"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C30" s="1">
         <v>3112</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
       </c>
       <c r="F30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1">
         <v>30043</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <v>1006</v>
       </c>
-      <c r="H30" s="1">
-        <v>10</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" s="1">
+      <c r="I30" s="1">
+        <v>10</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L30" s="1">
         <v>6</v>
       </c>
-      <c r="L30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M30" s="2"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M30" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C31" s="1">
         <v>3113</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
       </c>
       <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
         <v>30073</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <v>1006</v>
       </c>
-      <c r="H31" s="1">
-        <v>10</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" s="1">
+      <c r="I31" s="1">
+        <v>10</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L31" s="1">
         <v>6</v>
       </c>
-      <c r="L31" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="M31" s="2"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:13">
+      <c r="M31" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C32" s="1">
         <v>3114</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
       </c>
       <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1">
         <v>30024</v>
       </c>
-      <c r="G32" s="1">
+      <c r="H32" s="1">
         <v>1006</v>
       </c>
-      <c r="H32" s="1">
-        <v>10</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" s="1">
+      <c r="I32" s="1">
+        <v>10</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L32" s="1">
         <v>7</v>
       </c>
-      <c r="L32" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="M32" s="2"/>
-    </row>
-    <row r="33" customHeight="1" spans="3:13 16372:16384">
+      <c r="M32" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="N32" s="2"/>
+    </row>
+    <row r="33" customHeight="1" spans="3:14 16373:16384">
       <c r="C33" s="1">
         <v>3115</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
       </c>
       <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
         <v>30034</v>
       </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <v>1006</v>
       </c>
-      <c r="H33" s="1">
-        <v>10</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" s="1">
+      <c r="I33" s="1">
+        <v>10</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L33" s="1">
         <v>7</v>
       </c>
-      <c r="L33" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:13 16372:16384">
+      <c r="M33" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:14 16373:16384">
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -4722,9 +4941,9 @@
       <c r="I34" s="1"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="1"/>
-      <c r="XER34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="1"/>
       <c r="XES34" s="1"/>
       <c r="XET34" s="1"/>
       <c r="XEU34" s="1"/>
@@ -4738,7 +4957,7 @@
       <c r="XFC34" s="1"/>
       <c r="XFD34" s="1"/>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:13 16372:16384">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:14 16373:16384">
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -4750,7 +4969,7 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-      <c r="XER35" s="1"/>
+      <c r="N35" s="1"/>
       <c r="XES35" s="1"/>
       <c r="XET35" s="1"/>
       <c r="XEU35" s="1"/>
@@ -4764,7 +4983,7 @@
       <c r="XFC35" s="1"/>
       <c r="XFD35" s="1"/>
     </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:13 16372:16384">
+    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:14 16373:16384">
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -4775,7 +4994,7 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
-      <c r="XER37" s="1"/>
+      <c r="M37" s="1"/>
       <c r="XES37" s="1"/>
       <c r="XET37" s="1"/>
       <c r="XEU37" s="1"/>
@@ -4789,7 +5008,7 @@
       <c r="XFC37" s="1"/>
       <c r="XFD37" s="1"/>
     </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:13 16372:16384">
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:14 16373:16384">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -4800,7 +5019,7 @@
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
-      <c r="XER48" s="1"/>
+      <c r="M48" s="1"/>
       <c r="XES48" s="1"/>
       <c r="XET48" s="1"/>
       <c r="XEU48" s="1"/>
@@ -4814,7 +5033,7 @@
       <c r="XFC48" s="1"/>
       <c r="XFD48" s="1"/>
     </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -4825,7 +5044,7 @@
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
-      <c r="XER49" s="1"/>
+      <c r="M49" s="1"/>
       <c r="XES49" s="1"/>
       <c r="XET49" s="1"/>
       <c r="XEU49" s="1"/>
@@ -4839,7 +5058,7 @@
       <c r="XFC49" s="1"/>
       <c r="XFD49" s="1"/>
     </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -4850,7 +5069,7 @@
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
-      <c r="XER50" s="1"/>
+      <c r="M50" s="1"/>
       <c r="XES50" s="1"/>
       <c r="XET50" s="1"/>
       <c r="XEU50" s="1"/>
@@ -4864,7 +5083,7 @@
       <c r="XFC50" s="1"/>
       <c r="XFD50" s="1"/>
     </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -4875,7 +5094,7 @@
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
-      <c r="XER51" s="1"/>
+      <c r="M51" s="1"/>
       <c r="XES51" s="1"/>
       <c r="XET51" s="1"/>
       <c r="XEU51" s="1"/>
@@ -4889,7 +5108,7 @@
       <c r="XFC51" s="1"/>
       <c r="XFD51" s="1"/>
     </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -4900,7 +5119,7 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
-      <c r="XER52" s="1"/>
+      <c r="M52" s="1"/>
       <c r="XES52" s="1"/>
       <c r="XET52" s="1"/>
       <c r="XEU52" s="1"/>
@@ -4914,7 +5133,7 @@
       <c r="XFC52" s="1"/>
       <c r="XFD52" s="1"/>
     </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:12 16372:16384">
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -4925,7 +5144,7 @@
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
-      <c r="XER53" s="1"/>
+      <c r="M53" s="1"/>
       <c r="XES53" s="1"/>
       <c r="XET53" s="1"/>
       <c r="XEU53" s="1"/>
@@ -4941,7 +5160,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="K3:K5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="110">
   <si>
     <t>#</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>天下无敌</t>
-  </si>
-  <si>
-    <t>PreId</t>
   </si>
   <si>
     <t>八荒短刀</t>
@@ -1519,7 +1516,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -1557,7 +1554,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -1595,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="I9" s="1">
         <v>10</v>
@@ -1633,13 +1630,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="I10" s="1">
         <v>10</v>
@@ -1671,13 +1668,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="I11" s="1">
         <v>10</v>
@@ -1706,13 +1703,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="I12" s="1">
         <v>10</v>
@@ -1741,13 +1738,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="I13" s="1">
         <v>10</v>
@@ -1776,13 +1773,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
         <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="I14" s="1">
         <v>10</v>
@@ -1879,7 +1876,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>5</v>
@@ -1916,7 +1913,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>5</v>
@@ -1982,7 +1979,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -2012,7 +2009,7 @@
         <v>19</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2020,13 +2017,13 @@
         <v>1002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>1001</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -2050,7 +2047,7 @@
         <v>19</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1"/>
@@ -2069,7 +2066,7 @@
         <v>1101</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -2096,7 +2093,7 @@
         <v>5</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:18">
@@ -2104,7 +2101,7 @@
         <v>1102</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -2131,7 +2128,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
@@ -2139,7 +2136,7 @@
         <v>1103</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -2166,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:18">
@@ -2174,7 +2171,7 @@
         <v>1104</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -2201,7 +2198,7 @@
         <v>5</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:18">
@@ -2209,7 +2206,7 @@
         <v>1105</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -2236,7 +2233,7 @@
         <v>5</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:18">
@@ -2244,7 +2241,7 @@
         <v>1106</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -2271,7 +2268,7 @@
         <v>5</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:18">
@@ -2279,7 +2276,7 @@
         <v>1107</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -2306,7 +2303,7 @@
         <v>5</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R25" s="4"/>
     </row>
@@ -2315,13 +2312,13 @@
         <v>1108</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>1101</v>
       </c>
       <c r="G26" s="1">
         <v>10012</v>
@@ -2342,7 +2339,7 @@
         <v>6</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="R26" s="4"/>
     </row>
@@ -2351,13 +2348,13 @@
         <v>1109</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>1102</v>
       </c>
       <c r="G27" s="1">
         <v>10022</v>
@@ -2378,7 +2375,7 @@
         <v>6</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="R27" s="4"/>
     </row>
@@ -2387,13 +2384,13 @@
         <v>1110</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>1103</v>
       </c>
       <c r="G28" s="1">
         <v>10032</v>
@@ -2414,7 +2411,7 @@
         <v>6</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="O28" s="4"/>
       <c r="P28" s="1"/>
@@ -2425,13 +2422,13 @@
         <v>1111</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>1104</v>
       </c>
       <c r="G29" s="1">
         <v>10042</v>
@@ -2452,7 +2449,7 @@
         <v>6</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O29" s="4"/>
       <c r="P29" s="1"/>
@@ -2463,13 +2460,13 @@
         <v>1112</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>1107</v>
       </c>
       <c r="G30" s="1">
         <v>10072</v>
@@ -2490,7 +2487,7 @@
         <v>6</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="O30" s="4"/>
       <c r="P30" s="1"/>
@@ -2501,13 +2498,13 @@
         <v>1113</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>1109</v>
       </c>
       <c r="G31" s="1">
         <v>10023</v>
@@ -2528,7 +2525,7 @@
         <v>6</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O31" s="4"/>
       <c r="P31" s="1"/>
@@ -2539,13 +2536,13 @@
         <v>1114</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>1112</v>
       </c>
       <c r="G32" s="1">
         <v>10073</v>
@@ -2566,7 +2563,7 @@
         <v>7</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O32" s="4"/>
       <c r="P32" s="1"/>
@@ -2577,13 +2574,13 @@
         <v>1115</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>1109</v>
       </c>
       <c r="G33" s="1">
         <v>10024</v>
@@ -2604,7 +2601,7 @@
         <v>7</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -2616,12 +2613,14 @@
         <v>1116</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
-      <c r="F34" s="1"/>
+      <c r="F34" s="1">
+        <v>1110</v>
+      </c>
       <c r="G34" s="1">
         <v>10034</v>
       </c>
@@ -2641,7 +2640,7 @@
         <v>7</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="4"/>
@@ -2966,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>5</v>
@@ -3003,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>5</v>
@@ -3069,7 +3068,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -3097,7 +3096,7 @@
         <v>19</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="XES6" s="1"/>
       <c r="XET6" s="1"/>
@@ -3117,7 +3116,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -3145,7 +3144,7 @@
         <v>19</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="XES7" s="1"/>
       <c r="XET7" s="1"/>
@@ -3415,7 +3414,7 @@
         <v>2101</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -3442,7 +3441,7 @@
         <v>5</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="XES19" s="1"/>
       <c r="XET19" s="1"/>
@@ -3462,7 +3461,7 @@
         <v>2102</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -3489,7 +3488,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -3502,7 +3501,7 @@
         <v>2103</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -3529,7 +3528,7 @@
         <v>5</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
@@ -3542,7 +3541,7 @@
         <v>2104</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -3569,7 +3568,7 @@
         <v>5</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -3582,7 +3581,7 @@
         <v>2105</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
@@ -3609,7 +3608,7 @@
         <v>5</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -3622,7 +3621,7 @@
         <v>2106</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -3649,7 +3648,7 @@
         <v>5</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -3662,7 +3661,7 @@
         <v>2107</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -3689,7 +3688,7 @@
         <v>5</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -3702,7 +3701,7 @@
         <v>2108</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -3729,7 +3728,7 @@
         <v>6</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -3742,7 +3741,7 @@
         <v>2109</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -3769,7 +3768,7 @@
         <v>6</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -3782,7 +3781,7 @@
         <v>2110</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -3809,7 +3808,7 @@
         <v>6</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
@@ -3822,7 +3821,7 @@
         <v>2111</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -3849,7 +3848,7 @@
         <v>6</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
@@ -3874,7 +3873,7 @@
         <v>2112</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -3901,7 +3900,7 @@
         <v>6</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
@@ -3926,7 +3925,7 @@
         <v>2113</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
@@ -3953,7 +3952,7 @@
         <v>6</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
@@ -3978,7 +3977,7 @@
         <v>2114</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -4005,7 +4004,7 @@
         <v>7</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
@@ -4030,7 +4029,7 @@
         <v>2115</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -4057,7 +4056,7 @@
         <v>7</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -4070,7 +4069,7 @@
         <v>2116</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G34" s="1">
         <v>20034</v>
@@ -4091,7 +4090,7 @@
         <v>7</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
@@ -4189,7 +4188,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>5</v>
@@ -4226,7 +4225,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>5</v>
@@ -4292,7 +4291,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -4320,7 +4319,7 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -4328,7 +4327,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -4356,7 +4355,7 @@
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -4397,7 +4396,7 @@
         <v>3101</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -4424,7 +4423,7 @@
         <v>5</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N19" s="2"/>
     </row>
@@ -4433,7 +4432,7 @@
         <v>3102</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -4460,7 +4459,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N20" s="2"/>
     </row>
@@ -4469,7 +4468,7 @@
         <v>3103</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -4496,7 +4495,7 @@
         <v>5</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N21" s="2"/>
     </row>
@@ -4505,7 +4504,7 @@
         <v>3104</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -4532,7 +4531,7 @@
         <v>5</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N22" s="2"/>
     </row>
@@ -4541,7 +4540,7 @@
         <v>3105</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E23" s="1">
         <v>3</v>
@@ -4568,7 +4567,7 @@
         <v>5</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N23" s="2"/>
     </row>
@@ -4577,7 +4576,7 @@
         <v>3106</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -4604,7 +4603,7 @@
         <v>5</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -4613,7 +4612,7 @@
         <v>3107</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -4640,7 +4639,7 @@
         <v>5</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -4649,7 +4648,7 @@
         <v>3108</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -4676,7 +4675,7 @@
         <v>6</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -4685,7 +4684,7 @@
         <v>3109</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -4712,7 +4711,7 @@
         <v>6</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -4721,7 +4720,7 @@
         <v>3110</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -4748,7 +4747,7 @@
         <v>6</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -4757,7 +4756,7 @@
         <v>3111</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -4784,7 +4783,7 @@
         <v>6</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -4793,7 +4792,7 @@
         <v>3112</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -4820,7 +4819,7 @@
         <v>6</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -4829,7 +4828,7 @@
         <v>3113</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
@@ -4856,7 +4855,7 @@
         <v>6</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N31" s="2"/>
     </row>
@@ -4865,7 +4864,7 @@
         <v>3114</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -4892,7 +4891,7 @@
         <v>7</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -4901,7 +4900,7 @@
         <v>3115</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -4928,7 +4927,7 @@
         <v>7</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" customHeight="1" spans="3:14 16373:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="203">
   <si>
     <t>#</t>
   </si>
@@ -50,16 +50,16 @@
     <t>TalentId</t>
   </si>
   <si>
-    <t>AttrId</t>
-  </si>
-  <si>
-    <t>AttrValue</t>
-  </si>
-  <si>
-    <t>MaterialIdList</t>
-  </si>
-  <si>
-    <t>MaterialCountList</t>
+    <t>AtrIdList</t>
+  </si>
+  <si>
+    <t>AtrVueList</t>
+  </si>
+  <si>
+    <t>MidList</t>
+  </si>
+  <si>
+    <t>McList</t>
   </si>
   <si>
     <t>Quality</t>
@@ -80,96 +80,291 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>萌新之刃</t>
+    <t>铜钱袋</t>
+  </si>
+  <si>
+    <t>81,21,95</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
+    <t>40000001,40000002,40000002</t>
+  </si>
+  <si>
+    <t>10,3,1</t>
+  </si>
+  <si>
+    <t>没有特殊效果</t>
+  </si>
+  <si>
+    <t>金币加成</t>
+  </si>
+  <si>
+    <t>试炼卷轴</t>
+  </si>
+  <si>
+    <t>82,22,95</t>
+  </si>
+  <si>
+    <t>40000004,40000005,40000006</t>
+  </si>
+  <si>
+    <t>经验加成</t>
+  </si>
+  <si>
+    <t>寻金符</t>
+  </si>
+  <si>
+    <t>83,23,95</t>
+  </si>
+  <si>
+    <t>40000007,40000008,40000009</t>
+  </si>
+  <si>
+    <t>爆率加成</t>
+  </si>
+  <si>
+    <t>四叶草</t>
+  </si>
+  <si>
+    <t>84,24,95</t>
+  </si>
+  <si>
+    <t>40000010,40000011,40000012</t>
+  </si>
+  <si>
+    <t>品质加成</t>
+  </si>
+  <si>
+    <t>妙手扳指</t>
+  </si>
+  <si>
+    <t>85,27,95</t>
+  </si>
+  <si>
+    <t>10,1,1</t>
+  </si>
+  <si>
+    <t>40000002,40000005,40000008</t>
+  </si>
+  <si>
+    <t>3,3,3</t>
+  </si>
+  <si>
+    <t>杀怪金币</t>
+  </si>
+  <si>
+    <t>修行符</t>
+  </si>
+  <si>
+    <t>86,28,95</t>
+  </si>
+  <si>
+    <t>40000003,40000006,40000009</t>
+  </si>
+  <si>
+    <t>杀怪经验</t>
+  </si>
+  <si>
+    <t>招财挂坠</t>
+  </si>
+  <si>
+    <t>3,2,1</t>
+  </si>
+  <si>
+    <t>经验符</t>
+  </si>
+  <si>
+    <t>聚宝盆</t>
+  </si>
+  <si>
+    <t>幸运符</t>
+  </si>
+  <si>
+    <t>神偷护符</t>
+  </si>
+  <si>
+    <t>30,3,1</t>
+  </si>
+  <si>
+    <t>40000005,40000008,40000011</t>
+  </si>
+  <si>
+    <t>历练帖</t>
+  </si>
+  <si>
+    <t>40000006,40000009,40000012</t>
+  </si>
+  <si>
+    <t>聚兽铜印</t>
+  </si>
+  <si>
+    <t>2001,111,95</t>
+  </si>
+  <si>
+    <t>5,1,2</t>
+  </si>
+  <si>
+    <t>2,2,2</t>
+  </si>
+  <si>
+    <t>增加一个宠物备战位</t>
+  </si>
+  <si>
+    <t>驯兽金印</t>
+  </si>
+  <si>
+    <t>2003,112,95</t>
+  </si>
+  <si>
+    <t>增加一个宠物备出战位</t>
+  </si>
+  <si>
+    <t>粗铁刀</t>
+  </si>
+  <si>
+    <t>3,4,95</t>
+  </si>
+  <si>
+    <t>50,100,1</t>
   </si>
   <si>
     <t>40000001,40000002</t>
   </si>
   <si>
+    <t>50,5</t>
+  </si>
+  <si>
+    <t>硬皮甲</t>
+  </si>
+  <si>
+    <t>2,4,95</t>
+  </si>
+  <si>
+    <t>40000004,40000005</t>
+  </si>
+  <si>
+    <t>硬皮靴</t>
+  </si>
+  <si>
+    <t>1,4,95</t>
+  </si>
+  <si>
+    <t>1000,100,1</t>
+  </si>
+  <si>
+    <t>40000007,40000008</t>
+  </si>
+  <si>
+    <t>黑铁护腕</t>
+  </si>
+  <si>
+    <t>3,1004,95</t>
+  </si>
+  <si>
+    <t>100,5,1</t>
+  </si>
+  <si>
+    <t>40000001,40000003</t>
+  </si>
+  <si>
+    <t>100,1</t>
+  </si>
+  <si>
+    <t>黑铁指环</t>
+  </si>
+  <si>
+    <t>2,1004,95</t>
+  </si>
+  <si>
+    <t>黑铁头盔</t>
+  </si>
+  <si>
+    <t>1,1004,95</t>
+  </si>
+  <si>
+    <t>2000,5,1</t>
+  </si>
+  <si>
+    <t>凌风长剑</t>
+  </si>
+  <si>
+    <t>1003,1004,95</t>
+  </si>
+  <si>
+    <t>5,10,1</t>
+  </si>
+  <si>
+    <t>10,2</t>
+  </si>
+  <si>
+    <t>古铜戒指</t>
+  </si>
+  <si>
+    <t>1002,1004,95</t>
+  </si>
+  <si>
+    <t>10,10,1</t>
+  </si>
+  <si>
+    <t>40000005,40000007</t>
+  </si>
+  <si>
+    <t>古铜项链</t>
+  </si>
+  <si>
+    <t>1001,1004,95</t>
+  </si>
+  <si>
+    <t>20,10,1</t>
+  </si>
+  <si>
+    <t>40000008,40000009</t>
+  </si>
+  <si>
+    <t>基础战体</t>
+  </si>
+  <si>
+    <t>3,6,95</t>
+  </si>
+  <si>
+    <t>100,200,1</t>
+  </si>
+  <si>
     <t>100,10</t>
   </si>
   <si>
-    <t>没有特殊效果</t>
-  </si>
-  <si>
-    <t>生命加成</t>
-  </si>
-  <si>
-    <t>小试牛刀</t>
-  </si>
-  <si>
-    <t>40000001,40000003</t>
-  </si>
-  <si>
-    <t>防御加成</t>
-  </si>
-  <si>
-    <t>初露锋芒</t>
-  </si>
-  <si>
-    <t>40000002,40000003</t>
-  </si>
-  <si>
-    <t>血量加成</t>
-  </si>
-  <si>
-    <t>武林新秀</t>
-  </si>
-  <si>
-    <t>伤害加成</t>
-  </si>
-  <si>
-    <t>声名鹊起</t>
-  </si>
-  <si>
-    <t>伤害减免</t>
-  </si>
-  <si>
-    <t>过关斩将</t>
-  </si>
-  <si>
-    <t>独孤求败</t>
-  </si>
-  <si>
-    <t>武林至尊</t>
-  </si>
-  <si>
-    <t>天下无敌</t>
-  </si>
-  <si>
-    <t>八荒短刀</t>
-  </si>
-  <si>
-    <t>物攻加成</t>
-  </si>
-  <si>
-    <t>凌风长剑</t>
-  </si>
-  <si>
-    <t>物伤加成</t>
-  </si>
-  <si>
-    <t>基础战体</t>
-  </si>
-  <si>
     <t>基础心法·战体</t>
   </si>
   <si>
     <t>流光无断</t>
   </si>
   <si>
+    <t>2,6,95</t>
+  </si>
+  <si>
     <t>流光剑诀·无断</t>
   </si>
   <si>
     <t>四方破甲</t>
   </si>
   <si>
+    <t>1,6,95</t>
+  </si>
+  <si>
+    <t>2000,200,1</t>
+  </si>
+  <si>
     <t>四方剑阵·破甲</t>
   </si>
   <si>
     <t>重击破甲</t>
   </si>
   <si>
+    <t>200,5</t>
+  </si>
+  <si>
     <t>重击剑术·破甲</t>
   </si>
   <si>
@@ -188,6 +383,9 @@
     <t>火麟迅疾</t>
   </si>
   <si>
+    <t>30,10</t>
+  </si>
+  <si>
     <t>火麟剑诀·迅疾</t>
   </si>
   <si>
@@ -245,16 +443,58 @@
     <t>四方剑阵·疾速</t>
   </si>
   <si>
-    <t>海魂法杖</t>
-  </si>
-  <si>
-    <t>魔攻加成</t>
-  </si>
-  <si>
-    <t>炎月法杖</t>
-  </si>
-  <si>
-    <t>魔伤加成</t>
+    <t>乌木杖</t>
+  </si>
+  <si>
+    <t>3,5,95</t>
+  </si>
+  <si>
+    <t>软布衣</t>
+  </si>
+  <si>
+    <t>2,5,95</t>
+  </si>
+  <si>
+    <t>软布鞋</t>
+  </si>
+  <si>
+    <t>1,5,95</t>
+  </si>
+  <si>
+    <t>桃木护腕</t>
+  </si>
+  <si>
+    <t>3,1005,95</t>
+  </si>
+  <si>
+    <t>桃木指环</t>
+  </si>
+  <si>
+    <t>2,1005,95</t>
+  </si>
+  <si>
+    <t>桃木道冠</t>
+  </si>
+  <si>
+    <t>1,1005,95</t>
+  </si>
+  <si>
+    <t>海魂道剑</t>
+  </si>
+  <si>
+    <t>1003,1005,95</t>
+  </si>
+  <si>
+    <t>魔力耳环</t>
+  </si>
+  <si>
+    <t>1002,1005,95</t>
+  </si>
+  <si>
+    <t>水晶项链</t>
+  </si>
+  <si>
+    <t>1001,1005,95</t>
   </si>
   <si>
     <t>冥想法体</t>
@@ -305,16 +545,55 @@
     <t>火海疾速</t>
   </si>
   <si>
+    <t>竹节剑</t>
+  </si>
+  <si>
+    <t>道攻加成</t>
+  </si>
+  <si>
+    <t>粗麻袍</t>
+  </si>
+  <si>
+    <t>道伤加成</t>
+  </si>
+  <si>
+    <t>粗麻靴</t>
+  </si>
+  <si>
+    <t>青竹护腕</t>
+  </si>
+  <si>
+    <t>3,1006,95</t>
+  </si>
+  <si>
+    <t>青竹指环</t>
+  </si>
+  <si>
+    <t>2,1006,95</t>
+  </si>
+  <si>
+    <t>青竹道冠</t>
+  </si>
+  <si>
+    <t>1,1006,95</t>
+  </si>
+  <si>
     <t>半月道剑</t>
   </si>
   <si>
-    <t>道攻加成</t>
-  </si>
-  <si>
-    <t>破魂道剑</t>
-  </si>
-  <si>
-    <t>道伤加成</t>
+    <t>1003,1006,95</t>
+  </si>
+  <si>
+    <t>明珠耳环</t>
+  </si>
+  <si>
+    <t>1002,1006,95</t>
+  </si>
+  <si>
+    <t>虎齿项链</t>
+  </si>
+  <si>
+    <t>1001,1006,95</t>
   </si>
   <si>
     <t>祈福道体</t>
@@ -372,7 +651,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -390,6 +669,12 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -862,16 +1147,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -880,132 +1162,143 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -1327,7 +1620,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1335,7 +1628,7 @@
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
     <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.9166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.5" style="1" customWidth="1"/>
     <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
     <col min="15" max="16372" width="9" style="2"/>
@@ -1449,10 +1742,10 @@
         <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>15</v>
@@ -1483,325 +1776,522 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="1">
-        <v>1001</v>
-      </c>
-      <c r="I6" s="1">
-        <v>10</v>
-      </c>
-      <c r="J6" s="8" t="s">
+      <c r="H6" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="I6" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="J6" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="L6" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L7" s="1">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="1">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1002</v>
-      </c>
-      <c r="I7" s="1">
-        <v>10</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="1">
-        <v>4</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="N7" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>24</v>
+      <c r="D8" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
       </c>
       <c r="F8" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="1">
-        <v>1003</v>
-      </c>
-      <c r="I8" s="1">
-        <v>10</v>
-      </c>
-      <c r="J8" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="H8" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I8" s="10" t="s">
         <v>18</v>
       </c>
+      <c r="J8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="L8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>27</v>
+      <c r="D9" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
       </c>
       <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="1">
         <v>3</v>
       </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1001</v>
-      </c>
-      <c r="I9" s="1">
-        <v>10</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" s="1">
-        <v>4</v>
-      </c>
       <c r="M9" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>29</v>
+      <c r="D10" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
       </c>
       <c r="F10" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="1">
-        <v>1002</v>
-      </c>
-      <c r="I10" s="1">
-        <v>10</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>18</v>
+      <c r="H10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="L10" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>31</v>
+      <c r="D11" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
       </c>
       <c r="F11" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="1">
-        <v>1003</v>
-      </c>
-      <c r="I11" s="1">
-        <v>10</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="H11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>18</v>
       </c>
       <c r="L11" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>32</v>
+      <c r="D12" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H12" s="1">
-        <v>1001</v>
-      </c>
-      <c r="I12" s="1">
-        <v>10</v>
-      </c>
-      <c r="J12" s="8" t="s">
+      <c r="H12" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>18</v>
+      <c r="I12" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="L12" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>33</v>
+      <c r="D13" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
       </c>
       <c r="F13" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="1">
-        <v>1002</v>
-      </c>
-      <c r="I13" s="1">
-        <v>10</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>18</v>
+      <c r="H13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="L13" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1">
+        <v>3</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" s="1">
+        <v>4</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1">
+        <v>4</v>
+      </c>
+      <c r="G15" s="1">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" s="1">
+        <v>4</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>8</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1003</v>
-      </c>
-      <c r="I14" s="1">
-        <v>10</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="1" t="s">
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>5</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L16" s="1">
+        <v>4</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1">
+        <v>6</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L17" s="1">
+        <v>4</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" s="1">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="1">
         <v>5</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1"/>
-    <row r="16" s="1" customFormat="1" customHeight="1"/>
-    <row r="17" s="1" customFormat="1" customHeight="1"/>
-    <row r="18" s="1" customFormat="1" customHeight="1"/>
-    <row r="19" s="1" customFormat="1" customHeight="1"/>
+      <c r="M18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>13</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
     <row r="20" s="1" customFormat="1" customHeight="1"/>
     <row r="21" s="1" customFormat="1" customHeight="1"/>
     <row r="22" s="1" customFormat="1" customHeight="1"/>
@@ -1811,15 +2301,11 @@
     <row r="26" s="1" customFormat="1" customHeight="1"/>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
     <row r="28" s="1" customFormat="1" customHeight="1"/>
-    <row r="29" s="1" customFormat="1" customHeight="1"/>
-    <row r="30" s="1" customFormat="1" customHeight="1"/>
-    <row r="31" s="1" customFormat="1" customHeight="1"/>
-    <row r="32" s="1" customFormat="1" customHeight="1"/>
-    <row r="34" customHeight="1" spans="14:14">
-      <c r="N34" s="1"/>
-    </row>
-    <row r="35" customHeight="1" spans="14:14">
-      <c r="N35" s="1"/>
+    <row r="30" customHeight="1" spans="3:14">
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:14">
+      <c r="N31" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1835,14 +2321,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD53"/>
+  <dimension ref="A1:XFD54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="10" width="12.25" style="1" customWidth="1"/>
+    <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" style="1" customWidth="1"/>
     <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
     <col min="15" max="16372" width="9" style="2"/>
@@ -1956,10 +2443,10 @@
         <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>15</v>
@@ -1978,8 +2465,8 @@
       <c r="C6" s="1">
         <v>1001</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>35</v>
+      <c r="D6" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -1990,118 +2477,318 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I6" s="1">
-        <v>10</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>18</v>
+      <c r="H6" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="L6" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>37</v>
+      <c r="D7" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L7" s="1">
+        <v>3</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C8" s="1">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="1">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C9" s="1">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="1">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="1">
+        <v>4</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C10" s="1">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="1">
+        <v>4</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C11" s="1">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="1">
+        <v>4</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C12" s="1">
         <v>1007</v>
       </c>
-      <c r="I7" s="1">
-        <v>10</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L7" s="1">
-        <v>4</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1"/>
-    <row r="9" s="1" customFormat="1" customHeight="1"/>
-    <row r="10" s="1" customFormat="1" customHeight="1"/>
-    <row r="11" s="1" customFormat="1" customHeight="1"/>
-    <row r="12" s="1" customFormat="1" customHeight="1"/>
-    <row r="13" s="1" customFormat="1" customHeight="1"/>
-    <row r="14" s="1" customFormat="1" customHeight="1"/>
+      <c r="D12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="1">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" s="1">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C13" s="1">
+        <v>1008</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" s="1">
+        <v>5</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C14" s="1">
+        <v>1009</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14" s="1">
+        <v>5</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
     <row r="16" s="1" customFormat="1" customHeight="1"/>
-    <row r="17" s="1" customFormat="1" customHeight="1"/>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:18">
+      <c r="D17" s="4"/>
+    </row>
     <row r="18" s="1" customFormat="1" customHeight="1"/>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C19" s="1">
-        <v>1101</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
-        <v>10011</v>
-      </c>
-      <c r="H19" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I19" s="1">
-        <v>10</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" s="1">
-        <v>5</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1"/>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C20" s="1">
-        <v>1102</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>41</v>
+        <v>1101</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -2110,33 +2797,33 @@
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>10021</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I20" s="1">
-        <v>10</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>18</v>
+        <v>10011</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>42</v>
+      <c r="M20" s="6" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C21" s="1">
-        <v>1103</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>43</v>
+        <v>1102</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -2145,33 +2832,33 @@
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>10031</v>
-      </c>
-      <c r="H21" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I21" s="1">
-        <v>10</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>18</v>
+        <v>10021</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>44</v>
+      <c r="M21" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C22" s="1">
-        <v>1104</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>45</v>
+        <v>1103</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -2180,33 +2867,33 @@
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>10041</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I22" s="1">
-        <v>10</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>18</v>
+        <v>10031</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
-      <c r="M22" s="4" t="s">
-        <v>46</v>
+      <c r="M22" s="6" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C23" s="1">
-        <v>1105</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>47</v>
+        <v>1104</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -2215,33 +2902,33 @@
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>10051</v>
-      </c>
-      <c r="H23" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I23" s="1">
-        <v>10</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>18</v>
+        <v>10041</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
-      <c r="M23" s="4" t="s">
-        <v>48</v>
+      <c r="M23" s="6" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C24" s="1">
-        <v>1106</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>49</v>
+        <v>1105</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -2250,33 +2937,33 @@
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>10061</v>
-      </c>
-      <c r="H24" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I24" s="1">
-        <v>10</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>18</v>
+        <v>10051</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="M24" s="4" t="s">
-        <v>50</v>
+      <c r="M24" s="6" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C25" s="1">
-        <v>1107</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>51</v>
+        <v>1106</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -2285,395 +2972,404 @@
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>10071</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I25" s="1">
-        <v>10</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>18</v>
+        <v>10061</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="R25" s="4"/>
+      <c r="M25" s="6" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C26" s="1">
-        <v>1108</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>53</v>
+        <v>1107</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
       </c>
       <c r="F26" s="1">
-        <v>1101</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>10012</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I26" s="1">
-        <v>10</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>18</v>
+        <v>10071</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L26" s="1">
-        <v>6</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="R26" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="R26" s="6"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C27" s="1">
-        <v>1109</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>55</v>
+        <v>1108</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
       </c>
       <c r="F27" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G27" s="1">
-        <v>10022</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I27" s="1">
-        <v>10</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>18</v>
+        <v>10012</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L27" s="1">
         <v>6</v>
       </c>
-      <c r="M27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="R27" s="4"/>
+      <c r="M27" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="R27" s="6"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C28" s="1">
-        <v>1110</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>57</v>
+        <v>1109</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G28" s="1">
-        <v>10032</v>
-      </c>
-      <c r="H28" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I28" s="1">
-        <v>10</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>18</v>
+        <v>10022</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L28" s="1">
         <v>6</v>
       </c>
-      <c r="M28" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="O28" s="4"/>
-      <c r="P28" s="1"/>
-      <c r="R28" s="4"/>
+      <c r="M28" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="R28" s="6"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C29" s="1">
-        <v>1111</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>59</v>
+        <v>1110</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G29" s="1">
-        <v>10042</v>
-      </c>
-      <c r="H29" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I29" s="1">
-        <v>10</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>17</v>
+        <v>10032</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L29" s="1">
         <v>6</v>
       </c>
-      <c r="M29" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="O29" s="4"/>
+      <c r="M29" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="O29" s="6"/>
       <c r="P29" s="1"/>
-      <c r="R29" s="4"/>
+      <c r="R29" s="6"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C30" s="1">
-        <v>1112</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>61</v>
+        <v>1111</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="G30" s="1">
-        <v>10072</v>
-      </c>
-      <c r="H30" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I30" s="1">
-        <v>10</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>17</v>
+        <v>10042</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L30" s="1">
         <v>6</v>
       </c>
-      <c r="M30" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="O30" s="4"/>
+      <c r="M30" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="O30" s="6"/>
       <c r="P30" s="1"/>
-      <c r="R30" s="4"/>
+      <c r="R30" s="6"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C31" s="1">
-        <v>1113</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>63</v>
+        <v>1112</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G31" s="1">
-        <v>10023</v>
-      </c>
-      <c r="H31" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I31" s="1">
-        <v>10</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>17</v>
+        <v>10072</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L31" s="1">
         <v>6</v>
       </c>
-      <c r="M31" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="O31" s="4"/>
+      <c r="M31" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="O31" s="6"/>
       <c r="P31" s="1"/>
-      <c r="R31" s="4"/>
+      <c r="R31" s="6"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C32" s="1">
-        <v>1114</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>65</v>
+        <v>1113</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="G32" s="1">
-        <v>10073</v>
-      </c>
-      <c r="H32" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I32" s="1">
-        <v>10</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>17</v>
+        <v>10023</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L32" s="1">
-        <v>7</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="O32" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="O32" s="6"/>
       <c r="P32" s="1"/>
-      <c r="R32" s="4"/>
-    </row>
-    <row r="33" customHeight="1" spans="3:19 16373:16384">
+      <c r="R32" s="6"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
       <c r="C33" s="1">
-        <v>1115</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>67</v>
+        <v>1114</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="G33" s="1">
-        <v>10024</v>
-      </c>
-      <c r="H33" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I33" s="1">
-        <v>10</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>17</v>
+        <v>10073</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L33" s="1">
         <v>7</v>
       </c>
-      <c r="M33" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="O33" s="1"/>
+      <c r="M33" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="O33" s="6"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="S33" s="1"/>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+      <c r="R33" s="6"/>
+    </row>
+    <row r="34" customHeight="1" spans="1:19 16373:16384">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
       <c r="C34" s="1">
-        <v>1116</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>69</v>
+        <v>1115</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
       <c r="F34" s="1">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="G34" s="1">
-        <v>10034</v>
-      </c>
-      <c r="H34" s="1">
-        <v>1004</v>
-      </c>
-      <c r="I34" s="1">
-        <v>10</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>17</v>
+        <v>10024</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L34" s="1">
         <v>7</v>
       </c>
-      <c r="M34" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="4"/>
+      <c r="M34" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="XES34" s="1"/>
-      <c r="XET34" s="1"/>
-      <c r="XEU34" s="1"/>
-      <c r="XEV34" s="1"/>
-      <c r="XEW34" s="1"/>
-      <c r="XEX34" s="1"/>
-      <c r="XEY34" s="1"/>
-      <c r="XEZ34" s="1"/>
-      <c r="XFA34" s="1"/>
-      <c r="XFB34" s="1"/>
-      <c r="XFC34" s="1"/>
-      <c r="XFD34" s="1"/>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
-      <c r="C35" s="1"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
+    </row>
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1">
+        <v>1116</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>1110</v>
+      </c>
+      <c r="G35" s="1">
+        <v>10034</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L35" s="1">
+        <v>7</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="N35" s="1"/>
-      <c r="O35" s="4"/>
+      <c r="O35" s="6"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="S35" s="1"/>
@@ -2690,100 +3386,105 @@
       <c r="XFC35" s="1"/>
       <c r="XFD35" s="1"/>
     </row>
-    <row r="36" customHeight="1" spans="3:19 16373:16384">
-      <c r="O36" s="1"/>
+    <row r="36" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="C36" s="1"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="6"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="S36" s="1"/>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="O37" s="4"/>
+      <c r="XES36" s="1"/>
+      <c r="XET36" s="1"/>
+      <c r="XEU36" s="1"/>
+      <c r="XEV36" s="1"/>
+      <c r="XEW36" s="1"/>
+      <c r="XEX36" s="1"/>
+      <c r="XEY36" s="1"/>
+      <c r="XEZ36" s="1"/>
+      <c r="XFA36" s="1"/>
+      <c r="XFB36" s="1"/>
+      <c r="XFC36" s="1"/>
+      <c r="XFD36" s="1"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:19 16373:16384">
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="S37" s="1"/>
-      <c r="XES37" s="1"/>
-      <c r="XET37" s="1"/>
-      <c r="XEU37" s="1"/>
-      <c r="XEV37" s="1"/>
-      <c r="XEW37" s="1"/>
-      <c r="XEX37" s="1"/>
-      <c r="XEY37" s="1"/>
-      <c r="XEZ37" s="1"/>
-      <c r="XFA37" s="1"/>
-      <c r="XFB37" s="1"/>
-      <c r="XFC37" s="1"/>
-      <c r="XFD37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="3:19 16373:16384">
-      <c r="O38" s="4"/>
+    </row>
+    <row r="38" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="O38" s="6"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
       <c r="S38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="3:19 16373:16384">
+      <c r="XES38" s="1"/>
+      <c r="XET38" s="1"/>
+      <c r="XEU38" s="1"/>
+      <c r="XEV38" s="1"/>
+      <c r="XEW38" s="1"/>
+      <c r="XEX38" s="1"/>
+      <c r="XEY38" s="1"/>
+      <c r="XEZ38" s="1"/>
+      <c r="XFA38" s="1"/>
+      <c r="XFB38" s="1"/>
+      <c r="XFC38" s="1"/>
+      <c r="XFD38" s="1"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:19 16373:16384">
+      <c r="O39" s="6"/>
+      <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
       <c r="S39" s="1"/>
     </row>
-    <row r="40" customHeight="1" spans="3:19 16373:16384">
+    <row r="40" customHeight="1" spans="1:19 16373:16384">
       <c r="Q40" s="1"/>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="3:19 16373:16384">
-      <c r="O41" s="1"/>
+    <row r="41" customHeight="1" spans="1:19 16373:16384">
       <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" customHeight="1" spans="3:19 16373:16384">
+    <row r="42" customHeight="1" spans="1:19 16373:16384">
+      <c r="O42" s="1"/>
       <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" customHeight="1" spans="3:19 16373:16384">
+    <row r="43" customHeight="1" spans="1:19 16373:16384">
       <c r="Q43" s="1"/>
       <c r="S43" s="1"/>
     </row>
-    <row r="44" customHeight="1" spans="3:19 16373:16384">
+    <row r="44" customHeight="1" spans="1:19 16373:16384">
       <c r="Q44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="3:19 16373:16384">
+      <c r="S44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:19 16373:16384">
       <c r="Q45" s="1"/>
     </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="XES48" s="1"/>
-      <c r="XET48" s="1"/>
-      <c r="XEU48" s="1"/>
-      <c r="XEV48" s="1"/>
-      <c r="XEW48" s="1"/>
-      <c r="XEX48" s="1"/>
-      <c r="XEY48" s="1"/>
-      <c r="XEZ48" s="1"/>
-      <c r="XFA48" s="1"/>
-      <c r="XFB48" s="1"/>
-      <c r="XFC48" s="1"/>
-      <c r="XFD48" s="1"/>
+    <row r="46" customHeight="1" spans="1:19 16373:16384">
+      <c r="Q46" s="1"/>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C49" s="1"/>
@@ -2910,6 +3611,31 @@
       <c r="XFC53" s="1"/>
       <c r="XFD53" s="1"/>
     </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="XES54" s="1"/>
+      <c r="XET54" s="1"/>
+      <c r="XEU54" s="1"/>
+      <c r="XEV54" s="1"/>
+      <c r="XEW54" s="1"/>
+      <c r="XEX54" s="1"/>
+      <c r="XEY54" s="1"/>
+      <c r="XEZ54" s="1"/>
+      <c r="XFA54" s="1"/>
+      <c r="XFB54" s="1"/>
+      <c r="XFC54" s="1"/>
+      <c r="XFD54" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
@@ -2924,15 +3650,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD39"/>
+  <dimension ref="A1:XFD51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="10" width="12.25" style="1" customWidth="1"/>
-    <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.4166666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.1666666666667" style="1" customWidth="1"/>
+    <col min="12" max="13" width="15.9166666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
     <col min="15" max="16372" width="9" style="2"/>
     <col min="16373" max="16384" width="9" style="1"/>
@@ -3045,10 +3773,10 @@
         <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>15</v>
@@ -3063,12 +3791,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="6" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
       <c r="C6" s="1">
         <v>2001</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>71</v>
+      <c r="D6" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -3079,24 +3809,23 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>18</v>
+      <c r="H6" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="L6" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="XES6" s="1"/>
       <c r="XET6" s="1"/>
@@ -3111,12 +3840,14 @@
       <c r="XFC6" s="1"/>
       <c r="XFD6" s="1"/>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="7" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
       <c r="C7" s="1">
         <v>2002</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>73</v>
+      <c r="D7" s="4" t="s">
+        <v>139</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -3127,24 +3858,23 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="1">
-        <v>1008</v>
-      </c>
-      <c r="I7" s="1"/>
-      <c r="J7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>18</v>
+      <c r="H7" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="L7" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="XES7" s="1"/>
       <c r="XET7" s="1"/>
@@ -3159,18 +3889,91 @@
       <c r="XFC7" s="1"/>
       <c r="XFD7" s="1"/>
     </row>
+    <row r="8" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1">
+        <v>2003</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" s="1">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="1">
+        <v>3</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="XES8" s="1"/>
+      <c r="XET8" s="1"/>
+      <c r="XEU8" s="1"/>
+      <c r="XEV8" s="1"/>
+      <c r="XEW8" s="1"/>
+      <c r="XEX8" s="1"/>
+      <c r="XEY8" s="1"/>
+      <c r="XEZ8" s="1"/>
+      <c r="XFA8" s="1"/>
+      <c r="XFB8" s="1"/>
+      <c r="XFC8" s="1"/>
+      <c r="XFD8" s="1"/>
+    </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1">
+        <v>2004</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="1">
+        <v>4</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="XES9" s="1"/>
       <c r="XET9" s="1"/>
       <c r="XEU9" s="1"/>
@@ -3185,17 +3988,41 @@
       <c r="XFD9" s="1"/>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1">
+        <v>2005</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="1">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="1">
+        <v>4</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="XES10" s="1"/>
       <c r="XET10" s="1"/>
       <c r="XEU10" s="1"/>
@@ -3210,17 +4037,41 @@
       <c r="XFD10" s="1"/>
     </row>
     <row r="11" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1">
+        <v>2006</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="1">
+        <v>4</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="XES11" s="1"/>
       <c r="XET11" s="1"/>
       <c r="XEU11" s="1"/>
@@ -3235,17 +4086,41 @@
       <c r="XFD11" s="1"/>
     </row>
     <row r="12" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1">
+        <v>2007</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" s="1">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="XES12" s="1"/>
       <c r="XET12" s="1"/>
       <c r="XEU12" s="1"/>
@@ -3260,17 +4135,41 @@
       <c r="XFD12" s="1"/>
     </row>
     <row r="13" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1">
+        <v>2008</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" s="1">
+        <v>5</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="XES13" s="1"/>
       <c r="XET13" s="1"/>
       <c r="XEU13" s="1"/>
@@ -3285,17 +4184,41 @@
       <c r="XFD13" s="1"/>
     </row>
     <row r="14" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1">
+        <v>2009</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14" s="1">
+        <v>5</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="XES14" s="1"/>
       <c r="XET14" s="1"/>
       <c r="XEU14" s="1"/>
@@ -3310,8 +4233,9 @@
       <c r="XFD14" s="1"/>
     </row>
     <row r="15" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -3335,8 +4259,9 @@
       <c r="XFD15" s="1"/>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
       <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -3359,7 +4284,9 @@
       <c r="XFC16" s="1"/>
       <c r="XFD16" s="1"/>
     </row>
-    <row r="17" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+    <row r="17" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -3384,7 +4311,9 @@
       <c r="XFC17" s="1"/>
       <c r="XFD17" s="1"/>
     </row>
-    <row r="18" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+    <row r="18" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -3409,40 +4338,20 @@
       <c r="XFC18" s="1"/>
       <c r="XFD18" s="1"/>
     </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
-      <c r="C19" s="1">
-        <v>2101</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="1">
-        <v>2</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
-        <v>20011</v>
-      </c>
-      <c r="H19" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I19" s="1">
-        <v>10</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" s="1">
-        <v>5</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>40</v>
-      </c>
+    <row r="19" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
       <c r="XES19" s="1"/>
       <c r="XET19" s="1"/>
       <c r="XEU19" s="1"/>
@@ -3456,12 +4365,14 @@
       <c r="XFC19" s="1"/>
       <c r="XFD19" s="1"/>
     </row>
-    <row r="20" customHeight="1" spans="3:18 16373:16384">
+    <row r="20" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
       <c r="C20" s="1">
-        <v>2102</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>76</v>
+        <v>2101</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -3470,38 +4381,48 @@
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>20021</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I20" s="1">
-        <v>10</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>18</v>
+        <v>20011</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" spans="3:18 16373:16384">
+      <c r="M20" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="XES20" s="1"/>
+      <c r="XET20" s="1"/>
+      <c r="XEU20" s="1"/>
+      <c r="XEV20" s="1"/>
+      <c r="XEW20" s="1"/>
+      <c r="XEX20" s="1"/>
+      <c r="XEY20" s="1"/>
+      <c r="XEZ20" s="1"/>
+      <c r="XFA20" s="1"/>
+      <c r="XFB20" s="1"/>
+      <c r="XFC20" s="1"/>
+      <c r="XFD20" s="1"/>
+    </row>
+    <row r="21" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
       <c r="C21" s="1">
-        <v>2103</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>77</v>
+        <v>2102</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -3510,38 +4431,48 @@
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>20031</v>
-      </c>
-      <c r="H21" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I21" s="1">
-        <v>10</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>18</v>
+        <v>20021</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>44</v>
+      <c r="M21" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="1"/>
-    </row>
-    <row r="22" customHeight="1" spans="3:18 16373:16384">
+      <c r="XES21" s="1"/>
+      <c r="XET21" s="1"/>
+      <c r="XEU21" s="1"/>
+      <c r="XEV21" s="1"/>
+      <c r="XEW21" s="1"/>
+      <c r="XEX21" s="1"/>
+      <c r="XEY21" s="1"/>
+      <c r="XEZ21" s="1"/>
+      <c r="XFA21" s="1"/>
+      <c r="XFB21" s="1"/>
+      <c r="XFC21" s="1"/>
+      <c r="XFD21" s="1"/>
+    </row>
+    <row r="22" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
       <c r="C22" s="1">
-        <v>2104</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>78</v>
+        <v>2103</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -3550,38 +4481,48 @@
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>20041</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I22" s="1">
-        <v>10</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>18</v>
+        <v>20031</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
-      <c r="M22" s="4" t="s">
-        <v>46</v>
+      <c r="M22" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="1"/>
-    </row>
-    <row r="23" customHeight="1" spans="3:18 16373:16384">
+      <c r="XES22" s="1"/>
+      <c r="XET22" s="1"/>
+      <c r="XEU22" s="1"/>
+      <c r="XEV22" s="1"/>
+      <c r="XEW22" s="1"/>
+      <c r="XEX22" s="1"/>
+      <c r="XEY22" s="1"/>
+      <c r="XEZ22" s="1"/>
+      <c r="XFA22" s="1"/>
+      <c r="XFB22" s="1"/>
+      <c r="XFC22" s="1"/>
+      <c r="XFD22" s="1"/>
+    </row>
+    <row r="23" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
       <c r="C23" s="1">
-        <v>2105</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>79</v>
+        <v>2104</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>158</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
@@ -3590,38 +4531,48 @@
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>20051</v>
-      </c>
-      <c r="H23" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I23" s="1">
-        <v>10</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>18</v>
+        <v>20041</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
-      <c r="M23" s="4" t="s">
-        <v>48</v>
+      <c r="M23" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="1"/>
-    </row>
-    <row r="24" customHeight="1" spans="3:18 16373:16384">
+      <c r="XES23" s="1"/>
+      <c r="XET23" s="1"/>
+      <c r="XEU23" s="1"/>
+      <c r="XEV23" s="1"/>
+      <c r="XEW23" s="1"/>
+      <c r="XEX23" s="1"/>
+      <c r="XEY23" s="1"/>
+      <c r="XEZ23" s="1"/>
+      <c r="XFA23" s="1"/>
+      <c r="XFB23" s="1"/>
+      <c r="XFC23" s="1"/>
+      <c r="XFD23" s="1"/>
+    </row>
+    <row r="24" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
       <c r="C24" s="1">
-        <v>2106</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>80</v>
+        <v>2105</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -3630,38 +4581,48 @@
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>20061</v>
-      </c>
-      <c r="H24" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I24" s="1">
-        <v>10</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>18</v>
+        <v>20051</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="M24" s="4" t="s">
-        <v>50</v>
+      <c r="M24" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="1"/>
-    </row>
-    <row r="25" customHeight="1" spans="3:18 16373:16384">
+      <c r="XES24" s="1"/>
+      <c r="XET24" s="1"/>
+      <c r="XEU24" s="1"/>
+      <c r="XEV24" s="1"/>
+      <c r="XEW24" s="1"/>
+      <c r="XEX24" s="1"/>
+      <c r="XEY24" s="1"/>
+      <c r="XEZ24" s="1"/>
+      <c r="XFA24" s="1"/>
+      <c r="XFB24" s="1"/>
+      <c r="XFC24" s="1"/>
+      <c r="XFD24" s="1"/>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
       <c r="C25" s="1">
-        <v>2107</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>81</v>
+        <v>2106</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -3670,38 +4631,48 @@
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>20071</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I25" s="1">
-        <v>10</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>18</v>
+        <v>20061</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>52</v>
+      <c r="M25" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="1"/>
-    </row>
-    <row r="26" customHeight="1" spans="3:18 16373:16384">
+      <c r="XES25" s="1"/>
+      <c r="XET25" s="1"/>
+      <c r="XEU25" s="1"/>
+      <c r="XEV25" s="1"/>
+      <c r="XEW25" s="1"/>
+      <c r="XEX25" s="1"/>
+      <c r="XEY25" s="1"/>
+      <c r="XEZ25" s="1"/>
+      <c r="XFA25" s="1"/>
+      <c r="XFB25" s="1"/>
+      <c r="XFC25" s="1"/>
+      <c r="XFD25" s="1"/>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
       <c r="C26" s="1">
-        <v>2108</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>82</v>
+        <v>2107</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -3710,38 +4681,48 @@
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>20012</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I26" s="1">
-        <v>10</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>18</v>
+        <v>20071</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L26" s="1">
-        <v>6</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>54</v>
+        <v>5</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="1"/>
-    </row>
-    <row r="27" customHeight="1" spans="3:18 16373:16384">
+      <c r="XES26" s="1"/>
+      <c r="XET26" s="1"/>
+      <c r="XEU26" s="1"/>
+      <c r="XEV26" s="1"/>
+      <c r="XEW26" s="1"/>
+      <c r="XEX26" s="1"/>
+      <c r="XEY26" s="1"/>
+      <c r="XEZ26" s="1"/>
+      <c r="XFA26" s="1"/>
+      <c r="XFB26" s="1"/>
+      <c r="XFC26" s="1"/>
+      <c r="XFD26" s="1"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
       <c r="C27" s="1">
-        <v>2109</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>83</v>
+        <v>2108</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -3750,38 +4731,48 @@
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>20022</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I27" s="1">
-        <v>10</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>18</v>
+        <v>20012</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L27" s="1">
         <v>6</v>
       </c>
-      <c r="M27" s="4" t="s">
-        <v>56</v>
+      <c r="M27" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="1"/>
-    </row>
-    <row r="28" customHeight="1" spans="3:18 16373:16384">
+      <c r="XES27" s="1"/>
+      <c r="XET27" s="1"/>
+      <c r="XEU27" s="1"/>
+      <c r="XEV27" s="1"/>
+      <c r="XEW27" s="1"/>
+      <c r="XEX27" s="1"/>
+      <c r="XEY27" s="1"/>
+      <c r="XEZ27" s="1"/>
+      <c r="XFA27" s="1"/>
+      <c r="XFB27" s="1"/>
+      <c r="XFC27" s="1"/>
+      <c r="XFD27" s="1"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
       <c r="C28" s="1">
-        <v>2110</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>84</v>
+        <v>2109</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -3790,38 +4781,48 @@
         <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>20032</v>
-      </c>
-      <c r="H28" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I28" s="1">
-        <v>10</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>18</v>
+        <v>20022</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L28" s="1">
         <v>6</v>
       </c>
-      <c r="M28" s="4" t="s">
-        <v>58</v>
+      <c r="M28" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="4"/>
-      <c r="Q28" s="4"/>
-      <c r="R28" s="1"/>
-    </row>
-    <row r="29" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+      <c r="XES28" s="1"/>
+      <c r="XET28" s="1"/>
+      <c r="XEU28" s="1"/>
+      <c r="XEV28" s="1"/>
+      <c r="XEW28" s="1"/>
+      <c r="XEX28" s="1"/>
+      <c r="XEY28" s="1"/>
+      <c r="XEZ28" s="1"/>
+      <c r="XFA28" s="1"/>
+      <c r="XFB28" s="1"/>
+      <c r="XFC28" s="1"/>
+      <c r="XFD28" s="1"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
       <c r="C29" s="1">
-        <v>2111</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>85</v>
+        <v>2110</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -3830,31 +4831,27 @@
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>20072</v>
-      </c>
-      <c r="H29" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I29" s="1">
-        <v>10</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>17</v>
+        <v>20032</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L29" s="1">
         <v>6</v>
       </c>
-      <c r="M29" s="4" t="s">
-        <v>60</v>
+      <c r="M29" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="1"/>
       <c r="XES29" s="1"/>
       <c r="XET29" s="1"/>
       <c r="XEU29" s="1"/>
@@ -3868,12 +4865,14 @@
       <c r="XFC29" s="1"/>
       <c r="XFD29" s="1"/>
     </row>
-    <row r="30" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+    <row r="30" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
       <c r="C30" s="1">
-        <v>2112</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>86</v>
+        <v>2111</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -3882,31 +4881,27 @@
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>20023</v>
-      </c>
-      <c r="H30" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I30" s="1">
-        <v>10</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>17</v>
+        <v>20072</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L30" s="1">
         <v>6</v>
       </c>
-      <c r="M30" s="4" t="s">
-        <v>62</v>
+      <c r="M30" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="1"/>
       <c r="XES30" s="1"/>
       <c r="XET30" s="1"/>
       <c r="XEU30" s="1"/>
@@ -3920,12 +4915,14 @@
       <c r="XFC30" s="1"/>
       <c r="XFD30" s="1"/>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+    <row r="31" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
       <c r="C31" s="1">
-        <v>2113</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>87</v>
+        <v>2112</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
@@ -3934,31 +4931,27 @@
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>20033</v>
-      </c>
-      <c r="H31" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I31" s="1">
-        <v>10</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>17</v>
+        <v>20023</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L31" s="1">
         <v>6</v>
       </c>
-      <c r="M31" s="4" t="s">
-        <v>64</v>
+      <c r="M31" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="1"/>
       <c r="XES31" s="1"/>
       <c r="XET31" s="1"/>
       <c r="XEU31" s="1"/>
@@ -3972,12 +4965,14 @@
       <c r="XFC31" s="1"/>
       <c r="XFD31" s="1"/>
     </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+    <row r="32" customHeight="1" spans="1:18 16373:16384">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
       <c r="C32" s="1">
-        <v>2114</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>88</v>
+        <v>2113</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -3986,50 +4981,40 @@
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>20043</v>
-      </c>
-      <c r="H32" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I32" s="1">
-        <v>10</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>17</v>
+        <v>20033</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L32" s="1">
-        <v>7</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>66</v>
+        <v>6</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
       <c r="R32" s="1"/>
-      <c r="XES32" s="1"/>
-      <c r="XET32" s="1"/>
-      <c r="XEU32" s="1"/>
-      <c r="XEV32" s="1"/>
-      <c r="XEW32" s="1"/>
-      <c r="XEX32" s="1"/>
-      <c r="XEY32" s="1"/>
-      <c r="XEZ32" s="1"/>
-      <c r="XFA32" s="1"/>
-      <c r="XFB32" s="1"/>
-      <c r="XFC32" s="1"/>
-      <c r="XFD32" s="1"/>
-    </row>
-    <row r="33" customHeight="1" spans="3:18">
+    </row>
+    <row r="33" customHeight="1" spans="1:18 16373:16384">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
       <c r="C33" s="1">
-        <v>2115</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>89</v>
+        <v>2114</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -4038,100 +5023,312 @@
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>20024</v>
-      </c>
-      <c r="H33" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I33" s="1">
-        <v>10</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>17</v>
+        <v>20043</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L33" s="1">
         <v>7</v>
       </c>
-      <c r="M33" s="4" t="s">
-        <v>68</v>
+      <c r="M33" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="4"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" customHeight="1" spans="3:18">
+    <row r="34" customHeight="1" spans="1:18 16373:16384">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
       <c r="C34" s="1">
-        <v>2116</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>90</v>
+        <v>2115</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E34" s="1">
+        <v>2</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>20034</v>
-      </c>
-      <c r="H34" s="1">
-        <v>1005</v>
-      </c>
-      <c r="I34" s="1">
-        <v>10</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>17</v>
+        <v>20024</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>66</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="L34" s="1">
         <v>7</v>
       </c>
-      <c r="M34" s="4" t="s">
-        <v>70</v>
+      <c r="M34" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="4"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
       <c r="R34" s="1"/>
     </row>
-    <row r="35" customHeight="1" spans="3:18">
+    <row r="35" customHeight="1" spans="1:18 16373:16384">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1">
+        <v>2116</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E35" s="1">
+        <v>2</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>20034</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L35" s="1">
+        <v>7</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>136</v>
+      </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="4"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" customHeight="1" spans="3:18">
+    <row r="36" customHeight="1" spans="1:18 16373:16384">
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
       <c r="R36" s="1"/>
     </row>
-    <row r="37" customHeight="1" spans="3:18">
+    <row r="37" customHeight="1" spans="1:18 16373:16384">
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" customHeight="1" spans="3:18">
+    <row r="38" customHeight="1" spans="1:18 16373:16384">
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="4"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" customHeight="1" spans="3:18">
+    <row r="39" customHeight="1" spans="1:18 16373:16384">
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
-      <c r="Q39" s="4"/>
+      <c r="Q39" s="6"/>
       <c r="R39" s="1"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:18 16373:16384">
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="6"/>
+      <c r="R41" s="1"/>
+      <c r="XES41" s="1"/>
+      <c r="XET41" s="1"/>
+      <c r="XEU41" s="1"/>
+      <c r="XEV41" s="1"/>
+      <c r="XEW41" s="1"/>
+      <c r="XEX41" s="1"/>
+      <c r="XEY41" s="1"/>
+      <c r="XEZ41" s="1"/>
+      <c r="XFA41" s="1"/>
+      <c r="XFB41" s="1"/>
+      <c r="XFC41" s="1"/>
+      <c r="XFD41" s="1"/>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="1"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="1"/>
+      <c r="XES42" s="1"/>
+      <c r="XET42" s="1"/>
+      <c r="XEU42" s="1"/>
+      <c r="XEV42" s="1"/>
+      <c r="XEW42" s="1"/>
+      <c r="XEX42" s="1"/>
+      <c r="XEY42" s="1"/>
+      <c r="XEZ42" s="1"/>
+      <c r="XFA42" s="1"/>
+      <c r="XFB42" s="1"/>
+      <c r="XFC42" s="1"/>
+      <c r="XFD42" s="1"/>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="6"/>
+      <c r="R43" s="1"/>
+      <c r="XES43" s="1"/>
+      <c r="XET43" s="1"/>
+      <c r="XEU43" s="1"/>
+      <c r="XEV43" s="1"/>
+      <c r="XEW43" s="1"/>
+      <c r="XEX43" s="1"/>
+      <c r="XEY43" s="1"/>
+      <c r="XEZ43" s="1"/>
+      <c r="XFA43" s="1"/>
+      <c r="XFB43" s="1"/>
+      <c r="XFC43" s="1"/>
+      <c r="XFD43" s="1"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="XES44" s="1"/>
+      <c r="XET44" s="1"/>
+      <c r="XEU44" s="1"/>
+      <c r="XEV44" s="1"/>
+      <c r="XEW44" s="1"/>
+      <c r="XEX44" s="1"/>
+      <c r="XEY44" s="1"/>
+      <c r="XEZ44" s="1"/>
+      <c r="XFA44" s="1"/>
+      <c r="XFB44" s="1"/>
+      <c r="XFC44" s="1"/>
+      <c r="XFD44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:18 16373:16384">
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="6"/>
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:18 16373:16384">
+      <c r="O46" s="1"/>
+      <c r="P46" s="1"/>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="1"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:18 16373:16384">
+      <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
+      <c r="Q47" s="6"/>
+      <c r="R47" s="1"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:18 16373:16384">
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+    </row>
+    <row r="49" customHeight="1" spans="15:18">
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+    </row>
+    <row r="50" customHeight="1" spans="15:18">
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="6"/>
+      <c r="R50" s="1"/>
+    </row>
+    <row r="51" customHeight="1" spans="15:18">
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="6"/>
+      <c r="R51" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4147,14 +5344,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD53"/>
+  <dimension ref="A1:XFD58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="10" width="12.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
+    <col min="8" max="9" width="13.5" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.5833333333333" style="1" customWidth="1"/>
     <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
     <col min="15" max="16372" width="9" style="2"/>
@@ -4268,10 +5467,10 @@
         <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>15</v>
@@ -4290,8 +5489,8 @@
       <c r="C6" s="1">
         <v>3001</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>91</v>
+      <c r="D6" s="4" t="s">
+        <v>171</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -4302,32 +5501,32 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I6" s="1">
-        <v>10</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>18</v>
+      <c r="H6" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="L6" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C7" s="1">
         <v>3002</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>93</v>
+      <c r="D7" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -4338,45 +5537,255 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="1">
-        <v>1009</v>
-      </c>
-      <c r="I7" s="1">
-        <v>10</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>18</v>
+      <c r="H7" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>67</v>
       </c>
       <c r="L7" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>94</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C8" s="1">
+        <v>3003</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E8" s="1">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L8" s="1">
+        <v>3</v>
+      </c>
       <c r="N8" s="2"/>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C9" s="1">
+        <v>3004</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="E9" s="1">
+        <v>3</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="1">
+        <v>4</v>
+      </c>
       <c r="N9"/>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C10" s="1">
+        <v>3005</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L10" s="1">
+        <v>4</v>
+      </c>
       <c r="N10"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C11" s="1">
+        <v>3006</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" s="1">
+        <v>4</v>
+      </c>
       <c r="N11"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C12" s="1">
+        <v>3007</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L12" s="1">
+        <v>5</v>
+      </c>
       <c r="N12"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C13" s="1">
+        <v>3008</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" s="1">
+        <v>3</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L13" s="1">
+        <v>5</v>
+      </c>
       <c r="N13"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C14" s="1">
+        <v>3009</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" s="1">
+        <v>3</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="L14" s="1">
+        <v>5</v>
+      </c>
       <c r="N14"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -4386,197 +5795,35 @@
       <c r="N16"/>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="D17" s="4"/>
       <c r="N17"/>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="D18" s="4"/>
       <c r="N18"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C19" s="1">
-        <v>3101</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="1">
-        <v>3</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1">
-        <v>30011</v>
-      </c>
-      <c r="H19" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I19" s="1">
-        <v>10</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L19" s="1">
-        <v>5</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="N19" s="2"/>
+      <c r="D19" s="4"/>
+      <c r="N19"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C20" s="1">
-        <v>3102</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E20" s="1">
-        <v>3</v>
-      </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>30021</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I20" s="1">
-        <v>10</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L20" s="1">
-        <v>5</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N20" s="2"/>
+      <c r="N20"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C21" s="1">
-        <v>3103</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" s="1">
-        <v>3</v>
-      </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1">
-        <v>30031</v>
-      </c>
-      <c r="H21" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I21" s="1">
-        <v>10</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L21" s="1">
-        <v>5</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N21" s="2"/>
+      <c r="N21"/>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C22" s="1">
-        <v>3104</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" s="1">
-        <v>3</v>
-      </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
-      <c r="G22" s="1">
-        <v>30041</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I22" s="1">
-        <v>10</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L22" s="1">
-        <v>5</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="N22" s="2"/>
+      <c r="N22"/>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C23" s="1">
-        <v>3105</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" s="1">
-        <v>3</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>30051</v>
-      </c>
-      <c r="H23" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I23" s="1">
-        <v>10</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L23" s="1">
-        <v>5</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="N23" s="2"/>
+      <c r="N23"/>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="1">
-        <v>3106</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>100</v>
+        <v>3101</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -4585,34 +5832,34 @@
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>30061</v>
-      </c>
-      <c r="H24" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I24" s="1">
-        <v>10</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>18</v>
+        <v>30011</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="M24" s="4" t="s">
-        <v>50</v>
+      <c r="M24" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="N24" s="2"/>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C25" s="1">
-        <v>3107</v>
+        <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>101</v>
+        <v>189</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -4621,34 +5868,34 @@
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>30071</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I25" s="1">
-        <v>10</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>18</v>
+        <v>30021</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>52</v>
+      <c r="M25" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="N25" s="2"/>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="1">
-        <v>3108</v>
+        <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>102</v>
+        <v>190</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -4657,34 +5904,34 @@
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>30012</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I26" s="1">
-        <v>10</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>18</v>
+        <v>30031</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>100</v>
       </c>
       <c r="L26" s="1">
-        <v>6</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>54</v>
+        <v>5</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="N26" s="2"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="1">
-        <v>3109</v>
+        <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>103</v>
+        <v>191</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -4693,34 +5940,34 @@
         <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>30022</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I27" s="1">
-        <v>10</v>
-      </c>
-      <c r="J27" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>18</v>
+        <v>30041</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L27" s="1">
-        <v>6</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="N27" s="2"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C28" s="1">
-        <v>3110</v>
+        <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>104</v>
+        <v>192</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -4729,34 +5976,34 @@
         <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>30032</v>
-      </c>
-      <c r="H28" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I28" s="1">
-        <v>10</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>18</v>
+        <v>30051</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L28" s="1">
-        <v>6</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>58</v>
+        <v>5</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="N28" s="2"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C29" s="1">
-        <v>3111</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>105</v>
+        <v>3106</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -4765,34 +6012,34 @@
         <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>30033</v>
-      </c>
-      <c r="H29" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I29" s="1">
-        <v>10</v>
-      </c>
-      <c r="J29" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>18</v>
+        <v>30061</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L29" s="1">
-        <v>6</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>60</v>
+        <v>5</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="N29" s="2"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C30" s="1">
-        <v>3112</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>106</v>
+        <v>3107</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -4801,34 +6048,34 @@
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>30043</v>
-      </c>
-      <c r="H30" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I30" s="1">
-        <v>10</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>18</v>
+        <v>30071</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L30" s="1">
-        <v>6</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>62</v>
+        <v>5</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="N30" s="2"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C31" s="1">
-        <v>3113</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>107</v>
+        <v>3108</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
@@ -4837,34 +6084,34 @@
         <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>30073</v>
-      </c>
-      <c r="H31" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I31" s="1">
-        <v>10</v>
-      </c>
-      <c r="J31" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>18</v>
+        <v>30012</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L31" s="1">
         <v>6</v>
       </c>
-      <c r="M31" s="4" t="s">
-        <v>64</v>
+      <c r="M31" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="N31" s="2"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C32" s="1">
-        <v>3114</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>108</v>
+        <v>3109</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -4873,34 +6120,34 @@
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>30024</v>
-      </c>
-      <c r="H32" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I32" s="1">
-        <v>10</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>18</v>
+        <v>30022</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L32" s="1">
-        <v>7</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>66</v>
+        <v>6</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" customHeight="1" spans="3:14 16373:16384">
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C33" s="1">
-        <v>3115</v>
+        <v>3110</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -4909,228 +6156,285 @@
         <v>0</v>
       </c>
       <c r="G33" s="1">
+        <v>30032</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L33" s="1">
+        <v>6</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="N33" s="2"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C34" s="1">
+        <v>3111</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E34" s="1">
+        <v>3</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>30033</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L34" s="1">
+        <v>6</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="N34" s="2"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C35" s="1">
+        <v>3112</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E35" s="1">
+        <v>3</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>30043</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L35" s="1">
+        <v>6</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="N35" s="2"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C36" s="1">
+        <v>3113</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E36" s="1">
+        <v>3</v>
+      </c>
+      <c r="F36" s="1">
+        <v>0</v>
+      </c>
+      <c r="G36" s="1">
+        <v>30073</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L36" s="1">
+        <v>6</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="N36" s="2"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C37" s="1">
+        <v>3114</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E37" s="1">
+        <v>3</v>
+      </c>
+      <c r="F37" s="1">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1">
+        <v>30024</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L37" s="1">
+        <v>7</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="N37" s="2"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:14 16373:16384">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1">
+        <v>3115</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E38" s="1">
+        <v>3</v>
+      </c>
+      <c r="F38" s="1">
+        <v>0</v>
+      </c>
+      <c r="G38" s="1">
         <v>30034</v>
       </c>
-      <c r="H33" s="1">
-        <v>1006</v>
-      </c>
-      <c r="I33" s="1">
-        <v>10</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L33" s="1">
+      <c r="H38" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1">
         <v>7</v>
       </c>
-      <c r="M33" s="4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="3:14 16373:16384">
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="1"/>
-      <c r="XES34" s="1"/>
-      <c r="XET34" s="1"/>
-      <c r="XEU34" s="1"/>
-      <c r="XEV34" s="1"/>
-      <c r="XEW34" s="1"/>
-      <c r="XEX34" s="1"/>
-      <c r="XEY34" s="1"/>
-      <c r="XEZ34" s="1"/>
-      <c r="XFA34" s="1"/>
-      <c r="XFB34" s="1"/>
-      <c r="XFC34" s="1"/>
-      <c r="XFD34" s="1"/>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="3:14 16373:16384">
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="XES35" s="1"/>
-      <c r="XET35" s="1"/>
-      <c r="XEU35" s="1"/>
-      <c r="XEV35" s="1"/>
-      <c r="XEW35" s="1"/>
-      <c r="XEX35" s="1"/>
-      <c r="XEY35" s="1"/>
-      <c r="XEZ35" s="1"/>
-      <c r="XFA35" s="1"/>
-      <c r="XFB35" s="1"/>
-      <c r="XFC35" s="1"/>
-      <c r="XFD35" s="1"/>
-    </row>
-    <row r="37" s="2" customFormat="1" customHeight="1" spans="3:14 16373:16384">
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="XES37" s="1"/>
-      <c r="XET37" s="1"/>
-      <c r="XEU37" s="1"/>
-      <c r="XEV37" s="1"/>
-      <c r="XEW37" s="1"/>
-      <c r="XEX37" s="1"/>
-      <c r="XEY37" s="1"/>
-      <c r="XEZ37" s="1"/>
-      <c r="XFA37" s="1"/>
-      <c r="XFB37" s="1"/>
-      <c r="XFC37" s="1"/>
-      <c r="XFD37" s="1"/>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:14 16373:16384">
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="XES48" s="1"/>
-      <c r="XET48" s="1"/>
-      <c r="XEU48" s="1"/>
-      <c r="XEV48" s="1"/>
-      <c r="XEW48" s="1"/>
-      <c r="XEX48" s="1"/>
-      <c r="XEY48" s="1"/>
-      <c r="XEZ48" s="1"/>
-      <c r="XFA48" s="1"/>
-      <c r="XFB48" s="1"/>
-      <c r="XFC48" s="1"/>
-      <c r="XFD48" s="1"/>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="XES49" s="1"/>
-      <c r="XET49" s="1"/>
-      <c r="XEU49" s="1"/>
-      <c r="XEV49" s="1"/>
-      <c r="XEW49" s="1"/>
-      <c r="XEX49" s="1"/>
-      <c r="XEY49" s="1"/>
-      <c r="XEZ49" s="1"/>
-      <c r="XFA49" s="1"/>
-      <c r="XFB49" s="1"/>
-      <c r="XFC49" s="1"/>
-      <c r="XFD49" s="1"/>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="XES50" s="1"/>
-      <c r="XET50" s="1"/>
-      <c r="XEU50" s="1"/>
-      <c r="XEV50" s="1"/>
-      <c r="XEW50" s="1"/>
-      <c r="XEX50" s="1"/>
-      <c r="XEY50" s="1"/>
-      <c r="XEZ50" s="1"/>
-      <c r="XFA50" s="1"/>
-      <c r="XFB50" s="1"/>
-      <c r="XFC50" s="1"/>
-      <c r="XFD50" s="1"/>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="XES51" s="1"/>
-      <c r="XET51" s="1"/>
-      <c r="XEU51" s="1"/>
-      <c r="XEV51" s="1"/>
-      <c r="XEW51" s="1"/>
-      <c r="XEX51" s="1"/>
-      <c r="XEY51" s="1"/>
-      <c r="XEZ51" s="1"/>
-      <c r="XFA51" s="1"/>
-      <c r="XFB51" s="1"/>
-      <c r="XFC51" s="1"/>
-      <c r="XFD51" s="1"/>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="XES52" s="1"/>
-      <c r="XET52" s="1"/>
-      <c r="XEU52" s="1"/>
-      <c r="XEV52" s="1"/>
-      <c r="XEW52" s="1"/>
-      <c r="XEX52" s="1"/>
-      <c r="XEY52" s="1"/>
-      <c r="XEZ52" s="1"/>
-      <c r="XFA52" s="1"/>
-      <c r="XFB52" s="1"/>
-      <c r="XFC52" s="1"/>
-      <c r="XFD52" s="1"/>
+      <c r="M38" s="6" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="1"/>
+      <c r="XES39" s="1"/>
+      <c r="XET39" s="1"/>
+      <c r="XEU39" s="1"/>
+      <c r="XEV39" s="1"/>
+      <c r="XEW39" s="1"/>
+      <c r="XEX39" s="1"/>
+      <c r="XEY39" s="1"/>
+      <c r="XEZ39" s="1"/>
+      <c r="XFA39" s="1"/>
+      <c r="XFB39" s="1"/>
+      <c r="XFC39" s="1"/>
+      <c r="XFD39" s="1"/>
+    </row>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="XES40" s="1"/>
+      <c r="XET40" s="1"/>
+      <c r="XEU40" s="1"/>
+      <c r="XEV40" s="1"/>
+      <c r="XEW40" s="1"/>
+      <c r="XEX40" s="1"/>
+      <c r="XEY40" s="1"/>
+      <c r="XEZ40" s="1"/>
+      <c r="XFA40" s="1"/>
+      <c r="XFB40" s="1"/>
+      <c r="XFC40" s="1"/>
+      <c r="XFD40" s="1"/>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="XES42" s="1"/>
+      <c r="XET42" s="1"/>
+      <c r="XEU42" s="1"/>
+      <c r="XEV42" s="1"/>
+      <c r="XEW42" s="1"/>
+      <c r="XEX42" s="1"/>
+      <c r="XEY42" s="1"/>
+      <c r="XEZ42" s="1"/>
+      <c r="XFA42" s="1"/>
+      <c r="XFB42" s="1"/>
+      <c r="XFC42" s="1"/>
+      <c r="XFD42" s="1"/>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C53" s="1"/>
@@ -5157,6 +6461,131 @@
       <c r="XFC53" s="1"/>
       <c r="XFD53" s="1"/>
     </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="XES54" s="1"/>
+      <c r="XET54" s="1"/>
+      <c r="XEU54" s="1"/>
+      <c r="XEV54" s="1"/>
+      <c r="XEW54" s="1"/>
+      <c r="XEX54" s="1"/>
+      <c r="XEY54" s="1"/>
+      <c r="XEZ54" s="1"/>
+      <c r="XFA54" s="1"/>
+      <c r="XFB54" s="1"/>
+      <c r="XFC54" s="1"/>
+      <c r="XFD54" s="1"/>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="XES55" s="1"/>
+      <c r="XET55" s="1"/>
+      <c r="XEU55" s="1"/>
+      <c r="XEV55" s="1"/>
+      <c r="XEW55" s="1"/>
+      <c r="XEX55" s="1"/>
+      <c r="XEY55" s="1"/>
+      <c r="XEZ55" s="1"/>
+      <c r="XFA55" s="1"/>
+      <c r="XFB55" s="1"/>
+      <c r="XFC55" s="1"/>
+      <c r="XFD55" s="1"/>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="XES56" s="1"/>
+      <c r="XET56" s="1"/>
+      <c r="XEU56" s="1"/>
+      <c r="XEV56" s="1"/>
+      <c r="XEW56" s="1"/>
+      <c r="XEX56" s="1"/>
+      <c r="XEY56" s="1"/>
+      <c r="XEZ56" s="1"/>
+      <c r="XFA56" s="1"/>
+      <c r="XFB56" s="1"/>
+      <c r="XFC56" s="1"/>
+      <c r="XFD56" s="1"/>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="XES57" s="1"/>
+      <c r="XET57" s="1"/>
+      <c r="XEU57" s="1"/>
+      <c r="XEV57" s="1"/>
+      <c r="XEW57" s="1"/>
+      <c r="XEX57" s="1"/>
+      <c r="XEY57" s="1"/>
+      <c r="XEZ57" s="1"/>
+      <c r="XFA57" s="1"/>
+      <c r="XFB57" s="1"/>
+      <c r="XFC57" s="1"/>
+      <c r="XFD57" s="1"/>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="XES58" s="1"/>
+      <c r="XET58" s="1"/>
+      <c r="XEU58" s="1"/>
+      <c r="XEV58" s="1"/>
+      <c r="XEW58" s="1"/>
+      <c r="XEX58" s="1"/>
+      <c r="XEY58" s="1"/>
+      <c r="XEZ58" s="1"/>
+      <c r="XFA58" s="1"/>
+      <c r="XFB58" s="1"/>
+      <c r="XFC58" s="1"/>
+      <c r="XFD58" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="234">
   <si>
     <t>#</t>
   </si>
@@ -347,7 +347,7 @@
     <t>流光剑诀·无断</t>
   </si>
   <si>
-    <t>四方破甲</t>
+    <t>月华破甲</t>
   </si>
   <si>
     <t>1,6,95</t>
@@ -356,22 +356,22 @@
     <t>2000,200,1</t>
   </si>
   <si>
-    <t>四方剑阵·破甲</t>
-  </si>
-  <si>
-    <t>重击破甲</t>
+    <t>月华剑阵·破甲</t>
+  </si>
+  <si>
+    <t>蛮牛破甲</t>
   </si>
   <si>
     <t>200,5</t>
   </si>
   <si>
-    <t>重击剑术·破甲</t>
-  </si>
-  <si>
-    <t>武神无断</t>
-  </si>
-  <si>
-    <t>武神盾·无断</t>
+    <t>蛮牛冲撞·破甲</t>
+  </si>
+  <si>
+    <t>龙魂无断</t>
+  </si>
+  <si>
+    <t>龙魂护体·无断</t>
   </si>
   <si>
     <t>无求圣体</t>
@@ -401,16 +401,16 @@
     <t>流光剑诀·吸血</t>
   </si>
   <si>
-    <t>四方断河</t>
-  </si>
-  <si>
-    <t>四方剑阵·断河</t>
-  </si>
-  <si>
-    <t>重击致残</t>
-  </si>
-  <si>
-    <t>重击剑术·致残</t>
+    <t>月华断河</t>
+  </si>
+  <si>
+    <t>月华剑阵·断河</t>
+  </si>
+  <si>
+    <t>蛮牛致残</t>
+  </si>
+  <si>
+    <t>蛮牛冲撞·致残</t>
   </si>
   <si>
     <t>火麟破甲</t>
@@ -437,10 +437,10 @@
     <t>流光剑诀·疾速</t>
   </si>
   <si>
-    <t>四方疾速</t>
-  </si>
-  <si>
-    <t>四方剑阵·疾速</t>
+    <t>月华疾速</t>
+  </si>
+  <si>
+    <t>月华剑阵·疾速</t>
   </si>
   <si>
     <t>乌木杖</t>
@@ -500,49 +500,97 @@
     <t>冥想法体</t>
   </si>
   <si>
+    <t>冥想心法·法体</t>
+  </si>
+  <si>
     <t>神雷无断</t>
   </si>
   <si>
-    <t>火海破甲</t>
-  </si>
-  <si>
-    <t>烈焰破甲</t>
-  </si>
-  <si>
-    <t>念力无断</t>
-  </si>
-  <si>
-    <t>冰心圣体</t>
-  </si>
-  <si>
-    <t>冰封霜寒</t>
+    <t>紫电神雷·无断</t>
+  </si>
+  <si>
+    <t>火狱破甲</t>
+  </si>
+  <si>
+    <t>火狱阵法·破甲</t>
+  </si>
+  <si>
+    <t>焚天破甲</t>
+  </si>
+  <si>
+    <t>烈焰焚天·破甲</t>
+  </si>
+  <si>
+    <t>炎凰无断</t>
+  </si>
+  <si>
+    <t>炎凰法盾·无断</t>
+  </si>
+  <si>
+    <t>万法圣体</t>
+  </si>
+  <si>
+    <t>万法归宗·圣体</t>
+  </si>
+  <si>
+    <t>冰暴霜寒</t>
+  </si>
+  <si>
+    <t>极寒冰暴·霜寒</t>
   </si>
   <si>
     <t>冥想魔体</t>
   </si>
   <si>
+    <t>冥想心法·魔体</t>
+  </si>
+  <si>
     <t>神雷狂潮</t>
   </si>
   <si>
-    <t>火海炼狱</t>
-  </si>
-  <si>
-    <t>冰封蚀魂</t>
-  </si>
-  <si>
-    <t>烈焰燃魂</t>
-  </si>
-  <si>
-    <t>火海蚀骨</t>
-  </si>
-  <si>
-    <t>冰封冻结</t>
+    <t>紫电神雷·狂潮</t>
+  </si>
+  <si>
+    <t>火狱炼狱</t>
+  </si>
+  <si>
+    <t>火狱阵法·炼狱</t>
+  </si>
+  <si>
+    <t>冰暴蚀魂</t>
+  </si>
+  <si>
+    <t>极寒冰暴·蚀魂</t>
+  </si>
+  <si>
+    <t>火狱蚀骨</t>
+  </si>
+  <si>
+    <t>火狱阵法·蚀骨</t>
+  </si>
+  <si>
+    <t>焚天燃魂</t>
+  </si>
+  <si>
+    <t>烈焰焚天·燃魂</t>
+  </si>
+  <si>
+    <t>冰暴冻结</t>
+  </si>
+  <si>
+    <t>极寒冰暴·冻结</t>
   </si>
   <si>
     <t>神雷疾速</t>
   </si>
   <si>
-    <t>火海疾速</t>
+    <t>紫电神雷·疾速</t>
+  </si>
+  <si>
+    <t>火狱疾速</t>
+  </si>
+  <si>
+    <t>火狱阵法·疾速</t>
   </si>
   <si>
     <t>竹节剑</t>
@@ -596,49 +644,94 @@
     <t>1001,1006,95</t>
   </si>
   <si>
-    <t>祈福道体</t>
-  </si>
-  <si>
-    <t>灭魔无断</t>
+    <t>清心道体</t>
+  </si>
+  <si>
+    <t>清心咒·道体</t>
+  </si>
+  <si>
+    <t>破魔无断</t>
+  </si>
+  <si>
+    <t>破魔符咒·无断</t>
   </si>
   <si>
     <t>毒咒蚀甲</t>
   </si>
   <si>
-    <t>疗伤御甲</t>
-  </si>
-  <si>
-    <t>护魂无断</t>
-  </si>
-  <si>
-    <t>圣心道体</t>
-  </si>
-  <si>
-    <t>唤神御灵</t>
-  </si>
-  <si>
-    <t>祈福神体</t>
-  </si>
-  <si>
-    <t>灭魔双生</t>
+    <t>毒咒术·蚀甲</t>
+  </si>
+  <si>
+    <t>圣疗御甲</t>
+  </si>
+  <si>
+    <t>圣疗术·御甲</t>
+  </si>
+  <si>
+    <t>麟盾无断</t>
+  </si>
+  <si>
+    <t>太虚麟盾·无断</t>
+  </si>
+  <si>
+    <t>自然道体</t>
+  </si>
+  <si>
+    <t>道法自然·道体</t>
+  </si>
+  <si>
+    <t>英灵御灵</t>
+  </si>
+  <si>
+    <t>召唤英灵·御灵</t>
+  </si>
+  <si>
+    <t>清心神体</t>
+  </si>
+  <si>
+    <t>清心咒·神体</t>
+  </si>
+  <si>
+    <t>破魔双生</t>
+  </si>
+  <si>
+    <t>破魔符咒·双生</t>
   </si>
   <si>
     <t>毒咒蚀骨</t>
   </si>
   <si>
+    <t>毒咒术·蚀骨</t>
+  </si>
+  <si>
     <t>毒咒蛊体</t>
   </si>
   <si>
-    <t>疗伤太清</t>
-  </si>
-  <si>
-    <t>唤神同心</t>
-  </si>
-  <si>
-    <t>灭魔疾速</t>
+    <t>毒咒术·蛊体</t>
+  </si>
+  <si>
+    <t>圣疗太清</t>
+  </si>
+  <si>
+    <t>圣疗术·太清</t>
+  </si>
+  <si>
+    <t>英灵同心</t>
+  </si>
+  <si>
+    <t>召唤英灵·同心</t>
+  </si>
+  <si>
+    <t>破魔疾速</t>
+  </si>
+  <si>
+    <t>破魔符咒·疾速</t>
   </si>
   <si>
     <t>毒咒疾速</t>
+  </si>
+  <si>
+    <t>毒咒术·疾速</t>
   </si>
 </sst>
 </file>
@@ -4399,7 +4492,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="N20" s="2"/>
       <c r="XES20" s="1"/>
@@ -4422,7 +4515,7 @@
         <v>2102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -4449,7 +4542,7 @@
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="N21" s="1"/>
       <c r="XES21" s="1"/>
@@ -4472,7 +4565,7 @@
         <v>2103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -4499,7 +4592,7 @@
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="N22" s="1"/>
       <c r="XES22" s="1"/>
@@ -4522,7 +4615,7 @@
         <v>2104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
@@ -4549,7 +4642,7 @@
         <v>5</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="N23" s="1"/>
       <c r="XES23" s="1"/>
@@ -4572,7 +4665,7 @@
         <v>2105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -4599,7 +4692,7 @@
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>113</v>
+        <v>164</v>
       </c>
       <c r="N24" s="1"/>
       <c r="XES24" s="1"/>
@@ -4622,7 +4715,7 @@
         <v>2106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -4649,7 +4742,7 @@
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="N25" s="1"/>
       <c r="XES25" s="1"/>
@@ -4672,7 +4765,7 @@
         <v>2107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -4699,7 +4792,7 @@
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>118</v>
+        <v>168</v>
       </c>
       <c r="N26" s="1"/>
       <c r="XES26" s="1"/>
@@ -4722,13 +4815,13 @@
         <v>2108</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>2101</v>
       </c>
       <c r="G27" s="1">
         <v>20012</v>
@@ -4749,7 +4842,7 @@
         <v>6</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="N27" s="1"/>
       <c r="XES27" s="1"/>
@@ -4772,13 +4865,13 @@
         <v>2109</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>2102</v>
       </c>
       <c r="G28" s="1">
         <v>20022</v>
@@ -4799,7 +4892,7 @@
         <v>6</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="N28" s="1"/>
       <c r="XES28" s="1"/>
@@ -4822,13 +4915,13 @@
         <v>2110</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>2103</v>
       </c>
       <c r="G29" s="1">
         <v>20032</v>
@@ -4849,7 +4942,7 @@
         <v>6</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="N29" s="1"/>
       <c r="XES29" s="1"/>
@@ -4872,13 +4965,13 @@
         <v>2111</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>2107</v>
       </c>
       <c r="G30" s="1">
         <v>20072</v>
@@ -4899,7 +4992,7 @@
         <v>6</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="N30" s="1"/>
       <c r="XES30" s="1"/>
@@ -4915,29 +5008,29 @@
       <c r="XFC30" s="1"/>
       <c r="XFD30" s="1"/>
     </row>
-    <row r="31" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="31" customHeight="1" spans="1:18 16373:16384">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1">
         <v>2112</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>2110</v>
       </c>
       <c r="G31" s="1">
-        <v>20023</v>
+        <v>20033</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J31" s="10" t="s">
         <v>66</v>
@@ -4949,45 +5042,37 @@
         <v>6</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="N31" s="1"/>
-      <c r="XES31" s="1"/>
-      <c r="XET31" s="1"/>
-      <c r="XEU31" s="1"/>
-      <c r="XEV31" s="1"/>
-      <c r="XEW31" s="1"/>
-      <c r="XEX31" s="1"/>
-      <c r="XEY31" s="1"/>
-      <c r="XEZ31" s="1"/>
-      <c r="XFA31" s="1"/>
-      <c r="XFB31" s="1"/>
-      <c r="XFC31" s="1"/>
-      <c r="XFD31" s="1"/>
-    </row>
-    <row r="32" customHeight="1" spans="1:18 16373:16384">
+      <c r="O31" s="1"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="1"/>
+    </row>
+    <row r="32" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1">
         <v>2113</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>2104</v>
       </c>
       <c r="G32" s="1">
-        <v>20033</v>
+        <v>20043</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J32" s="10" t="s">
         <v>66</v>
@@ -4999,13 +5084,21 @@
         <v>6</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="6"/>
-      <c r="Q32" s="6"/>
-      <c r="R32" s="1"/>
+      <c r="XES32" s="1"/>
+      <c r="XET32" s="1"/>
+      <c r="XEU32" s="1"/>
+      <c r="XEV32" s="1"/>
+      <c r="XEW32" s="1"/>
+      <c r="XEX32" s="1"/>
+      <c r="XEY32" s="1"/>
+      <c r="XEZ32" s="1"/>
+      <c r="XFA32" s="1"/>
+      <c r="XFB32" s="1"/>
+      <c r="XFC32" s="1"/>
+      <c r="XFD32" s="1"/>
     </row>
     <row r="33" customHeight="1" spans="1:18 16373:16384">
       <c r="A33" s="1"/>
@@ -5014,16 +5107,16 @@
         <v>2114</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>2111</v>
       </c>
       <c r="G33" s="1">
-        <v>20043</v>
+        <v>20073</v>
       </c>
       <c r="H33" s="10" t="s">
         <v>103</v>
@@ -5041,7 +5134,7 @@
         <v>7</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>132</v>
+        <v>182</v>
       </c>
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
@@ -5056,13 +5149,13 @@
         <v>2115</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>2109</v>
       </c>
       <c r="G34" s="1">
         <v>20024</v>
@@ -5083,7 +5176,7 @@
         <v>7</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
@@ -5098,13 +5191,13 @@
         <v>2116</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>2112</v>
       </c>
       <c r="G35" s="1">
         <v>20034</v>
@@ -5125,7 +5218,7 @@
         <v>7</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
@@ -5490,7 +5583,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -5518,7 +5611,7 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -5526,7 +5619,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -5554,7 +5647,7 @@
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -5562,7 +5655,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -5595,7 +5688,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -5607,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>77</v>
@@ -5628,7 +5721,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -5640,7 +5733,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>77</v>
@@ -5661,7 +5754,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -5673,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>84</v>
@@ -5694,7 +5787,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -5706,7 +5799,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>87</v>
@@ -5727,7 +5820,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -5739,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>91</v>
@@ -5760,7 +5853,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -5772,7 +5865,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>95</v>
@@ -5823,7 +5916,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -5849,8 +5942,8 @@
       <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="M24" s="6" t="s">
-        <v>101</v>
+      <c r="M24" s="2" t="s">
+        <v>205</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -5859,7 +5952,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -5885,8 +5978,8 @@
       <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="M25" s="6" t="s">
-        <v>104</v>
+      <c r="M25" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -5895,7 +5988,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -5921,8 +6014,8 @@
       <c r="L26" s="1">
         <v>5</v>
       </c>
-      <c r="M26" s="6" t="s">
-        <v>108</v>
+      <c r="M26" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -5931,7 +6024,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -5957,8 +6050,8 @@
       <c r="L27" s="1">
         <v>5</v>
       </c>
-      <c r="M27" s="6" t="s">
-        <v>111</v>
+      <c r="M27" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -5967,7 +6060,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -5993,8 +6086,8 @@
       <c r="L28" s="1">
         <v>5</v>
       </c>
-      <c r="M28" s="6" t="s">
-        <v>113</v>
+      <c r="M28" s="1" t="s">
+        <v>213</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -6003,7 +6096,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -6029,8 +6122,8 @@
       <c r="L29" s="1">
         <v>5</v>
       </c>
-      <c r="M29" s="6" t="s">
-        <v>115</v>
+      <c r="M29" s="1" t="s">
+        <v>215</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -6039,7 +6132,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -6065,8 +6158,8 @@
       <c r="L30" s="1">
         <v>5</v>
       </c>
-      <c r="M30" s="6" t="s">
-        <v>118</v>
+      <c r="M30" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -6075,13 +6168,13 @@
         <v>3108</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>3101</v>
       </c>
       <c r="G31" s="1">
         <v>30012</v>
@@ -6101,8 +6194,8 @@
       <c r="L31" s="1">
         <v>6</v>
       </c>
-      <c r="M31" s="6" t="s">
-        <v>120</v>
+      <c r="M31" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="N31" s="2"/>
     </row>
@@ -6111,13 +6204,13 @@
         <v>3109</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>3102</v>
       </c>
       <c r="G32" s="1">
         <v>30022</v>
@@ -6137,8 +6230,8 @@
       <c r="L32" s="1">
         <v>6</v>
       </c>
-      <c r="M32" s="6" t="s">
-        <v>122</v>
+      <c r="M32" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -6147,13 +6240,13 @@
         <v>3110</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>3103</v>
       </c>
       <c r="G33" s="1">
         <v>30032</v>
@@ -6173,8 +6266,8 @@
       <c r="L33" s="1">
         <v>6</v>
       </c>
-      <c r="M33" s="6" t="s">
-        <v>124</v>
+      <c r="M33" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="N33" s="2"/>
     </row>
@@ -6183,13 +6276,13 @@
         <v>3111</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>3110</v>
       </c>
       <c r="G34" s="1">
         <v>30033</v>
@@ -6209,8 +6302,8 @@
       <c r="L34" s="1">
         <v>6</v>
       </c>
-      <c r="M34" s="6" t="s">
-        <v>126</v>
+      <c r="M34" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="N34" s="2"/>
     </row>
@@ -6219,13 +6312,13 @@
         <v>3112</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>3104</v>
       </c>
       <c r="G35" s="1">
         <v>30043</v>
@@ -6245,8 +6338,8 @@
       <c r="L35" s="1">
         <v>6</v>
       </c>
-      <c r="M35" s="6" t="s">
-        <v>128</v>
+      <c r="M35" s="2" t="s">
+        <v>227</v>
       </c>
       <c r="N35" s="2"/>
     </row>
@@ -6255,13 +6348,13 @@
         <v>3113</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="E36" s="1">
         <v>3</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>3107</v>
       </c>
       <c r="G36" s="1">
         <v>30073</v>
@@ -6281,8 +6374,8 @@
       <c r="L36" s="1">
         <v>6</v>
       </c>
-      <c r="M36" s="6" t="s">
-        <v>130</v>
+      <c r="M36" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="N36" s="2"/>
     </row>
@@ -6291,13 +6384,13 @@
         <v>3114</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1">
-        <v>0</v>
+        <v>3109</v>
       </c>
       <c r="G37" s="1">
         <v>30024</v>
@@ -6317,8 +6410,8 @@
       <c r="L37" s="1">
         <v>7</v>
       </c>
-      <c r="M37" s="6" t="s">
-        <v>132</v>
+      <c r="M37" s="2" t="s">
+        <v>231</v>
       </c>
       <c r="N37" s="2"/>
     </row>
@@ -6329,13 +6422,13 @@
         <v>3115</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>3111</v>
       </c>
       <c r="G38" s="1">
         <v>30034</v>
@@ -6355,8 +6448,8 @@
       <c r="L38" s="1">
         <v>7</v>
       </c>
-      <c r="M38" s="6" t="s">
-        <v>134</v>
+      <c r="M38" s="1" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="236">
   <si>
     <t>#</t>
   </si>
@@ -344,7 +344,7 @@
     <t>2,6,95</t>
   </si>
   <si>
-    <t>流光剑诀·无断</t>
+    <t>流光剑诀·灵动</t>
   </si>
   <si>
     <t>月华破甲</t>
@@ -380,13 +380,13 @@
     <t>无求易决·圣体</t>
   </si>
   <si>
-    <t>火麟迅疾</t>
+    <t>火麟灵动</t>
   </si>
   <si>
     <t>30,10</t>
   </si>
   <si>
-    <t>火麟剑诀·迅疾</t>
+    <t>火麟剑诀·灵动</t>
   </si>
   <si>
     <t>基础圣体</t>
@@ -431,16 +431,16 @@
     <t>火麟剑诀·焚魂</t>
   </si>
   <si>
-    <t>流光疾速</t>
-  </si>
-  <si>
-    <t>流光剑诀·疾速</t>
-  </si>
-  <si>
-    <t>月华疾速</t>
-  </si>
-  <si>
-    <t>月华剑阵·疾速</t>
+    <t>流光疾风</t>
+  </si>
+  <si>
+    <t>流光剑诀·疾风</t>
+  </si>
+  <si>
+    <t>月华疾风</t>
+  </si>
+  <si>
+    <t>月华剑阵·疾风</t>
   </si>
   <si>
     <t>乌木杖</t>
@@ -503,16 +503,16 @@
     <t>冥想心法·法体</t>
   </si>
   <si>
-    <t>神雷无断</t>
-  </si>
-  <si>
-    <t>紫电神雷·无断</t>
-  </si>
-  <si>
-    <t>火狱破甲</t>
-  </si>
-  <si>
-    <t>火狱阵法·破甲</t>
+    <t>神雷灵动</t>
+  </si>
+  <si>
+    <t>紫电神雷·灵动</t>
+  </si>
+  <si>
+    <t>火狱蚀骨</t>
+  </si>
+  <si>
+    <t>火狱阵法·蚀骨</t>
   </si>
   <si>
     <t>焚天破甲</t>
@@ -563,10 +563,10 @@
     <t>极寒冰暴·蚀魂</t>
   </si>
   <si>
-    <t>火狱蚀骨</t>
-  </si>
-  <si>
-    <t>火狱阵法·蚀骨</t>
+    <t>神雷汲取</t>
+  </si>
+  <si>
+    <t>紫电神雷·汲取</t>
   </si>
   <si>
     <t>焚天燃魂</t>
@@ -581,16 +581,16 @@
     <t>极寒冰暴·冻结</t>
   </si>
   <si>
-    <t>神雷疾速</t>
-  </si>
-  <si>
-    <t>紫电神雷·疾速</t>
-  </si>
-  <si>
-    <t>火狱疾速</t>
-  </si>
-  <si>
-    <t>火狱阵法·疾速</t>
+    <t>神雷疾风</t>
+  </si>
+  <si>
+    <t>紫电神雷·疾风</t>
+  </si>
+  <si>
+    <t>火狱疾风</t>
+  </si>
+  <si>
+    <t>火狱阵法·疾风</t>
   </si>
   <si>
     <t>竹节剑</t>
@@ -650,16 +650,16 @@
     <t>清心咒·道体</t>
   </si>
   <si>
-    <t>破魔无断</t>
-  </si>
-  <si>
-    <t>破魔符咒·无断</t>
-  </si>
-  <si>
-    <t>毒咒蚀甲</t>
-  </si>
-  <si>
-    <t>毒咒术·蚀甲</t>
+    <t>破魔灵动</t>
+  </si>
+  <si>
+    <t>破魔符咒·灵动</t>
+  </si>
+  <si>
+    <t>毒咒禁疗</t>
+  </si>
+  <si>
+    <t>毒咒术·禁疗</t>
   </si>
   <si>
     <t>圣疗御甲</t>
@@ -692,18 +692,24 @@
     <t>清心咒·神体</t>
   </si>
   <si>
+    <t>破魔回复</t>
+  </si>
+  <si>
+    <t>破魔符咒·回复</t>
+  </si>
+  <si>
+    <t>毒咒蚀骨</t>
+  </si>
+  <si>
+    <t>毒咒术·蚀骨</t>
+  </si>
+  <si>
     <t>破魔双生</t>
   </si>
   <si>
     <t>破魔符咒·双生</t>
   </si>
   <si>
-    <t>毒咒蚀骨</t>
-  </si>
-  <si>
-    <t>毒咒术·蚀骨</t>
-  </si>
-  <si>
     <t>毒咒蛊体</t>
   </si>
   <si>
@@ -722,16 +728,16 @@
     <t>召唤英灵·同心</t>
   </si>
   <si>
-    <t>破魔疾速</t>
-  </si>
-  <si>
-    <t>破魔符咒·疾速</t>
-  </si>
-  <si>
-    <t>毒咒疾速</t>
-  </si>
-  <si>
-    <t>毒咒术·疾速</t>
+    <t>破魔疾风</t>
+  </si>
+  <si>
+    <t>破魔符咒·疾风</t>
+  </si>
+  <si>
+    <t>毒咒疾风</t>
+  </si>
+  <si>
+    <t>毒咒术·疾风</t>
   </si>
 </sst>
 </file>
@@ -2414,7 +2420,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD54"/>
+  <dimension ref="A1:XFD57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -3123,65 +3129,34 @@
       <c r="R26" s="6"/>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C27" s="1">
-        <v>1108</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1101</v>
-      </c>
-      <c r="G27" s="1">
-        <v>10012</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="L27" s="1">
-        <v>6</v>
-      </c>
-      <c r="M27" s="6" t="s">
-        <v>120</v>
-      </c>
+      <c r="D27" s="6"/>
+      <c r="M27" s="6"/>
       <c r="R27" s="6"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C28" s="1">
-        <v>1109</v>
+        <v>1201</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
       </c>
       <c r="F28" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G28" s="1">
-        <v>10022</v>
+        <v>10012</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K28" s="10" t="s">
         <v>117</v>
@@ -3190,66 +3165,64 @@
         <v>6</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="R28" s="6"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C29" s="1">
-        <v>1110</v>
+        <v>1202</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G29" s="1">
-        <v>10032</v>
+        <v>10022</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L29" s="1">
         <v>6</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="O29" s="6"/>
-      <c r="P29" s="1"/>
+        <v>122</v>
+      </c>
       <c r="R29" s="6"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C30" s="1">
-        <v>1111</v>
+        <v>1203</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G30" s="1">
-        <v>10042</v>
+        <v>10032</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>99</v>
@@ -3264,7 +3237,7 @@
         <v>6</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="1"/>
@@ -3272,25 +3245,25 @@
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C31" s="1">
-        <v>1112</v>
+        <v>1204</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="G31" s="1">
-        <v>10072</v>
+        <v>10042</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J31" s="10" t="s">
         <v>66</v>
@@ -3302,7 +3275,7 @@
         <v>6</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="1"/>
@@ -3310,25 +3283,25 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C32" s="1">
-        <v>1113</v>
+        <v>1207</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="G32" s="1">
-        <v>10023</v>
+        <v>10072</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J32" s="10" t="s">
         <v>66</v>
@@ -3340,73 +3313,39 @@
         <v>6</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="1"/>
       <c r="R32" s="6"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C33" s="1">
-        <v>1114</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1112</v>
-      </c>
-      <c r="G33" s="1">
-        <v>10073</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L33" s="1">
-        <v>7</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>132</v>
-      </c>
+      <c r="D33" s="6"/>
+      <c r="M33" s="6"/>
       <c r="O33" s="6"/>
-      <c r="P33" s="1"/>
       <c r="R33" s="6"/>
     </row>
-    <row r="34" customHeight="1" spans="1:19 16373:16384">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
       <c r="C34" s="1">
-        <v>1115</v>
+        <v>1302</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
       <c r="F34" s="1">
-        <v>1109</v>
+        <v>1202</v>
       </c>
       <c r="G34" s="1">
-        <v>10024</v>
+        <v>10023</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J34" s="10" t="s">
         <v>66</v>
@@ -3415,39 +3354,36 @@
         <v>100</v>
       </c>
       <c r="L34" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="O34" s="1"/>
+        <v>130</v>
+      </c>
+      <c r="O34" s="6"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="S34" s="1"/>
-    </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
+      <c r="R34" s="6"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
       <c r="C35" s="1">
-        <v>1116</v>
+        <v>1307</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
       </c>
       <c r="F35" s="1">
-        <v>1110</v>
+        <v>1207</v>
       </c>
       <c r="G35" s="1">
-        <v>10034</v>
+        <v>10073</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>66</v>
@@ -3459,74 +3395,96 @@
         <v>7</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="N35" s="1"/>
+        <v>132</v>
+      </c>
       <c r="O35" s="6"/>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="XES35" s="1"/>
-      <c r="XET35" s="1"/>
-      <c r="XEU35" s="1"/>
-      <c r="XEV35" s="1"/>
-      <c r="XEW35" s="1"/>
-      <c r="XEX35" s="1"/>
-      <c r="XEY35" s="1"/>
-      <c r="XEZ35" s="1"/>
-      <c r="XFA35" s="1"/>
-      <c r="XFB35" s="1"/>
-      <c r="XFC35" s="1"/>
-      <c r="XFD35" s="1"/>
-    </row>
-    <row r="36" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C36" s="1"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
+      <c r="R35" s="6"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="D36" s="6"/>
+      <c r="M36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="XES36" s="1"/>
-      <c r="XET36" s="1"/>
-      <c r="XEU36" s="1"/>
-      <c r="XEV36" s="1"/>
-      <c r="XEW36" s="1"/>
-      <c r="XEX36" s="1"/>
-      <c r="XEY36" s="1"/>
-      <c r="XEZ36" s="1"/>
-      <c r="XFA36" s="1"/>
-      <c r="XFB36" s="1"/>
-      <c r="XFC36" s="1"/>
-      <c r="XFD36" s="1"/>
+      <c r="R36" s="6"/>
     </row>
     <row r="37" customHeight="1" spans="1:19 16373:16384">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1">
+        <v>1402</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1302</v>
+      </c>
+      <c r="G37" s="1">
+        <v>10024</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L37" s="1">
+        <v>7</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="S37" s="1"/>
     </row>
     <row r="38" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1">
+        <v>1403</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1203</v>
+      </c>
+      <c r="G38" s="1">
+        <v>10034</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1">
+        <v>7</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="N38" s="1"/>
       <c r="O38" s="6"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
@@ -3544,23 +3502,74 @@
       <c r="XFC38" s="1"/>
       <c r="XFD38" s="1"/>
     </row>
-    <row r="39" customHeight="1" spans="1:19 16373:16384">
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="C39" s="1"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
       <c r="O39" s="6"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
       <c r="S39" s="1"/>
+      <c r="XES39" s="1"/>
+      <c r="XET39" s="1"/>
+      <c r="XEU39" s="1"/>
+      <c r="XEV39" s="1"/>
+      <c r="XEW39" s="1"/>
+      <c r="XEX39" s="1"/>
+      <c r="XEY39" s="1"/>
+      <c r="XEZ39" s="1"/>
+      <c r="XFA39" s="1"/>
+      <c r="XFB39" s="1"/>
+      <c r="XFC39" s="1"/>
+      <c r="XFD39" s="1"/>
     </row>
     <row r="40" customHeight="1" spans="1:19 16373:16384">
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="1:19 16373:16384">
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="S41" s="1"/>
+      <c r="XES41" s="1"/>
+      <c r="XET41" s="1"/>
+      <c r="XEU41" s="1"/>
+      <c r="XEV41" s="1"/>
+      <c r="XEW41" s="1"/>
+      <c r="XEX41" s="1"/>
+      <c r="XEY41" s="1"/>
+      <c r="XEZ41" s="1"/>
+      <c r="XFA41" s="1"/>
+      <c r="XFB41" s="1"/>
+      <c r="XFC41" s="1"/>
+      <c r="XFD41" s="1"/>
     </row>
     <row r="42" customHeight="1" spans="1:19 16373:16384">
-      <c r="O42" s="1"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
@@ -3574,87 +3583,26 @@
       <c r="S44" s="1"/>
     </row>
     <row r="45" customHeight="1" spans="1:19 16373:16384">
+      <c r="O45" s="1"/>
       <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
     </row>
     <row r="46" customHeight="1" spans="1:19 16373:16384">
       <c r="Q46" s="1"/>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="XES49" s="1"/>
-      <c r="XET49" s="1"/>
-      <c r="XEU49" s="1"/>
-      <c r="XEV49" s="1"/>
-      <c r="XEW49" s="1"/>
-      <c r="XEX49" s="1"/>
-      <c r="XEY49" s="1"/>
-      <c r="XEZ49" s="1"/>
-      <c r="XFA49" s="1"/>
-      <c r="XFB49" s="1"/>
-      <c r="XFC49" s="1"/>
-      <c r="XFD49" s="1"/>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="XES50" s="1"/>
-      <c r="XET50" s="1"/>
-      <c r="XEU50" s="1"/>
-      <c r="XEV50" s="1"/>
-      <c r="XEW50" s="1"/>
-      <c r="XEX50" s="1"/>
-      <c r="XEY50" s="1"/>
-      <c r="XEZ50" s="1"/>
-      <c r="XFA50" s="1"/>
-      <c r="XFB50" s="1"/>
-      <c r="XFC50" s="1"/>
-      <c r="XFD50" s="1"/>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="XES51" s="1"/>
-      <c r="XET51" s="1"/>
-      <c r="XEU51" s="1"/>
-      <c r="XEV51" s="1"/>
-      <c r="XEW51" s="1"/>
-      <c r="XEX51" s="1"/>
-      <c r="XEY51" s="1"/>
-      <c r="XEZ51" s="1"/>
-      <c r="XFA51" s="1"/>
-      <c r="XFB51" s="1"/>
-      <c r="XFC51" s="1"/>
-      <c r="XFD51" s="1"/>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="S46" s="1"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:19 16373:16384">
+      <c r="Q47" s="1"/>
+      <c r="S47" s="1"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:19 16373:16384">
+      <c r="Q48" s="1"/>
+    </row>
+    <row r="49" customHeight="1" spans="3:17 16373:16384">
+      <c r="Q49" s="1"/>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -3679,7 +3627,7 @@
       <c r="XFC52" s="1"/>
       <c r="XFD52" s="1"/>
     </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -3704,7 +3652,7 @@
       <c r="XFC53" s="1"/>
       <c r="XFD53" s="1"/>
     </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -3729,6 +3677,81 @@
       <c r="XFC54" s="1"/>
       <c r="XFD54" s="1"/>
     </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="XES55" s="1"/>
+      <c r="XET55" s="1"/>
+      <c r="XEU55" s="1"/>
+      <c r="XEV55" s="1"/>
+      <c r="XEW55" s="1"/>
+      <c r="XEX55" s="1"/>
+      <c r="XEY55" s="1"/>
+      <c r="XEZ55" s="1"/>
+      <c r="XFA55" s="1"/>
+      <c r="XFB55" s="1"/>
+      <c r="XFC55" s="1"/>
+      <c r="XFD55" s="1"/>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
+      <c r="K56" s="1"/>
+      <c r="L56" s="1"/>
+      <c r="M56" s="1"/>
+      <c r="XES56" s="1"/>
+      <c r="XET56" s="1"/>
+      <c r="XEU56" s="1"/>
+      <c r="XEV56" s="1"/>
+      <c r="XEW56" s="1"/>
+      <c r="XEX56" s="1"/>
+      <c r="XEY56" s="1"/>
+      <c r="XEZ56" s="1"/>
+      <c r="XFA56" s="1"/>
+      <c r="XFB56" s="1"/>
+      <c r="XFC56" s="1"/>
+      <c r="XFD56" s="1"/>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="XES57" s="1"/>
+      <c r="XET57" s="1"/>
+      <c r="XEU57" s="1"/>
+      <c r="XEV57" s="1"/>
+      <c r="XEW57" s="1"/>
+      <c r="XEX57" s="1"/>
+      <c r="XEY57" s="1"/>
+      <c r="XEZ57" s="1"/>
+      <c r="XFA57" s="1"/>
+      <c r="XFB57" s="1"/>
+      <c r="XFC57" s="1"/>
+      <c r="XFD57" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
@@ -3743,7 +3766,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD51"/>
+  <dimension ref="A1:XFD54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -4377,7 +4400,7 @@
       <c r="XFC16" s="1"/>
       <c r="XFD16" s="1"/>
     </row>
-    <row r="17" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="17" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -4404,7 +4427,7 @@
       <c r="XFC17" s="1"/>
       <c r="XFD17" s="1"/>
     </row>
-    <row r="18" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="18" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -4431,7 +4454,7 @@
       <c r="XFC18" s="1"/>
       <c r="XFD18" s="1"/>
     </row>
-    <row r="19" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="19" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -4458,7 +4481,7 @@
       <c r="XFC19" s="1"/>
       <c r="XFD19" s="1"/>
     </row>
-    <row r="20" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="20" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1">
@@ -4508,7 +4531,7 @@
       <c r="XFC20" s="1"/>
       <c r="XFD20" s="1"/>
     </row>
-    <row r="21" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="21" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1">
@@ -4558,7 +4581,7 @@
       <c r="XFC21" s="1"/>
       <c r="XFD21" s="1"/>
     </row>
-    <row r="22" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="22" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1">
@@ -4608,7 +4631,7 @@
       <c r="XFC22" s="1"/>
       <c r="XFD22" s="1"/>
     </row>
-    <row r="23" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="23" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1">
@@ -4658,7 +4681,7 @@
       <c r="XFC23" s="1"/>
       <c r="XFD23" s="1"/>
     </row>
-    <row r="24" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="24" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1">
@@ -4708,7 +4731,7 @@
       <c r="XFC24" s="1"/>
       <c r="XFD24" s="1"/>
     </row>
-    <row r="25" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="25" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1">
@@ -4758,7 +4781,7 @@
       <c r="XFC25" s="1"/>
       <c r="XFD25" s="1"/>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="26" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1">
@@ -4808,42 +4831,20 @@
       <c r="XFC26" s="1"/>
       <c r="XFD26" s="1"/>
     </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="27" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-      <c r="C27" s="1">
-        <v>2108</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2</v>
-      </c>
-      <c r="F27" s="1">
-        <v>2101</v>
-      </c>
-      <c r="G27" s="1">
-        <v>20012</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="L27" s="1">
-        <v>6</v>
-      </c>
-      <c r="M27" s="6" t="s">
-        <v>170</v>
-      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="6"/>
       <c r="N27" s="1"/>
       <c r="XES27" s="1"/>
       <c r="XET27" s="1"/>
@@ -4858,32 +4859,32 @@
       <c r="XFC27" s="1"/>
       <c r="XFD27" s="1"/>
     </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="28" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1">
-        <v>2109</v>
+        <v>2201</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
       <c r="F28" s="1">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="G28" s="1">
-        <v>20022</v>
+        <v>20012</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K28" s="10" t="s">
         <v>117</v>
@@ -4892,7 +4893,7 @@
         <v>6</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N28" s="1"/>
       <c r="XES28" s="1"/>
@@ -4908,41 +4909,41 @@
       <c r="XFC28" s="1"/>
       <c r="XFD28" s="1"/>
     </row>
-    <row r="29" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="29" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1">
-        <v>2110</v>
+        <v>2202</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
       <c r="F29" s="1">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="G29" s="1">
-        <v>20032</v>
+        <v>20022</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L29" s="1">
         <v>6</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N29" s="1"/>
       <c r="XES29" s="1"/>
@@ -4958,26 +4959,26 @@
       <c r="XFC29" s="1"/>
       <c r="XFD29" s="1"/>
     </row>
-    <row r="30" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="30" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1">
-        <v>2111</v>
+        <v>2203</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="F30" s="1">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="G30" s="1">
-        <v>20072</v>
+        <v>20032</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I30" s="10" t="s">
         <v>99</v>
@@ -4992,7 +4993,7 @@
         <v>6</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N30" s="1"/>
       <c r="XES30" s="1"/>
@@ -5008,26 +5009,26 @@
       <c r="XFC30" s="1"/>
       <c r="XFD30" s="1"/>
     </row>
-    <row r="31" customHeight="1" spans="1:18 16373:16384">
+    <row r="31" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1">
-        <v>2112</v>
+        <v>2207</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="1">
-        <v>2110</v>
+        <v>2107</v>
       </c>
       <c r="G31" s="1">
-        <v>20033</v>
+        <v>20072</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="I31" s="10" t="s">
         <v>99</v>
@@ -5042,50 +5043,36 @@
         <v>6</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="1"/>
-    </row>
-    <row r="32" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="XES31" s="1"/>
+      <c r="XET31" s="1"/>
+      <c r="XEU31" s="1"/>
+      <c r="XEV31" s="1"/>
+      <c r="XEW31" s="1"/>
+      <c r="XEX31" s="1"/>
+      <c r="XEY31" s="1"/>
+      <c r="XEZ31" s="1"/>
+      <c r="XFA31" s="1"/>
+      <c r="XFB31" s="1"/>
+      <c r="XFC31" s="1"/>
+      <c r="XFD31" s="1"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="1">
-        <v>2113</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E32" s="1">
-        <v>2</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2104</v>
-      </c>
-      <c r="G32" s="1">
-        <v>20043</v>
-      </c>
-      <c r="H32" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L32" s="1">
-        <v>6</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>180</v>
-      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="6"/>
       <c r="N32" s="1"/>
       <c r="XES32" s="1"/>
       <c r="XET32" s="1"/>
@@ -5100,29 +5087,29 @@
       <c r="XFC32" s="1"/>
       <c r="XFD32" s="1"/>
     </row>
-    <row r="33" customHeight="1" spans="1:18 16373:16384">
+    <row r="33" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1">
-        <v>2114</v>
+        <v>2302</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
       </c>
       <c r="F33" s="1">
-        <v>2111</v>
+        <v>2202</v>
       </c>
       <c r="G33" s="1">
-        <v>20073</v>
+        <v>20023</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>66</v>
@@ -5131,34 +5118,42 @@
         <v>100</v>
       </c>
       <c r="L33" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="1"/>
-    </row>
-    <row r="34" customHeight="1" spans="1:18 16373:16384">
+      <c r="XES33" s="1"/>
+      <c r="XET33" s="1"/>
+      <c r="XEU33" s="1"/>
+      <c r="XEV33" s="1"/>
+      <c r="XEW33" s="1"/>
+      <c r="XEX33" s="1"/>
+      <c r="XEY33" s="1"/>
+      <c r="XEZ33" s="1"/>
+      <c r="XFA33" s="1"/>
+      <c r="XFB33" s="1"/>
+      <c r="XFC33" s="1"/>
+      <c r="XFD33" s="1"/>
+    </row>
+    <row r="34" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1">
-        <v>2115</v>
+        <v>2304</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="F34" s="1">
-        <v>2109</v>
+        <v>2104</v>
       </c>
       <c r="G34" s="1">
-        <v>20024</v>
+        <v>20043</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>106</v>
@@ -5173,40 +5168,48 @@
         <v>100</v>
       </c>
       <c r="L34" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="6"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="1"/>
+      <c r="XES34" s="1"/>
+      <c r="XET34" s="1"/>
+      <c r="XEU34" s="1"/>
+      <c r="XEV34" s="1"/>
+      <c r="XEW34" s="1"/>
+      <c r="XEX34" s="1"/>
+      <c r="XEY34" s="1"/>
+      <c r="XEZ34" s="1"/>
+      <c r="XFA34" s="1"/>
+      <c r="XFB34" s="1"/>
+      <c r="XFC34" s="1"/>
+      <c r="XFD34" s="1"/>
     </row>
     <row r="35" customHeight="1" spans="1:18 16373:16384">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1">
-        <v>2116</v>
+        <v>2307</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="F35" s="1">
-        <v>2112</v>
+        <v>2207</v>
       </c>
       <c r="G35" s="1">
-        <v>20034</v>
+        <v>20073</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>66</v>
@@ -5218,7 +5221,7 @@
         <v>7</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
@@ -5227,6 +5230,10 @@
       <c r="R35" s="1"/>
     </row>
     <row r="36" customHeight="1" spans="1:18 16373:16384">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="D36" s="6"/>
+      <c r="M36" s="6"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="6"/>
@@ -5234,6 +5241,41 @@
       <c r="R36" s="1"/>
     </row>
     <row r="37" customHeight="1" spans="1:18 16373:16384">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1">
+        <v>2402</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E37" s="1">
+        <v>2</v>
+      </c>
+      <c r="F37" s="1">
+        <v>2302</v>
+      </c>
+      <c r="G37" s="1">
+        <v>20024</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L37" s="1">
+        <v>7</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>184</v>
+      </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="6"/>
@@ -5241,6 +5283,41 @@
       <c r="R37" s="1"/>
     </row>
     <row r="38" customHeight="1" spans="1:18 16373:16384">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1">
+        <v>2403</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2</v>
+      </c>
+      <c r="F38" s="1">
+        <v>2203</v>
+      </c>
+      <c r="G38" s="1">
+        <v>20034</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L38" s="1">
+        <v>7</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>186</v>
+      </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="6"/>
@@ -5250,7 +5327,7 @@
     <row r="39" customHeight="1" spans="1:18 16373:16384">
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
+      <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="1"/>
     </row>
@@ -5261,95 +5338,26 @@
       <c r="Q40" s="6"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="2"/>
+    <row r="41" customHeight="1" spans="1:18 16373:16384">
+      <c r="N41" s="1"/>
       <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
+      <c r="P41" s="6"/>
       <c r="Q41" s="6"/>
       <c r="R41" s="1"/>
-      <c r="XES41" s="1"/>
-      <c r="XET41" s="1"/>
-      <c r="XEU41" s="1"/>
-      <c r="XEV41" s="1"/>
-      <c r="XEW41" s="1"/>
-      <c r="XEX41" s="1"/>
-      <c r="XEY41" s="1"/>
-      <c r="XEZ41" s="1"/>
-      <c r="XFA41" s="1"/>
-      <c r="XFB41" s="1"/>
-      <c r="XFC41" s="1"/>
-      <c r="XFD41" s="1"/>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="2"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:18 16373:16384">
+      <c r="N42" s="1"/>
       <c r="O42" s="1"/>
-      <c r="P42" s="6"/>
+      <c r="P42" s="1"/>
       <c r="Q42" s="6"/>
       <c r="R42" s="1"/>
-      <c r="XES42" s="1"/>
-      <c r="XET42" s="1"/>
-      <c r="XEU42" s="1"/>
-      <c r="XEV42" s="1"/>
-      <c r="XEW42" s="1"/>
-      <c r="XEX42" s="1"/>
-      <c r="XEY42" s="1"/>
-      <c r="XEZ42" s="1"/>
-      <c r="XFA42" s="1"/>
-      <c r="XFB42" s="1"/>
-      <c r="XFC42" s="1"/>
-      <c r="XFD42" s="1"/>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="2"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:18 16373:16384">
+      <c r="N43" s="1"/>
       <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
+      <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
       <c r="R43" s="1"/>
-      <c r="XES43" s="1"/>
-      <c r="XET43" s="1"/>
-      <c r="XEU43" s="1"/>
-      <c r="XEV43" s="1"/>
-      <c r="XEW43" s="1"/>
-      <c r="XEX43" s="1"/>
-      <c r="XEY43" s="1"/>
-      <c r="XEZ43" s="1"/>
-      <c r="XFA43" s="1"/>
-      <c r="XFB43" s="1"/>
-      <c r="XFC43" s="1"/>
-      <c r="XFD43" s="1"/>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="C44" s="1"/>
@@ -5366,7 +5374,7 @@
       <c r="N44" s="2"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
+      <c r="Q44" s="6"/>
       <c r="R44" s="1"/>
       <c r="XES44" s="1"/>
       <c r="XET44" s="1"/>
@@ -5381,34 +5389,106 @@
       <c r="XFC44" s="1"/>
       <c r="XFD44" s="1"/>
     </row>
-    <row r="45" customHeight="1" spans="1:18 16373:16384">
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="2"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
+      <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
       <c r="R45" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:18 16373:16384">
+      <c r="XES45" s="1"/>
+      <c r="XET45" s="1"/>
+      <c r="XEU45" s="1"/>
+      <c r="XEV45" s="1"/>
+      <c r="XEW45" s="1"/>
+      <c r="XEX45" s="1"/>
+      <c r="XEY45" s="1"/>
+      <c r="XEZ45" s="1"/>
+      <c r="XFA45" s="1"/>
+      <c r="XFB45" s="1"/>
+      <c r="XFC45" s="1"/>
+      <c r="XFD45" s="1"/>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="2"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
       <c r="Q46" s="6"/>
       <c r="R46" s="1"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:18 16373:16384">
+      <c r="XES46" s="1"/>
+      <c r="XET46" s="1"/>
+      <c r="XEU46" s="1"/>
+      <c r="XEV46" s="1"/>
+      <c r="XEW46" s="1"/>
+      <c r="XEX46" s="1"/>
+      <c r="XEY46" s="1"/>
+      <c r="XEZ46" s="1"/>
+      <c r="XFA46" s="1"/>
+      <c r="XFB46" s="1"/>
+      <c r="XFC46" s="1"/>
+      <c r="XFD46" s="1"/>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="N47" s="2"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
-      <c r="Q47" s="6"/>
+      <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
+      <c r="XES47" s="1"/>
+      <c r="XET47" s="1"/>
+      <c r="XEU47" s="1"/>
+      <c r="XEV47" s="1"/>
+      <c r="XEW47" s="1"/>
+      <c r="XEX47" s="1"/>
+      <c r="XEY47" s="1"/>
+      <c r="XEZ47" s="1"/>
+      <c r="XFA47" s="1"/>
+      <c r="XFB47" s="1"/>
+      <c r="XFC47" s="1"/>
+      <c r="XFD47" s="1"/>
     </row>
     <row r="48" customHeight="1" spans="1:18 16373:16384">
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
+      <c r="Q48" s="6"/>
       <c r="R48" s="1"/>
     </row>
     <row r="49" customHeight="1" spans="15:18">
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
+      <c r="Q49" s="6"/>
       <c r="R49" s="1"/>
     </row>
     <row r="50" customHeight="1" spans="15:18">
@@ -5420,8 +5500,26 @@
     <row r="51" customHeight="1" spans="15:18">
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
-      <c r="Q51" s="6"/>
+      <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
+    </row>
+    <row r="52" customHeight="1" spans="15:18">
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+    </row>
+    <row r="53" customHeight="1" spans="15:18">
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="6"/>
+      <c r="R53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="15:18">
+      <c r="O54" s="1"/>
+      <c r="P54" s="1"/>
+      <c r="Q54" s="6"/>
+      <c r="R54" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5437,7 +5535,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD58"/>
+  <dimension ref="A1:XFD62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -6164,65 +6262,32 @@
       <c r="N30" s="2"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C31" s="1">
-        <v>3108</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E31" s="1">
-        <v>3</v>
-      </c>
-      <c r="F31" s="1">
-        <v>3101</v>
-      </c>
-      <c r="G31" s="1">
-        <v>30012</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="L31" s="1">
-        <v>6</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="N31" s="2"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C32" s="1">
-        <v>3109</v>
+        <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
       </c>
       <c r="F32" s="1">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="G32" s="1">
-        <v>30022</v>
+        <v>30012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K32" s="10" t="s">
         <v>117</v>
@@ -6231,64 +6296,64 @@
         <v>6</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N32" s="2"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C33" s="1">
-        <v>3110</v>
+        <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
       </c>
       <c r="F33" s="1">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="G33" s="1">
-        <v>30032</v>
+        <v>30022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="N33" s="2"/>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C34" s="1">
-        <v>3111</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>224</v>
+        <v>3203</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
       </c>
       <c r="F34" s="1">
-        <v>3110</v>
+        <v>3103</v>
       </c>
       <c r="G34" s="1">
-        <v>30033</v>
+        <v>30032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I34" s="10" t="s">
         <v>99</v>
@@ -6302,71 +6367,38 @@
       <c r="L34" s="1">
         <v>6</v>
       </c>
-      <c r="M34" s="2" t="s">
-        <v>225</v>
+      <c r="M34" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="N34" s="2"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C35" s="1">
-        <v>3112</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E35" s="1">
-        <v>3</v>
-      </c>
-      <c r="F35" s="1">
-        <v>3104</v>
-      </c>
-      <c r="G35" s="1">
-        <v>30043</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L35" s="1">
-        <v>6</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="N35" s="2"/>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C36" s="1">
-        <v>3113</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>228</v>
+        <v>3302</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="E36" s="1">
         <v>3</v>
       </c>
       <c r="F36" s="1">
-        <v>3107</v>
+        <v>3202</v>
       </c>
       <c r="G36" s="1">
-        <v>30073</v>
+        <v>30023</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>100</v>
@@ -6374,26 +6406,26 @@
       <c r="L36" s="1">
         <v>6</v>
       </c>
-      <c r="M36" s="2" t="s">
-        <v>229</v>
+      <c r="M36" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="N36" s="2"/>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C37" s="1">
-        <v>3114</v>
+        <v>3303</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1">
-        <v>3109</v>
+        <v>3203</v>
       </c>
       <c r="G37" s="1">
-        <v>30024</v>
+        <v>30033</v>
       </c>
       <c r="H37" s="10" t="s">
         <v>103</v>
@@ -6408,30 +6440,28 @@
         <v>100</v>
       </c>
       <c r="L37" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" customHeight="1" spans="1:14 16373:16384">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C38" s="1">
-        <v>3115</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>232</v>
+        <v>3304</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
       </c>
       <c r="F38" s="1">
-        <v>3111</v>
+        <v>3104</v>
       </c>
       <c r="G38" s="1">
-        <v>30034</v>
+        <v>30043</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>106</v>
@@ -6446,188 +6476,203 @@
         <v>100</v>
       </c>
       <c r="L38" s="1">
+        <v>6</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C39" s="1">
+        <v>3307</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E39" s="1">
+        <v>3</v>
+      </c>
+      <c r="F39" s="1">
+        <v>3107</v>
+      </c>
+      <c r="G39" s="1">
+        <v>30073</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1">
+        <v>6</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="N39" s="2"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="D40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C41" s="1">
+        <v>3402</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E41" s="1">
+        <v>3</v>
+      </c>
+      <c r="F41" s="1">
+        <v>3302</v>
+      </c>
+      <c r="G41" s="1">
+        <v>30024</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L41" s="1">
         <v>7</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="M41" s="2" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="1"/>
-      <c r="XES39" s="1"/>
-      <c r="XET39" s="1"/>
-      <c r="XEU39" s="1"/>
-      <c r="XEV39" s="1"/>
-      <c r="XEW39" s="1"/>
-      <c r="XEX39" s="1"/>
-      <c r="XEY39" s="1"/>
-      <c r="XEZ39" s="1"/>
-      <c r="XFA39" s="1"/>
-      <c r="XFB39" s="1"/>
-      <c r="XFC39" s="1"/>
-      <c r="XFD39" s="1"/>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="XES40" s="1"/>
-      <c r="XET40" s="1"/>
-      <c r="XEU40" s="1"/>
-      <c r="XEV40" s="1"/>
-      <c r="XEW40" s="1"/>
-      <c r="XEX40" s="1"/>
-      <c r="XEY40" s="1"/>
-      <c r="XEZ40" s="1"/>
-      <c r="XFA40" s="1"/>
-      <c r="XFB40" s="1"/>
-      <c r="XFC40" s="1"/>
-      <c r="XFD40" s="1"/>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="XES42" s="1"/>
-      <c r="XET42" s="1"/>
-      <c r="XEU42" s="1"/>
-      <c r="XEV42" s="1"/>
-      <c r="XEW42" s="1"/>
-      <c r="XEX42" s="1"/>
-      <c r="XEY42" s="1"/>
-      <c r="XEZ42" s="1"/>
-      <c r="XFA42" s="1"/>
-      <c r="XFB42" s="1"/>
-      <c r="XFC42" s="1"/>
-      <c r="XFD42" s="1"/>
-    </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="XES53" s="1"/>
-      <c r="XET53" s="1"/>
-      <c r="XEU53" s="1"/>
-      <c r="XEV53" s="1"/>
-      <c r="XEW53" s="1"/>
-      <c r="XEX53" s="1"/>
-      <c r="XEY53" s="1"/>
-      <c r="XEZ53" s="1"/>
-      <c r="XFA53" s="1"/>
-      <c r="XFB53" s="1"/>
-      <c r="XFC53" s="1"/>
-      <c r="XFD53" s="1"/>
-    </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="XES54" s="1"/>
-      <c r="XET54" s="1"/>
-      <c r="XEU54" s="1"/>
-      <c r="XEV54" s="1"/>
-      <c r="XEW54" s="1"/>
-      <c r="XEX54" s="1"/>
-      <c r="XEY54" s="1"/>
-      <c r="XEZ54" s="1"/>
-      <c r="XFA54" s="1"/>
-      <c r="XFB54" s="1"/>
-      <c r="XFC54" s="1"/>
-      <c r="XFD54" s="1"/>
-    </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="XES55" s="1"/>
-      <c r="XET55" s="1"/>
-      <c r="XEU55" s="1"/>
-      <c r="XEV55" s="1"/>
-      <c r="XEW55" s="1"/>
-      <c r="XEX55" s="1"/>
-      <c r="XEY55" s="1"/>
-      <c r="XEZ55" s="1"/>
-      <c r="XFA55" s="1"/>
-      <c r="XFB55" s="1"/>
-      <c r="XFC55" s="1"/>
-      <c r="XFD55" s="1"/>
-    </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="XES56" s="1"/>
-      <c r="XET56" s="1"/>
-      <c r="XEU56" s="1"/>
-      <c r="XEV56" s="1"/>
-      <c r="XEW56" s="1"/>
-      <c r="XEX56" s="1"/>
-      <c r="XEY56" s="1"/>
-      <c r="XEZ56" s="1"/>
-      <c r="XFA56" s="1"/>
-      <c r="XFB56" s="1"/>
-      <c r="XFC56" s="1"/>
-      <c r="XFD56" s="1"/>
+      <c r="N41" s="2"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:14 16373:16384">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1">
+        <v>3403</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E42" s="1">
+        <v>3</v>
+      </c>
+      <c r="F42" s="1">
+        <v>3303</v>
+      </c>
+      <c r="G42" s="1">
+        <v>30034</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L42" s="1">
+        <v>7</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="1"/>
+      <c r="XES43" s="1"/>
+      <c r="XET43" s="1"/>
+      <c r="XEU43" s="1"/>
+      <c r="XEV43" s="1"/>
+      <c r="XEW43" s="1"/>
+      <c r="XEX43" s="1"/>
+      <c r="XEY43" s="1"/>
+      <c r="XEZ43" s="1"/>
+      <c r="XFA43" s="1"/>
+      <c r="XFB43" s="1"/>
+      <c r="XFC43" s="1"/>
+      <c r="XFD43" s="1"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="XES44" s="1"/>
+      <c r="XET44" s="1"/>
+      <c r="XEU44" s="1"/>
+      <c r="XEV44" s="1"/>
+      <c r="XEW44" s="1"/>
+      <c r="XEX44" s="1"/>
+      <c r="XEY44" s="1"/>
+      <c r="XEZ44" s="1"/>
+      <c r="XFA44" s="1"/>
+      <c r="XFB44" s="1"/>
+      <c r="XFC44" s="1"/>
+      <c r="XFD44" s="1"/>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="XES46" s="1"/>
+      <c r="XET46" s="1"/>
+      <c r="XEU46" s="1"/>
+      <c r="XEV46" s="1"/>
+      <c r="XEW46" s="1"/>
+      <c r="XEX46" s="1"/>
+      <c r="XEY46" s="1"/>
+      <c r="XEZ46" s="1"/>
+      <c r="XFA46" s="1"/>
+      <c r="XFB46" s="1"/>
+      <c r="XFC46" s="1"/>
+      <c r="XFD46" s="1"/>
     </row>
     <row r="57" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C57" s="1"/>
@@ -6679,6 +6724,106 @@
       <c r="XFC58" s="1"/>
       <c r="XFD58" s="1"/>
     </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="XES59" s="1"/>
+      <c r="XET59" s="1"/>
+      <c r="XEU59" s="1"/>
+      <c r="XEV59" s="1"/>
+      <c r="XEW59" s="1"/>
+      <c r="XEX59" s="1"/>
+      <c r="XEY59" s="1"/>
+      <c r="XEZ59" s="1"/>
+      <c r="XFA59" s="1"/>
+      <c r="XFB59" s="1"/>
+      <c r="XFC59" s="1"/>
+      <c r="XFD59" s="1"/>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="M60" s="1"/>
+      <c r="XES60" s="1"/>
+      <c r="XET60" s="1"/>
+      <c r="XEU60" s="1"/>
+      <c r="XEV60" s="1"/>
+      <c r="XEW60" s="1"/>
+      <c r="XEX60" s="1"/>
+      <c r="XEY60" s="1"/>
+      <c r="XEZ60" s="1"/>
+      <c r="XFA60" s="1"/>
+      <c r="XFB60" s="1"/>
+      <c r="XFC60" s="1"/>
+      <c r="XFD60" s="1"/>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="XES61" s="1"/>
+      <c r="XET61" s="1"/>
+      <c r="XEU61" s="1"/>
+      <c r="XEV61" s="1"/>
+      <c r="XEW61" s="1"/>
+      <c r="XEX61" s="1"/>
+      <c r="XEY61" s="1"/>
+      <c r="XEZ61" s="1"/>
+      <c r="XFA61" s="1"/>
+      <c r="XFB61" s="1"/>
+      <c r="XFC61" s="1"/>
+      <c r="XFD61" s="1"/>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="XES62" s="1"/>
+      <c r="XET62" s="1"/>
+      <c r="XEU62" s="1"/>
+      <c r="XEV62" s="1"/>
+      <c r="XEW62" s="1"/>
+      <c r="XEX62" s="1"/>
+      <c r="XEY62" s="1"/>
+      <c r="XEZ62" s="1"/>
+      <c r="XFA62" s="1"/>
+      <c r="XFB62" s="1"/>
+      <c r="XFC62" s="1"/>
+      <c r="XFD62" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="242">
   <si>
     <t>#</t>
   </si>
@@ -368,51 +368,57 @@
     <t>蛮牛冲撞·破甲</t>
   </si>
   <si>
+    <t>龙魂灵动</t>
+  </si>
+  <si>
+    <t>龙魂护体·灵动</t>
+  </si>
+  <si>
+    <t>无求圣体</t>
+  </si>
+  <si>
+    <t>无求易决·圣体</t>
+  </si>
+  <si>
+    <t>火麟灵动</t>
+  </si>
+  <si>
+    <t>30,10</t>
+  </si>
+  <si>
+    <t>火麟剑诀·灵动</t>
+  </si>
+  <si>
+    <t>基础圣体</t>
+  </si>
+  <si>
+    <t>基础心法·圣体</t>
+  </si>
+  <si>
+    <t>流光吸血</t>
+  </si>
+  <si>
+    <t>流光剑诀·吸血</t>
+  </si>
+  <si>
+    <t>月华断河</t>
+  </si>
+  <si>
+    <t>月华剑阵·断河</t>
+  </si>
+  <si>
+    <t>蛮牛致残</t>
+  </si>
+  <si>
+    <t>蛮牛冲撞·致残</t>
+  </si>
+  <si>
     <t>龙魂无断</t>
   </si>
   <si>
     <t>龙魂护体·无断</t>
   </si>
   <si>
-    <t>无求圣体</t>
-  </si>
-  <si>
-    <t>无求易决·圣体</t>
-  </si>
-  <si>
-    <t>火麟灵动</t>
-  </si>
-  <si>
-    <t>30,10</t>
-  </si>
-  <si>
-    <t>火麟剑诀·灵动</t>
-  </si>
-  <si>
-    <t>基础圣体</t>
-  </si>
-  <si>
-    <t>基础心法·圣体</t>
-  </si>
-  <si>
-    <t>流光吸血</t>
-  </si>
-  <si>
-    <t>流光剑诀·吸血</t>
-  </si>
-  <si>
-    <t>月华断河</t>
-  </si>
-  <si>
-    <t>月华剑阵·断河</t>
-  </si>
-  <si>
-    <t>蛮牛致残</t>
-  </si>
-  <si>
-    <t>蛮牛冲撞·致残</t>
-  </si>
-  <si>
     <t>火麟破甲</t>
   </si>
   <si>
@@ -521,42 +527,48 @@
     <t>烈焰焚天·破甲</t>
   </si>
   <si>
+    <t>炎凰灵动</t>
+  </si>
+  <si>
+    <t>炎凰法盾·灵动</t>
+  </si>
+  <si>
+    <t>万法圣体</t>
+  </si>
+  <si>
+    <t>万法归宗·圣体</t>
+  </si>
+  <si>
+    <t>冰暴霜寒</t>
+  </si>
+  <si>
+    <t>极寒冰暴·霜寒</t>
+  </si>
+  <si>
+    <t>冥想魔体</t>
+  </si>
+  <si>
+    <t>冥想心法·魔体</t>
+  </si>
+  <si>
+    <t>神雷狂潮</t>
+  </si>
+  <si>
+    <t>紫电神雷·狂潮</t>
+  </si>
+  <si>
+    <t>火狱炼狱</t>
+  </si>
+  <si>
+    <t>火狱阵法·炼狱</t>
+  </si>
+  <si>
     <t>炎凰无断</t>
   </si>
   <si>
     <t>炎凰法盾·无断</t>
   </si>
   <si>
-    <t>万法圣体</t>
-  </si>
-  <si>
-    <t>万法归宗·圣体</t>
-  </si>
-  <si>
-    <t>冰暴霜寒</t>
-  </si>
-  <si>
-    <t>极寒冰暴·霜寒</t>
-  </si>
-  <si>
-    <t>冥想魔体</t>
-  </si>
-  <si>
-    <t>冥想心法·魔体</t>
-  </si>
-  <si>
-    <t>神雷狂潮</t>
-  </si>
-  <si>
-    <t>紫电神雷·狂潮</t>
-  </si>
-  <si>
-    <t>火狱炼狱</t>
-  </si>
-  <si>
-    <t>火狱阵法·炼狱</t>
-  </si>
-  <si>
     <t>冰暴蚀魂</t>
   </si>
   <si>
@@ -668,40 +680,46 @@
     <t>圣疗术·御甲</t>
   </si>
   <si>
+    <t>麟盾灵动</t>
+  </si>
+  <si>
+    <t>太虚麟盾·灵动</t>
+  </si>
+  <si>
+    <t>自然道体</t>
+  </si>
+  <si>
+    <t>道法自然·道体</t>
+  </si>
+  <si>
+    <t>英灵御灵</t>
+  </si>
+  <si>
+    <t>召唤英灵·御灵</t>
+  </si>
+  <si>
+    <t>清心神体</t>
+  </si>
+  <si>
+    <t>清心咒·神体</t>
+  </si>
+  <si>
+    <t>破魔回复</t>
+  </si>
+  <si>
+    <t>破魔符咒·回复</t>
+  </si>
+  <si>
+    <t>毒咒蚀骨</t>
+  </si>
+  <si>
+    <t>毒咒术·蚀骨</t>
+  </si>
+  <si>
     <t>麟盾无断</t>
   </si>
   <si>
     <t>太虚麟盾·无断</t>
-  </si>
-  <si>
-    <t>自然道体</t>
-  </si>
-  <si>
-    <t>道法自然·道体</t>
-  </si>
-  <si>
-    <t>英灵御灵</t>
-  </si>
-  <si>
-    <t>召唤英灵·御灵</t>
-  </si>
-  <si>
-    <t>清心神体</t>
-  </si>
-  <si>
-    <t>清心咒·神体</t>
-  </si>
-  <si>
-    <t>破魔回复</t>
-  </si>
-  <si>
-    <t>破魔符咒·回复</t>
-  </si>
-  <si>
-    <t>毒咒蚀骨</t>
-  </si>
-  <si>
-    <t>毒咒术·蚀骨</t>
   </si>
   <si>
     <t>破魔双生</t>
@@ -2420,7 +2438,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD57"/>
+  <dimension ref="A1:XFD58"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -3283,7 +3301,7 @@
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:18">
       <c r="C32" s="1">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>127</v>
@@ -3292,80 +3310,79 @@
         <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="G32" s="1">
-        <v>10072</v>
+        <v>10052</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>100</v>
+        <v>78</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L32" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>128</v>
       </c>
       <c r="O32" s="6"/>
-      <c r="P32" s="1"/>
       <c r="R32" s="6"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="D33" s="6"/>
-      <c r="M33" s="6"/>
+      <c r="C33" s="1">
+        <v>1207</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="1">
+        <v>1</v>
+      </c>
+      <c r="F33" s="1">
+        <v>1107</v>
+      </c>
+      <c r="G33" s="1">
+        <v>10072</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L33" s="1">
+        <v>6</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>130</v>
+      </c>
       <c r="O33" s="6"/>
+      <c r="P33" s="1"/>
       <c r="R33" s="6"/>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C34" s="1">
-        <v>1302</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1202</v>
-      </c>
-      <c r="G34" s="1">
-        <v>10023</v>
-      </c>
-      <c r="H34" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L34" s="1">
-        <v>6</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>130</v>
-      </c>
+      <c r="D34" s="6"/>
+      <c r="M34" s="6"/>
       <c r="O34" s="6"/>
-      <c r="P34" s="1"/>
       <c r="R34" s="6"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
       <c r="C35" s="1">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>131</v>
@@ -3374,13 +3391,13 @@
         <v>1</v>
       </c>
       <c r="F35" s="1">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="G35" s="1">
-        <v>10073</v>
+        <v>10023</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I35" s="10" t="s">
         <v>99</v>
@@ -3392,7 +3409,7 @@
         <v>100</v>
       </c>
       <c r="L35" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>132</v>
@@ -3402,57 +3419,54 @@
       <c r="R35" s="6"/>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="D36" s="6"/>
-      <c r="M36" s="6"/>
+      <c r="C36" s="1">
+        <v>1307</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36" s="1">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1">
+        <v>1207</v>
+      </c>
+      <c r="G36" s="1">
+        <v>10073</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L36" s="1">
+        <v>7</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>134</v>
+      </c>
       <c r="O36" s="6"/>
+      <c r="P36" s="1"/>
       <c r="R36" s="6"/>
     </row>
-    <row r="37" customHeight="1" spans="1:19 16373:16384">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1">
-        <v>1402</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1">
-        <v>1302</v>
-      </c>
-      <c r="G37" s="1">
-        <v>10024</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L37" s="1">
-        <v>7</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="S37" s="1"/>
-    </row>
-    <row r="38" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="D37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="R37" s="6"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:19 16373:16384">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>135</v>
@@ -3461,10 +3475,10 @@
         <v>1</v>
       </c>
       <c r="F38" s="1">
-        <v>1203</v>
+        <v>1302</v>
       </c>
       <c r="G38" s="1">
-        <v>10034</v>
+        <v>10024</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>106</v>
@@ -3484,36 +3498,47 @@
       <c r="M38" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="6"/>
+      <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
       <c r="S38" s="1"/>
-      <c r="XES38" s="1"/>
-      <c r="XET38" s="1"/>
-      <c r="XEU38" s="1"/>
-      <c r="XEV38" s="1"/>
-      <c r="XEW38" s="1"/>
-      <c r="XEX38" s="1"/>
-      <c r="XEY38" s="1"/>
-      <c r="XEZ38" s="1"/>
-      <c r="XFA38" s="1"/>
-      <c r="XFB38" s="1"/>
-      <c r="XFC38" s="1"/>
-      <c r="XFD38" s="1"/>
     </row>
     <row r="39" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C39" s="1"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1">
+        <v>1403</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1203</v>
+      </c>
+      <c r="G39" s="1">
+        <v>10034</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1">
+        <v>7</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>138</v>
+      </c>
       <c r="N39" s="1"/>
       <c r="O39" s="6"/>
       <c r="P39" s="1"/>
@@ -3532,50 +3557,76 @@
       <c r="XFC39" s="1"/>
       <c r="XFD39" s="1"/>
     </row>
-    <row r="40" customHeight="1" spans="1:19 16373:16384">
-      <c r="O40" s="1"/>
+    <row r="40" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="C40" s="1"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="6"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
       <c r="S40" s="1"/>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="O41" s="6"/>
+      <c r="XES40" s="1"/>
+      <c r="XET40" s="1"/>
+      <c r="XEU40" s="1"/>
+      <c r="XEV40" s="1"/>
+      <c r="XEW40" s="1"/>
+      <c r="XEX40" s="1"/>
+      <c r="XEY40" s="1"/>
+      <c r="XEZ40" s="1"/>
+      <c r="XFA40" s="1"/>
+      <c r="XFB40" s="1"/>
+      <c r="XFC40" s="1"/>
+      <c r="XFD40" s="1"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:19 16373:16384">
+      <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="S41" s="1"/>
-      <c r="XES41" s="1"/>
-      <c r="XET41" s="1"/>
-      <c r="XEU41" s="1"/>
-      <c r="XEV41" s="1"/>
-      <c r="XEW41" s="1"/>
-      <c r="XEX41" s="1"/>
-      <c r="XEY41" s="1"/>
-      <c r="XEZ41" s="1"/>
-      <c r="XFA41" s="1"/>
-      <c r="XFB41" s="1"/>
-      <c r="XFC41" s="1"/>
-      <c r="XFD41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:19 16373:16384">
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
       <c r="O42" s="6"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
       <c r="S42" s="1"/>
+      <c r="XES42" s="1"/>
+      <c r="XET42" s="1"/>
+      <c r="XEU42" s="1"/>
+      <c r="XEV42" s="1"/>
+      <c r="XEW42" s="1"/>
+      <c r="XEX42" s="1"/>
+      <c r="XEY42" s="1"/>
+      <c r="XEZ42" s="1"/>
+      <c r="XFA42" s="1"/>
+      <c r="XFB42" s="1"/>
+      <c r="XFC42" s="1"/>
+      <c r="XFD42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="1:19 16373:16384">
+      <c r="O43" s="6"/>
+      <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
       <c r="S43" s="1"/>
     </row>
     <row r="44" customHeight="1" spans="1:19 16373:16384">
@@ -3583,13 +3634,13 @@
       <c r="S44" s="1"/>
     </row>
     <row r="45" customHeight="1" spans="1:19 16373:16384">
-      <c r="O45" s="1"/>
       <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
       <c r="S45" s="1"/>
     </row>
     <row r="46" customHeight="1" spans="1:19 16373:16384">
+      <c r="O46" s="1"/>
       <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
       <c r="S46" s="1"/>
     </row>
     <row r="47" customHeight="1" spans="1:19 16373:16384">
@@ -3598,34 +3649,13 @@
     </row>
     <row r="48" customHeight="1" spans="1:19 16373:16384">
       <c r="Q48" s="1"/>
+      <c r="S48" s="1"/>
     </row>
     <row r="49" customHeight="1" spans="3:17 16373:16384">
       <c r="Q49" s="1"/>
     </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="XES52" s="1"/>
-      <c r="XET52" s="1"/>
-      <c r="XEU52" s="1"/>
-      <c r="XEV52" s="1"/>
-      <c r="XEW52" s="1"/>
-      <c r="XEX52" s="1"/>
-      <c r="XEY52" s="1"/>
-      <c r="XEZ52" s="1"/>
-      <c r="XFA52" s="1"/>
-      <c r="XFB52" s="1"/>
-      <c r="XFC52" s="1"/>
-      <c r="XFD52" s="1"/>
+    <row r="50" customHeight="1" spans="3:17 16373:16384">
+      <c r="Q50" s="1"/>
     </row>
     <row r="53" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
       <c r="C53" s="1"/>
@@ -3752,6 +3782,31 @@
       <c r="XFC57" s="1"/>
       <c r="XFD57" s="1"/>
     </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="XES58" s="1"/>
+      <c r="XET58" s="1"/>
+      <c r="XEU58" s="1"/>
+      <c r="XEV58" s="1"/>
+      <c r="XEW58" s="1"/>
+      <c r="XEX58" s="1"/>
+      <c r="XEY58" s="1"/>
+      <c r="XEZ58" s="1"/>
+      <c r="XFA58" s="1"/>
+      <c r="XFB58" s="1"/>
+      <c r="XFC58" s="1"/>
+      <c r="XFD58" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
@@ -3766,7 +3821,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD54"/>
+  <dimension ref="A1:XFD55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -3914,7 +3969,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -3926,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>65</v>
@@ -3963,7 +4018,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -3975,7 +4030,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>65</v>
@@ -4012,7 +4067,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -4024,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>73</v>
@@ -4061,7 +4116,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -4073,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>77</v>
@@ -4110,7 +4165,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -4122,7 +4177,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>77</v>
@@ -4159,7 +4214,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -4171,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>84</v>
@@ -4208,7 +4263,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -4220,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>87</v>
@@ -4257,7 +4312,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -4269,7 +4324,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>91</v>
@@ -4306,7 +4361,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -4318,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>95</v>
@@ -4488,7 +4543,7 @@
         <v>2101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -4515,7 +4570,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N20" s="2"/>
       <c r="XES20" s="1"/>
@@ -4538,7 +4593,7 @@
         <v>2102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -4565,7 +4620,7 @@
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N21" s="1"/>
       <c r="XES21" s="1"/>
@@ -4588,7 +4643,7 @@
         <v>2103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -4615,7 +4670,7 @@
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N22" s="1"/>
       <c r="XES22" s="1"/>
@@ -4638,7 +4693,7 @@
         <v>2104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
@@ -4665,7 +4720,7 @@
         <v>5</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N23" s="1"/>
       <c r="XES23" s="1"/>
@@ -4688,7 +4743,7 @@
         <v>2105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -4715,7 +4770,7 @@
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N24" s="1"/>
       <c r="XES24" s="1"/>
@@ -4738,7 +4793,7 @@
         <v>2106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -4765,7 +4820,7 @@
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N25" s="1"/>
       <c r="XES25" s="1"/>
@@ -4788,7 +4843,7 @@
         <v>2107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -4815,7 +4870,7 @@
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N26" s="1"/>
       <c r="XES26" s="1"/>
@@ -4866,7 +4921,7 @@
         <v>2201</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -4893,7 +4948,7 @@
         <v>6</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="N28" s="1"/>
       <c r="XES28" s="1"/>
@@ -4916,7 +4971,7 @@
         <v>2202</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -4943,7 +4998,7 @@
         <v>6</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="N29" s="1"/>
       <c r="XES29" s="1"/>
@@ -4966,7 +5021,7 @@
         <v>2203</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -4993,7 +5048,7 @@
         <v>6</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N30" s="1"/>
       <c r="XES30" s="1"/>
@@ -5013,19 +5068,19 @@
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1">
-        <v>2207</v>
+        <v>2205</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
       </c>
       <c r="F31" s="1">
-        <v>2107</v>
+        <v>2105</v>
       </c>
       <c r="G31" s="1">
-        <v>20072</v>
+        <v>20052</v>
       </c>
       <c r="H31" s="10" t="s">
         <v>103</v>
@@ -5034,16 +5089,16 @@
         <v>99</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>100</v>
+        <v>78</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>110</v>
       </c>
       <c r="L31" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N31" s="1"/>
       <c r="XES31" s="1"/>
@@ -5062,17 +5117,39 @@
     <row r="32" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="6"/>
+      <c r="C32" s="1">
+        <v>2207</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E32" s="1">
+        <v>2</v>
+      </c>
+      <c r="F32" s="1">
+        <v>2107</v>
+      </c>
+      <c r="G32" s="1">
+        <v>20072</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L32" s="1">
+        <v>6</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>180</v>
+      </c>
       <c r="N32" s="1"/>
       <c r="XES32" s="1"/>
       <c r="XET32" s="1"/>
@@ -5090,39 +5167,17 @@
     <row r="33" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
-      <c r="C33" s="1">
-        <v>2302</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33" s="1">
-        <v>2</v>
-      </c>
-      <c r="F33" s="1">
-        <v>2202</v>
-      </c>
-      <c r="G33" s="1">
-        <v>20023</v>
-      </c>
-      <c r="H33" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L33" s="1">
-        <v>6</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>178</v>
-      </c>
+      <c r="C33" s="1"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="6"/>
       <c r="N33" s="1"/>
       <c r="XES33" s="1"/>
       <c r="XET33" s="1"/>
@@ -5137,23 +5192,23 @@
       <c r="XFC33" s="1"/>
       <c r="XFD33" s="1"/>
     </row>
-    <row r="34" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="34" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="F34" s="1">
-        <v>2104</v>
+        <v>2202</v>
       </c>
       <c r="G34" s="1">
-        <v>20043</v>
+        <v>20023</v>
       </c>
       <c r="H34" s="10" t="s">
         <v>106</v>
@@ -5171,7 +5226,7 @@
         <v>6</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N34" s="1"/>
       <c r="XES34" s="1"/>
@@ -5187,29 +5242,29 @@
       <c r="XFC34" s="1"/>
       <c r="XFD34" s="1"/>
     </row>
-    <row r="35" customHeight="1" spans="1:18 16373:16384">
+    <row r="35" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1">
-        <v>2307</v>
+        <v>2304</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="F35" s="1">
-        <v>2207</v>
+        <v>2104</v>
       </c>
       <c r="G35" s="1">
-        <v>20073</v>
+        <v>20043</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>66</v>
@@ -5218,22 +5273,61 @@
         <v>100</v>
       </c>
       <c r="L35" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="1"/>
+      <c r="XES35" s="1"/>
+      <c r="XET35" s="1"/>
+      <c r="XEU35" s="1"/>
+      <c r="XEV35" s="1"/>
+      <c r="XEW35" s="1"/>
+      <c r="XEX35" s="1"/>
+      <c r="XEY35" s="1"/>
+      <c r="XEZ35" s="1"/>
+      <c r="XFA35" s="1"/>
+      <c r="XFB35" s="1"/>
+      <c r="XFC35" s="1"/>
+      <c r="XFD35" s="1"/>
     </row>
     <row r="36" customHeight="1" spans="1:18 16373:16384">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
-      <c r="D36" s="6"/>
-      <c r="M36" s="6"/>
+      <c r="C36" s="1">
+        <v>2307</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" s="1">
+        <v>2</v>
+      </c>
+      <c r="F36" s="1">
+        <v>2207</v>
+      </c>
+      <c r="G36" s="1">
+        <v>20073</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L36" s="1">
+        <v>7</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>186</v>
+      </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="6"/>
@@ -5243,39 +5337,8 @@
     <row r="37" customHeight="1" spans="1:18 16373:16384">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
-      <c r="C37" s="1">
-        <v>2402</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="E37" s="1">
-        <v>2</v>
-      </c>
-      <c r="F37" s="1">
-        <v>2302</v>
-      </c>
-      <c r="G37" s="1">
-        <v>20024</v>
-      </c>
-      <c r="H37" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L37" s="1">
-        <v>7</v>
-      </c>
-      <c r="M37" s="6" t="s">
-        <v>184</v>
-      </c>
+      <c r="D37" s="6"/>
+      <c r="M37" s="6"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="6"/>
@@ -5286,19 +5349,19 @@
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="1">
-        <v>2203</v>
+        <v>2302</v>
       </c>
       <c r="G38" s="1">
-        <v>20034</v>
+        <v>20024</v>
       </c>
       <c r="H38" s="10" t="s">
         <v>106</v>
@@ -5316,7 +5379,7 @@
         <v>7</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -5325,6 +5388,41 @@
       <c r="R38" s="1"/>
     </row>
     <row r="39" customHeight="1" spans="1:18 16373:16384">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1">
+        <v>2403</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E39" s="1">
+        <v>2</v>
+      </c>
+      <c r="F39" s="1">
+        <v>2203</v>
+      </c>
+      <c r="G39" s="1">
+        <v>20034</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L39" s="1">
+        <v>7</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>190</v>
+      </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="6"/>
@@ -5348,46 +5446,23 @@
     <row r="42" customHeight="1" spans="1:18 16373:16384">
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
+      <c r="P42" s="6"/>
       <c r="Q42" s="6"/>
       <c r="R42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="1:18 16373:16384">
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
-      <c r="P43" s="6"/>
+      <c r="P43" s="1"/>
       <c r="Q43" s="6"/>
       <c r="R43" s="1"/>
     </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="2"/>
+    <row r="44" customHeight="1" spans="1:18 16373:16384">
+      <c r="N44" s="1"/>
       <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
+      <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
       <c r="R44" s="1"/>
-      <c r="XES44" s="1"/>
-      <c r="XET44" s="1"/>
-      <c r="XEU44" s="1"/>
-      <c r="XEV44" s="1"/>
-      <c r="XEW44" s="1"/>
-      <c r="XEX44" s="1"/>
-      <c r="XEY44" s="1"/>
-      <c r="XEZ44" s="1"/>
-      <c r="XFA44" s="1"/>
-      <c r="XFB44" s="1"/>
-      <c r="XFC44" s="1"/>
-      <c r="XFD44" s="1"/>
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="C45" s="1"/>
@@ -5403,7 +5478,7 @@
       <c r="M45" s="1"/>
       <c r="N45" s="2"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="6"/>
+      <c r="P45" s="1"/>
       <c r="Q45" s="6"/>
       <c r="R45" s="1"/>
       <c r="XES45" s="1"/>
@@ -5433,7 +5508,7 @@
       <c r="M46" s="1"/>
       <c r="N46" s="2"/>
       <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
+      <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
       <c r="R46" s="1"/>
       <c r="XES46" s="1"/>
@@ -5464,7 +5539,7 @@
       <c r="N47" s="2"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
+      <c r="Q47" s="6"/>
       <c r="R47" s="1"/>
       <c r="XES47" s="1"/>
       <c r="XET47" s="1"/>
@@ -5479,11 +5554,35 @@
       <c r="XFC47" s="1"/>
       <c r="XFD47" s="1"/>
     </row>
-    <row r="48" customHeight="1" spans="1:18 16373:16384">
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
+      <c r="J48" s="1"/>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="2"/>
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
-      <c r="Q48" s="6"/>
+      <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
+      <c r="XES48" s="1"/>
+      <c r="XET48" s="1"/>
+      <c r="XEU48" s="1"/>
+      <c r="XEV48" s="1"/>
+      <c r="XEW48" s="1"/>
+      <c r="XEX48" s="1"/>
+      <c r="XEY48" s="1"/>
+      <c r="XEZ48" s="1"/>
+      <c r="XFA48" s="1"/>
+      <c r="XFB48" s="1"/>
+      <c r="XFC48" s="1"/>
+      <c r="XFD48" s="1"/>
     </row>
     <row r="49" customHeight="1" spans="15:18">
       <c r="O49" s="1"/>
@@ -5500,7 +5599,7 @@
     <row r="51" customHeight="1" spans="15:18">
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
+      <c r="Q51" s="6"/>
       <c r="R51" s="1"/>
     </row>
     <row r="52" customHeight="1" spans="15:18">
@@ -5512,7 +5611,7 @@
     <row r="53" customHeight="1" spans="15:18">
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
-      <c r="Q53" s="6"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
     </row>
     <row r="54" customHeight="1" spans="15:18">
@@ -5520,6 +5619,12 @@
       <c r="P54" s="1"/>
       <c r="Q54" s="6"/>
       <c r="R54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="15:18">
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="6"/>
+      <c r="R55" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -5535,7 +5640,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD62"/>
+  <dimension ref="A1:XFD63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -5681,7 +5786,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -5709,7 +5814,7 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -5717,7 +5822,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -5745,7 +5850,7 @@
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -5753,7 +5858,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -5786,7 +5891,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -5798,7 +5903,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>77</v>
@@ -5819,7 +5924,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -5831,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>77</v>
@@ -5852,7 +5957,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -5864,7 +5969,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>84</v>
@@ -5885,7 +5990,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -5897,7 +6002,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="I12" s="10" t="s">
         <v>87</v>
@@ -5918,7 +6023,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -5930,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I13" s="10" t="s">
         <v>91</v>
@@ -5951,7 +6056,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -5963,7 +6068,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="I14" s="10" t="s">
         <v>95</v>
@@ -6014,7 +6119,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -6041,7 +6146,7 @@
         <v>5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -6050,7 +6155,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -6077,7 +6182,7 @@
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -6086,7 +6191,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -6113,7 +6218,7 @@
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -6122,7 +6227,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -6149,7 +6254,7 @@
         <v>5</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -6158,7 +6263,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -6185,7 +6290,7 @@
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -6194,7 +6299,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -6221,7 +6326,7 @@
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -6230,7 +6335,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -6257,7 +6362,7 @@
         <v>5</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -6269,7 +6374,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -6296,7 +6401,7 @@
         <v>6</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -6305,7 +6410,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -6332,7 +6437,7 @@
         <v>6</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N33" s="2"/>
     </row>
@@ -6341,7 +6446,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -6368,73 +6473,73 @@
         <v>6</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="N34" s="2"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C35" s="1">
+        <v>3205</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" s="1">
+        <v>3</v>
+      </c>
+      <c r="F35" s="1">
+        <v>3105</v>
+      </c>
+      <c r="G35" s="1">
+        <v>30052</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L35" s="1">
+        <v>5</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>229</v>
+      </c>
       <c r="N35" s="2"/>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C36" s="1">
-        <v>3302</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="E36" s="1">
-        <v>3</v>
-      </c>
-      <c r="F36" s="1">
-        <v>3202</v>
-      </c>
-      <c r="G36" s="1">
-        <v>30023</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L36" s="1">
-        <v>6</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="N36" s="2"/>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C37" s="1">
-        <v>3303</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>226</v>
+        <v>3302</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
       </c>
       <c r="F37" s="1">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="G37" s="1">
-        <v>30033</v>
+        <v>30023</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>100</v>
@@ -6442,32 +6547,32 @@
       <c r="L37" s="1">
         <v>6</v>
       </c>
-      <c r="M37" s="2" t="s">
-        <v>227</v>
+      <c r="M37" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="N37" s="2"/>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C38" s="1">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
       </c>
       <c r="F38" s="1">
-        <v>3104</v>
+        <v>3203</v>
       </c>
       <c r="G38" s="1">
-        <v>30043</v>
+        <v>30033</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J38" s="10" t="s">
         <v>66</v>
@@ -6479,31 +6584,31 @@
         <v>6</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N38" s="2"/>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C39" s="1">
-        <v>3307</v>
+        <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
       </c>
       <c r="F39" s="1">
-        <v>3107</v>
+        <v>3104</v>
       </c>
       <c r="G39" s="1">
-        <v>30073</v>
+        <v>30043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J39" s="10" t="s">
         <v>66</v>
@@ -6515,74 +6620,72 @@
         <v>6</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="N39" s="2"/>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="D40" s="2"/>
-      <c r="M40" s="2"/>
+      <c r="C40" s="1">
+        <v>3307</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E40" s="1">
+        <v>3</v>
+      </c>
+      <c r="F40" s="1">
+        <v>3107</v>
+      </c>
+      <c r="G40" s="1">
+        <v>30073</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L40" s="1">
+        <v>6</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>237</v>
+      </c>
       <c r="N40" s="2"/>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C41" s="1">
+      <c r="D41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C42" s="1">
         <v>3402</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E41" s="1">
-        <v>3</v>
-      </c>
-      <c r="F41" s="1">
-        <v>3302</v>
-      </c>
-      <c r="G41" s="1">
-        <v>30024</v>
-      </c>
-      <c r="H41" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L41" s="1">
-        <v>7</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="N41" s="2"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:14 16373:16384">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1">
-        <v>3403</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>234</v>
+      <c r="D42" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
       </c>
       <c r="F42" s="1">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="G42" s="1">
-        <v>30034</v>
+        <v>30024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="J42" s="10" t="s">
         <v>66</v>
@@ -6593,35 +6696,47 @@
       <c r="L42" s="1">
         <v>7</v>
       </c>
-      <c r="M42" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="1"/>
-      <c r="XES43" s="1"/>
-      <c r="XET43" s="1"/>
-      <c r="XEU43" s="1"/>
-      <c r="XEV43" s="1"/>
-      <c r="XEW43" s="1"/>
-      <c r="XEX43" s="1"/>
-      <c r="XEY43" s="1"/>
-      <c r="XEZ43" s="1"/>
-      <c r="XFA43" s="1"/>
-      <c r="XFB43" s="1"/>
-      <c r="XFC43" s="1"/>
-      <c r="XFD43" s="1"/>
+      <c r="M42" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="N42" s="2"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:14 16373:16384">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1">
+        <v>3403</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E43" s="1">
+        <v>3</v>
+      </c>
+      <c r="F43" s="1">
+        <v>3303</v>
+      </c>
+      <c r="G43" s="1">
+        <v>30034</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L43" s="1">
+        <v>7</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C44" s="1"/>
@@ -6634,7 +6749,7 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
+      <c r="M44" s="6"/>
       <c r="N44" s="1"/>
       <c r="XES44" s="1"/>
       <c r="XET44" s="1"/>
@@ -6649,55 +6764,56 @@
       <c r="XFC44" s="1"/>
       <c r="XFD44" s="1"/>
     </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="XES46" s="1"/>
-      <c r="XET46" s="1"/>
-      <c r="XEU46" s="1"/>
-      <c r="XEV46" s="1"/>
-      <c r="XEW46" s="1"/>
-      <c r="XEX46" s="1"/>
-      <c r="XEY46" s="1"/>
-      <c r="XEZ46" s="1"/>
-      <c r="XFA46" s="1"/>
-      <c r="XFB46" s="1"/>
-      <c r="XFC46" s="1"/>
-      <c r="XFD46" s="1"/>
-    </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="XES57" s="1"/>
-      <c r="XET57" s="1"/>
-      <c r="XEU57" s="1"/>
-      <c r="XEV57" s="1"/>
-      <c r="XEW57" s="1"/>
-      <c r="XEX57" s="1"/>
-      <c r="XEY57" s="1"/>
-      <c r="XEZ57" s="1"/>
-      <c r="XFA57" s="1"/>
-      <c r="XFB57" s="1"/>
-      <c r="XFC57" s="1"/>
-      <c r="XFD57" s="1"/>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="XES45" s="1"/>
+      <c r="XET45" s="1"/>
+      <c r="XEU45" s="1"/>
+      <c r="XEV45" s="1"/>
+      <c r="XEW45" s="1"/>
+      <c r="XEX45" s="1"/>
+      <c r="XEY45" s="1"/>
+      <c r="XEZ45" s="1"/>
+      <c r="XFA45" s="1"/>
+      <c r="XFB45" s="1"/>
+      <c r="XFC45" s="1"/>
+      <c r="XFD45" s="1"/>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+      <c r="K47" s="1"/>
+      <c r="L47" s="1"/>
+      <c r="M47" s="1"/>
+      <c r="XES47" s="1"/>
+      <c r="XET47" s="1"/>
+      <c r="XEU47" s="1"/>
+      <c r="XEV47" s="1"/>
+      <c r="XEW47" s="1"/>
+      <c r="XEX47" s="1"/>
+      <c r="XEY47" s="1"/>
+      <c r="XEZ47" s="1"/>
+      <c r="XFA47" s="1"/>
+      <c r="XFB47" s="1"/>
+      <c r="XFC47" s="1"/>
+      <c r="XFD47" s="1"/>
     </row>
     <row r="58" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
       <c r="C58" s="1"/>
@@ -6824,6 +6940,31 @@
       <c r="XFC62" s="1"/>
       <c r="XFD62" s="1"/>
     </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="XES63" s="1"/>
+      <c r="XET63" s="1"/>
+      <c r="XEU63" s="1"/>
+      <c r="XEV63" s="1"/>
+      <c r="XEW63" s="1"/>
+      <c r="XEX63" s="1"/>
+      <c r="XEY63" s="1"/>
+      <c r="XEZ63" s="1"/>
+      <c r="XFA63" s="1"/>
+      <c r="XFB63" s="1"/>
+      <c r="XFC63" s="1"/>
+      <c r="XFD63" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="278">
   <si>
     <t>#</t>
   </si>
@@ -80,133 +80,178 @@
     <t>int[]</t>
   </si>
   <si>
+    <t>妙手扳指</t>
+  </si>
+  <si>
+    <t>85,3,95</t>
+  </si>
+  <si>
+    <t>20,100,1</t>
+  </si>
+  <si>
+    <t>40000001,40000002,40000003</t>
+  </si>
+  <si>
+    <t>25,3,1</t>
+  </si>
+  <si>
+    <t>没有特殊效果</t>
+  </si>
+  <si>
+    <t>杀怪金币</t>
+  </si>
+  <si>
+    <t>修行符</t>
+  </si>
+  <si>
+    <t>86,3,95</t>
+  </si>
+  <si>
+    <t>40000004,40000005,40000006</t>
+  </si>
+  <si>
+    <t>杀怪经验</t>
+  </si>
+  <si>
+    <t>妙手布鞋</t>
+  </si>
+  <si>
+    <t>85,1003,95</t>
+  </si>
+  <si>
+    <t>40,5,2</t>
+  </si>
+  <si>
+    <t>40000007,40000008,40000009</t>
+  </si>
+  <si>
+    <t>50,6,2</t>
+  </si>
+  <si>
+    <t>修行手册</t>
+  </si>
+  <si>
+    <t>86,1003,95</t>
+  </si>
+  <si>
+    <t>40000010,40000011,40000012</t>
+  </si>
+  <si>
     <t>铜钱袋</t>
   </si>
   <si>
+    <t>81,27,95</t>
+  </si>
+  <si>
+    <t>3,3,2</t>
+  </si>
+  <si>
+    <t>75,9,3</t>
+  </si>
+  <si>
+    <t>金币加成</t>
+  </si>
+  <si>
+    <t>试炼卷轴</t>
+  </si>
+  <si>
+    <t>82,27,95</t>
+  </si>
+  <si>
+    <t>经验加成</t>
+  </si>
+  <si>
+    <t>寻金符</t>
+  </si>
+  <si>
+    <t>83,27,95</t>
+  </si>
+  <si>
+    <t>爆率加成</t>
+  </si>
+  <si>
+    <t>四叶草</t>
+  </si>
+  <si>
+    <t>84,27,95</t>
+  </si>
+  <si>
+    <t>品质加成</t>
+  </si>
+  <si>
+    <t>招财挂坠</t>
+  </si>
+  <si>
     <t>81,21,95</t>
   </si>
   <si>
+    <t>3,2,1</t>
+  </si>
+  <si>
+    <t>40000001,40000002,40000002</t>
+  </si>
+  <si>
+    <t>10,3,1</t>
+  </si>
+  <si>
+    <t>经验符</t>
+  </si>
+  <si>
+    <t>82,22,95</t>
+  </si>
+  <si>
+    <t>聚宝盆</t>
+  </si>
+  <si>
+    <t>83,23,95</t>
+  </si>
+  <si>
+    <t>幸运符</t>
+  </si>
+  <si>
+    <t>84,24,95</t>
+  </si>
+  <si>
+    <t>神偷护符</t>
+  </si>
+  <si>
+    <t>85,27,95</t>
+  </si>
+  <si>
+    <t>30,3,1</t>
+  </si>
+  <si>
+    <t>40000005,40000008,40000011</t>
+  </si>
+  <si>
+    <t>3,3,3</t>
+  </si>
+  <si>
+    <t>历练帖</t>
+  </si>
+  <si>
+    <t>86,28,95</t>
+  </si>
+  <si>
+    <t>40000006,40000009,40000012</t>
+  </si>
+  <si>
     <t>1,1,1</t>
   </si>
   <si>
-    <t>40000001,40000002,40000002</t>
-  </si>
-  <si>
-    <t>10,3,1</t>
-  </si>
-  <si>
-    <t>没有特殊效果</t>
-  </si>
-  <si>
-    <t>金币加成</t>
-  </si>
-  <si>
-    <t>试炼卷轴</t>
-  </si>
-  <si>
-    <t>82,22,95</t>
-  </si>
-  <si>
-    <t>40000004,40000005,40000006</t>
-  </si>
-  <si>
-    <t>经验加成</t>
-  </si>
-  <si>
-    <t>寻金符</t>
-  </si>
-  <si>
-    <t>83,23,95</t>
-  </si>
-  <si>
-    <t>40000007,40000008,40000009</t>
-  </si>
-  <si>
-    <t>爆率加成</t>
-  </si>
-  <si>
-    <t>四叶草</t>
-  </si>
-  <si>
-    <t>84,24,95</t>
-  </si>
-  <si>
-    <t>40000010,40000011,40000012</t>
-  </si>
-  <si>
-    <t>品质加成</t>
-  </si>
-  <si>
-    <t>妙手扳指</t>
-  </si>
-  <si>
-    <t>85,27,95</t>
-  </si>
-  <si>
-    <t>10,1,1</t>
-  </si>
-  <si>
-    <t>40000002,40000005,40000008</t>
-  </si>
-  <si>
-    <t>3,3,3</t>
-  </si>
-  <si>
-    <t>杀怪金币</t>
-  </si>
-  <si>
-    <t>修行符</t>
-  </si>
-  <si>
-    <t>86,28,95</t>
+    <t>聚兽铜印</t>
+  </si>
+  <si>
+    <t>2003,111,95</t>
+  </si>
+  <si>
+    <t>5,1,5</t>
   </si>
   <si>
     <t>40000003,40000006,40000009</t>
   </si>
   <si>
-    <t>杀怪经验</t>
-  </si>
-  <si>
-    <t>招财挂坠</t>
-  </si>
-  <si>
-    <t>3,2,1</t>
-  </si>
-  <si>
-    <t>经验符</t>
-  </si>
-  <si>
-    <t>聚宝盆</t>
-  </si>
-  <si>
-    <t>幸运符</t>
-  </si>
-  <si>
-    <t>神偷护符</t>
-  </si>
-  <si>
-    <t>30,3,1</t>
-  </si>
-  <si>
-    <t>40000005,40000008,40000011</t>
-  </si>
-  <si>
-    <t>历练帖</t>
-  </si>
-  <si>
-    <t>40000006,40000009,40000012</t>
-  </si>
-  <si>
-    <t>聚兽铜印</t>
-  </si>
-  <si>
-    <t>2001,111,95</t>
-  </si>
-  <si>
-    <t>5,1,2</t>
-  </si>
-  <si>
-    <t>2,2,2</t>
+    <t>15,15,15</t>
   </si>
   <si>
     <t>增加一个宠物备战位</t>
@@ -218,120 +263,174 @@
     <t>2003,112,95</t>
   </si>
   <si>
+    <t>10,1,10</t>
+  </si>
+  <si>
+    <t>40000012,40000015,40000018</t>
+  </si>
+  <si>
+    <t>30,30,30</t>
+  </si>
+  <si>
     <t>增加一个宠物备出战位</t>
   </si>
   <si>
+    <t>技能手册</t>
+  </si>
+  <si>
+    <t>2003,113,95</t>
+  </si>
+  <si>
+    <t>增加一个技能出站栏位</t>
+  </si>
+  <si>
+    <t>神灵印记</t>
+  </si>
+  <si>
+    <t>2003,114,95</t>
+  </si>
+  <si>
+    <t>技能词条套装所需数量-1</t>
+  </si>
+  <si>
+    <t>装备词条套装所需数量-1</t>
+  </si>
+  <si>
     <t>粗铁刀</t>
   </si>
   <si>
-    <t>3,4,95</t>
-  </si>
-  <si>
-    <t>50,100,1</t>
+    <t>4,3,95</t>
+  </si>
+  <si>
+    <t>100,100,1</t>
+  </si>
+  <si>
+    <t>物攻基础</t>
+  </si>
+  <si>
+    <t>粗铁剑</t>
+  </si>
+  <si>
+    <t>1004,3,95</t>
+  </si>
+  <si>
+    <t>5,300,1</t>
+  </si>
+  <si>
+    <t>物攻加成</t>
+  </si>
+  <si>
+    <t>粗铁斧</t>
+  </si>
+  <si>
+    <t>1007,27,95</t>
+  </si>
+  <si>
+    <t>5,5,2</t>
+  </si>
+  <si>
+    <t>物伤加成</t>
+  </si>
+  <si>
+    <t>粗铁枪</t>
+  </si>
+  <si>
+    <t>2007,27,95</t>
+  </si>
+  <si>
+    <t>100,12,4</t>
+  </si>
+  <si>
+    <t>物攻增幅</t>
+  </si>
+  <si>
+    <t>黑铁指环</t>
+  </si>
+  <si>
+    <t>2,1004,95</t>
+  </si>
+  <si>
+    <t>100,5,1</t>
+  </si>
+  <si>
+    <t>40000001,40000003</t>
+  </si>
+  <si>
+    <t>100,1</t>
+  </si>
+  <si>
+    <t>黑铁头盔</t>
+  </si>
+  <si>
+    <t>1,1004,95</t>
+  </si>
+  <si>
+    <t>2000,5,1</t>
+  </si>
+  <si>
+    <t>40000004,40000005</t>
+  </si>
+  <si>
+    <t>凌风长剑</t>
+  </si>
+  <si>
+    <t>1003,1004,95</t>
+  </si>
+  <si>
+    <t>5,10,1</t>
+  </si>
+  <si>
+    <t>40000007,40000008</t>
+  </si>
+  <si>
+    <t>10,2</t>
+  </si>
+  <si>
+    <t>古铜戒指</t>
+  </si>
+  <si>
+    <t>1002,1004,95</t>
+  </si>
+  <si>
+    <t>10,10,1</t>
+  </si>
+  <si>
+    <t>40000005,40000007</t>
+  </si>
+  <si>
+    <t>古铜项链</t>
+  </si>
+  <si>
+    <t>1001,1004,95</t>
+  </si>
+  <si>
+    <t>20,10,1</t>
+  </si>
+  <si>
+    <t>40000008,40000009</t>
+  </si>
+  <si>
+    <t>法系技能全等级+1</t>
+  </si>
+  <si>
+    <t>法系技能攻速+5%</t>
+  </si>
+  <si>
+    <t>法系技能冷却+5%</t>
+  </si>
+  <si>
+    <t>基础战体</t>
+  </si>
+  <si>
+    <t>3,6,95</t>
+  </si>
+  <si>
+    <t>100,200,1</t>
   </si>
   <si>
     <t>40000001,40000002</t>
   </si>
   <si>
-    <t>50,5</t>
-  </si>
-  <si>
-    <t>硬皮甲</t>
-  </si>
-  <si>
-    <t>2,4,95</t>
-  </si>
-  <si>
-    <t>40000004,40000005</t>
-  </si>
-  <si>
-    <t>硬皮靴</t>
-  </si>
-  <si>
-    <t>1,4,95</t>
-  </si>
-  <si>
-    <t>1000,100,1</t>
-  </si>
-  <si>
-    <t>40000007,40000008</t>
-  </si>
-  <si>
-    <t>黑铁护腕</t>
-  </si>
-  <si>
-    <t>3,1004,95</t>
-  </si>
-  <si>
-    <t>100,5,1</t>
-  </si>
-  <si>
-    <t>40000001,40000003</t>
-  </si>
-  <si>
-    <t>100,1</t>
-  </si>
-  <si>
-    <t>黑铁指环</t>
-  </si>
-  <si>
-    <t>2,1004,95</t>
-  </si>
-  <si>
-    <t>黑铁头盔</t>
-  </si>
-  <si>
-    <t>1,1004,95</t>
-  </si>
-  <si>
-    <t>2000,5,1</t>
-  </si>
-  <si>
-    <t>凌风长剑</t>
-  </si>
-  <si>
-    <t>1003,1004,95</t>
-  </si>
-  <si>
-    <t>5,10,1</t>
-  </si>
-  <si>
-    <t>10,2</t>
-  </si>
-  <si>
-    <t>古铜戒指</t>
-  </si>
-  <si>
-    <t>1002,1004,95</t>
-  </si>
-  <si>
-    <t>10,10,1</t>
-  </si>
-  <si>
-    <t>40000005,40000007</t>
-  </si>
-  <si>
-    <t>古铜项链</t>
-  </si>
-  <si>
-    <t>1001,1004,95</t>
-  </si>
-  <si>
-    <t>20,10,1</t>
-  </si>
-  <si>
-    <t>40000008,40000009</t>
-  </si>
-  <si>
-    <t>基础战体</t>
-  </si>
-  <si>
-    <t>3,6,95</t>
-  </si>
-  <si>
-    <t>100,200,1</t>
-  </si>
-  <si>
     <t>100,10</t>
   </si>
   <si>
@@ -452,25 +551,25 @@
     <t>乌木杖</t>
   </si>
   <si>
-    <t>3,5,95</t>
-  </si>
-  <si>
-    <t>软布衣</t>
-  </si>
-  <si>
-    <t>2,5,95</t>
-  </si>
-  <si>
-    <t>软布鞋</t>
-  </si>
-  <si>
-    <t>1,5,95</t>
-  </si>
-  <si>
-    <t>桃木护腕</t>
-  </si>
-  <si>
-    <t>3,1005,95</t>
+    <t>5,3,95</t>
+  </si>
+  <si>
+    <t>乌木戒</t>
+  </si>
+  <si>
+    <t>1005,3,95</t>
+  </si>
+  <si>
+    <t>乌木坠</t>
+  </si>
+  <si>
+    <t>1008,27,95</t>
+  </si>
+  <si>
+    <t>乌木佩</t>
+  </si>
+  <si>
+    <t>2008,27,95</t>
   </si>
   <si>
     <t>桃木指环</t>
@@ -605,25 +704,34 @@
     <t>火狱阵法·疾风</t>
   </si>
   <si>
-    <t>竹节剑</t>
+    <t>青竹剑</t>
+  </si>
+  <si>
+    <t>6,3,95</t>
   </si>
   <si>
     <t>道攻加成</t>
   </si>
   <si>
-    <t>粗麻袍</t>
+    <t>青竹罗盘</t>
+  </si>
+  <si>
+    <t>1006,3,95</t>
   </si>
   <si>
     <t>道伤加成</t>
   </si>
   <si>
-    <t>粗麻靴</t>
-  </si>
-  <si>
-    <t>青竹护腕</t>
-  </si>
-  <si>
-    <t>3,1006,95</t>
+    <t>桃木剑</t>
+  </si>
+  <si>
+    <t>1009,27,95</t>
+  </si>
+  <si>
+    <t>桃木罗盘</t>
+  </si>
+  <si>
+    <t>2009,27,95</t>
   </si>
   <si>
     <t>青竹指环</t>
@@ -1737,7 +1845,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1745,8 +1853,9 @@
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
     <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.5" style="1" customWidth="1"/>
-    <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.5833333333333" style="1" customWidth="1"/>
+    <col min="11" max="12" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="20.6666666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
     <col min="15" max="16372" width="9" style="2"/>
     <col min="16373" max="16384" width="9" style="1"/>
@@ -1919,7 +2028,7 @@
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="7" t="s">
         <v>23</v>
       </c>
       <c r="E7" s="1">
@@ -1957,7 +2066,7 @@
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="5" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="1">
@@ -1973,13 +2082,13 @@
         <v>28</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -1988,36 +2097,36 @@
         <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>31</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>20</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
@@ -2026,7 +2135,7 @@
         <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2052,10 +2161,10 @@
         <v>37</v>
       </c>
       <c r="J10" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="10" t="s">
         <v>38</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>39</v>
       </c>
       <c r="L10" s="1">
         <v>3</v>
@@ -2064,36 +2173,36 @@
         <v>21</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>42</v>
       </c>
       <c r="I11" s="10" t="s">
         <v>37</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="L11" s="1">
         <v>3</v>
@@ -2102,179 +2211,109 @@
         <v>21</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>45</v>
+      <c r="D12" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="L12" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="1">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>24</v>
-      </c>
       <c r="I13" s="10" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="L13" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="1">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1">
-        <v>3</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="L14" s="1">
-        <v>4</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="9" t="s">
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>7</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1">
-        <v>4</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K15" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="L15" s="1">
-        <v>4</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
-        <v>5</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>36</v>
       </c>
       <c r="I16" s="10" t="s">
         <v>51</v>
@@ -2283,7 +2322,7 @@
         <v>52</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L16" s="1">
         <v>4</v>
@@ -2292,36 +2331,42 @@
         <v>21</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C17" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>51</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="L17" s="1">
         <v>4</v>
@@ -2330,99 +2375,352 @@
         <v>21</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C18" s="1">
-        <v>13</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>55</v>
+        <v>9</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="K18" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="1">
+        <v>4</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>10</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="L18" s="1">
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1">
+        <v>4</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L19" s="1">
+        <v>4</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>11</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1">
         <v>5</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1">
-        <v>13</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="10" t="s">
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L19" s="1">
+      <c r="I20" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="L20" s="1">
+        <v>4</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>12</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1">
+        <v>6</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L21" s="1">
+        <v>4</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C23" s="1">
+        <v>101</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="L23" s="1">
         <v>5</v>
       </c>
-      <c r="M19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1"/>
-    <row r="21" s="1" customFormat="1" customHeight="1"/>
-    <row r="22" s="1" customFormat="1" customHeight="1"/>
-    <row r="23" s="1" customFormat="1" customHeight="1"/>
-    <row r="24" s="1" customFormat="1" customHeight="1"/>
-    <row r="25" s="1" customFormat="1" customHeight="1"/>
-    <row r="26" s="1" customFormat="1" customHeight="1"/>
+      <c r="M23" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C24" s="1">
+        <v>102</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1">
+        <v>101</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L24" s="1">
+        <v>6</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C25" s="1">
+        <v>103</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="L25" s="1">
+        <v>5</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C26" s="1">
+        <v>104</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="L26" s="1">
+        <v>6</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
     <row r="28" s="1" customFormat="1" customHeight="1"/>
-    <row r="30" customHeight="1" spans="3:14">
-      <c r="N30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:14">
-      <c r="N31" s="1"/>
+    <row r="29" s="1" customFormat="1" customHeight="1"/>
+    <row r="30" s="1" customFormat="1" customHeight="1"/>
+    <row r="31" s="1" customFormat="1" customHeight="1"/>
+    <row r="32" s="1" customFormat="1" customHeight="1"/>
+    <row r="33" s="1" customFormat="1" customHeight="1"/>
+    <row r="35" customHeight="1" spans="14:14">
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" customHeight="1" spans="14:14">
+      <c r="N36" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2438,7 +2736,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD58"/>
+  <dimension ref="A1:XFD59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2446,7 +2744,7 @@
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
     <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.75" style="1" customWidth="1"/>
     <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
     <col min="15" max="16372" width="9" style="2"/>
@@ -2583,7 +2881,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -2595,22 +2893,25 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2618,7 +2919,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -2630,22 +2931,25 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2653,7 +2957,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2665,22 +2969,25 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2688,7 +2995,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -2700,16 +3007,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -2717,13 +3024,22 @@
       <c r="M9" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="N9" s="1" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C10" s="1">
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -2735,16 +3051,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -2754,11 +3070,17 @@
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C11" s="1">
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -2770,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -2789,11 +3111,17 @@
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C12" s="1">
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -2805,16 +3133,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -2824,11 +3152,17 @@
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C13" s="1">
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -2840,16 +3174,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -2859,11 +3193,17 @@
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C14" s="1">
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -2875,16 +3215,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -2894,53 +3234,54 @@
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
-    <row r="16" s="1" customFormat="1" customHeight="1"/>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="D17" s="4"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1"/>
+      <c r="M17" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C20" s="1">
+    <row r="20" s="1" customFormat="1" customHeight="1"/>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1">
         <v>1101</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
-      <c r="G20" s="1">
-        <v>10011</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="L20" s="1">
-        <v>5</v>
-      </c>
-      <c r="M20" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C21" s="1">
-        <v>1102</v>
-      </c>
       <c r="D21" s="6" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -2949,33 +3290,39 @@
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>10021</v>
+        <v>10011</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:18">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C22" s="1">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -2984,33 +3331,39 @@
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>10031</v>
+        <v>10021</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:18">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C23" s="1">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3019,33 +3372,39 @@
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>10041</v>
+        <v>10031</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:18">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C24" s="1">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3054,33 +3413,39 @@
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>10051</v>
+        <v>10041</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:18">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C25" s="1">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3089,33 +3454,39 @@
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>10061</v>
+        <v>10051</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="I25" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="J25" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="J25" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="K25" s="10" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:18">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C26" s="1">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3124,451 +3495,536 @@
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>10071</v>
+        <v>10061</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="R26" s="6"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="D27" s="6"/>
-      <c r="M27" s="6"/>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1107</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>10071</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="L27" s="1">
+        <v>5</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>151</v>
+      </c>
       <c r="R27" s="6"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C28" s="1">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="R28" s="6"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="1">
         <v>1201</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1101</v>
-      </c>
-      <c r="G28" s="1">
-        <v>10012</v>
-      </c>
-      <c r="H28" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="L28" s="1">
-        <v>6</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="R28" s="6"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:18">
-      <c r="C29" s="1">
-        <v>1202</v>
-      </c>
       <c r="D29" s="6" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G29" s="1">
-        <v>10022</v>
+        <v>10012</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>106</v>
+        <v>136</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="L29" s="1">
         <v>6</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="R29" s="6"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C30" s="1">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G30" s="1">
-        <v>10032</v>
+        <v>10022</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>100</v>
+        <v>125</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>150</v>
       </c>
       <c r="L30" s="1">
         <v>6</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="O30" s="6"/>
-      <c r="P30" s="1"/>
+        <v>155</v>
+      </c>
       <c r="R30" s="6"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C31" s="1">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>125</v>
+        <v>156</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="G31" s="1">
-        <v>10042</v>
+        <v>10032</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L31" s="1">
         <v>6</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="1"/>
       <c r="R31" s="6"/>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:18">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:18">
+      <c r="A32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C32" s="1">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="G32" s="1">
-        <v>10052</v>
+        <v>10042</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>110</v>
+        <v>132</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="L32" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>128</v>
+        <v>159</v>
       </c>
       <c r="O32" s="6"/>
+      <c r="P32" s="1"/>
       <c r="R32" s="6"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C33" s="1">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>129</v>
+        <v>160</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1">
+        <v>1105</v>
+      </c>
+      <c r="G33" s="1">
+        <v>10052</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="L33" s="1">
+        <v>5</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="O33" s="6"/>
+      <c r="R33" s="6"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1207</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="E34" s="1">
+        <v>1</v>
+      </c>
+      <c r="F34" s="1">
         <v>1107</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G34" s="1">
         <v>10072</v>
       </c>
-      <c r="H33" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L33" s="1">
+      <c r="H34" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L34" s="1">
         <v>6</v>
       </c>
-      <c r="M33" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="O33" s="6"/>
-      <c r="P33" s="1"/>
-      <c r="R33" s="6"/>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="D34" s="6"/>
-      <c r="M34" s="6"/>
+      <c r="M34" s="6" t="s">
+        <v>163</v>
+      </c>
       <c r="O34" s="6"/>
+      <c r="P34" s="1"/>
       <c r="R34" s="6"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C35" s="1">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="R35" s="6"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" s="1">
         <v>1302</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1202</v>
-      </c>
-      <c r="G35" s="1">
-        <v>10023</v>
-      </c>
-      <c r="H35" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L35" s="1">
-        <v>6</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="O35" s="6"/>
-      <c r="P35" s="1"/>
-      <c r="R35" s="6"/>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C36" s="1">
-        <v>1307</v>
-      </c>
       <c r="D36" s="6" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
       </c>
       <c r="F36" s="1">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="G36" s="1">
-        <v>10073</v>
+        <v>10023</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L36" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>134</v>
+        <v>165</v>
       </c>
       <c r="O36" s="6"/>
       <c r="P36" s="1"/>
       <c r="R36" s="6"/>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="D37" s="6"/>
-      <c r="M37" s="6"/>
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1307</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E37" s="1">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1">
+        <v>1207</v>
+      </c>
+      <c r="G37" s="1">
+        <v>10073</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L37" s="1">
+        <v>7</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>167</v>
+      </c>
       <c r="O37" s="6"/>
+      <c r="P37" s="1"/>
       <c r="R37" s="6"/>
     </row>
-    <row r="38" customHeight="1" spans="1:19 16373:16384">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1">
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="R38" s="6"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:19 16373:16384">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1">
         <v>1402</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1">
-        <v>1302</v>
-      </c>
-      <c r="G38" s="1">
-        <v>10024</v>
-      </c>
-      <c r="H38" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L38" s="1">
-        <v>7</v>
-      </c>
-      <c r="M38" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="S38" s="1"/>
-    </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1">
-        <v>1403</v>
-      </c>
       <c r="D39" s="6" t="s">
-        <v>137</v>
+        <v>168</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
       </c>
       <c r="F39" s="1">
-        <v>1203</v>
+        <v>1302</v>
       </c>
       <c r="G39" s="1">
-        <v>10034</v>
+        <v>10024</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L39" s="1">
         <v>7</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="6"/>
+        <v>169</v>
+      </c>
+      <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
       <c r="S39" s="1"/>
-      <c r="XES39" s="1"/>
-      <c r="XET39" s="1"/>
-      <c r="XEU39" s="1"/>
-      <c r="XEV39" s="1"/>
-      <c r="XEW39" s="1"/>
-      <c r="XEX39" s="1"/>
-      <c r="XEY39" s="1"/>
-      <c r="XEZ39" s="1"/>
-      <c r="XFA39" s="1"/>
-      <c r="XFB39" s="1"/>
-      <c r="XFC39" s="1"/>
-      <c r="XFD39" s="1"/>
     </row>
     <row r="40" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C40" s="1"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1403</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1203</v>
+      </c>
+      <c r="G40" s="1">
+        <v>10034</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L40" s="1">
+        <v>7</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>171</v>
+      </c>
       <c r="N40" s="1"/>
       <c r="O40" s="6"/>
       <c r="P40" s="1"/>
@@ -3587,50 +4043,76 @@
       <c r="XFC40" s="1"/>
       <c r="XFD40" s="1"/>
     </row>
-    <row r="41" customHeight="1" spans="1:19 16373:16384">
-      <c r="O41" s="1"/>
+    <row r="41" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="C41" s="1"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="6"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
       <c r="S41" s="1"/>
-    </row>
-    <row r="42" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="O42" s="6"/>
+      <c r="XES41" s="1"/>
+      <c r="XET41" s="1"/>
+      <c r="XEU41" s="1"/>
+      <c r="XEV41" s="1"/>
+      <c r="XEW41" s="1"/>
+      <c r="XEX41" s="1"/>
+      <c r="XEY41" s="1"/>
+      <c r="XEZ41" s="1"/>
+      <c r="XFA41" s="1"/>
+      <c r="XFB41" s="1"/>
+      <c r="XFC41" s="1"/>
+      <c r="XFD41" s="1"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:19 16373:16384">
+      <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
       <c r="S42" s="1"/>
-      <c r="XES42" s="1"/>
-      <c r="XET42" s="1"/>
-      <c r="XEU42" s="1"/>
-      <c r="XEV42" s="1"/>
-      <c r="XEW42" s="1"/>
-      <c r="XEX42" s="1"/>
-      <c r="XEY42" s="1"/>
-      <c r="XEZ42" s="1"/>
-      <c r="XFA42" s="1"/>
-      <c r="XFB42" s="1"/>
-      <c r="XFC42" s="1"/>
-      <c r="XFD42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:19 16373:16384">
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
       <c r="O43" s="6"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
       <c r="S43" s="1"/>
+      <c r="XES43" s="1"/>
+      <c r="XET43" s="1"/>
+      <c r="XEU43" s="1"/>
+      <c r="XEV43" s="1"/>
+      <c r="XEW43" s="1"/>
+      <c r="XEX43" s="1"/>
+      <c r="XEY43" s="1"/>
+      <c r="XEZ43" s="1"/>
+      <c r="XFA43" s="1"/>
+      <c r="XFB43" s="1"/>
+      <c r="XFC43" s="1"/>
+      <c r="XFD43" s="1"/>
     </row>
     <row r="44" customHeight="1" spans="1:19 16373:16384">
+      <c r="O44" s="6"/>
+      <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
       <c r="S44" s="1"/>
     </row>
     <row r="45" customHeight="1" spans="1:19 16373:16384">
@@ -3638,51 +4120,30 @@
       <c r="S45" s="1"/>
     </row>
     <row r="46" customHeight="1" spans="1:19 16373:16384">
-      <c r="O46" s="1"/>
       <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
       <c r="S46" s="1"/>
     </row>
     <row r="47" customHeight="1" spans="1:19 16373:16384">
+      <c r="O47" s="1"/>
       <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
       <c r="S47" s="1"/>
     </row>
     <row r="48" customHeight="1" spans="1:19 16373:16384">
       <c r="Q48" s="1"/>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" customHeight="1" spans="3:17 16373:16384">
+    <row r="49" customHeight="1" spans="3:19 16373:16384">
       <c r="Q49" s="1"/>
-    </row>
-    <row r="50" customHeight="1" spans="3:17 16373:16384">
+      <c r="S49" s="1"/>
+    </row>
+    <row r="50" customHeight="1" spans="3:19 16373:16384">
       <c r="Q50" s="1"/>
     </row>
-    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="XES53" s="1"/>
-      <c r="XET53" s="1"/>
-      <c r="XEU53" s="1"/>
-      <c r="XEV53" s="1"/>
-      <c r="XEW53" s="1"/>
-      <c r="XEX53" s="1"/>
-      <c r="XEY53" s="1"/>
-      <c r="XEZ53" s="1"/>
-      <c r="XFA53" s="1"/>
-      <c r="XFB53" s="1"/>
-      <c r="XFC53" s="1"/>
-      <c r="XFD53" s="1"/>
-    </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
+    <row r="51" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q51" s="1"/>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -3707,7 +4168,7 @@
       <c r="XFC54" s="1"/>
       <c r="XFD54" s="1"/>
     </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -3732,7 +4193,7 @@
       <c r="XFC55" s="1"/>
       <c r="XFD55" s="1"/>
     </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -3757,7 +4218,7 @@
       <c r="XFC56" s="1"/>
       <c r="XFD56" s="1"/>
     </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -3782,7 +4243,7 @@
       <c r="XFC57" s="1"/>
       <c r="XFD57" s="1"/>
     </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:17 16373:16384">
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -3807,6 +4268,31 @@
       <c r="XFC58" s="1"/>
       <c r="XFD58" s="1"/>
     </row>
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="M59" s="1"/>
+      <c r="XES59" s="1"/>
+      <c r="XET59" s="1"/>
+      <c r="XEU59" s="1"/>
+      <c r="XEV59" s="1"/>
+      <c r="XEW59" s="1"/>
+      <c r="XEX59" s="1"/>
+      <c r="XEY59" s="1"/>
+      <c r="XEZ59" s="1"/>
+      <c r="XFA59" s="1"/>
+      <c r="XFB59" s="1"/>
+      <c r="XFC59" s="1"/>
+      <c r="XFD59" s="1"/>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
@@ -3829,7 +4315,7 @@
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
     <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.4166666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="26" style="1" customWidth="1"/>
     <col min="11" max="11" width="17.1666666666667" style="1" customWidth="1"/>
     <col min="12" max="13" width="15.9166666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
@@ -3969,7 +4455,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -3981,16 +4467,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -4018,7 +4504,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -4030,16 +4516,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>142</v>
+        <v>175</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -4066,8 +4552,8 @@
       <c r="C8" s="1">
         <v>2003</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>143</v>
+      <c r="D8" s="4" t="s">
+        <v>176</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -4079,16 +4565,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>144</v>
+        <v>177</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -4115,8 +4601,8 @@
       <c r="C9" s="1">
         <v>2004</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>145</v>
+      <c r="D9" s="4" t="s">
+        <v>178</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -4128,16 +4614,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -4159,13 +4645,17 @@
       <c r="XFD9" s="1"/>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C10" s="1">
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>147</v>
+        <v>180</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -4177,16 +4667,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -4208,13 +4698,17 @@
       <c r="XFD10" s="1"/>
     </row>
     <row r="11" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C11" s="1">
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>149</v>
+        <v>182</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -4226,16 +4720,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -4257,13 +4751,17 @@
       <c r="XFD11" s="1"/>
     </row>
     <row r="12" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C12" s="1">
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>151</v>
+        <v>184</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -4275,16 +4773,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -4306,13 +4804,17 @@
       <c r="XFD12" s="1"/>
     </row>
     <row r="13" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C13" s="1">
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -4324,16 +4826,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -4355,13 +4857,17 @@
       <c r="XFD13" s="1"/>
     </row>
     <row r="14" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C14" s="1">
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -4373,16 +4879,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -4537,13 +5043,17 @@
       <c r="XFD19" s="1"/>
     </row>
     <row r="20" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="A20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C20" s="1">
         <v>2101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>157</v>
+        <v>190</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -4555,22 +5065,22 @@
         <v>20011</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>158</v>
+        <v>191</v>
       </c>
       <c r="N20" s="2"/>
       <c r="XES20" s="1"/>
@@ -4587,13 +5097,17 @@
       <c r="XFD20" s="1"/>
     </row>
     <row r="21" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C21" s="1">
         <v>2102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -4605,22 +5119,22 @@
         <v>20021</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>160</v>
+        <v>193</v>
       </c>
       <c r="N21" s="1"/>
       <c r="XES21" s="1"/>
@@ -4637,13 +5151,17 @@
       <c r="XFD21" s="1"/>
     </row>
     <row r="22" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C22" s="1">
         <v>2103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>161</v>
+        <v>194</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -4655,22 +5173,22 @@
         <v>20031</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="N22" s="1"/>
       <c r="XES22" s="1"/>
@@ -4687,13 +5205,17 @@
       <c r="XFD22" s="1"/>
     </row>
     <row r="23" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C23" s="1">
         <v>2104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="E23" s="1">
         <v>2</v>
@@ -4705,22 +5227,22 @@
         <v>20041</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="N23" s="1"/>
       <c r="XES23" s="1"/>
@@ -4737,13 +5259,17 @@
       <c r="XFD23" s="1"/>
     </row>
     <row r="24" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C24" s="1">
         <v>2105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -4755,22 +5281,22 @@
         <v>20051</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="N24" s="1"/>
       <c r="XES24" s="1"/>
@@ -4787,13 +5313,17 @@
       <c r="XFD24" s="1"/>
     </row>
     <row r="25" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C25" s="1">
         <v>2106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>167</v>
+        <v>200</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -4805,22 +5335,22 @@
         <v>20061</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="N25" s="1"/>
       <c r="XES25" s="1"/>
@@ -4837,13 +5367,17 @@
       <c r="XFD25" s="1"/>
     </row>
     <row r="26" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C26" s="1">
         <v>2107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -4855,22 +5389,22 @@
         <v>20071</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="N26" s="1"/>
       <c r="XES26" s="1"/>
@@ -4887,8 +5421,12 @@
       <c r="XFD26" s="1"/>
     </row>
     <row r="27" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C27" s="1"/>
       <c r="D27" s="6"/>
       <c r="E27" s="1"/>
@@ -4915,13 +5453,17 @@
       <c r="XFD27" s="1"/>
     </row>
     <row r="28" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C28" s="1">
         <v>2201</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>171</v>
+        <v>204</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -4933,22 +5475,22 @@
         <v>20012</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="L28" s="1">
         <v>6</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="N28" s="1"/>
       <c r="XES28" s="1"/>
@@ -4965,13 +5507,17 @@
       <c r="XFD28" s="1"/>
     </row>
     <row r="29" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C29" s="1">
         <v>2202</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>173</v>
+        <v>206</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -4983,22 +5529,22 @@
         <v>20022</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="L29" s="1">
         <v>6</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>174</v>
+        <v>207</v>
       </c>
       <c r="N29" s="1"/>
       <c r="XES29" s="1"/>
@@ -5015,13 +5561,17 @@
       <c r="XFD29" s="1"/>
     </row>
     <row r="30" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C30" s="1">
         <v>2203</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -5033,22 +5583,22 @@
         <v>20032</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L30" s="1">
         <v>6</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="N30" s="1"/>
       <c r="XES30" s="1"/>
@@ -5065,13 +5615,17 @@
       <c r="XFD30" s="1"/>
     </row>
     <row r="31" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C31" s="1">
         <v>2205</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="E31" s="1">
         <v>2</v>
@@ -5083,22 +5637,22 @@
         <v>20052</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="N31" s="1"/>
       <c r="XES31" s="1"/>
@@ -5115,13 +5669,17 @@
       <c r="XFD31" s="1"/>
     </row>
     <row r="32" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
+      <c r="A32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C32" s="1">
         <v>2207</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -5133,22 +5691,22 @@
         <v>20072</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="N32" s="1"/>
       <c r="XES32" s="1"/>
@@ -5165,8 +5723,12 @@
       <c r="XFD32" s="1"/>
     </row>
     <row r="33" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C33" s="1"/>
       <c r="D33" s="6"/>
       <c r="E33" s="1"/>
@@ -5193,13 +5755,17 @@
       <c r="XFD33" s="1"/>
     </row>
     <row r="34" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+      <c r="A34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C34" s="1">
         <v>2302</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -5211,22 +5777,22 @@
         <v>20023</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="N34" s="1"/>
       <c r="XES34" s="1"/>
@@ -5243,13 +5809,17 @@
       <c r="XFD34" s="1"/>
     </row>
     <row r="35" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C35" s="1">
         <v>2304</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -5261,22 +5831,22 @@
         <v>20043</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L35" s="1">
         <v>6</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="N35" s="1"/>
       <c r="XES35" s="1"/>
@@ -5293,13 +5863,17 @@
       <c r="XFD35" s="1"/>
     </row>
     <row r="36" customHeight="1" spans="1:18 16373:16384">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
+      <c r="A36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C36" s="1">
         <v>2307</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -5311,22 +5885,22 @@
         <v>20073</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L36" s="1">
         <v>7</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
@@ -5335,8 +5909,12 @@
       <c r="R36" s="1"/>
     </row>
     <row r="37" customHeight="1" spans="1:18 16373:16384">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="D37" s="6"/>
       <c r="M37" s="6"/>
       <c r="N37" s="1"/>
@@ -5346,13 +5924,17 @@
       <c r="R37" s="1"/>
     </row>
     <row r="38" customHeight="1" spans="1:18 16373:16384">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
+      <c r="A38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C38" s="1">
         <v>2402</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -5364,22 +5946,22 @@
         <v>20024</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L38" s="1">
         <v>7</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -5388,13 +5970,17 @@
       <c r="R38" s="1"/>
     </row>
     <row r="39" customHeight="1" spans="1:18 16373:16384">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C39" s="1">
         <v>2403</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -5406,22 +5992,22 @@
         <v>20034</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L39" s="1">
         <v>7</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
@@ -5786,7 +6372,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -5798,23 +6384,23 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -5822,7 +6408,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -5834,23 +6420,23 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>103</v>
+        <v>228</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -5858,7 +6444,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -5870,16 +6456,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>106</v>
+        <v>231</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -5891,7 +6477,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -5903,16 +6489,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -5920,11 +6506,17 @@
       <c r="N9"/>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C10" s="1">
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -5936,16 +6528,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -5953,11 +6545,17 @@
       <c r="N10"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C11" s="1">
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -5969,16 +6567,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>201</v>
+        <v>237</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -5986,11 +6584,17 @@
       <c r="N11"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C12" s="1">
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -6002,16 +6606,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>203</v>
+        <v>239</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -6019,11 +6623,17 @@
       <c r="N12"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C13" s="1">
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>204</v>
+        <v>240</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -6035,16 +6645,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -6052,11 +6662,17 @@
       <c r="N13"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C14" s="1">
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>206</v>
+        <v>242</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -6068,16 +6684,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -6090,36 +6706,42 @@
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="N16"/>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="D17" s="4"/>
       <c r="N17"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="D18" s="4"/>
       <c r="N18"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="D19" s="4"/>
       <c r="N19"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="N20"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="N21"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="N22"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="N23"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C24" s="1">
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -6131,31 +6753,37 @@
         <v>30011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="N24" s="2"/>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C25" s="1">
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -6167,31 +6795,37 @@
         <v>30021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="N25" s="2"/>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C26" s="1">
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -6203,31 +6837,37 @@
         <v>30031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="N26" s="2"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C27" s="1">
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -6239,31 +6879,37 @@
         <v>30041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="N27" s="2"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C28" s="1">
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -6275,31 +6921,37 @@
         <v>30051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="N28" s="2"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C29" s="1">
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -6311,31 +6963,37 @@
         <v>30061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>219</v>
+        <v>255</v>
       </c>
       <c r="N29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C30" s="1">
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>220</v>
+        <v>256</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -6347,34 +7005,46 @@
         <v>30071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="N30" s="2"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A32" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C32" s="1">
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>222</v>
+        <v>258</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -6386,31 +7056,37 @@
         <v>30012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>92</v>
+        <v>121</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>223</v>
+        <v>259</v>
       </c>
       <c r="N32" s="2"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A33" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C33" s="1">
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>224</v>
+        <v>260</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -6422,31 +7098,37 @@
         <v>30022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>225</v>
+        <v>261</v>
       </c>
       <c r="N33" s="2"/>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A34" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C34" s="1">
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>226</v>
+        <v>262</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -6458,31 +7140,37 @@
         <v>30032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>227</v>
+        <v>263</v>
       </c>
       <c r="N34" s="2"/>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C35" s="1">
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -6494,34 +7182,46 @@
         <v>30052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>229</v>
+        <v>265</v>
       </c>
       <c r="N35" s="2"/>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="N36" s="2"/>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A37" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C37" s="1">
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -6533,31 +7233,37 @@
         <v>30023</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="N37" s="2"/>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A38" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C38" s="1">
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -6569,31 +7275,37 @@
         <v>30033</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>233</v>
+        <v>269</v>
       </c>
       <c r="N38" s="2"/>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C39" s="1">
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>234</v>
+        <v>270</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -6605,31 +7317,37 @@
         <v>30043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>235</v>
+        <v>271</v>
       </c>
       <c r="N39" s="2"/>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C40" s="1">
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>236</v>
+        <v>272</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -6641,36 +7359,48 @@
         <v>30073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>237</v>
+        <v>273</v>
       </c>
       <c r="N40" s="2"/>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="D41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="A42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C42" s="1">
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>238</v>
+        <v>274</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -6682,33 +7412,37 @@
         <v>30024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>239</v>
+        <v>275</v>
       </c>
       <c r="N42" s="2"/>
     </row>
     <row r="43" customHeight="1" spans="1:14 16373:16384">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C43" s="1">
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>240</v>
+        <v>276</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -6720,22 +7454,22 @@
         <v>30034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>241</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="343">
   <si>
     <t>#</t>
   </si>
@@ -92,258 +92,276 @@
     <t>40000001,40000002,40000003</t>
   </si>
   <si>
+    <t>50,10,2</t>
+  </si>
+  <si>
+    <t>没有特殊效果</t>
+  </si>
+  <si>
+    <t>杀怪金币</t>
+  </si>
+  <si>
+    <t>修行符</t>
+  </si>
+  <si>
+    <t>86,3,95</t>
+  </si>
+  <si>
+    <t>40000004,40000005,40000006</t>
+  </si>
+  <si>
+    <t>杀怪经验</t>
+  </si>
+  <si>
+    <t>妙手布鞋</t>
+  </si>
+  <si>
+    <t>85,1003,95</t>
+  </si>
+  <si>
+    <t>40,1,1</t>
+  </si>
+  <si>
+    <t>40000007,40000008,40000009</t>
+  </si>
+  <si>
+    <t>100,15,4</t>
+  </si>
+  <si>
+    <t>修行手册</t>
+  </si>
+  <si>
+    <t>86,1003,95</t>
+  </si>
+  <si>
+    <t>40000010,40000011,40000012</t>
+  </si>
+  <si>
+    <t>铜钱袋</t>
+  </si>
+  <si>
+    <t>81,27,95</t>
+  </si>
+  <si>
+    <t>3,1,1</t>
+  </si>
+  <si>
+    <t>150,18,6</t>
+  </si>
+  <si>
+    <t>金币加成</t>
+  </si>
+  <si>
+    <t>试炼卷轴</t>
+  </si>
+  <si>
+    <t>82,27,95</t>
+  </si>
+  <si>
+    <t>经验加成</t>
+  </si>
+  <si>
+    <t>寻金符</t>
+  </si>
+  <si>
+    <t>83,27,95</t>
+  </si>
+  <si>
+    <t>爆率加成</t>
+  </si>
+  <si>
+    <t>四叶草</t>
+  </si>
+  <si>
+    <t>84,27,95</t>
+  </si>
+  <si>
+    <t>品质加成</t>
+  </si>
+  <si>
+    <t>招财挂坠</t>
+  </si>
+  <si>
+    <t>81,21,95</t>
+  </si>
+  <si>
+    <t>3,2,1</t>
+  </si>
+  <si>
+    <t>40000001,40000002,40000002</t>
+  </si>
+  <si>
+    <t>10,3,1</t>
+  </si>
+  <si>
+    <t>经验符</t>
+  </si>
+  <si>
+    <t>82,22,95</t>
+  </si>
+  <si>
+    <t>聚宝盆</t>
+  </si>
+  <si>
+    <t>83,23,95</t>
+  </si>
+  <si>
+    <t>幸运符</t>
+  </si>
+  <si>
+    <t>84,24,95</t>
+  </si>
+  <si>
+    <t>神偷护符</t>
+  </si>
+  <si>
+    <t>85,27,95</t>
+  </si>
+  <si>
+    <t>30,3,1</t>
+  </si>
+  <si>
+    <t>40000005,40000008,40000011</t>
+  </si>
+  <si>
+    <t>3,3,3</t>
+  </si>
+  <si>
+    <t>历练帖</t>
+  </si>
+  <si>
+    <t>86,28,95</t>
+  </si>
+  <si>
+    <t>40000006,40000009,40000012</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
+    <t>聚兽号角</t>
+  </si>
+  <si>
+    <t>2003,111,95</t>
+  </si>
+  <si>
+    <t>2,1,2</t>
+  </si>
+  <si>
+    <t>40000003,40000006,40000009</t>
+  </si>
+  <si>
+    <t>15,15,15</t>
+  </si>
+  <si>
+    <t>增加一个宠物备战位</t>
+  </si>
+  <si>
+    <t>技能手册</t>
+  </si>
+  <si>
+    <t>2003,113,95</t>
+  </si>
+  <si>
+    <t>增加一个技能出站栏位</t>
+  </si>
+  <si>
+    <t>神灵印记</t>
+  </si>
+  <si>
+    <t>2003,114,95</t>
+  </si>
+  <si>
+    <t>3,1,3</t>
+  </si>
+  <si>
+    <t>40000012,40000015,40000018</t>
+  </si>
+  <si>
+    <t>30,30,30</t>
+  </si>
+  <si>
+    <t>技能词条套装所需数量-1</t>
+  </si>
+  <si>
+    <t>装备词条套装所需数量-1</t>
+  </si>
+  <si>
+    <t>2003,95</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>低概率刷新低于当前地图的区域boss</t>
+  </si>
+  <si>
+    <t>传世勋章</t>
+  </si>
+  <si>
+    <t>解锁传世高级挑战</t>
+  </si>
+  <si>
+    <t>传世印记</t>
+  </si>
+  <si>
+    <t>解锁传世超级挑战</t>
+  </si>
+  <si>
+    <t>驯兽金印</t>
+  </si>
+  <si>
+    <t>2003,112,95</t>
+  </si>
+  <si>
+    <t>10,1,10</t>
+  </si>
+  <si>
+    <t>增加一个宠物备出战位</t>
+  </si>
+  <si>
+    <t>粗铁刀</t>
+  </si>
+  <si>
+    <t>4,3,95</t>
+  </si>
+  <si>
+    <t>100,100,1</t>
+  </si>
+  <si>
     <t>25,3,1</t>
   </si>
   <si>
-    <t>没有特殊效果</t>
-  </si>
-  <si>
-    <t>杀怪金币</t>
-  </si>
-  <si>
-    <t>修行符</t>
-  </si>
-  <si>
-    <t>86,3,95</t>
-  </si>
-  <si>
-    <t>40000004,40000005,40000006</t>
-  </si>
-  <si>
-    <t>杀怪经验</t>
-  </si>
-  <si>
-    <t>妙手布鞋</t>
-  </si>
-  <si>
-    <t>85,1003,95</t>
-  </si>
-  <si>
-    <t>40,5,2</t>
-  </si>
-  <si>
-    <t>40000007,40000008,40000009</t>
+    <t>物攻基础</t>
+  </si>
+  <si>
+    <t>粗铁剑</t>
+  </si>
+  <si>
+    <t>150,150,1</t>
   </si>
   <si>
     <t>50,6,2</t>
   </si>
   <si>
-    <t>修行手册</t>
-  </si>
-  <si>
-    <t>86,1003,95</t>
-  </si>
-  <si>
-    <t>40000010,40000011,40000012</t>
-  </si>
-  <si>
-    <t>铜钱袋</t>
-  </si>
-  <si>
-    <t>81,27,95</t>
-  </si>
-  <si>
-    <t>3,3,2</t>
+    <t>粗铁斧</t>
+  </si>
+  <si>
+    <t>200,200,1</t>
   </si>
   <si>
     <t>75,9,3</t>
   </si>
   <si>
-    <t>金币加成</t>
-  </si>
-  <si>
-    <t>试炼卷轴</t>
-  </si>
-  <si>
-    <t>82,27,95</t>
-  </si>
-  <si>
-    <t>经验加成</t>
-  </si>
-  <si>
-    <t>寻金符</t>
-  </si>
-  <si>
-    <t>83,27,95</t>
-  </si>
-  <si>
-    <t>爆率加成</t>
-  </si>
-  <si>
-    <t>四叶草</t>
-  </si>
-  <si>
-    <t>84,27,95</t>
-  </si>
-  <si>
-    <t>品质加成</t>
-  </si>
-  <si>
-    <t>招财挂坠</t>
-  </si>
-  <si>
-    <t>81,21,95</t>
-  </si>
-  <si>
-    <t>3,2,1</t>
-  </si>
-  <si>
-    <t>40000001,40000002,40000002</t>
-  </si>
-  <si>
-    <t>10,3,1</t>
-  </si>
-  <si>
-    <t>经验符</t>
-  </si>
-  <si>
-    <t>82,22,95</t>
-  </si>
-  <si>
-    <t>聚宝盆</t>
-  </si>
-  <si>
-    <t>83,23,95</t>
-  </si>
-  <si>
-    <t>幸运符</t>
-  </si>
-  <si>
-    <t>84,24,95</t>
-  </si>
-  <si>
-    <t>神偷护符</t>
-  </si>
-  <si>
-    <t>85,27,95</t>
-  </si>
-  <si>
-    <t>30,3,1</t>
-  </si>
-  <si>
-    <t>40000005,40000008,40000011</t>
-  </si>
-  <si>
-    <t>3,3,3</t>
-  </si>
-  <si>
-    <t>历练帖</t>
-  </si>
-  <si>
-    <t>86,28,95</t>
-  </si>
-  <si>
-    <t>40000006,40000009,40000012</t>
-  </si>
-  <si>
-    <t>1,1,1</t>
-  </si>
-  <si>
-    <t>聚兽铜印</t>
-  </si>
-  <si>
-    <t>2003,111,95</t>
-  </si>
-  <si>
-    <t>5,1,5</t>
-  </si>
-  <si>
-    <t>40000003,40000006,40000009</t>
-  </si>
-  <si>
-    <t>15,15,15</t>
-  </si>
-  <si>
-    <t>增加一个宠物备战位</t>
-  </si>
-  <si>
-    <t>驯兽金印</t>
-  </si>
-  <si>
-    <t>2003,112,95</t>
-  </si>
-  <si>
-    <t>10,1,10</t>
-  </si>
-  <si>
-    <t>40000012,40000015,40000018</t>
-  </si>
-  <si>
-    <t>30,30,30</t>
-  </si>
-  <si>
-    <t>增加一个宠物备出战位</t>
-  </si>
-  <si>
-    <t>技能手册</t>
-  </si>
-  <si>
-    <t>2003,113,95</t>
-  </si>
-  <si>
-    <t>增加一个技能出站栏位</t>
-  </si>
-  <si>
-    <t>神灵印记</t>
-  </si>
-  <si>
-    <t>2003,114,95</t>
-  </si>
-  <si>
-    <t>技能词条套装所需数量-1</t>
-  </si>
-  <si>
-    <t>装备词条套装所需数量-1</t>
-  </si>
-  <si>
-    <t>粗铁刀</t>
-  </si>
-  <si>
-    <t>4,3,95</t>
-  </si>
-  <si>
-    <t>100,100,1</t>
-  </si>
-  <si>
-    <t>物攻基础</t>
-  </si>
-  <si>
-    <t>粗铁剑</t>
-  </si>
-  <si>
-    <t>1004,3,95</t>
-  </si>
-  <si>
-    <t>5,300,1</t>
-  </si>
-  <si>
-    <t>物攻加成</t>
-  </si>
-  <si>
-    <t>粗铁斧</t>
-  </si>
-  <si>
-    <t>1007,27,95</t>
-  </si>
-  <si>
-    <t>5,5,2</t>
-  </si>
-  <si>
-    <t>物伤加成</t>
-  </si>
-  <si>
     <t>粗铁枪</t>
   </si>
   <si>
-    <t>2007,27,95</t>
+    <t>250,250,1</t>
   </si>
   <si>
     <t>100,12,4</t>
   </si>
   <si>
-    <t>物攻增幅</t>
-  </si>
-  <si>
     <t>黑铁指环</t>
   </si>
   <si>
@@ -419,6 +437,81 @@
     <t>法系技能冷却+5%</t>
   </si>
   <si>
+    <t>基础心法·传承</t>
+  </si>
+  <si>
+    <t>1004,21001,95</t>
+  </si>
+  <si>
+    <t>2,1,1</t>
+  </si>
+  <si>
+    <t>基础心法等级+1</t>
+  </si>
+  <si>
+    <t>流光剑诀·传承</t>
+  </si>
+  <si>
+    <t>1004,21002,95</t>
+  </si>
+  <si>
+    <t>流光剑诀等级+1</t>
+  </si>
+  <si>
+    <t>月华剑阵·传承</t>
+  </si>
+  <si>
+    <t>1004,21003,95</t>
+  </si>
+  <si>
+    <t>月华剑阵等级+1</t>
+  </si>
+  <si>
+    <t>蛮牛冲撞·传承</t>
+  </si>
+  <si>
+    <t>1004,21004,95</t>
+  </si>
+  <si>
+    <t>蛮牛冲撞等级+1</t>
+  </si>
+  <si>
+    <t>龙魂护体·传承</t>
+  </si>
+  <si>
+    <t>1004,21005,95</t>
+  </si>
+  <si>
+    <t>40000013,40000014,40000015</t>
+  </si>
+  <si>
+    <t>龙魂护体等级+1</t>
+  </si>
+  <si>
+    <t>无求易决·传承</t>
+  </si>
+  <si>
+    <t>1004,21006,95</t>
+  </si>
+  <si>
+    <t>40000016,40000017,40000018</t>
+  </si>
+  <si>
+    <t>无求易决等级+1</t>
+  </si>
+  <si>
+    <t>火麟剑诀·传承</t>
+  </si>
+  <si>
+    <t>1004,21007,95</t>
+  </si>
+  <si>
+    <t>40000019,40000020,40000021</t>
+  </si>
+  <si>
+    <t>火麟剑诀等级+1</t>
+  </si>
+  <si>
     <t>基础战体</t>
   </si>
   <si>
@@ -557,21 +650,12 @@
     <t>乌木戒</t>
   </si>
   <si>
-    <t>1005,3,95</t>
-  </si>
-  <si>
     <t>乌木坠</t>
   </si>
   <si>
-    <t>1008,27,95</t>
-  </si>
-  <si>
     <t>乌木佩</t>
   </si>
   <si>
-    <t>2008,27,95</t>
-  </si>
-  <si>
     <t>桃木指环</t>
   </si>
   <si>
@@ -602,6 +686,69 @@
     <t>1001,1005,95</t>
   </si>
   <si>
+    <t>冥想心法</t>
+  </si>
+  <si>
+    <t>1005,22001,95</t>
+  </si>
+  <si>
+    <t>冥想心法等级+1</t>
+  </si>
+  <si>
+    <t>紫电神雷</t>
+  </si>
+  <si>
+    <t>1005,22002,95</t>
+  </si>
+  <si>
+    <t>紫电神雷等级+1</t>
+  </si>
+  <si>
+    <t>火狱阵法</t>
+  </si>
+  <si>
+    <t>1005,22003,95</t>
+  </si>
+  <si>
+    <t>火狱阵法等级+1</t>
+  </si>
+  <si>
+    <t>烈焰焚天</t>
+  </si>
+  <si>
+    <t>1005,22004,95</t>
+  </si>
+  <si>
+    <t>烈焰焚天等级+1</t>
+  </si>
+  <si>
+    <t>炎凰法盾</t>
+  </si>
+  <si>
+    <t>1005,22005,95</t>
+  </si>
+  <si>
+    <t>炎凰法盾等级+1</t>
+  </si>
+  <si>
+    <t>万法归宗</t>
+  </si>
+  <si>
+    <t>1005,22006,95</t>
+  </si>
+  <si>
+    <t>万法归宗等级+1</t>
+  </si>
+  <si>
+    <t>极寒冰暴</t>
+  </si>
+  <si>
+    <t>1005,22007,95</t>
+  </si>
+  <si>
+    <t>极寒冰暴等级+1</t>
+  </si>
+  <si>
     <t>冥想法体</t>
   </si>
   <si>
@@ -710,30 +857,15 @@
     <t>6,3,95</t>
   </si>
   <si>
-    <t>道攻加成</t>
-  </si>
-  <si>
     <t>青竹罗盘</t>
   </si>
   <si>
-    <t>1006,3,95</t>
-  </si>
-  <si>
-    <t>道伤加成</t>
-  </si>
-  <si>
     <t>桃木剑</t>
   </si>
   <si>
-    <t>1009,27,95</t>
-  </si>
-  <si>
     <t>桃木罗盘</t>
   </si>
   <si>
-    <t>2009,27,95</t>
-  </si>
-  <si>
     <t>青竹指环</t>
   </si>
   <si>
@@ -762,6 +894,69 @@
   </si>
   <si>
     <t>1001,1006,95</t>
+  </si>
+  <si>
+    <t>清心咒</t>
+  </si>
+  <si>
+    <t>1006,23001,95</t>
+  </si>
+  <si>
+    <t>清心咒等级+1</t>
+  </si>
+  <si>
+    <t>破魔符咒</t>
+  </si>
+  <si>
+    <t>1006,23002,95</t>
+  </si>
+  <si>
+    <t>破魔符咒等级+1</t>
+  </si>
+  <si>
+    <t>毒咒术</t>
+  </si>
+  <si>
+    <t>1006,23003,95</t>
+  </si>
+  <si>
+    <t>毒咒术等级+1</t>
+  </si>
+  <si>
+    <t>圣疗术</t>
+  </si>
+  <si>
+    <t>1006,23004,95</t>
+  </si>
+  <si>
+    <t>圣疗术等级+1</t>
+  </si>
+  <si>
+    <t>太虚麟盾</t>
+  </si>
+  <si>
+    <t>1006,23005,95</t>
+  </si>
+  <si>
+    <t>太虚麟盾等级+1</t>
+  </si>
+  <si>
+    <t>道法自然</t>
+  </si>
+  <si>
+    <t>1006,23006,95</t>
+  </si>
+  <si>
+    <t>道法自然等级+1</t>
+  </si>
+  <si>
+    <t>召唤英灵</t>
+  </si>
+  <si>
+    <t>1006,23007,95</t>
+  </si>
+  <si>
+    <t>召唤英灵等级+1</t>
   </si>
   <si>
     <t>清心道体</t>
@@ -1845,7 +2040,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1855,7 +2050,7 @@
     <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="24.5833333333333" style="1" customWidth="1"/>
     <col min="11" max="12" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="20.6666666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="29" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
     <col min="15" max="16372" width="9" style="2"/>
     <col min="16373" max="16384" width="9" style="1"/>
@@ -2290,49 +2485,21 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="1">
-        <v>7</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="K16" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" s="1">
-        <v>4</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>39</v>
-      </c>
+    <row r="16" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="2"/>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
@@ -2342,28 +2509,28 @@
         <v>0</v>
       </c>
       <c r="C17" s="1">
-        <v>8</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>54</v>
+        <v>7</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="E17" s="1">
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>51</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="K17" s="10" t="s">
         <v>53</v>
@@ -2375,7 +2542,7 @@
         <v>21</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2386,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="C18" s="1">
-        <v>9</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>56</v>
+        <v>8</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="E18" s="1">
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="1">
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>51</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K18" s="10" t="s">
         <v>53</v>
@@ -2419,7 +2586,7 @@
         <v>21</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2430,28 +2597,28 @@
         <v>0</v>
       </c>
       <c r="C19" s="1">
-        <v>10</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>58</v>
+        <v>9</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="E19" s="1">
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I19" s="10" t="s">
         <v>51</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K19" s="10" t="s">
         <v>53</v>
@@ -2463,7 +2630,7 @@
         <v>21</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2474,31 +2641,31 @@
         <v>0</v>
       </c>
       <c r="C20" s="1">
-        <v>11</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>60</v>
+        <v>10</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="E20" s="1">
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="L20" s="1">
         <v>4</v>
@@ -2507,7 +2674,7 @@
         <v>21</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2518,31 +2685,31 @@
         <v>0</v>
       </c>
       <c r="C21" s="1">
-        <v>12</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>65</v>
+        <v>11</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="E21" s="1">
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>62</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L21" s="1">
         <v>4</v>
@@ -2551,94 +2718,100 @@
         <v>21</v>
       </c>
       <c r="N21" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>12</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="1">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1">
+        <v>6</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L22" s="1">
+        <v>4</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N22" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="D22" s="7"/>
-    </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="C23" s="1">
-        <v>101</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="L23" s="1">
-        <v>5</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="D23" s="7"/>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C24" s="1">
-        <v>102</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>75</v>
+        <v>101</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="L24" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C25" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -2650,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I25" s="10" t="s">
         <v>71</v>
@@ -2665,18 +2838,18 @@
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C26" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -2688,39 +2861,188 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="L26" s="1">
         <v>6</v>
       </c>
       <c r="M26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C27" s="1">
+        <v>104</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>0</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="N26" s="1" t="s">
+      <c r="J27" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L27" s="1">
+        <v>6</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1"/>
-    <row r="28" s="1" customFormat="1" customHeight="1"/>
-    <row r="29" s="1" customFormat="1" customHeight="1"/>
+      <c r="N27" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C28" s="1">
+        <v>105</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1">
+        <v>0</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="L28" s="1">
+        <v>5</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="C29" s="1">
+        <v>106</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1">
+        <v>0</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L29" s="1">
+        <v>5</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
     <row r="30" s="1" customFormat="1" customHeight="1"/>
     <row r="31" s="1" customFormat="1" customHeight="1"/>
     <row r="32" s="1" customFormat="1" customHeight="1"/>
     <row r="33" s="1" customFormat="1" customHeight="1"/>
-    <row r="35" customHeight="1" spans="14:14">
+    <row r="35" customHeight="1" spans="1:14">
       <c r="N35" s="1"/>
     </row>
-    <row r="36" customHeight="1" spans="14:14">
+    <row r="36" customHeight="1" spans="1:14">
       <c r="N36" s="1"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="A39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="1">
+        <v>102</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0</v>
+      </c>
+      <c r="F39" s="1">
+        <v>101</v>
+      </c>
+      <c r="G39" s="1">
+        <v>0</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="L39" s="1">
+        <v>6</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>95</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2736,14 +3058,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD59"/>
+  <dimension ref="A1:XFD67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
-    <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
+    <col min="7" max="8" width="12.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.1666666666667" style="1" customWidth="1"/>
     <col min="10" max="10" width="24.75" style="1" customWidth="1"/>
     <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
     <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
@@ -2881,7 +3204,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -2893,16 +3216,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -2911,7 +3234,7 @@
         <v>21</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2919,7 +3242,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -2931,16 +3254,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -2949,7 +3272,7 @@
         <v>21</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2957,7 +3280,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2972,13 +3295,13 @@
         <v>97</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -2987,7 +3310,7 @@
         <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2995,7 +3318,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -3007,25 +3330,25 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L9" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3039,7 +3362,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3051,16 +3374,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -3080,7 +3403,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3092,16 +3415,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -3121,7 +3444,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3133,16 +3456,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -3162,7 +3485,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3174,16 +3497,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -3203,7 +3526,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3215,16 +3538,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="K14" s="10" t="s">
         <v>123</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>117</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -3242,10 +3565,10 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:18">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -3254,10 +3577,10 @@
       </c>
       <c r="D17" s="4"/>
       <c r="M17" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:18">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
@@ -3265,23 +3588,51 @@
         <v>0</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
-    <row r="20" s="1" customFormat="1" customHeight="1"/>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="C20" s="1">
+        <v>1101</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" s="1">
+        <v>1</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L20" s="1">
+        <v>5</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C21" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3290,39 +3641,33 @@
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>10011</v>
+        <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C22" s="1">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3331,39 +3676,33 @@
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>10021</v>
+        <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C23" s="1">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3372,39 +3711,33 @@
         <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>10031</v>
+        <v>0</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A24" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C24" s="1">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3413,39 +3746,33 @@
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>10041</v>
+        <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A25" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="C25" s="1">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3454,28 +3781,28 @@
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>10051</v>
+        <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:18">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -3483,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="1">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3495,81 +3822,30 @@
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>10061</v>
+        <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="1">
-        <v>1107</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1">
-        <v>10071</v>
-      </c>
-      <c r="H27" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="L27" s="1">
-        <v>5</v>
-      </c>
-      <c r="M27" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="R27" s="6"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:18">
-      <c r="A28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="R28" s="6"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:18">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1"/>
+    <row r="28" s="1" customFormat="1" customHeight="1"/>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -3577,41 +3853,40 @@
         <v>0</v>
       </c>
       <c r="C29" s="1">
-        <v>1201</v>
+        <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>1101</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="L29" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="R29" s="6"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:18">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -3619,41 +3894,40 @@
         <v>0</v>
       </c>
       <c r="C30" s="1">
-        <v>1202</v>
+        <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
       </c>
       <c r="F30" s="1">
-        <v>1102</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>10022</v>
+        <v>10021</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="L30" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="R30" s="6"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:18">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -3661,43 +3935,40 @@
         <v>0</v>
       </c>
       <c r="C31" s="1">
-        <v>1203</v>
+        <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" s="1">
-        <v>1103</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>10032</v>
+        <v>10031</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
+      </c>
+      <c r="K31" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="L31" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="O31" s="6"/>
-      <c r="P31" s="1"/>
-      <c r="R31" s="6"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:18">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:13">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -3705,41 +3976,38 @@
         <v>0</v>
       </c>
       <c r="C32" s="1">
-        <v>1204</v>
+        <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>1104</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>10042</v>
+        <v>10041</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>133</v>
+        <v>113</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="L32" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="O32" s="6"/>
-      <c r="P32" s="1"/>
-      <c r="R32" s="6"/>
+        <v>175</v>
+      </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
       <c r="A33" s="1" t="s">
@@ -3749,40 +4017,38 @@
         <v>0</v>
       </c>
       <c r="C33" s="1">
-        <v>1205</v>
+        <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
       </c>
       <c r="F33" s="1">
-        <v>1105</v>
+        <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>10052</v>
+        <v>10051</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="O33" s="6"/>
-      <c r="R33" s="6"/>
+        <v>177</v>
+      </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
       <c r="A34" s="1" t="s">
@@ -3792,41 +4058,38 @@
         <v>0</v>
       </c>
       <c r="C34" s="1">
-        <v>1207</v>
+        <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
       <c r="F34" s="1">
-        <v>1107</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>10072</v>
+        <v>10061</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="L34" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="O34" s="6"/>
-      <c r="P34" s="1"/>
-      <c r="R34" s="6"/>
+        <v>179</v>
+      </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
       <c r="A35" s="1" t="s">
@@ -3835,9 +4098,39 @@
       <c r="B35" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="O35" s="6"/>
+      <c r="C35" s="1">
+        <v>1107</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" s="1">
+        <v>1</v>
+      </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1">
+        <v>10071</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="L35" s="1">
+        <v>5</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>182</v>
+      </c>
       <c r="R35" s="6"/>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -3847,41 +4140,8 @@
       <c r="B36" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C36" s="1">
-        <v>1302</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="E36" s="1">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1">
-        <v>1202</v>
-      </c>
-      <c r="G36" s="1">
-        <v>10023</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="L36" s="1">
-        <v>6</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="O36" s="6"/>
-      <c r="P36" s="1"/>
+      <c r="D36" s="6"/>
+      <c r="M36" s="6"/>
       <c r="R36" s="6"/>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -3892,40 +4152,38 @@
         <v>0</v>
       </c>
       <c r="C37" s="1">
-        <v>1307</v>
+        <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
       </c>
       <c r="F37" s="1">
-        <v>1207</v>
+        <v>1101</v>
       </c>
       <c r="G37" s="1">
-        <v>10073</v>
+        <v>10012</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="L37" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="O37" s="6"/>
-      <c r="P37" s="1"/>
+        <v>184</v>
+      </c>
       <c r="R37" s="6"/>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -3935,12 +4193,42 @@
       <c r="B38" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="O38" s="6"/>
+      <c r="C38" s="1">
+        <v>1202</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1102</v>
+      </c>
+      <c r="G38" s="1">
+        <v>10022</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="L38" s="1">
+        <v>6</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>186</v>
+      </c>
       <c r="R38" s="6"/>
     </row>
-    <row r="39" customHeight="1" spans="1:19 16373:16384">
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -3948,44 +4236,43 @@
         <v>0</v>
       </c>
       <c r="C39" s="1">
-        <v>1402</v>
+        <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
       </c>
       <c r="F39" s="1">
-        <v>1302</v>
+        <v>1103</v>
       </c>
       <c r="G39" s="1">
-        <v>10024</v>
+        <v>10032</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L39" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="O39" s="1"/>
+        <v>188</v>
+      </c>
+      <c r="O39" s="6"/>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="S39" s="1"/>
-    </row>
-    <row r="40" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="R39" s="6"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -3993,305 +4280,593 @@
         <v>0</v>
       </c>
       <c r="C40" s="1">
-        <v>1403</v>
+        <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
       </c>
       <c r="F40" s="1">
-        <v>1203</v>
+        <v>1104</v>
       </c>
       <c r="G40" s="1">
-        <v>10034</v>
+        <v>10042</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L40" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="N40" s="1"/>
+        <v>190</v>
+      </c>
       <c r="O40" s="6"/>
       <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="S40" s="1"/>
-      <c r="XES40" s="1"/>
-      <c r="XET40" s="1"/>
-      <c r="XEU40" s="1"/>
-      <c r="XEV40" s="1"/>
-      <c r="XEW40" s="1"/>
-      <c r="XEX40" s="1"/>
-      <c r="XEY40" s="1"/>
-      <c r="XEZ40" s="1"/>
-      <c r="XFA40" s="1"/>
-      <c r="XFB40" s="1"/>
-      <c r="XFC40" s="1"/>
-      <c r="XFD40" s="1"/>
-    </row>
-    <row r="41" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C41" s="1"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
+      <c r="R40" s="6"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1205</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1105</v>
+      </c>
+      <c r="G41" s="1">
+        <v>10052</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="L41" s="1">
+        <v>5</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>192</v>
+      </c>
       <c r="O41" s="6"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="S41" s="1"/>
-      <c r="XES41" s="1"/>
-      <c r="XET41" s="1"/>
-      <c r="XEU41" s="1"/>
-      <c r="XEV41" s="1"/>
-      <c r="XEW41" s="1"/>
-      <c r="XEX41" s="1"/>
-      <c r="XEY41" s="1"/>
-      <c r="XEZ41" s="1"/>
-      <c r="XFA41" s="1"/>
-      <c r="XFB41" s="1"/>
-      <c r="XFC41" s="1"/>
-      <c r="XFD41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:19 16373:16384">
-      <c r="O42" s="1"/>
+      <c r="R41" s="6"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1207</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1107</v>
+      </c>
+      <c r="G42" s="1">
+        <v>10072</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L42" s="1">
+        <v>6</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="O42" s="6"/>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="S42" s="1"/>
-    </row>
-    <row r="43" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
+      <c r="R42" s="6"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="6"/>
+      <c r="M43" s="6"/>
       <c r="O43" s="6"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="S43" s="1"/>
-      <c r="XES43" s="1"/>
-      <c r="XET43" s="1"/>
-      <c r="XEU43" s="1"/>
-      <c r="XEV43" s="1"/>
-      <c r="XEW43" s="1"/>
-      <c r="XEX43" s="1"/>
-      <c r="XEY43" s="1"/>
-      <c r="XEZ43" s="1"/>
-      <c r="XFA43" s="1"/>
-      <c r="XFB43" s="1"/>
-      <c r="XFC43" s="1"/>
-      <c r="XFD43" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:19 16373:16384">
+      <c r="R43" s="6"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1302</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1202</v>
+      </c>
+      <c r="G44" s="1">
+        <v>10023</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L44" s="1">
+        <v>6</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>196</v>
+      </c>
       <c r="O44" s="6"/>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:19 16373:16384">
-      <c r="Q45" s="1"/>
-      <c r="S45" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:19 16373:16384">
-      <c r="Q46" s="1"/>
-      <c r="S46" s="1"/>
+      <c r="R44" s="6"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1307</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1207</v>
+      </c>
+      <c r="G45" s="1">
+        <v>10073</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L45" s="1">
+        <v>7</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="O45" s="6"/>
+      <c r="P45" s="1"/>
+      <c r="R45" s="6"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="R46" s="6"/>
     </row>
     <row r="47" customHeight="1" spans="1:19 16373:16384">
+      <c r="A47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1402</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1302</v>
+      </c>
+      <c r="G47" s="1">
+        <v>10024</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L47" s="1">
+        <v>7</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>200</v>
+      </c>
       <c r="O47" s="1"/>
+      <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" customHeight="1" spans="1:19 16373:16384">
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="A48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1403</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1203</v>
+      </c>
+      <c r="G48" s="1">
+        <v>10034</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L48" s="1">
+        <v>7</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="N48" s="1"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="S48" s="1"/>
-    </row>
-    <row r="49" customHeight="1" spans="3:19 16373:16384">
+      <c r="XES48" s="1"/>
+      <c r="XET48" s="1"/>
+      <c r="XEU48" s="1"/>
+      <c r="XEV48" s="1"/>
+      <c r="XEW48" s="1"/>
+      <c r="XEX48" s="1"/>
+      <c r="XEY48" s="1"/>
+      <c r="XEZ48" s="1"/>
+      <c r="XFA48" s="1"/>
+      <c r="XFB48" s="1"/>
+      <c r="XFC48" s="1"/>
+      <c r="XFD48" s="1"/>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+      <c r="C49" s="1"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="6"/>
+      <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
       <c r="S49" s="1"/>
+      <c r="XES49" s="1"/>
+      <c r="XET49" s="1"/>
+      <c r="XEU49" s="1"/>
+      <c r="XEV49" s="1"/>
+      <c r="XEW49" s="1"/>
+      <c r="XEX49" s="1"/>
+      <c r="XEY49" s="1"/>
+      <c r="XEZ49" s="1"/>
+      <c r="XFA49" s="1"/>
+      <c r="XFB49" s="1"/>
+      <c r="XFC49" s="1"/>
+      <c r="XFD49" s="1"/>
     </row>
     <row r="50" customHeight="1" spans="3:19 16373:16384">
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
-    </row>
-    <row r="51" customHeight="1" spans="3:19 16373:16384">
+      <c r="S50" s="1"/>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="O51" s="6"/>
+      <c r="P51" s="1"/>
       <c r="Q51" s="1"/>
-    </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="XES54" s="1"/>
-      <c r="XET54" s="1"/>
-      <c r="XEU54" s="1"/>
-      <c r="XEV54" s="1"/>
-      <c r="XEW54" s="1"/>
-      <c r="XEX54" s="1"/>
-      <c r="XEY54" s="1"/>
-      <c r="XEZ54" s="1"/>
-      <c r="XFA54" s="1"/>
-      <c r="XFB54" s="1"/>
-      <c r="XFC54" s="1"/>
-      <c r="XFD54" s="1"/>
-    </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="XES55" s="1"/>
-      <c r="XET55" s="1"/>
-      <c r="XEU55" s="1"/>
-      <c r="XEV55" s="1"/>
-      <c r="XEW55" s="1"/>
-      <c r="XEX55" s="1"/>
-      <c r="XEY55" s="1"/>
-      <c r="XEZ55" s="1"/>
-      <c r="XFA55" s="1"/>
-      <c r="XFB55" s="1"/>
-      <c r="XFC55" s="1"/>
-      <c r="XFD55" s="1"/>
-    </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="XES56" s="1"/>
-      <c r="XET56" s="1"/>
-      <c r="XEU56" s="1"/>
-      <c r="XEV56" s="1"/>
-      <c r="XEW56" s="1"/>
-      <c r="XEX56" s="1"/>
-      <c r="XEY56" s="1"/>
-      <c r="XEZ56" s="1"/>
-      <c r="XFA56" s="1"/>
-      <c r="XFB56" s="1"/>
-      <c r="XFC56" s="1"/>
-      <c r="XFD56" s="1"/>
-    </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="XES57" s="1"/>
-      <c r="XET57" s="1"/>
-      <c r="XEU57" s="1"/>
-      <c r="XEV57" s="1"/>
-      <c r="XEW57" s="1"/>
-      <c r="XEX57" s="1"/>
-      <c r="XEY57" s="1"/>
-      <c r="XEZ57" s="1"/>
-      <c r="XFA57" s="1"/>
-      <c r="XFB57" s="1"/>
-      <c r="XFC57" s="1"/>
-      <c r="XFD57" s="1"/>
-    </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="XES58" s="1"/>
-      <c r="XET58" s="1"/>
-      <c r="XEU58" s="1"/>
-      <c r="XEV58" s="1"/>
-      <c r="XEW58" s="1"/>
-      <c r="XEX58" s="1"/>
-      <c r="XEY58" s="1"/>
-      <c r="XEZ58" s="1"/>
-      <c r="XFA58" s="1"/>
-      <c r="XFB58" s="1"/>
-      <c r="XFC58" s="1"/>
-      <c r="XFD58" s="1"/>
-    </row>
-    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="XES59" s="1"/>
-      <c r="XET59" s="1"/>
-      <c r="XEU59" s="1"/>
-      <c r="XEV59" s="1"/>
-      <c r="XEW59" s="1"/>
-      <c r="XEX59" s="1"/>
-      <c r="XEY59" s="1"/>
-      <c r="XEZ59" s="1"/>
-      <c r="XFA59" s="1"/>
-      <c r="XFB59" s="1"/>
-      <c r="XFC59" s="1"/>
-      <c r="XFD59" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="XES51" s="1"/>
+      <c r="XET51" s="1"/>
+      <c r="XEU51" s="1"/>
+      <c r="XEV51" s="1"/>
+      <c r="XEW51" s="1"/>
+      <c r="XEX51" s="1"/>
+      <c r="XEY51" s="1"/>
+      <c r="XEZ51" s="1"/>
+      <c r="XFA51" s="1"/>
+      <c r="XFB51" s="1"/>
+      <c r="XFC51" s="1"/>
+      <c r="XFD51" s="1"/>
+    </row>
+    <row r="52" customHeight="1" spans="3:19 16373:16384">
+      <c r="O52" s="6"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
+    </row>
+    <row r="53" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q53" s="1"/>
+      <c r="S53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q54" s="1"/>
+      <c r="S54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="3:19 16373:16384">
+      <c r="O55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1"/>
+      <c r="S55" s="1"/>
+    </row>
+    <row r="56" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q56" s="1"/>
+      <c r="S56" s="1"/>
+    </row>
+    <row r="57" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q57" s="1"/>
+      <c r="S57" s="1"/>
+    </row>
+    <row r="58" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q58" s="1"/>
+    </row>
+    <row r="59" customHeight="1" spans="3:19 16373:16384">
+      <c r="Q59" s="1"/>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="M62" s="1"/>
+      <c r="XES62" s="1"/>
+      <c r="XET62" s="1"/>
+      <c r="XEU62" s="1"/>
+      <c r="XEV62" s="1"/>
+      <c r="XEW62" s="1"/>
+      <c r="XEX62" s="1"/>
+      <c r="XEY62" s="1"/>
+      <c r="XEZ62" s="1"/>
+      <c r="XFA62" s="1"/>
+      <c r="XFB62" s="1"/>
+      <c r="XFC62" s="1"/>
+      <c r="XFD62" s="1"/>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="XES63" s="1"/>
+      <c r="XET63" s="1"/>
+      <c r="XEU63" s="1"/>
+      <c r="XEV63" s="1"/>
+      <c r="XEW63" s="1"/>
+      <c r="XEX63" s="1"/>
+      <c r="XEY63" s="1"/>
+      <c r="XEZ63" s="1"/>
+      <c r="XFA63" s="1"/>
+      <c r="XFB63" s="1"/>
+      <c r="XFC63" s="1"/>
+      <c r="XFD63" s="1"/>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="XES64" s="1"/>
+      <c r="XET64" s="1"/>
+      <c r="XEU64" s="1"/>
+      <c r="XEV64" s="1"/>
+      <c r="XEW64" s="1"/>
+      <c r="XEX64" s="1"/>
+      <c r="XEY64" s="1"/>
+      <c r="XEZ64" s="1"/>
+      <c r="XFA64" s="1"/>
+      <c r="XFB64" s="1"/>
+      <c r="XFC64" s="1"/>
+      <c r="XFD64" s="1"/>
+    </row>
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="XES65" s="1"/>
+      <c r="XET65" s="1"/>
+      <c r="XEU65" s="1"/>
+      <c r="XEV65" s="1"/>
+      <c r="XEW65" s="1"/>
+      <c r="XEX65" s="1"/>
+      <c r="XEY65" s="1"/>
+      <c r="XEZ65" s="1"/>
+      <c r="XFA65" s="1"/>
+      <c r="XFB65" s="1"/>
+      <c r="XFC65" s="1"/>
+      <c r="XFD65" s="1"/>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="XES66" s="1"/>
+      <c r="XET66" s="1"/>
+      <c r="XEU66" s="1"/>
+      <c r="XEV66" s="1"/>
+      <c r="XEW66" s="1"/>
+      <c r="XEX66" s="1"/>
+      <c r="XEY66" s="1"/>
+      <c r="XEZ66" s="1"/>
+      <c r="XFA66" s="1"/>
+      <c r="XFB66" s="1"/>
+      <c r="XFC66" s="1"/>
+      <c r="XFD66" s="1"/>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="XES67" s="1"/>
+      <c r="XET67" s="1"/>
+      <c r="XEU67" s="1"/>
+      <c r="XEV67" s="1"/>
+      <c r="XEW67" s="1"/>
+      <c r="XEX67" s="1"/>
+      <c r="XEY67" s="1"/>
+      <c r="XEZ67" s="1"/>
+      <c r="XFA67" s="1"/>
+      <c r="XFB67" s="1"/>
+      <c r="XFC67" s="1"/>
+      <c r="XFD67" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4307,7 +4882,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:XFD55"/>
+  <dimension ref="A1:XFD59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -4455,7 +5030,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4467,16 +5042,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>173</v>
+        <v>204</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -4504,7 +5079,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -4516,16 +5091,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -4553,7 +5128,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -4565,16 +5140,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -4602,7 +5177,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -4614,16 +5189,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -4655,7 +5230,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -4667,16 +5242,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>181</v>
+        <v>209</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -4708,7 +5283,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -4720,16 +5295,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -4761,7 +5336,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -4773,16 +5348,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -4814,7 +5389,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -4826,16 +5401,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -4867,7 +5442,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -4879,16 +5454,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -4935,125 +5510,152 @@
       <c r="XFC15" s="1"/>
       <c r="XFD15" s="1"/>
     </row>
-    <row r="16" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="XES16" s="1"/>
-      <c r="XET16" s="1"/>
-      <c r="XEU16" s="1"/>
-      <c r="XEV16" s="1"/>
-      <c r="XEW16" s="1"/>
-      <c r="XEX16" s="1"/>
-      <c r="XEY16" s="1"/>
-      <c r="XEZ16" s="1"/>
-      <c r="XFA16" s="1"/>
-      <c r="XFB16" s="1"/>
-      <c r="XFC16" s="1"/>
-      <c r="XFD16" s="1"/>
-    </row>
-    <row r="17" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="XES17" s="1"/>
-      <c r="XET17" s="1"/>
-      <c r="XEU17" s="1"/>
-      <c r="XEV17" s="1"/>
-      <c r="XEW17" s="1"/>
-      <c r="XEX17" s="1"/>
-      <c r="XEY17" s="1"/>
-      <c r="XEZ17" s="1"/>
-      <c r="XFA17" s="1"/>
-      <c r="XFB17" s="1"/>
-      <c r="XFC17" s="1"/>
-      <c r="XFD17" s="1"/>
-    </row>
-    <row r="18" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="XES18" s="1"/>
-      <c r="XET18" s="1"/>
-      <c r="XEU18" s="1"/>
-      <c r="XEV18" s="1"/>
-      <c r="XEW18" s="1"/>
-      <c r="XEX18" s="1"/>
-      <c r="XEY18" s="1"/>
-      <c r="XEZ18" s="1"/>
-      <c r="XFA18" s="1"/>
-      <c r="XFB18" s="1"/>
-      <c r="XFC18" s="1"/>
-      <c r="XFD18" s="1"/>
-    </row>
-    <row r="19" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="XES19" s="1"/>
-      <c r="XET19" s="1"/>
-      <c r="XEU19" s="1"/>
-      <c r="XEV19" s="1"/>
-      <c r="XEW19" s="1"/>
-      <c r="XEX19" s="1"/>
-      <c r="XEY19" s="1"/>
-      <c r="XEZ19" s="1"/>
-      <c r="XFA19" s="1"/>
-      <c r="XFB19" s="1"/>
-      <c r="XFC19" s="1"/>
-      <c r="XFD19" s="1"/>
-    </row>
-    <row r="20" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>0</v>
-      </c>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C16" s="1">
+        <v>2101</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E16" s="1">
+        <v>2</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="1">
+        <v>5</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C17" s="1">
+        <v>2102</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C18" s="1">
+        <v>2103</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="1">
+        <v>5</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="C19" s="1">
+        <v>2104</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E19" s="1">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C20" s="1">
-        <v>2101</v>
+        <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5062,52 +5664,33 @@
         <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>20011</v>
+        <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>130</v>
+        <v>231</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="XES20" s="1"/>
-      <c r="XET20" s="1"/>
-      <c r="XEU20" s="1"/>
-      <c r="XEV20" s="1"/>
-      <c r="XEW20" s="1"/>
-      <c r="XEX20" s="1"/>
-      <c r="XEY20" s="1"/>
-      <c r="XEZ20" s="1"/>
-      <c r="XFA20" s="1"/>
-      <c r="XFB20" s="1"/>
-      <c r="XFC20" s="1"/>
-      <c r="XFD20" s="1"/>
-    </row>
-    <row r="21" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
+        <v>232</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="C21" s="1">
-        <v>2102</v>
+        <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5116,41 +5699,28 @@
         <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>20021</v>
+        <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>136</v>
+        <v>234</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="N21" s="1"/>
-      <c r="XES21" s="1"/>
-      <c r="XET21" s="1"/>
-      <c r="XEU21" s="1"/>
-      <c r="XEV21" s="1"/>
-      <c r="XEW21" s="1"/>
-      <c r="XEX21" s="1"/>
-      <c r="XEY21" s="1"/>
-      <c r="XEZ21" s="1"/>
-      <c r="XFA21" s="1"/>
-      <c r="XFB21" s="1"/>
-      <c r="XFC21" s="1"/>
-      <c r="XFD21" s="1"/>
-    </row>
-    <row r="22" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -5158,10 +5728,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="1">
-        <v>2103</v>
+        <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5170,93 +5740,30 @@
         <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>20031</v>
+        <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>139</v>
+        <v>237</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>116</v>
+        <v>158</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="N22" s="1"/>
-      <c r="XES22" s="1"/>
-      <c r="XET22" s="1"/>
-      <c r="XEU22" s="1"/>
-      <c r="XEV22" s="1"/>
-      <c r="XEW22" s="1"/>
-      <c r="XEX22" s="1"/>
-      <c r="XEY22" s="1"/>
-      <c r="XEZ22" s="1"/>
-      <c r="XFA22" s="1"/>
-      <c r="XFB22" s="1"/>
-      <c r="XFC22" s="1"/>
-      <c r="XFD22" s="1"/>
-    </row>
-    <row r="23" customFormat="1" customHeight="1" spans="1:14 16373:16384">
-      <c r="A23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1">
-        <v>2104</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E23" s="1">
-        <v>2</v>
-      </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>20041</v>
-      </c>
-      <c r="H23" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="K23" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="L23" s="1">
-        <v>5</v>
-      </c>
-      <c r="M23" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="N23" s="1"/>
-      <c r="XES23" s="1"/>
-      <c r="XET23" s="1"/>
-      <c r="XEU23" s="1"/>
-      <c r="XEV23" s="1"/>
-      <c r="XEW23" s="1"/>
-      <c r="XEX23" s="1"/>
-      <c r="XEY23" s="1"/>
-      <c r="XEZ23" s="1"/>
-      <c r="XFA23" s="1"/>
-      <c r="XFB23" s="1"/>
-      <c r="XFC23" s="1"/>
-      <c r="XFD23" s="1"/>
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="D23" s="6"/>
+      <c r="M23" s="6"/>
     </row>
     <row r="24" customFormat="1" customHeight="1" spans="1:14 16373:16384">
       <c r="A24" s="1" t="s">
@@ -5266,10 +5773,10 @@
         <v>0</v>
       </c>
       <c r="C24" s="1">
-        <v>2105</v>
+        <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5278,27 +5785,27 @@
         <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>20051</v>
+        <v>20011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="N24" s="1"/>
+        <v>240</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="XES24" s="1"/>
       <c r="XET24" s="1"/>
       <c r="XEU24" s="1"/>
@@ -5320,10 +5827,10 @@
         <v>0</v>
       </c>
       <c r="C25" s="1">
-        <v>2106</v>
+        <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5332,25 +5839,25 @@
         <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>20061</v>
+        <v>20021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="N25" s="1"/>
       <c r="XES25" s="1"/>
@@ -5374,10 +5881,10 @@
         <v>0</v>
       </c>
       <c r="C26" s="1">
-        <v>2107</v>
+        <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5386,25 +5893,25 @@
         <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>20071</v>
+        <v>20031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="N26" s="1"/>
       <c r="XES26" s="1"/>
@@ -5427,17 +5934,39 @@
       <c r="B27" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="6"/>
+      <c r="C27" s="1">
+        <v>2104</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E27" s="1">
+        <v>2</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>20041</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="L27" s="1">
+        <v>5</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>246</v>
+      </c>
       <c r="N27" s="1"/>
       <c r="XES27" s="1"/>
       <c r="XET27" s="1"/>
@@ -5460,37 +5989,37 @@
         <v>0</v>
       </c>
       <c r="C28" s="1">
-        <v>2201</v>
+        <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
       </c>
       <c r="F28" s="1">
-        <v>2101</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>20012</v>
+        <v>20051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="L28" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
       <c r="N28" s="1"/>
       <c r="XES28" s="1"/>
@@ -5514,37 +6043,37 @@
         <v>0</v>
       </c>
       <c r="C29" s="1">
-        <v>2202</v>
+        <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
       </c>
       <c r="F29" s="1">
-        <v>2102</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>20022</v>
+        <v>20061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="L29" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="N29" s="1"/>
       <c r="XES29" s="1"/>
@@ -5568,37 +6097,37 @@
         <v>0</v>
       </c>
       <c r="C30" s="1">
-        <v>2203</v>
+        <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
       </c>
       <c r="F30" s="1">
-        <v>2103</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>20032</v>
+        <v>20071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="L30" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>209</v>
+        <v>252</v>
       </c>
       <c r="N30" s="1"/>
       <c r="XES30" s="1"/>
@@ -5621,39 +6150,17 @@
       <c r="B31" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C31" s="1">
-        <v>2205</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="E31" s="1">
-        <v>2</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2105</v>
-      </c>
-      <c r="G31" s="1">
-        <v>20052</v>
-      </c>
-      <c r="H31" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="L31" s="1">
-        <v>5</v>
-      </c>
-      <c r="M31" s="6" t="s">
-        <v>211</v>
-      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="6"/>
       <c r="N31" s="1"/>
       <c r="XES31" s="1"/>
       <c r="XET31" s="1"/>
@@ -5676,37 +6183,37 @@
         <v>0</v>
       </c>
       <c r="C32" s="1">
-        <v>2207</v>
+        <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
       </c>
       <c r="F32" s="1">
-        <v>2107</v>
+        <v>2101</v>
       </c>
       <c r="G32" s="1">
-        <v>20072</v>
+        <v>20012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>133</v>
+        <v>127</v>
+      </c>
+      <c r="K32" s="10" t="s">
+        <v>181</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="N32" s="1"/>
       <c r="XES32" s="1"/>
@@ -5729,17 +6236,39 @@
       <c r="B33" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="6"/>
+      <c r="C33" s="1">
+        <v>2202</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2102</v>
+      </c>
+      <c r="G33" s="1">
+        <v>20022</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="K33" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="L33" s="1">
+        <v>6</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>256</v>
+      </c>
       <c r="N33" s="1"/>
       <c r="XES33" s="1"/>
       <c r="XET33" s="1"/>
@@ -5762,37 +6291,37 @@
         <v>0</v>
       </c>
       <c r="C34" s="1">
-        <v>2302</v>
+        <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>214</v>
+        <v>257</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
       </c>
       <c r="F34" s="1">
-        <v>2202</v>
+        <v>2103</v>
       </c>
       <c r="G34" s="1">
-        <v>20023</v>
+        <v>20032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="N34" s="1"/>
       <c r="XES34" s="1"/>
@@ -5808,7 +6337,7 @@
       <c r="XFC34" s="1"/>
       <c r="XFD34" s="1"/>
     </row>
-    <row r="35" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="35" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -5816,37 +6345,37 @@
         <v>0</v>
       </c>
       <c r="C35" s="1">
-        <v>2304</v>
+        <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
       </c>
       <c r="F35" s="1">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="G35" s="1">
-        <v>20043</v>
+        <v>20052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>133</v>
+        <v>113</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="L35" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="N35" s="1"/>
       <c r="XES35" s="1"/>
@@ -5862,7 +6391,7 @@
       <c r="XFC35" s="1"/>
       <c r="XFD35" s="1"/>
     </row>
-    <row r="36" customHeight="1" spans="1:18 16373:16384">
+    <row r="36" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
@@ -5870,60 +6399,85 @@
         <v>0</v>
       </c>
       <c r="C36" s="1">
-        <v>2307</v>
+        <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
       </c>
       <c r="F36" s="1">
-        <v>2207</v>
+        <v>2107</v>
       </c>
       <c r="G36" s="1">
-        <v>20073</v>
+        <v>20072</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L36" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="1"/>
-    </row>
-    <row r="37" customHeight="1" spans="1:18 16373:16384">
+      <c r="XES36" s="1"/>
+      <c r="XET36" s="1"/>
+      <c r="XEU36" s="1"/>
+      <c r="XEV36" s="1"/>
+      <c r="XEW36" s="1"/>
+      <c r="XEX36" s="1"/>
+      <c r="XEY36" s="1"/>
+      <c r="XEZ36" s="1"/>
+      <c r="XFA36" s="1"/>
+      <c r="XFB36" s="1"/>
+      <c r="XFC36" s="1"/>
+      <c r="XFD36" s="1"/>
+    </row>
+    <row r="37" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C37" s="1"/>
       <c r="D37" s="6"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="6"/>
       <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="1"/>
-    </row>
-    <row r="38" customHeight="1" spans="1:18 16373:16384">
+      <c r="XES37" s="1"/>
+      <c r="XET37" s="1"/>
+      <c r="XEU37" s="1"/>
+      <c r="XEV37" s="1"/>
+      <c r="XEW37" s="1"/>
+      <c r="XEX37" s="1"/>
+      <c r="XEY37" s="1"/>
+      <c r="XEZ37" s="1"/>
+      <c r="XFA37" s="1"/>
+      <c r="XFB37" s="1"/>
+      <c r="XFC37" s="1"/>
+      <c r="XFD37" s="1"/>
+    </row>
+    <row r="38" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -5931,45 +6485,53 @@
         <v>0</v>
       </c>
       <c r="C38" s="1">
-        <v>2402</v>
+        <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
       </c>
       <c r="F38" s="1">
-        <v>2302</v>
+        <v>2202</v>
       </c>
       <c r="G38" s="1">
-        <v>20024</v>
+        <v>20023</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L38" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="1"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:18 16373:16384">
+      <c r="XES38" s="1"/>
+      <c r="XET38" s="1"/>
+      <c r="XEU38" s="1"/>
+      <c r="XEV38" s="1"/>
+      <c r="XEW38" s="1"/>
+      <c r="XEX38" s="1"/>
+      <c r="XEY38" s="1"/>
+      <c r="XEZ38" s="1"/>
+      <c r="XFA38" s="1"/>
+      <c r="XFB38" s="1"/>
+      <c r="XFC38" s="1"/>
+      <c r="XFD38" s="1"/>
+    </row>
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -5977,45 +6539,92 @@
         <v>0</v>
       </c>
       <c r="C39" s="1">
-        <v>2403</v>
+        <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>222</v>
+        <v>265</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
       </c>
       <c r="F39" s="1">
-        <v>2203</v>
+        <v>2104</v>
       </c>
       <c r="G39" s="1">
-        <v>20034</v>
+        <v>20043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L39" s="1">
+        <v>6</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="N39" s="1"/>
+      <c r="XES39" s="1"/>
+      <c r="XET39" s="1"/>
+      <c r="XEU39" s="1"/>
+      <c r="XEV39" s="1"/>
+      <c r="XEW39" s="1"/>
+      <c r="XEX39" s="1"/>
+      <c r="XEY39" s="1"/>
+      <c r="XEZ39" s="1"/>
+      <c r="XFA39" s="1"/>
+      <c r="XFB39" s="1"/>
+      <c r="XFC39" s="1"/>
+      <c r="XFD39" s="1"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:18 16373:16384">
+      <c r="A40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="1">
+        <v>2307</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E40" s="1">
+        <v>2</v>
+      </c>
+      <c r="F40" s="1">
+        <v>2207</v>
+      </c>
+      <c r="G40" s="1">
+        <v>20073</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L40" s="1">
         <v>7</v>
       </c>
-      <c r="M39" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="1"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:18 16373:16384">
+      <c r="M40" s="6" t="s">
+        <v>268</v>
+      </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="6"/>
@@ -6023,6 +6632,14 @@
       <c r="R40" s="1"/>
     </row>
     <row r="41" customHeight="1" spans="1:18 16373:16384">
+      <c r="A41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="M41" s="6"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="6"/>
@@ -6030,6 +6647,45 @@
       <c r="R41" s="1"/>
     </row>
     <row r="42" customHeight="1" spans="1:18 16373:16384">
+      <c r="A42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="1">
+        <v>2402</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E42" s="1">
+        <v>2</v>
+      </c>
+      <c r="F42" s="1">
+        <v>2302</v>
+      </c>
+      <c r="G42" s="1">
+        <v>20024</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L42" s="1">
+        <v>7</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>270</v>
+      </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="6"/>
@@ -6037,9 +6693,48 @@
       <c r="R42" s="1"/>
     </row>
     <row r="43" customHeight="1" spans="1:18 16373:16384">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="1">
+        <v>2403</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="E43" s="1">
+        <v>2</v>
+      </c>
+      <c r="F43" s="1">
+        <v>2203</v>
+      </c>
+      <c r="G43" s="1">
+        <v>20034</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="L43" s="1">
+        <v>7</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>272</v>
+      </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
+      <c r="P43" s="6"/>
       <c r="Q43" s="6"/>
       <c r="R43" s="1"/>
     </row>
@@ -6050,167 +6745,195 @@
       <c r="Q44" s="6"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="2"/>
+    <row r="45" customHeight="1" spans="1:18 16373:16384">
+      <c r="N45" s="1"/>
       <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
+      <c r="P45" s="6"/>
       <c r="Q45" s="6"/>
       <c r="R45" s="1"/>
-      <c r="XES45" s="1"/>
-      <c r="XET45" s="1"/>
-      <c r="XEU45" s="1"/>
-      <c r="XEV45" s="1"/>
-      <c r="XEW45" s="1"/>
-      <c r="XEX45" s="1"/>
-      <c r="XEY45" s="1"/>
-      <c r="XEZ45" s="1"/>
-      <c r="XFA45" s="1"/>
-      <c r="XFB45" s="1"/>
-      <c r="XFC45" s="1"/>
-      <c r="XFD45" s="1"/>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="2"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:18 16373:16384">
+      <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
       <c r="R46" s="1"/>
-      <c r="XES46" s="1"/>
-      <c r="XET46" s="1"/>
-      <c r="XEU46" s="1"/>
-      <c r="XEV46" s="1"/>
-      <c r="XEW46" s="1"/>
-      <c r="XEX46" s="1"/>
-      <c r="XEY46" s="1"/>
-      <c r="XEZ46" s="1"/>
-      <c r="XFA46" s="1"/>
-      <c r="XFB46" s="1"/>
-      <c r="XFC46" s="1"/>
-      <c r="XFD46" s="1"/>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="2"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:18 16373:16384">
+      <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="6"/>
       <c r="R47" s="1"/>
-      <c r="XES47" s="1"/>
-      <c r="XET47" s="1"/>
-      <c r="XEU47" s="1"/>
-      <c r="XEV47" s="1"/>
-      <c r="XEW47" s="1"/>
-      <c r="XEX47" s="1"/>
-      <c r="XEY47" s="1"/>
-      <c r="XEZ47" s="1"/>
-      <c r="XFA47" s="1"/>
-      <c r="XFB47" s="1"/>
-      <c r="XFC47" s="1"/>
-      <c r="XFD47" s="1"/>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="2"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:18 16373:16384">
+      <c r="N48" s="1"/>
       <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="6"/>
       <c r="R48" s="1"/>
-      <c r="XES48" s="1"/>
-      <c r="XET48" s="1"/>
-      <c r="XEU48" s="1"/>
-      <c r="XEV48" s="1"/>
-      <c r="XEW48" s="1"/>
-      <c r="XEX48" s="1"/>
-      <c r="XEY48" s="1"/>
-      <c r="XEZ48" s="1"/>
-      <c r="XFA48" s="1"/>
-      <c r="XFB48" s="1"/>
-      <c r="XFC48" s="1"/>
-      <c r="XFD48" s="1"/>
-    </row>
-    <row r="49" customHeight="1" spans="15:18">
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="2"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="6"/>
       <c r="R49" s="1"/>
-    </row>
-    <row r="50" customHeight="1" spans="15:18">
+      <c r="XES49" s="1"/>
+      <c r="XET49" s="1"/>
+      <c r="XEU49" s="1"/>
+      <c r="XEV49" s="1"/>
+      <c r="XEW49" s="1"/>
+      <c r="XEX49" s="1"/>
+      <c r="XEY49" s="1"/>
+      <c r="XEZ49" s="1"/>
+      <c r="XFA49" s="1"/>
+      <c r="XFB49" s="1"/>
+      <c r="XFC49" s="1"/>
+      <c r="XFD49" s="1"/>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="2"/>
       <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
+      <c r="P50" s="6"/>
       <c r="Q50" s="6"/>
       <c r="R50" s="1"/>
-    </row>
-    <row r="51" customHeight="1" spans="15:18">
+      <c r="XES50" s="1"/>
+      <c r="XET50" s="1"/>
+      <c r="XEU50" s="1"/>
+      <c r="XEV50" s="1"/>
+      <c r="XEW50" s="1"/>
+      <c r="XEX50" s="1"/>
+      <c r="XEY50" s="1"/>
+      <c r="XEZ50" s="1"/>
+      <c r="XFA50" s="1"/>
+      <c r="XFB50" s="1"/>
+      <c r="XFC50" s="1"/>
+      <c r="XFD50" s="1"/>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="2"/>
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
       <c r="Q51" s="6"/>
       <c r="R51" s="1"/>
-    </row>
-    <row r="52" customHeight="1" spans="15:18">
+      <c r="XES51" s="1"/>
+      <c r="XET51" s="1"/>
+      <c r="XEU51" s="1"/>
+      <c r="XEV51" s="1"/>
+      <c r="XEW51" s="1"/>
+      <c r="XEX51" s="1"/>
+      <c r="XEY51" s="1"/>
+      <c r="XEZ51" s="1"/>
+      <c r="XFA51" s="1"/>
+      <c r="XFB51" s="1"/>
+      <c r="XFC51" s="1"/>
+      <c r="XFD51" s="1"/>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="2"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="15:18">
+      <c r="XES52" s="1"/>
+      <c r="XET52" s="1"/>
+      <c r="XEU52" s="1"/>
+      <c r="XEV52" s="1"/>
+      <c r="XEW52" s="1"/>
+      <c r="XEX52" s="1"/>
+      <c r="XEY52" s="1"/>
+      <c r="XEZ52" s="1"/>
+      <c r="XFA52" s="1"/>
+      <c r="XFB52" s="1"/>
+      <c r="XFC52" s="1"/>
+      <c r="XFD52" s="1"/>
+    </row>
+    <row r="53" customHeight="1" spans="3:18 16373:16384">
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
+      <c r="Q53" s="6"/>
       <c r="R53" s="1"/>
     </row>
-    <row r="54" customHeight="1" spans="15:18">
+    <row r="54" customHeight="1" spans="3:18 16373:16384">
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
       <c r="Q54" s="6"/>
       <c r="R54" s="1"/>
     </row>
-    <row r="55" customHeight="1" spans="15:18">
+    <row r="55" customHeight="1" spans="3:18 16373:16384">
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
       <c r="Q55" s="6"/>
       <c r="R55" s="1"/>
+    </row>
+    <row r="56" customHeight="1" spans="3:18 16373:16384">
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1"/>
+    </row>
+    <row r="57" customHeight="1" spans="3:18 16373:16384">
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+    </row>
+    <row r="58" customHeight="1" spans="3:18 16373:16384">
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="1"/>
+    </row>
+    <row r="59" customHeight="1" spans="3:18 16373:16384">
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="Q59" s="6"/>
+      <c r="R59" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6372,7 +7095,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -6384,23 +7107,22 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>225</v>
+        <v>274</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1" t="s">
-        <v>226</v>
+      <c r="M6" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -6408,7 +7130,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>227</v>
+        <v>275</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -6420,23 +7142,22 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>31</v>
+        <v>103</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1" t="s">
-        <v>229</v>
+      <c r="M7" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -6444,7 +7165,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -6456,19 +7177,22 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>38</v>
+        <v>106</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="N8" s="2"/>
     </row>
@@ -6477,7 +7201,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>232</v>
+        <v>277</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -6489,20 +7213,23 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
       </c>
+      <c r="M9" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="N9"/>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -6516,7 +7243,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -6528,20 +7255,23 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
       </c>
+      <c r="M10" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="N10"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -6555,7 +7285,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -6567,20 +7297,23 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
       </c>
+      <c r="M11" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="N11"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -6594,7 +7327,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>238</v>
+        <v>282</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -6606,20 +7339,23 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>239</v>
+        <v>283</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
       </c>
+      <c r="M12" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="N12"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -6633,7 +7369,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -6645,20 +7381,23 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
       </c>
+      <c r="M13" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="N13"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -6672,7 +7411,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -6684,48 +7423,278 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
       </c>
+      <c r="M14" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="N14"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="N15"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="N16"/>
+      <c r="C16" s="1">
+        <v>3101</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L16" s="1">
+        <v>5</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="D17" s="4"/>
-      <c r="N17"/>
+      <c r="C17" s="1">
+        <v>3102</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E17" s="1">
+        <v>3</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>293</v>
+      </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="D18" s="4"/>
-      <c r="N18"/>
+      <c r="C18" s="1">
+        <v>3103</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1">
+        <v>0</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="1">
+        <v>5</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="D19" s="4"/>
-      <c r="N19"/>
+      <c r="C19" s="1">
+        <v>3104</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1">
+        <v>0</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>299</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="N20"/>
+      <c r="C20" s="1">
+        <v>3105</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>301</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L20" s="1">
+        <v>5</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="N21"/>
+      <c r="C21" s="1">
+        <v>3106</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E21" s="1">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
+      <c r="G21" s="1">
+        <v>0</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L21" s="1">
+        <v>5</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="N22"/>
+      <c r="A22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3107</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="E22" s="1">
+        <v>3</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="L22" s="1">
+        <v>5</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="N23"/>
@@ -6741,7 +7710,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -6753,22 +7722,22 @@
         <v>30011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>245</v>
+        <v>310</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -6783,7 +7752,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>246</v>
+        <v>311</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -6795,22 +7764,22 @@
         <v>30021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>247</v>
+        <v>312</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -6825,7 +7794,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>248</v>
+        <v>313</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -6837,22 +7806,22 @@
         <v>30031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -6867,7 +7836,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>250</v>
+        <v>315</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -6879,22 +7848,22 @@
         <v>30041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>251</v>
+        <v>316</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -6909,7 +7878,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>252</v>
+        <v>317</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -6921,22 +7890,22 @@
         <v>30051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>253</v>
+        <v>318</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -6951,7 +7920,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>254</v>
+        <v>319</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -6963,22 +7932,22 @@
         <v>30061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>143</v>
+        <v>174</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>255</v>
+        <v>320</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -6993,7 +7962,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>256</v>
+        <v>321</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7005,22 +7974,22 @@
         <v>30071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>257</v>
+        <v>322</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -7044,7 +8013,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>258</v>
+        <v>323</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -7056,22 +8025,22 @@
         <v>30012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>259</v>
+        <v>324</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -7086,7 +8055,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>260</v>
+        <v>325</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -7098,22 +8067,22 @@
         <v>30022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>261</v>
+        <v>326</v>
       </c>
       <c r="N33" s="2"/>
     </row>
@@ -7128,7 +8097,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -7140,22 +8109,22 @@
         <v>30032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>263</v>
+        <v>328</v>
       </c>
       <c r="N34" s="2"/>
     </row>
@@ -7170,7 +8139,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>264</v>
+        <v>329</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -7182,22 +8151,22 @@
         <v>30052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>265</v>
+        <v>330</v>
       </c>
       <c r="N35" s="2"/>
     </row>
@@ -7221,7 +8190,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>266</v>
+        <v>331</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -7233,22 +8202,22 @@
         <v>30023</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>267</v>
+        <v>332</v>
       </c>
       <c r="N37" s="2"/>
     </row>
@@ -7263,7 +8232,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>268</v>
+        <v>333</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -7275,22 +8244,22 @@
         <v>30033</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>269</v>
+        <v>334</v>
       </c>
       <c r="N38" s="2"/>
     </row>
@@ -7305,7 +8274,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>270</v>
+        <v>335</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -7317,22 +8286,22 @@
         <v>30043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>271</v>
+        <v>336</v>
       </c>
       <c r="N39" s="2"/>
     </row>
@@ -7347,7 +8316,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>272</v>
+        <v>337</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -7359,22 +8328,22 @@
         <v>30073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>273</v>
+        <v>338</v>
       </c>
       <c r="N40" s="2"/>
     </row>
@@ -7400,7 +8369,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>274</v>
+        <v>339</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -7412,22 +8381,22 @@
         <v>30024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>275</v>
+        <v>340</v>
       </c>
       <c r="N42" s="2"/>
     </row>
@@ -7442,7 +8411,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>276</v>
+        <v>341</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -7454,22 +8423,22 @@
         <v>30034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>277</v>
+        <v>342</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="344">
   <si>
     <t>#</t>
   </si>
@@ -239,7 +239,7 @@
     <t>1,1,1</t>
   </si>
   <si>
-    <t>聚兽号角</t>
+    <t>宠物袋</t>
   </si>
   <si>
     <t>2003,111,95</t>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>装备词条套装所需数量-1</t>
+  </si>
+  <si>
+    <t>勇气号角</t>
   </si>
   <si>
     <t>2003,95</t>
@@ -2887,7 +2890,7 @@
         <v>104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -2899,10 +2902,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J27" s="10" t="s">
         <v>81</v>
@@ -2914,10 +2917,10 @@
         <v>6</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2925,7 +2928,7 @@
         <v>105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -2937,10 +2940,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J28" s="10" t="s">
         <v>72</v>
@@ -2952,7 +2955,7 @@
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2960,7 +2963,7 @@
         <v>106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -2972,10 +2975,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J29" s="10" t="s">
         <v>81</v>
@@ -2987,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1"/>
@@ -3011,7 +3014,7 @@
         <v>102</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E39" s="1">
         <v>0</v>
@@ -3023,10 +3026,10 @@
         <v>0</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J39" s="10" t="s">
         <v>81</v>
@@ -3038,10 +3041,10 @@
         <v>6</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3204,7 +3207,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -3216,16 +3219,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -3234,7 +3237,7 @@
         <v>21</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3242,7 +3245,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3254,16 +3257,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -3272,7 +3275,7 @@
         <v>21</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3280,7 +3283,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -3292,16 +3295,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -3310,7 +3313,7 @@
         <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3318,7 +3321,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -3330,16 +3333,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
@@ -3348,7 +3351,7 @@
         <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3362,7 +3365,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3374,16 +3377,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -3403,7 +3406,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3415,16 +3418,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -3444,7 +3447,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3456,16 +3459,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -3485,7 +3488,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3497,16 +3500,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -3526,7 +3529,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3538,16 +3541,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -3565,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3577,7 +3580,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="M17" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3588,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
@@ -3597,7 +3600,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3609,22 +3612,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3632,7 +3635,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3644,22 +3647,22 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3667,7 +3670,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3679,22 +3682,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3702,7 +3705,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3714,22 +3717,22 @@
         <v>0</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3737,7 +3740,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3749,22 +3752,22 @@
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3772,7 +3775,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3784,22 +3787,22 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3813,7 +3816,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3825,22 +3828,22 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
@@ -3856,7 +3859,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3868,22 +3871,22 @@
         <v>10011</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3897,7 +3900,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3909,22 +3912,22 @@
         <v>10021</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3938,7 +3941,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3950,22 +3953,22 @@
         <v>10031</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3979,7 +3982,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3991,22 +3994,22 @@
         <v>10041</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4020,7 +4023,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -4032,22 +4035,22 @@
         <v>10051</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4061,7 +4064,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -4073,22 +4076,22 @@
         <v>10061</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4102,7 +4105,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -4114,22 +4117,22 @@
         <v>10071</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="R35" s="6"/>
     </row>
@@ -4155,7 +4158,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4167,22 +4170,22 @@
         <v>10012</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R37" s="6"/>
     </row>
@@ -4197,7 +4200,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4209,22 +4212,22 @@
         <v>10022</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="R38" s="6"/>
     </row>
@@ -4239,7 +4242,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4251,22 +4254,22 @@
         <v>10032</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="1"/>
@@ -4283,7 +4286,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4295,22 +4298,22 @@
         <v>10042</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O40" s="6"/>
       <c r="P40" s="1"/>
@@ -4327,7 +4330,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4339,22 +4342,22 @@
         <v>10052</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O41" s="6"/>
       <c r="R41" s="6"/>
@@ -4370,7 +4373,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4382,22 +4385,22 @@
         <v>10072</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O42" s="6"/>
       <c r="P42" s="1"/>
@@ -4426,7 +4429,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4438,22 +4441,22 @@
         <v>10023</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="1"/>
@@ -4470,7 +4473,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4482,22 +4485,22 @@
         <v>10073</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O45" s="6"/>
       <c r="P45" s="1"/>
@@ -4526,7 +4529,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4538,22 +4541,22 @@
         <v>10024</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -4571,7 +4574,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4583,22 +4586,22 @@
         <v>10034</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="6"/>
@@ -5030,7 +5033,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -5042,16 +5045,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -5079,7 +5082,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -5091,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -5128,7 +5131,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -5140,16 +5143,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -5177,7 +5180,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -5189,16 +5192,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -5230,7 +5233,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -5242,16 +5245,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -5283,7 +5286,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -5295,16 +5298,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -5336,7 +5339,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5348,16 +5351,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -5389,7 +5392,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5401,16 +5404,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -5442,7 +5445,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5454,16 +5457,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -5515,7 +5518,7 @@
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5527,22 +5530,22 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5550,7 +5553,7 @@
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5562,22 +5565,22 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5585,7 +5588,7 @@
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5597,22 +5600,22 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5620,7 +5623,7 @@
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5632,22 +5635,22 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5655,7 +5658,7 @@
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5667,22 +5670,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5690,7 +5693,7 @@
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5702,22 +5705,22 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5731,7 +5734,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5743,22 +5746,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5776,7 +5779,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5788,22 +5791,22 @@
         <v>20011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N24" s="2"/>
       <c r="XES24" s="1"/>
@@ -5830,7 +5833,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5842,22 +5845,22 @@
         <v>20021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N25" s="1"/>
       <c r="XES25" s="1"/>
@@ -5884,7 +5887,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5896,22 +5899,22 @@
         <v>20031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N26" s="1"/>
       <c r="XES26" s="1"/>
@@ -5938,7 +5941,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5950,22 +5953,22 @@
         <v>20041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N27" s="1"/>
       <c r="XES27" s="1"/>
@@ -5992,7 +5995,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -6004,22 +6007,22 @@
         <v>20051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N28" s="1"/>
       <c r="XES28" s="1"/>
@@ -6046,7 +6049,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -6058,22 +6061,22 @@
         <v>20061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N29" s="1"/>
       <c r="XES29" s="1"/>
@@ -6100,7 +6103,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -6112,22 +6115,22 @@
         <v>20071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N30" s="1"/>
       <c r="XES30" s="1"/>
@@ -6186,7 +6189,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -6198,22 +6201,22 @@
         <v>20012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N32" s="1"/>
       <c r="XES32" s="1"/>
@@ -6240,7 +6243,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -6252,22 +6255,22 @@
         <v>20022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N33" s="1"/>
       <c r="XES33" s="1"/>
@@ -6294,7 +6297,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -6306,22 +6309,22 @@
         <v>20032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N34" s="1"/>
       <c r="XES34" s="1"/>
@@ -6348,7 +6351,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6360,22 +6363,22 @@
         <v>20052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N35" s="1"/>
       <c r="XES35" s="1"/>
@@ -6402,7 +6405,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6414,22 +6417,22 @@
         <v>20072</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N36" s="1"/>
       <c r="XES36" s="1"/>
@@ -6488,7 +6491,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6500,22 +6503,22 @@
         <v>20023</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N38" s="1"/>
       <c r="XES38" s="1"/>
@@ -6542,7 +6545,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6554,22 +6557,22 @@
         <v>20043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N39" s="1"/>
       <c r="XES39" s="1"/>
@@ -6596,7 +6599,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6608,22 +6611,22 @@
         <v>20073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
@@ -6657,7 +6660,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6669,22 +6672,22 @@
         <v>20024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
@@ -6703,7 +6706,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6715,22 +6718,22 @@
         <v>20034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
@@ -7095,7 +7098,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -7107,16 +7110,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -7130,7 +7133,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -7142,16 +7145,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -7165,7 +7168,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -7177,16 +7180,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -7201,7 +7204,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -7213,16 +7216,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -7243,7 +7246,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -7255,16 +7258,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -7285,7 +7288,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -7297,16 +7300,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -7327,7 +7330,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7339,16 +7342,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -7369,7 +7372,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7381,16 +7384,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -7411,7 +7414,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7423,16 +7426,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -7450,7 +7453,7 @@
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7462,22 +7465,22 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7485,7 +7488,7 @@
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7497,22 +7500,22 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7520,7 +7523,7 @@
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7532,22 +7535,22 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7555,7 +7558,7 @@
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7567,22 +7570,22 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7590,7 +7593,7 @@
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7602,22 +7605,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7625,7 +7628,7 @@
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7637,22 +7640,22 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7666,7 +7669,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7678,22 +7681,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7710,7 +7713,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7722,22 +7725,22 @@
         <v>30011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -7752,7 +7755,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7764,22 +7767,22 @@
         <v>30021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -7794,7 +7797,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7806,22 +7809,22 @@
         <v>30031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -7836,7 +7839,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7848,22 +7851,22 @@
         <v>30041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -7878,7 +7881,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7890,22 +7893,22 @@
         <v>30051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -7920,7 +7923,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7932,22 +7935,22 @@
         <v>30061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -7962,7 +7965,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7974,22 +7977,22 @@
         <v>30071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -8013,7 +8016,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -8025,22 +8028,22 @@
         <v>30012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -8055,7 +8058,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -8067,22 +8070,22 @@
         <v>30022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N33" s="2"/>
     </row>
@@ -8097,7 +8100,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -8109,22 +8112,22 @@
         <v>30032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N34" s="2"/>
     </row>
@@ -8139,7 +8142,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -8151,22 +8154,22 @@
         <v>30052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N35" s="2"/>
     </row>
@@ -8190,7 +8193,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -8202,22 +8205,22 @@
         <v>30023</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N37" s="2"/>
     </row>
@@ -8232,7 +8235,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -8244,22 +8247,22 @@
         <v>30033</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N38" s="2"/>
     </row>
@@ -8274,7 +8277,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -8286,22 +8289,22 @@
         <v>30043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N39" s="2"/>
     </row>
@@ -8316,7 +8319,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8328,22 +8331,22 @@
         <v>30073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N40" s="2"/>
     </row>
@@ -8369,7 +8372,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8381,22 +8384,22 @@
         <v>30024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N42" s="2"/>
     </row>
@@ -8411,7 +8414,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8423,22 +8426,22 @@
         <v>30034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1062" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="340">
   <si>
     <t>#</t>
   </si>
@@ -309,18 +309,6 @@
   </si>
   <si>
     <t>解锁传世超级挑战</t>
-  </si>
-  <si>
-    <t>驯兽金印</t>
-  </si>
-  <si>
-    <t>2003,112,95</t>
-  </si>
-  <si>
-    <t>10,1,10</t>
-  </si>
-  <si>
-    <t>增加一个宠物备出战位</t>
   </si>
   <si>
     <t>粗铁刀</t>
@@ -2997,55 +2985,14 @@
     <row r="31" s="1" customFormat="1" customHeight="1"/>
     <row r="32" s="1" customFormat="1" customHeight="1"/>
     <row r="33" s="1" customFormat="1" customHeight="1"/>
-    <row r="35" customHeight="1" spans="1:14">
+    <row r="35" customHeight="1" spans="4:14">
       <c r="N35" s="1"/>
     </row>
-    <row r="36" customHeight="1" spans="1:14">
+    <row r="36" customHeight="1" spans="4:14">
       <c r="N36" s="1"/>
     </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C39" s="1">
-        <v>102</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="1">
-        <v>0</v>
-      </c>
-      <c r="F39" s="1">
-        <v>101</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
-      </c>
-      <c r="H39" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="K39" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="L39" s="1">
-        <v>6</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>96</v>
-      </c>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="4:14">
+      <c r="D39"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -3207,7 +3154,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -3219,16 +3166,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -3237,7 +3184,7 @@
         <v>21</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3245,7 +3192,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3257,16 +3204,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -3275,7 +3222,7 @@
         <v>21</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3283,7 +3230,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -3295,16 +3242,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -3313,7 +3260,7 @@
         <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3321,7 +3268,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -3333,16 +3280,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
@@ -3351,7 +3298,7 @@
         <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3365,7 +3312,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3377,16 +3324,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -3406,7 +3353,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3418,16 +3365,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -3447,7 +3394,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3459,16 +3406,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -3488,7 +3435,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3500,16 +3447,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -3529,7 +3476,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3541,16 +3488,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -3568,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3580,7 +3527,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="M17" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3591,7 +3538,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
@@ -3600,7 +3547,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3612,22 +3559,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3635,7 +3582,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3647,22 +3594,22 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3670,7 +3617,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3682,22 +3629,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3705,7 +3652,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3717,22 +3664,22 @@
         <v>0</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3740,7 +3687,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3752,22 +3699,22 @@
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3775,7 +3722,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3787,22 +3734,22 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3816,7 +3763,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3828,22 +3775,22 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
@@ -3859,7 +3806,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3871,22 +3818,22 @@
         <v>10011</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3900,7 +3847,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3912,22 +3859,22 @@
         <v>10021</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3941,7 +3888,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3953,22 +3900,22 @@
         <v>10031</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3982,7 +3929,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3994,22 +3941,22 @@
         <v>10041</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4023,7 +3970,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -4035,22 +3982,22 @@
         <v>10051</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4064,7 +4011,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -4076,22 +4023,22 @@
         <v>10061</v>
       </c>
       <c r="H34" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="K34" s="10" t="s">
         <v>171</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4105,7 +4052,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -4117,22 +4064,22 @@
         <v>10071</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="R35" s="6"/>
     </row>
@@ -4158,7 +4105,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4170,22 +4117,22 @@
         <v>10012</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="R37" s="6"/>
     </row>
@@ -4200,7 +4147,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4212,22 +4159,22 @@
         <v>10022</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="R38" s="6"/>
     </row>
@@ -4242,7 +4189,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4254,22 +4201,22 @@
         <v>10032</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="1"/>
@@ -4286,7 +4233,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4298,22 +4245,22 @@
         <v>10042</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="O40" s="6"/>
       <c r="P40" s="1"/>
@@ -4330,7 +4277,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4342,22 +4289,22 @@
         <v>10052</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="O41" s="6"/>
       <c r="R41" s="6"/>
@@ -4373,7 +4320,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4385,22 +4332,22 @@
         <v>10072</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="O42" s="6"/>
       <c r="P42" s="1"/>
@@ -4429,7 +4376,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4441,22 +4388,22 @@
         <v>10023</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="1"/>
@@ -4473,7 +4420,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4485,22 +4432,22 @@
         <v>10073</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="O45" s="6"/>
       <c r="P45" s="1"/>
@@ -4529,7 +4476,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4541,22 +4488,22 @@
         <v>10024</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -4574,7 +4521,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4586,22 +4533,22 @@
         <v>10034</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="6"/>
@@ -5033,7 +4980,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -5045,16 +4992,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -5082,7 +5029,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -5094,16 +5041,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -5131,7 +5078,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -5143,16 +5090,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -5180,7 +5127,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -5192,16 +5139,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -5233,7 +5180,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -5245,16 +5192,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -5286,7 +5233,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -5298,16 +5245,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -5339,7 +5286,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5351,16 +5298,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -5392,7 +5339,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5404,16 +5351,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -5445,7 +5392,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5457,16 +5404,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -5518,7 +5465,7 @@
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5530,22 +5477,22 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5553,7 +5500,7 @@
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5565,22 +5512,22 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5588,7 +5535,7 @@
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5600,22 +5547,22 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5623,7 +5570,7 @@
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5635,22 +5582,22 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5658,7 +5605,7 @@
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5670,22 +5617,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5693,7 +5640,7 @@
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5705,22 +5652,22 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5734,7 +5681,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5746,22 +5693,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5779,7 +5726,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5791,22 +5738,22 @@
         <v>20011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="N24" s="2"/>
       <c r="XES24" s="1"/>
@@ -5833,7 +5780,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5845,22 +5792,22 @@
         <v>20021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N25" s="1"/>
       <c r="XES25" s="1"/>
@@ -5887,7 +5834,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5899,22 +5846,22 @@
         <v>20031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="N26" s="1"/>
       <c r="XES26" s="1"/>
@@ -5941,7 +5888,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5953,22 +5900,22 @@
         <v>20041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="N27" s="1"/>
       <c r="XES27" s="1"/>
@@ -5995,7 +5942,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -6007,22 +5954,22 @@
         <v>20051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N28" s="1"/>
       <c r="XES28" s="1"/>
@@ -6049,7 +5996,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -6061,22 +6008,22 @@
         <v>20061</v>
       </c>
       <c r="H29" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="K29" s="10" t="s">
         <v>171</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="N29" s="1"/>
       <c r="XES29" s="1"/>
@@ -6103,7 +6050,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -6115,22 +6062,22 @@
         <v>20071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="N30" s="1"/>
       <c r="XES30" s="1"/>
@@ -6189,7 +6136,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -6201,22 +6148,22 @@
         <v>20012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="N32" s="1"/>
       <c r="XES32" s="1"/>
@@ -6243,7 +6190,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -6255,22 +6202,22 @@
         <v>20022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="N33" s="1"/>
       <c r="XES33" s="1"/>
@@ -6297,7 +6244,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -6309,22 +6256,22 @@
         <v>20032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="N34" s="1"/>
       <c r="XES34" s="1"/>
@@ -6351,7 +6298,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6363,22 +6310,22 @@
         <v>20052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="N35" s="1"/>
       <c r="XES35" s="1"/>
@@ -6405,7 +6352,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6417,22 +6364,22 @@
         <v>20072</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="N36" s="1"/>
       <c r="XES36" s="1"/>
@@ -6491,7 +6438,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6503,22 +6450,22 @@
         <v>20023</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="N38" s="1"/>
       <c r="XES38" s="1"/>
@@ -6545,7 +6492,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6557,22 +6504,22 @@
         <v>20043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="N39" s="1"/>
       <c r="XES39" s="1"/>
@@ -6599,7 +6546,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6611,22 +6558,22 @@
         <v>20073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
@@ -6660,7 +6607,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6672,22 +6619,22 @@
         <v>20024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
@@ -6706,7 +6653,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6718,22 +6665,22 @@
         <v>20034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
@@ -7098,7 +7045,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -7110,16 +7057,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -7133,7 +7080,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -7145,16 +7092,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -7168,7 +7115,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -7180,16 +7127,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -7204,7 +7151,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -7216,16 +7163,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -7246,7 +7193,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -7258,16 +7205,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -7288,7 +7235,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -7300,16 +7247,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -7330,7 +7277,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7342,16 +7289,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -7372,7 +7319,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7384,16 +7331,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -7414,7 +7361,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7426,16 +7373,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -7453,7 +7400,7 @@
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7465,22 +7412,22 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7488,7 +7435,7 @@
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7500,22 +7447,22 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7523,7 +7470,7 @@
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7535,22 +7482,22 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7558,7 +7505,7 @@
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7570,22 +7517,22 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7593,7 +7540,7 @@
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7605,22 +7552,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7628,7 +7575,7 @@
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7640,22 +7587,22 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7669,7 +7616,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7681,22 +7628,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7713,7 +7660,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7725,22 +7672,22 @@
         <v>30011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -7755,7 +7702,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7767,22 +7714,22 @@
         <v>30021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -7797,7 +7744,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7809,22 +7756,22 @@
         <v>30031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -7839,7 +7786,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7851,22 +7798,22 @@
         <v>30041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -7881,7 +7828,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7893,22 +7840,22 @@
         <v>30051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -7923,7 +7870,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7935,22 +7882,22 @@
         <v>30061</v>
       </c>
       <c r="H29" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="K29" s="10" t="s">
         <v>171</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -7965,7 +7912,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7977,22 +7924,22 @@
         <v>30071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -8016,7 +7963,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -8028,22 +7975,22 @@
         <v>30012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -8058,7 +8005,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -8070,22 +8017,22 @@
         <v>30022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="N33" s="2"/>
     </row>
@@ -8100,7 +8047,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -8112,22 +8059,22 @@
         <v>30032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="N34" s="2"/>
     </row>
@@ -8142,7 +8089,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -8154,22 +8101,22 @@
         <v>30052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="N35" s="2"/>
     </row>
@@ -8193,7 +8140,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -8205,22 +8152,22 @@
         <v>30023</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N37" s="2"/>
     </row>
@@ -8235,7 +8182,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -8247,22 +8194,22 @@
         <v>30033</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="N38" s="2"/>
     </row>
@@ -8277,7 +8224,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -8289,22 +8236,22 @@
         <v>30043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="N39" s="2"/>
     </row>
@@ -8319,7 +8266,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8331,22 +8278,22 @@
         <v>30073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N40" s="2"/>
     </row>
@@ -8372,7 +8319,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8384,22 +8331,22 @@
         <v>30024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="N42" s="2"/>
     </row>
@@ -8414,7 +8361,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8426,22 +8373,22 @@
         <v>30034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="346">
   <si>
     <t>#</t>
   </si>
@@ -368,6 +368,9 @@
     <t>100,1</t>
   </si>
   <si>
+    <t>物攻加成</t>
+  </si>
+  <si>
     <t>黑铁头盔</t>
   </si>
   <si>
@@ -380,36 +383,36 @@
     <t>40000004,40000005</t>
   </si>
   <si>
+    <t>古铜戒指</t>
+  </si>
+  <si>
+    <t>1003,1004,95</t>
+  </si>
+  <si>
+    <t>5,10,1</t>
+  </si>
+  <si>
+    <t>40000007,40000008</t>
+  </si>
+  <si>
+    <t>10,2</t>
+  </si>
+  <si>
+    <t>古铜项链</t>
+  </si>
+  <si>
+    <t>1002,1004,95</t>
+  </si>
+  <si>
+    <t>10,10,1</t>
+  </si>
+  <si>
+    <t>40000005,40000007</t>
+  </si>
+  <si>
     <t>凌风长剑</t>
   </si>
   <si>
-    <t>1003,1004,95</t>
-  </si>
-  <si>
-    <t>5,10,1</t>
-  </si>
-  <si>
-    <t>40000007,40000008</t>
-  </si>
-  <si>
-    <t>10,2</t>
-  </si>
-  <si>
-    <t>古铜戒指</t>
-  </si>
-  <si>
-    <t>1002,1004,95</t>
-  </si>
-  <si>
-    <t>10,10,1</t>
-  </si>
-  <si>
-    <t>40000005,40000007</t>
-  </si>
-  <si>
-    <t>古铜项链</t>
-  </si>
-  <si>
     <t>1001,1004,95</t>
   </si>
   <si>
@@ -419,6 +422,9 @@
     <t>40000008,40000009</t>
   </si>
   <si>
+    <t>物伤加成</t>
+  </si>
+  <si>
     <t>法系技能全等级+1</t>
   </si>
   <si>
@@ -431,7 +437,7 @@
     <t>基础心法·传承</t>
   </si>
   <si>
-    <t>1004,21001,95</t>
+    <t>1007,21001,95</t>
   </si>
   <si>
     <t>2,1,1</t>
@@ -443,7 +449,7 @@
     <t>流光剑诀·传承</t>
   </si>
   <si>
-    <t>1004,21002,95</t>
+    <t>1007,21002,95</t>
   </si>
   <si>
     <t>流光剑诀等级+1</t>
@@ -452,7 +458,10 @@
     <t>月华剑阵·传承</t>
   </si>
   <si>
-    <t>1004,21003,95</t>
+    <t>1007,21003,95</t>
+  </si>
+  <si>
+    <t>4,1,1</t>
   </si>
   <si>
     <t>月华剑阵等级+1</t>
@@ -461,7 +470,10 @@
     <t>蛮牛冲撞·传承</t>
   </si>
   <si>
-    <t>1004,21004,95</t>
+    <t>1007,21007,95</t>
+  </si>
+  <si>
+    <t>5,1,1</t>
   </si>
   <si>
     <t>蛮牛冲撞等级+1</t>
@@ -470,7 +482,10 @@
     <t>龙魂护体·传承</t>
   </si>
   <si>
-    <t>1004,21005,95</t>
+    <t>1007,21005,95</t>
+  </si>
+  <si>
+    <t>6,1,1</t>
   </si>
   <si>
     <t>40000013,40000014,40000015</t>
@@ -482,7 +497,10 @@
     <t>无求易决·传承</t>
   </si>
   <si>
-    <t>1004,21006,95</t>
+    <t>1007,21006,95</t>
+  </si>
+  <si>
+    <t>7,1,1</t>
   </si>
   <si>
     <t>40000016,40000017,40000018</t>
@@ -494,7 +512,7 @@
     <t>火麟剑诀·传承</t>
   </si>
   <si>
-    <t>1004,21007,95</t>
+    <t>8,1,1</t>
   </si>
   <si>
     <t>40000019,40000020,40000021</t>
@@ -680,7 +698,7 @@
     <t>冥想心法</t>
   </si>
   <si>
-    <t>1005,22001,95</t>
+    <t>1008,22001,95</t>
   </si>
   <si>
     <t>冥想心法等级+1</t>
@@ -689,7 +707,7 @@
     <t>紫电神雷</t>
   </si>
   <si>
-    <t>1005,22002,95</t>
+    <t>1008,22002,95</t>
   </si>
   <si>
     <t>紫电神雷等级+1</t>
@@ -698,7 +716,7 @@
     <t>火狱阵法</t>
   </si>
   <si>
-    <t>1005,22003,95</t>
+    <t>1008,22003,95</t>
   </si>
   <si>
     <t>火狱阵法等级+1</t>
@@ -707,7 +725,7 @@
     <t>烈焰焚天</t>
   </si>
   <si>
-    <t>1005,22004,95</t>
+    <t>1008,22004,95</t>
   </si>
   <si>
     <t>烈焰焚天等级+1</t>
@@ -716,7 +734,7 @@
     <t>炎凰法盾</t>
   </si>
   <si>
-    <t>1005,22005,95</t>
+    <t>1008,22005,95</t>
   </si>
   <si>
     <t>炎凰法盾等级+1</t>
@@ -725,7 +743,7 @@
     <t>万法归宗</t>
   </si>
   <si>
-    <t>1005,22006,95</t>
+    <t>1008,22006,95</t>
   </si>
   <si>
     <t>万法归宗等级+1</t>
@@ -734,7 +752,7 @@
     <t>极寒冰暴</t>
   </si>
   <si>
-    <t>1005,22007,95</t>
+    <t>1008,22007,95</t>
   </si>
   <si>
     <t>极寒冰暴等级+1</t>
@@ -890,7 +908,7 @@
     <t>清心咒</t>
   </si>
   <si>
-    <t>1006,23001,95</t>
+    <t>1009,23001,95</t>
   </si>
   <si>
     <t>清心咒等级+1</t>
@@ -899,7 +917,7 @@
     <t>破魔符咒</t>
   </si>
   <si>
-    <t>1006,23002,95</t>
+    <t>1009,23002,95</t>
   </si>
   <si>
     <t>破魔符咒等级+1</t>
@@ -908,7 +926,7 @@
     <t>毒咒术</t>
   </si>
   <si>
-    <t>1006,23003,95</t>
+    <t>1009,23003,95</t>
   </si>
   <si>
     <t>毒咒术等级+1</t>
@@ -917,7 +935,7 @@
     <t>圣疗术</t>
   </si>
   <si>
-    <t>1006,23004,95</t>
+    <t>1009,23004,95</t>
   </si>
   <si>
     <t>圣疗术等级+1</t>
@@ -926,7 +944,7 @@
     <t>太虚麟盾</t>
   </si>
   <si>
-    <t>1006,23005,95</t>
+    <t>1009,23005,95</t>
   </si>
   <si>
     <t>太虚麟盾等级+1</t>
@@ -935,7 +953,7 @@
     <t>道法自然</t>
   </si>
   <si>
-    <t>1006,23006,95</t>
+    <t>1009,23006,95</t>
   </si>
   <si>
     <t>道法自然等级+1</t>
@@ -944,7 +962,7 @@
     <t>召唤英灵</t>
   </si>
   <si>
-    <t>1006,23007,95</t>
+    <t>1009,23007,95</t>
   </si>
   <si>
     <t>召唤英灵等级+1</t>
@@ -3341,6 +3359,9 @@
       <c r="M10" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="N10" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A11" s="1" t="s">
@@ -3353,7 +3374,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3365,13 +3386,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>111</v>
@@ -3382,6 +3403,9 @@
       <c r="M11" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="N11" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A12" s="1" t="s">
@@ -3394,7 +3418,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3406,16 +3430,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -3423,6 +3447,9 @@
       <c r="M12" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="N12" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A13" s="1" t="s">
@@ -3435,7 +3462,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3447,16 +3474,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -3464,6 +3491,9 @@
       <c r="M13" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="N13" s="1" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A14" s="1" t="s">
@@ -3476,7 +3506,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3488,22 +3518,25 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
@@ -3515,7 +3548,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3527,7 +3560,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="M17" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3538,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
@@ -3547,7 +3580,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3559,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>19</v>
@@ -3574,7 +3607,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3582,7 +3615,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3594,10 +3627,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>25</v>
@@ -3609,7 +3642,7 @@
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3617,7 +3650,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3629,10 +3662,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>30</v>
@@ -3644,7 +3677,7 @@
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3652,7 +3685,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3664,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>34</v>
@@ -3679,7 +3712,7 @@
         <v>5</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3687,7 +3720,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3699,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K24" s="10" t="s">
         <v>106</v>
@@ -3714,7 +3747,7 @@
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3722,7 +3755,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3734,13 +3767,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K25" s="10" t="s">
         <v>106</v>
@@ -3749,7 +3782,7 @@
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3763,7 +3796,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3775,13 +3808,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="K26" s="10" t="s">
         <v>106</v>
@@ -3790,7 +3823,7 @@
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
@@ -3806,7 +3839,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3818,22 +3851,22 @@
         <v>10011</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3847,7 +3880,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3859,22 +3892,22 @@
         <v>10021</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3888,7 +3921,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3900,22 +3933,22 @@
         <v>10031</v>
       </c>
       <c r="H31" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="K31" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3929,7 +3962,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3941,22 +3974,22 @@
         <v>10041</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J32" s="10" t="s">
         <v>110</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -3970,7 +4003,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3982,22 +4015,22 @@
         <v>10051</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J33" s="10" t="s">
         <v>110</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4011,7 +4044,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -4023,22 +4056,22 @@
         <v>10061</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4052,7 +4085,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -4064,22 +4097,22 @@
         <v>10071</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="R35" s="6"/>
     </row>
@@ -4105,7 +4138,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4117,22 +4150,22 @@
         <v>10012</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="R37" s="6"/>
     </row>
@@ -4147,7 +4180,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4159,22 +4192,22 @@
         <v>10022</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="R38" s="6"/>
     </row>
@@ -4189,7 +4222,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4201,22 +4234,22 @@
         <v>10032</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="1"/>
@@ -4233,7 +4266,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4245,22 +4278,22 @@
         <v>10042</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="O40" s="6"/>
       <c r="P40" s="1"/>
@@ -4277,7 +4310,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4289,22 +4322,22 @@
         <v>10052</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J41" s="10" t="s">
         <v>110</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="O41" s="6"/>
       <c r="R41" s="6"/>
@@ -4320,7 +4353,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4332,22 +4365,22 @@
         <v>10072</v>
       </c>
       <c r="H42" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J42" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="O42" s="6"/>
       <c r="P42" s="1"/>
@@ -4376,7 +4409,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4388,22 +4421,22 @@
         <v>10023</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="1"/>
@@ -4420,7 +4453,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4432,22 +4465,22 @@
         <v>10073</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="O45" s="6"/>
       <c r="P45" s="1"/>
@@ -4476,7 +4509,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4488,22 +4521,22 @@
         <v>10024</v>
       </c>
       <c r="H47" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J47" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -4521,7 +4554,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4533,22 +4566,22 @@
         <v>10034</v>
       </c>
       <c r="H48" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="6"/>
@@ -4980,7 +5013,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4992,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>95</v>
@@ -5029,7 +5062,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -5041,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>99</v>
@@ -5078,7 +5111,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -5090,7 +5123,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>102</v>
@@ -5127,7 +5160,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -5139,7 +5172,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>105</v>
@@ -5180,7 +5213,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -5192,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>109</v>
@@ -5233,7 +5266,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -5245,13 +5278,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>111</v>
@@ -5286,7 +5319,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5298,16 +5331,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -5339,7 +5372,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5351,16 +5384,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -5392,7 +5425,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5404,16 +5437,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -5465,7 +5498,7 @@
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5477,10 +5510,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>19</v>
@@ -5492,7 +5525,7 @@
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5500,7 +5533,7 @@
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5512,10 +5545,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>25</v>
@@ -5527,7 +5560,7 @@
         <v>5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5535,7 +5568,7 @@
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5547,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>30</v>
@@ -5562,7 +5595,7 @@
         <v>5</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5570,7 +5603,7 @@
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5582,10 +5615,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>34</v>
@@ -5597,7 +5630,7 @@
         <v>5</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5605,7 +5638,7 @@
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5617,13 +5650,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>106</v>
@@ -5632,7 +5665,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5640,7 +5673,7 @@
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5652,13 +5685,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>106</v>
@@ -5667,7 +5700,7 @@
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5681,7 +5714,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5693,13 +5726,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="K22" s="10" t="s">
         <v>106</v>
@@ -5708,7 +5741,7 @@
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5726,7 +5759,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5738,22 +5771,22 @@
         <v>20011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="N24" s="2"/>
       <c r="XES24" s="1"/>
@@ -5780,7 +5813,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5792,22 +5825,22 @@
         <v>20021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="N25" s="1"/>
       <c r="XES25" s="1"/>
@@ -5834,7 +5867,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5846,22 +5879,22 @@
         <v>20031</v>
       </c>
       <c r="H26" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="K26" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="N26" s="1"/>
       <c r="XES26" s="1"/>
@@ -5888,7 +5921,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5900,22 +5933,22 @@
         <v>20041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J27" s="10" t="s">
         <v>110</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="N27" s="1"/>
       <c r="XES27" s="1"/>
@@ -5942,7 +5975,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -5954,22 +5987,22 @@
         <v>20051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J28" s="10" t="s">
         <v>110</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="N28" s="1"/>
       <c r="XES28" s="1"/>
@@ -5996,7 +6029,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -6008,22 +6041,22 @@
         <v>20061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="N29" s="1"/>
       <c r="XES29" s="1"/>
@@ -6050,7 +6083,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -6062,22 +6095,22 @@
         <v>20071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="N30" s="1"/>
       <c r="XES30" s="1"/>
@@ -6136,7 +6169,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -6148,22 +6181,22 @@
         <v>20012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="N32" s="1"/>
       <c r="XES32" s="1"/>
@@ -6190,7 +6223,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -6202,22 +6235,22 @@
         <v>20022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="N33" s="1"/>
       <c r="XES33" s="1"/>
@@ -6244,7 +6277,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -6256,22 +6289,22 @@
         <v>20032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="N34" s="1"/>
       <c r="XES34" s="1"/>
@@ -6298,7 +6331,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6310,22 +6343,22 @@
         <v>20052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>110</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="N35" s="1"/>
       <c r="XES35" s="1"/>
@@ -6352,7 +6385,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6364,22 +6397,22 @@
         <v>20072</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="N36" s="1"/>
       <c r="XES36" s="1"/>
@@ -6438,7 +6471,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6450,22 +6483,22 @@
         <v>20023</v>
       </c>
       <c r="H38" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="N38" s="1"/>
       <c r="XES38" s="1"/>
@@ -6492,7 +6525,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6504,22 +6537,22 @@
         <v>20043</v>
       </c>
       <c r="H39" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="N39" s="1"/>
       <c r="XES39" s="1"/>
@@ -6546,7 +6579,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6558,22 +6591,22 @@
         <v>20073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
@@ -6607,7 +6640,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6619,22 +6652,22 @@
         <v>20024</v>
       </c>
       <c r="H42" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J42" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
@@ -6653,7 +6686,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6665,22 +6698,22 @@
         <v>20034</v>
       </c>
       <c r="H43" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
@@ -7045,7 +7078,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -7057,7 +7090,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I6" s="10" t="s">
         <v>95</v>
@@ -7080,7 +7113,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -7092,7 +7125,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>99</v>
@@ -7115,7 +7148,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -7127,7 +7160,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I8" s="10" t="s">
         <v>102</v>
@@ -7151,7 +7184,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -7163,7 +7196,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="I9" s="10" t="s">
         <v>105</v>
@@ -7193,7 +7226,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -7205,7 +7238,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="I10" s="10" t="s">
         <v>109</v>
@@ -7235,7 +7268,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -7247,13 +7280,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K11" s="10" t="s">
         <v>111</v>
@@ -7277,7 +7310,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7289,16 +7322,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -7319,7 +7352,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7331,16 +7364,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -7361,7 +7394,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7373,16 +7406,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -7400,7 +7433,7 @@
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7412,10 +7445,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>19</v>
@@ -7427,7 +7460,7 @@
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7435,7 +7468,7 @@
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7447,10 +7480,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>134</v>
+        <v>37</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>25</v>
@@ -7462,7 +7495,7 @@
         <v>5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7470,7 +7503,7 @@
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7482,10 +7515,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>30</v>
@@ -7497,7 +7530,7 @@
         <v>5</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7505,7 +7538,7 @@
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7517,10 +7550,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>34</v>
@@ -7532,7 +7565,7 @@
         <v>5</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7540,7 +7573,7 @@
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7552,13 +7585,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K20" s="10" t="s">
         <v>106</v>
@@ -7567,7 +7600,7 @@
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7575,7 +7608,7 @@
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7587,13 +7620,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K21" s="10" t="s">
         <v>106</v>
@@ -7602,7 +7635,7 @@
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7616,7 +7649,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7628,13 +7661,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="K22" s="10" t="s">
         <v>106</v>
@@ -7643,7 +7676,7 @@
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7660,7 +7693,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7672,22 +7705,22 @@
         <v>30011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -7702,7 +7735,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7714,22 +7747,22 @@
         <v>30021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -7744,7 +7777,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7756,22 +7789,22 @@
         <v>30031</v>
       </c>
       <c r="H26" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="K26" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>161</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -7786,7 +7819,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7798,22 +7831,22 @@
         <v>30041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J27" s="10" t="s">
         <v>110</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -7828,7 +7861,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7840,22 +7873,22 @@
         <v>30051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J28" s="10" t="s">
         <v>110</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -7870,7 +7903,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7882,22 +7915,22 @@
         <v>30061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -7912,7 +7945,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7924,22 +7957,22 @@
         <v>30071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -7963,7 +7996,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -7975,22 +8008,22 @@
         <v>30012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -8005,7 +8038,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -8017,22 +8050,22 @@
         <v>30022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="N33" s="2"/>
     </row>
@@ -8047,7 +8080,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -8059,22 +8092,22 @@
         <v>30032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="N34" s="2"/>
     </row>
@@ -8089,7 +8122,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -8101,22 +8134,22 @@
         <v>30052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J35" s="10" t="s">
         <v>110</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="N35" s="2"/>
     </row>
@@ -8140,7 +8173,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -8152,22 +8185,22 @@
         <v>30023</v>
       </c>
       <c r="H37" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="N37" s="2"/>
     </row>
@@ -8182,7 +8215,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -8194,22 +8227,22 @@
         <v>30033</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="N38" s="2"/>
     </row>
@@ -8224,7 +8257,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -8236,22 +8269,22 @@
         <v>30043</v>
       </c>
       <c r="H39" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="N39" s="2"/>
     </row>
@@ -8266,7 +8299,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8278,22 +8311,22 @@
         <v>30073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="N40" s="2"/>
     </row>
@@ -8319,7 +8352,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8331,22 +8364,22 @@
         <v>30024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="N42" s="2"/>
     </row>
@@ -8361,7 +8394,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8373,22 +8406,22 @@
         <v>30034</v>
       </c>
       <c r="H43" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>161</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="326">
   <si>
     <t>#</t>
   </si>
@@ -177,66 +177,6 @@
   </si>
   <si>
     <t>品质加成</t>
-  </si>
-  <si>
-    <t>招财挂坠</t>
-  </si>
-  <si>
-    <t>81,21,95</t>
-  </si>
-  <si>
-    <t>3,2,1</t>
-  </si>
-  <si>
-    <t>40000001,40000002,40000002</t>
-  </si>
-  <si>
-    <t>10,3,1</t>
-  </si>
-  <si>
-    <t>经验符</t>
-  </si>
-  <si>
-    <t>82,22,95</t>
-  </si>
-  <si>
-    <t>聚宝盆</t>
-  </si>
-  <si>
-    <t>83,23,95</t>
-  </si>
-  <si>
-    <t>幸运符</t>
-  </si>
-  <si>
-    <t>84,24,95</t>
-  </si>
-  <si>
-    <t>神偷护符</t>
-  </si>
-  <si>
-    <t>85,27,95</t>
-  </si>
-  <si>
-    <t>30,3,1</t>
-  </si>
-  <si>
-    <t>40000005,40000008,40000011</t>
-  </si>
-  <si>
-    <t>3,3,3</t>
-  </si>
-  <si>
-    <t>历练帖</t>
-  </si>
-  <si>
-    <t>86,28,95</t>
-  </si>
-  <si>
-    <t>40000006,40000009,40000012</t>
-  </si>
-  <si>
-    <t>1,1,1</t>
   </si>
   <si>
     <t>宠物袋</t>
@@ -2510,279 +2450,33 @@
       <c r="M16" s="1"/>
       <c r="N16" s="2"/>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="1">
-        <v>7</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="K17" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L17" s="1">
-        <v>4</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="1">
-        <v>8</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1">
-        <v>2</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L18" s="1">
-        <v>4</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="1">
-        <v>9</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1">
-        <v>3</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L19" s="1">
-        <v>4</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="1">
-        <v>10</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
-        <v>4</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L20" s="1">
-        <v>4</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1">
-        <v>11</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
-        <v>5</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="L21" s="1">
-        <v>4</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1">
-        <v>12</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1">
-        <v>6</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="L22" s="1">
-        <v>4</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="D20" s="9"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="D21" s="5"/>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="D23" s="7"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C24" s="1">
         <v>101</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
@@ -2794,33 +2488,33 @@
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C25" s="1">
         <v>102</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -2832,33 +2526,33 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C26" s="1">
         <v>103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -2870,33 +2564,33 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="L26" s="1">
         <v>6</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C27" s="1">
         <v>104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -2908,33 +2602,33 @@
         <v>0</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="L27" s="1">
         <v>6</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C28" s="1">
         <v>105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -2946,30 +2640,30 @@
         <v>0</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:14">
       <c r="C29" s="1">
         <v>106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -2981,22 +2675,22 @@
         <v>0</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1"/>
@@ -3172,7 +2866,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -3184,16 +2878,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -3202,7 +2896,7 @@
         <v>21</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3210,7 +2904,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3222,16 +2916,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -3240,7 +2934,7 @@
         <v>21</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3248,7 +2942,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -3260,16 +2954,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -3278,7 +2972,7 @@
         <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3286,7 +2980,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -3298,16 +2992,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
@@ -3316,7 +3010,7 @@
         <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3330,7 +3024,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3342,16 +3036,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -3360,7 +3054,7 @@
         <v>21</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3374,7 +3068,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3386,16 +3080,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -3404,7 +3098,7 @@
         <v>21</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3418,7 +3112,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3430,16 +3124,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -3448,7 +3142,7 @@
         <v>21</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3462,7 +3156,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3474,16 +3168,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -3492,7 +3186,7 @@
         <v>21</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3506,7 +3200,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3518,16 +3212,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -3536,7 +3230,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
@@ -3548,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3560,7 +3254,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="M17" s="1" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3571,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
@@ -3580,7 +3274,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3592,22 +3286,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3615,7 +3309,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3627,7 +3321,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>37</v>
@@ -3636,13 +3330,13 @@
         <v>25</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3650,7 +3344,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3662,22 +3356,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3685,7 +3379,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3697,22 +3391,22 @@
         <v>0</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3720,7 +3414,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3732,22 +3426,22 @@
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3755,7 +3449,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3767,22 +3461,22 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3796,7 +3490,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3808,22 +3502,22 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
@@ -3839,7 +3533,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3851,22 +3545,22 @@
         <v>10011</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3880,7 +3574,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3892,22 +3586,22 @@
         <v>10021</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3921,7 +3615,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3933,22 +3627,22 @@
         <v>10031</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3962,7 +3656,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3974,22 +3668,22 @@
         <v>10041</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4003,7 +3697,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -4015,22 +3709,22 @@
         <v>10051</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4044,7 +3738,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -4056,22 +3750,22 @@
         <v>10061</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -4085,7 +3779,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -4097,22 +3791,22 @@
         <v>10071</v>
       </c>
       <c r="H35" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K35" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="R35" s="6"/>
     </row>
@@ -4138,7 +3832,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4150,22 +3844,22 @@
         <v>10012</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="R37" s="6"/>
     </row>
@@ -4180,7 +3874,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4192,22 +3886,22 @@
         <v>10022</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="R38" s="6"/>
     </row>
@@ -4222,7 +3916,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4234,22 +3928,22 @@
         <v>10032</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="1"/>
@@ -4266,7 +3960,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4278,22 +3972,22 @@
         <v>10042</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="O40" s="6"/>
       <c r="P40" s="1"/>
@@ -4310,7 +4004,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4322,22 +4016,22 @@
         <v>10052</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="O41" s="6"/>
       <c r="R41" s="6"/>
@@ -4353,7 +4047,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4365,22 +4059,22 @@
         <v>10072</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="O42" s="6"/>
       <c r="P42" s="1"/>
@@ -4409,7 +4103,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4421,22 +4115,22 @@
         <v>10023</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="1"/>
@@ -4453,7 +4147,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4465,22 +4159,22 @@
         <v>10073</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="O45" s="6"/>
       <c r="P45" s="1"/>
@@ -4509,7 +4203,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4521,22 +4215,22 @@
         <v>10024</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -4554,7 +4248,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4566,22 +4260,22 @@
         <v>10034</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="6"/>
@@ -5013,7 +4707,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -5025,16 +4719,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -5062,7 +4756,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -5074,16 +4768,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -5111,7 +4805,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -5123,16 +4817,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -5160,7 +4854,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -5172,16 +4866,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -5213,7 +4907,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -5225,16 +4919,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -5266,7 +4960,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -5278,16 +4972,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -5319,7 +5013,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5331,16 +5025,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -5372,7 +5066,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5384,16 +5078,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -5425,7 +5119,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5437,16 +5131,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -5498,7 +5192,7 @@
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5510,22 +5204,22 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5533,7 +5227,7 @@
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5545,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>37</v>
@@ -5554,13 +5248,13 @@
         <v>25</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5568,7 +5262,7 @@
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5580,22 +5274,22 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5603,7 +5297,7 @@
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5615,22 +5309,22 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5638,7 +5332,7 @@
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5650,22 +5344,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5673,7 +5367,7 @@
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5685,22 +5379,22 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5714,7 +5408,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5726,22 +5420,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5759,7 +5453,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5771,22 +5465,22 @@
         <v>20011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="N24" s="2"/>
       <c r="XES24" s="1"/>
@@ -5813,7 +5507,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5825,22 +5519,22 @@
         <v>20021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="N25" s="1"/>
       <c r="XES25" s="1"/>
@@ -5867,7 +5561,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5879,22 +5573,22 @@
         <v>20031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="N26" s="1"/>
       <c r="XES26" s="1"/>
@@ -5921,7 +5615,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5933,22 +5627,22 @@
         <v>20041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="N27" s="1"/>
       <c r="XES27" s="1"/>
@@ -5975,7 +5669,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -5987,22 +5681,22 @@
         <v>20051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="N28" s="1"/>
       <c r="XES28" s="1"/>
@@ -6029,7 +5723,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -6041,22 +5735,22 @@
         <v>20061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="N29" s="1"/>
       <c r="XES29" s="1"/>
@@ -6083,7 +5777,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -6095,22 +5789,22 @@
         <v>20071</v>
       </c>
       <c r="H30" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K30" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="N30" s="1"/>
       <c r="XES30" s="1"/>
@@ -6169,7 +5863,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -6181,22 +5875,22 @@
         <v>20012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="N32" s="1"/>
       <c r="XES32" s="1"/>
@@ -6223,7 +5917,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -6235,22 +5929,22 @@
         <v>20022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="N33" s="1"/>
       <c r="XES33" s="1"/>
@@ -6277,7 +5971,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -6289,22 +5983,22 @@
         <v>20032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="N34" s="1"/>
       <c r="XES34" s="1"/>
@@ -6331,7 +6025,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6343,22 +6037,22 @@
         <v>20052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="N35" s="1"/>
       <c r="XES35" s="1"/>
@@ -6385,7 +6079,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6397,22 +6091,22 @@
         <v>20072</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="N36" s="1"/>
       <c r="XES36" s="1"/>
@@ -6471,7 +6165,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6483,22 +6177,22 @@
         <v>20023</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="N38" s="1"/>
       <c r="XES38" s="1"/>
@@ -6525,7 +6219,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6537,22 +6231,22 @@
         <v>20043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="N39" s="1"/>
       <c r="XES39" s="1"/>
@@ -6579,7 +6273,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6591,22 +6285,22 @@
         <v>20073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
@@ -6640,7 +6334,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6652,22 +6346,22 @@
         <v>20024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
@@ -6686,7 +6380,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6698,22 +6392,22 @@
         <v>20034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
@@ -7078,7 +6772,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -7090,16 +6784,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -7113,7 +6807,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -7125,16 +6819,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -7148,7 +6842,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -7160,16 +6854,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -7184,7 +6878,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -7196,16 +6890,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -7226,7 +6920,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -7238,16 +6932,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -7268,7 +6962,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -7280,16 +6974,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -7310,7 +7004,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7322,16 +7016,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -7352,7 +7046,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7364,16 +7058,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -7394,7 +7088,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7406,16 +7100,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -7433,7 +7127,7 @@
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7445,22 +7139,22 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7468,7 +7162,7 @@
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7480,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>37</v>
@@ -7489,13 +7183,13 @@
         <v>25</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7503,7 +7197,7 @@
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7515,22 +7209,22 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7538,7 +7232,7 @@
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7550,22 +7244,22 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7573,7 +7267,7 @@
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7585,22 +7279,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7608,7 +7302,7 @@
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7620,22 +7314,22 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7649,7 +7343,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7661,22 +7355,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7693,7 +7387,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7705,22 +7399,22 @@
         <v>30011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -7735,7 +7429,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7747,22 +7441,22 @@
         <v>30021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -7777,7 +7471,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7789,22 +7483,22 @@
         <v>30031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -7819,7 +7513,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7831,22 +7525,22 @@
         <v>30041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -7861,7 +7555,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7873,22 +7567,22 @@
         <v>30051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -7903,7 +7597,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7915,22 +7609,22 @@
         <v>30061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -7945,7 +7639,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7957,22 +7651,22 @@
         <v>30071</v>
       </c>
       <c r="H30" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="K30" s="10" t="s">
         <v>164</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -7996,7 +7690,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -8008,22 +7702,22 @@
         <v>30012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -8038,7 +7732,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -8050,22 +7744,22 @@
         <v>30022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="N33" s="2"/>
     </row>
@@ -8080,7 +7774,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -8092,22 +7786,22 @@
         <v>30032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="N34" s="2"/>
     </row>
@@ -8122,7 +7816,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -8134,22 +7828,22 @@
         <v>30052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="N35" s="2"/>
     </row>
@@ -8173,7 +7867,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -8185,22 +7879,22 @@
         <v>30023</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="N37" s="2"/>
     </row>
@@ -8215,7 +7909,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -8227,22 +7921,22 @@
         <v>30033</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="N38" s="2"/>
     </row>
@@ -8257,7 +7951,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -8269,22 +7963,22 @@
         <v>30043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="N39" s="2"/>
     </row>
@@ -8299,7 +7993,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8311,22 +8005,22 @@
         <v>30073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="N40" s="2"/>
     </row>
@@ -8352,7 +8046,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8364,22 +8058,22 @@
         <v>30024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="N42" s="2"/>
     </row>
@@ -8394,7 +8088,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8406,22 +8100,22 @@
         <v>30034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="327">
   <si>
     <t>#</t>
   </si>
@@ -201,6 +201,9 @@
   </si>
   <si>
     <t>2003,113,95</t>
+  </si>
+  <si>
+    <t>增加一个技能出战栏位</t>
   </si>
   <si>
     <t>增加一个技能出站栏位</t>
@@ -2544,7 +2547,7 @@
         <v>57</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -2552,7 +2555,7 @@
         <v>103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -2564,25 +2567,25 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L26" s="1">
         <v>6</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -2590,7 +2593,7 @@
         <v>104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -2602,25 +2605,25 @@
         <v>0</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L27" s="1">
         <v>6</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -2628,7 +2631,7 @@
         <v>105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -2640,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J28" s="10" t="s">
         <v>52</v>
@@ -2655,7 +2658,7 @@
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:14">
@@ -2663,7 +2666,7 @@
         <v>106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -2675,22 +2678,22 @@
         <v>0</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1"/>
@@ -2866,7 +2869,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -2878,16 +2881,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -2896,7 +2899,7 @@
         <v>21</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2904,7 +2907,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -2916,16 +2919,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -2934,7 +2937,7 @@
         <v>21</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2942,7 +2945,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2954,16 +2957,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -2972,7 +2975,7 @@
         <v>21</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -2980,7 +2983,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -2992,16 +2995,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
@@ -3010,7 +3013,7 @@
         <v>21</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3024,7 +3027,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3036,16 +3039,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -3054,7 +3057,7 @@
         <v>21</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3068,7 +3071,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3080,16 +3083,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -3098,7 +3101,7 @@
         <v>21</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3112,7 +3115,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3124,16 +3127,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -3142,7 +3145,7 @@
         <v>21</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3156,7 +3159,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3168,16 +3171,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -3186,7 +3189,7 @@
         <v>21</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3200,7 +3203,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3212,16 +3215,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -3230,7 +3233,7 @@
         <v>21</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
@@ -3242,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3254,7 +3257,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="M17" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3265,7 +3268,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
@@ -3274,7 +3277,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3286,22 +3289,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3309,7 +3312,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3321,7 +3324,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I21" s="10" t="s">
         <v>37</v>
@@ -3330,13 +3333,13 @@
         <v>25</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3344,7 +3347,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3356,22 +3359,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3379,7 +3382,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3391,22 +3394,22 @@
         <v>0</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3414,7 +3417,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3426,22 +3429,22 @@
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3449,7 +3452,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3461,22 +3464,22 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3490,7 +3493,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3502,22 +3505,22 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
@@ -3533,7 +3536,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3545,22 +3548,22 @@
         <v>10011</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3574,7 +3577,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3586,22 +3589,22 @@
         <v>10021</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3615,7 +3618,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3627,22 +3630,22 @@
         <v>10031</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:13">
@@ -3656,7 +3659,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3668,22 +3671,22 @@
         <v>10041</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -3697,7 +3700,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3709,22 +3712,22 @@
         <v>10051</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -3738,7 +3741,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -3750,22 +3753,22 @@
         <v>10061</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
@@ -3779,7 +3782,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -3791,22 +3794,22 @@
         <v>10071</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="R35" s="6"/>
     </row>
@@ -3832,7 +3835,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -3844,22 +3847,22 @@
         <v>10012</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="R37" s="6"/>
     </row>
@@ -3874,7 +3877,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -3886,22 +3889,22 @@
         <v>10022</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R38" s="6"/>
     </row>
@@ -3916,7 +3919,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -3928,22 +3931,22 @@
         <v>10032</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="1"/>
@@ -3960,7 +3963,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -3972,22 +3975,22 @@
         <v>10042</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O40" s="6"/>
       <c r="P40" s="1"/>
@@ -4004,7 +4007,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4016,22 +4019,22 @@
         <v>10052</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O41" s="6"/>
       <c r="R41" s="6"/>
@@ -4047,7 +4050,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4059,22 +4062,22 @@
         <v>10072</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O42" s="6"/>
       <c r="P42" s="1"/>
@@ -4103,7 +4106,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4115,22 +4118,22 @@
         <v>10023</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O44" s="6"/>
       <c r="P44" s="1"/>
@@ -4147,7 +4150,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4159,22 +4162,22 @@
         <v>10073</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O45" s="6"/>
       <c r="P45" s="1"/>
@@ -4203,7 +4206,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4215,22 +4218,22 @@
         <v>10024</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -4248,7 +4251,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4260,22 +4263,22 @@
         <v>10034</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N48" s="1"/>
       <c r="O48" s="6"/>
@@ -4707,7 +4710,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4719,16 +4722,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -4756,7 +4759,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -4768,16 +4771,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -4805,7 +4808,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -4817,16 +4820,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -4854,7 +4857,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -4866,16 +4869,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -4907,7 +4910,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -4919,16 +4922,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -4960,7 +4963,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -4972,16 +4975,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -5013,7 +5016,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5025,16 +5028,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -5066,7 +5069,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5078,16 +5081,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -5119,7 +5122,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5131,16 +5134,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -5192,7 +5195,7 @@
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5204,22 +5207,22 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5227,7 +5230,7 @@
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5239,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>37</v>
@@ -5248,13 +5251,13 @@
         <v>25</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5262,7 +5265,7 @@
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5274,22 +5277,22 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5297,7 +5300,7 @@
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5309,22 +5312,22 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5332,7 +5335,7 @@
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5344,22 +5347,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5367,7 +5370,7 @@
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5379,22 +5382,22 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5408,7 +5411,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5420,22 +5423,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
@@ -5453,7 +5456,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5465,22 +5468,22 @@
         <v>20011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N24" s="2"/>
       <c r="XES24" s="1"/>
@@ -5507,7 +5510,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5519,22 +5522,22 @@
         <v>20021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N25" s="1"/>
       <c r="XES25" s="1"/>
@@ -5561,7 +5564,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5573,22 +5576,22 @@
         <v>20031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N26" s="1"/>
       <c r="XES26" s="1"/>
@@ -5615,7 +5618,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5627,22 +5630,22 @@
         <v>20041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N27" s="1"/>
       <c r="XES27" s="1"/>
@@ -5669,7 +5672,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -5681,22 +5684,22 @@
         <v>20051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N28" s="1"/>
       <c r="XES28" s="1"/>
@@ -5723,7 +5726,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -5735,22 +5738,22 @@
         <v>20061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N29" s="1"/>
       <c r="XES29" s="1"/>
@@ -5777,7 +5780,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -5789,22 +5792,22 @@
         <v>20071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N30" s="1"/>
       <c r="XES30" s="1"/>
@@ -5863,7 +5866,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -5875,22 +5878,22 @@
         <v>20012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N32" s="1"/>
       <c r="XES32" s="1"/>
@@ -5917,7 +5920,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -5929,22 +5932,22 @@
         <v>20022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N33" s="1"/>
       <c r="XES33" s="1"/>
@@ -5971,7 +5974,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -5983,22 +5986,22 @@
         <v>20032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N34" s="1"/>
       <c r="XES34" s="1"/>
@@ -6025,7 +6028,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6037,22 +6040,22 @@
         <v>20052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N35" s="1"/>
       <c r="XES35" s="1"/>
@@ -6079,7 +6082,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6091,22 +6094,22 @@
         <v>20072</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N36" s="1"/>
       <c r="XES36" s="1"/>
@@ -6165,7 +6168,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6177,22 +6180,22 @@
         <v>20023</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N38" s="1"/>
       <c r="XES38" s="1"/>
@@ -6219,7 +6222,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6231,22 +6234,22 @@
         <v>20043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N39" s="1"/>
       <c r="XES39" s="1"/>
@@ -6273,7 +6276,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6285,22 +6288,22 @@
         <v>20073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
@@ -6334,7 +6337,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6346,22 +6349,22 @@
         <v>20024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
@@ -6380,7 +6383,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6392,22 +6395,22 @@
         <v>20034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
@@ -6772,7 +6775,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -6784,16 +6787,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
@@ -6807,7 +6810,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -6819,16 +6822,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>25</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
@@ -6842,7 +6845,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -6854,16 +6857,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
@@ -6878,7 +6881,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -6890,16 +6893,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L9" s="1">
         <v>4</v>
@@ -6920,7 +6923,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -6932,16 +6935,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -6962,7 +6965,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -6974,16 +6977,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -7004,7 +7007,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7016,16 +7019,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -7046,7 +7049,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7058,16 +7061,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -7088,7 +7091,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7100,16 +7103,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -7127,7 +7130,7 @@
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7139,22 +7142,22 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7162,7 +7165,7 @@
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7174,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>37</v>
@@ -7183,13 +7186,13 @@
         <v>25</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7197,7 +7200,7 @@
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7209,22 +7212,22 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>30</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7232,7 +7235,7 @@
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7244,22 +7247,22 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>34</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7267,7 +7270,7 @@
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7279,22 +7282,22 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7302,7 +7305,7 @@
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7314,22 +7317,22 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7343,7 +7346,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7355,22 +7358,22 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -7387,7 +7390,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7399,22 +7402,22 @@
         <v>30011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N24" s="2"/>
     </row>
@@ -7429,7 +7432,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7441,22 +7444,22 @@
         <v>30021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N25" s="2"/>
     </row>
@@ -7471,7 +7474,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7483,22 +7486,22 @@
         <v>30031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N26" s="2"/>
     </row>
@@ -7513,7 +7516,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7525,22 +7528,22 @@
         <v>30041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N27" s="2"/>
     </row>
@@ -7555,7 +7558,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7567,22 +7570,22 @@
         <v>30051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N28" s="2"/>
     </row>
@@ -7597,7 +7600,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7609,22 +7612,22 @@
         <v>30061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N29" s="2"/>
     </row>
@@ -7639,7 +7642,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7651,22 +7654,22 @@
         <v>30071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N30" s="2"/>
     </row>
@@ -7690,7 +7693,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -7702,22 +7705,22 @@
         <v>30012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N32" s="2"/>
     </row>
@@ -7732,7 +7735,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -7744,22 +7747,22 @@
         <v>30022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N33" s="2"/>
     </row>
@@ -7774,7 +7777,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -7786,22 +7789,22 @@
         <v>30032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N34" s="2"/>
     </row>
@@ -7816,7 +7819,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -7828,22 +7831,22 @@
         <v>30052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N35" s="2"/>
     </row>
@@ -7867,7 +7870,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -7879,22 +7882,22 @@
         <v>30023</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N37" s="2"/>
     </row>
@@ -7909,7 +7912,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -7921,22 +7924,22 @@
         <v>30033</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N38" s="2"/>
     </row>
@@ -7951,7 +7954,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -7963,22 +7966,22 @@
         <v>30043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N39" s="2"/>
     </row>
@@ -7993,7 +7996,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8005,22 +8008,22 @@
         <v>30073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N40" s="2"/>
     </row>
@@ -8046,7 +8049,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8058,22 +8061,22 @@
         <v>30024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N42" s="2"/>
     </row>
@@ -8088,7 +8091,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8100,22 +8103,22 @@
         <v>30034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="348">
   <si>
     <t>#</t>
   </si>
@@ -65,6 +65,9 @@
     <t>Quality</t>
   </si>
   <si>
+    <t>LogoId</t>
+  </si>
+  <si>
     <t>Des</t>
   </si>
   <si>
@@ -95,6 +98,9 @@
     <t>50,10,2</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive1</t>
+  </si>
+  <si>
     <t>没有特殊效果</t>
   </si>
   <si>
@@ -110,10 +116,13 @@
     <t>40000004,40000005,40000006</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive2</t>
+  </si>
+  <si>
     <t>杀怪经验</t>
   </si>
   <si>
-    <t>妙手布鞋</t>
+    <t>摸金符</t>
   </si>
   <si>
     <t>85,1003,95</t>
@@ -128,6 +137,9 @@
     <t>100,15,4</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive3</t>
+  </si>
+  <si>
     <t>修行手册</t>
   </si>
   <si>
@@ -137,6 +149,9 @@
     <t>40000010,40000011,40000012</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive4</t>
+  </si>
+  <si>
     <t>铜钱袋</t>
   </si>
   <si>
@@ -149,6 +164,9 @@
     <t>150,18,6</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive5</t>
+  </si>
+  <si>
     <t>金币加成</t>
   </si>
   <si>
@@ -158,6 +176,9 @@
     <t>82,27,95</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive6</t>
+  </si>
+  <si>
     <t>经验加成</t>
   </si>
   <si>
@@ -167,6 +188,9 @@
     <t>83,27,95</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive7</t>
+  </si>
+  <si>
     <t>爆率加成</t>
   </si>
   <si>
@@ -176,6 +200,9 @@
     <t>84,27,95</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive8</t>
+  </si>
+  <si>
     <t>品质加成</t>
   </si>
   <si>
@@ -194,6 +221,9 @@
     <t>15,15,15</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive101</t>
+  </si>
+  <si>
     <t>增加一个宠物备战位</t>
   </si>
   <si>
@@ -203,6 +233,9 @@
     <t>2003,113,95</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive102</t>
+  </si>
+  <si>
     <t>增加一个技能出战栏位</t>
   </si>
   <si>
@@ -224,6 +257,9 @@
     <t>30,30,30</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive103</t>
+  </si>
+  <si>
     <t>技能词条套装所需数量-1</t>
   </si>
   <si>
@@ -239,18 +275,27 @@
     <t>3,3</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive104</t>
+  </si>
+  <si>
     <t>低概率刷新低于当前地图的区域boss</t>
   </si>
   <si>
     <t>传世勋章</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive105</t>
+  </si>
+  <si>
     <t>解锁传世高级挑战</t>
   </si>
   <si>
     <t>传世印记</t>
   </si>
   <si>
+    <t>Exclusive/Exclusive106</t>
+  </si>
+  <si>
     <t>解锁传世超级挑战</t>
   </si>
   <si>
@@ -266,6 +311,9 @@
     <t>25,3,1</t>
   </si>
   <si>
+    <t>Bag/Equip/Box_Equip_1_1</t>
+  </si>
+  <si>
     <t>物攻基础</t>
   </si>
   <si>
@@ -386,6 +434,9 @@
     <t>2,1,1</t>
   </si>
   <si>
+    <t>ItemLogo/sb1</t>
+  </si>
+  <si>
     <t>基础心法等级+1</t>
   </si>
   <si>
@@ -599,6 +650,9 @@
     <t>5,3,95</t>
   </si>
   <si>
+    <t>Bag/Equip/Box_Equip_2_1</t>
+  </si>
+  <si>
     <t>乌木戒</t>
   </si>
   <si>
@@ -644,6 +698,9 @@
     <t>1008,22001,95</t>
   </si>
   <si>
+    <t>ItemLogo/sb2</t>
+  </si>
+  <si>
     <t>冥想心法等级+1</t>
   </si>
   <si>
@@ -809,6 +866,9 @@
     <t>6,3,95</t>
   </si>
   <si>
+    <t>Bag/Equip/Box_Equip_3_1</t>
+  </si>
+  <si>
     <t>青竹罗盘</t>
   </si>
   <si>
@@ -852,6 +912,9 @@
   </si>
   <si>
     <t>1009,23001,95</t>
+  </si>
+  <si>
+    <t>ItemLogo/sb3</t>
   </si>
   <si>
     <t>清心咒等级+1</t>
@@ -1992,7 +2055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2001,28 +2064,30 @@
     <col min="4" max="6" width="12.125" style="1" customWidth="1"/>
     <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="24.5833333333333" style="1" customWidth="1"/>
-    <col min="11" max="12" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="29" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
-    <col min="15" max="16372" width="9" style="2"/>
-    <col min="16373" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.25" style="1" customWidth="1"/>
+    <col min="13" max="13" width="16" style="1" customWidth="1"/>
+    <col min="14" max="14" width="29" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.1666666666667" style="2" customWidth="1"/>
+    <col min="16" max="16373" width="9" style="2"/>
+    <col min="16374" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="N1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -2058,12 +2123,15 @@
       <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -2095,50 +2163,56 @@
       <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -2150,33 +2224,36 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -2188,33 +2265,36 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -2226,71 +2306,77 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="1">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>29</v>
-      </c>
       <c r="J9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" s="10" t="s">
         <v>34</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>31</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -2302,33 +2388,36 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L10" s="1">
         <v>3</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -2340,71 +2429,77 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L11" s="1">
         <v>3</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>43</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
-      </c>
-      <c r="H12" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>38</v>
       </c>
       <c r="L12" s="1">
         <v>3</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -2416,28 +2511,31 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L13" s="1">
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="1:15">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="1"/>
@@ -2451,35 +2549,36 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-      <c r="N16" s="2"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="N16" s="1"/>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D17" s="5"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D18" s="7"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D19" s="5"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D20" s="9"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D21" s="5"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D22" s="7"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="D23" s="7"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:14">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C24" s="1">
         <v>101</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
@@ -2491,33 +2590,36 @@
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>64</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C25" s="1">
         <v>102</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -2529,33 +2631,36 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>68</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C26" s="1">
         <v>103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -2567,33 +2672,36 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="L26" s="1">
         <v>6</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>76</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C27" s="1">
         <v>104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -2605,33 +2713,36 @@
         <v>0</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="L27" s="1">
         <v>6</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>82</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C28" s="1">
         <v>105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -2643,30 +2754,33 @@
         <v>0</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:14">
+        <v>84</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
       <c r="C29" s="1">
         <v>106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -2678,40 +2792,43 @@
         <v>0</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>73</v>
+        <v>87</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1"/>
     <row r="31" s="1" customFormat="1" customHeight="1"/>
     <row r="32" s="1" customFormat="1" customHeight="1"/>
     <row r="33" s="1" customFormat="1" customHeight="1"/>
-    <row r="35" customHeight="1" spans="4:14">
-      <c r="N35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="4:14">
-      <c r="N36" s="1"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="4:14">
+    <row r="35" customHeight="1" spans="4:15">
+      <c r="O35" s="1"/>
+    </row>
+    <row r="36" customHeight="1" spans="4:15">
+      <c r="O36" s="1"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="4:15">
       <c r="D39"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3 M4 M5 L3:L5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2733,27 +2850,29 @@
     <col min="7" max="8" width="12.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="13.1666666666667" style="1" customWidth="1"/>
     <col min="10" max="10" width="24.75" style="1" customWidth="1"/>
-    <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
-    <col min="15" max="16372" width="9" style="2"/>
-    <col min="16373" max="16384" width="9" style="1"/>
+    <col min="11" max="12" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.1666666666667" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.1666666666667" style="2" customWidth="1"/>
+    <col min="16" max="16373" width="9" style="2"/>
+    <col min="16374" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="N1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -2789,12 +2908,15 @@
       <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -2826,50 +2948,56 @@
       <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -2881,33 +3009,36 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -2919,33 +3050,36 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -2957,33 +3091,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -2995,28 +3132,31 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -3027,7 +3167,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3039,28 +3179,28 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="N10" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -3071,7 +3211,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3083,28 +3223,28 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="N11" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -3115,7 +3255,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3127,28 +3267,28 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="N12" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -3159,7 +3299,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3171,28 +3311,28 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="N13" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O13" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -3203,7 +3343,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3215,40 +3355,40 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="N14" s="1" t="s">
-        <v>111</v>
+        <v>23</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="M16" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N16" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
@@ -3256,28 +3396,28 @@
         <v>0</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="M17" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N17" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>114</v>
+      <c r="N18" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:13">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C20" s="1">
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3289,30 +3429,33 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
-      <c r="M20" s="6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M20" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C21" s="1">
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3324,30 +3467,33 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
-      <c r="M21" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C22" s="1">
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3359,30 +3505,33 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
-      <c r="M22" s="6" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C23" s="1">
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3394,30 +3543,33 @@
         <v>0</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
-      <c r="M23" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M23" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N23" s="6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C24" s="1">
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3429,30 +3581,33 @@
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="M24" s="1" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N24" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="C25" s="1">
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3464,25 +3619,28 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="M25" s="6" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="M25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -3493,7 +3651,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3505,27 +3663,30 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
-      <c r="M26" s="6" t="s">
-        <v>143</v>
+      <c r="M26" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
     <row r="28" s="1" customFormat="1" customHeight="1"/>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:13">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -3536,7 +3697,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3548,25 +3709,25 @@
         <v>10011</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
-      <c r="M29" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N29" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -3577,7 +3738,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3589,25 +3750,25 @@
         <v>10021</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
-      <c r="M30" s="6" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N30" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -3618,7 +3779,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3630,25 +3791,25 @@
         <v>10031</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
-      <c r="M31" s="6" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="N31" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -3659,7 +3820,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3671,25 +3832,25 @@
         <v>10041</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
-      <c r="M32" s="6" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N32" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -3700,7 +3861,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3712,25 +3873,25 @@
         <v>10051</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
-      <c r="M33" s="6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N33" s="6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -3741,7 +3902,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -3753,25 +3914,25 @@
         <v>10061</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
-      <c r="M34" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N34" s="6" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -3782,7 +3943,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -3794,26 +3955,26 @@
         <v>10071</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
-      <c r="M35" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="R35" s="6"/>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N35" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="S35" s="6"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
@@ -3821,10 +3982,10 @@
         <v>0</v>
       </c>
       <c r="D36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="R36" s="6"/>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N36" s="6"/>
+      <c r="S36" s="6"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -3835,7 +3996,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -3847,26 +4008,26 @@
         <v>10012</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
-      <c r="M37" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="R37" s="6"/>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N37" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="S37" s="6"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -3877,7 +4038,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -3889,26 +4050,26 @@
         <v>10022</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
-      <c r="M38" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="R38" s="6"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N38" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="S38" s="6"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -3919,7 +4080,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -3931,28 +4092,28 @@
         <v>10032</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
-      <c r="M39" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="O39" s="6"/>
-      <c r="P39" s="1"/>
-      <c r="R39" s="6"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N39" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="1"/>
+      <c r="S39" s="6"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -3963,7 +4124,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>173</v>
+        <v>190</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -3975,28 +4136,28 @@
         <v>10042</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
-      <c r="M40" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="O40" s="6"/>
-      <c r="P40" s="1"/>
-      <c r="R40" s="6"/>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N40" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="1"/>
+      <c r="S40" s="6"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A41" s="1" t="s">
         <v>0</v>
       </c>
@@ -4007,7 +4168,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4019,27 +4180,27 @@
         <v>10052</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
-      <c r="M41" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="O41" s="6"/>
-      <c r="R41" s="6"/>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N41" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="P41" s="6"/>
+      <c r="S41" s="6"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A42" s="1" t="s">
         <v>0</v>
       </c>
@@ -4050,7 +4211,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4062,28 +4223,28 @@
         <v>10072</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
-      <c r="M42" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="O42" s="6"/>
-      <c r="P42" s="1"/>
-      <c r="R42" s="6"/>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N42" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="1"/>
+      <c r="S42" s="6"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -4091,11 +4252,11 @@
         <v>0</v>
       </c>
       <c r="D43" s="6"/>
-      <c r="M43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="R43" s="6"/>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N43" s="6"/>
+      <c r="P43" s="6"/>
+      <c r="S43" s="6"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A44" s="1" t="s">
         <v>0</v>
       </c>
@@ -4106,7 +4267,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4118,28 +4279,28 @@
         <v>10023</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
-      <c r="M44" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="O44" s="6"/>
-      <c r="P44" s="1"/>
-      <c r="R44" s="6"/>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N44" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="1"/>
+      <c r="S44" s="6"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A45" s="1" t="s">
         <v>0</v>
       </c>
@@ -4150,7 +4311,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4162,28 +4323,28 @@
         <v>10073</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
-      <c r="M45" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="O45" s="6"/>
-      <c r="P45" s="1"/>
-      <c r="R45" s="6"/>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="N45" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="P45" s="6"/>
+      <c r="Q45" s="1"/>
+      <c r="S45" s="6"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
@@ -4191,11 +4352,11 @@
         <v>0</v>
       </c>
       <c r="D46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="R46" s="6"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:19 16373:16384">
+      <c r="N46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="S46" s="6"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:20 16374:16384">
       <c r="A47" s="1" t="s">
         <v>0</v>
       </c>
@@ -4206,7 +4367,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4218,29 +4379,29 @@
         <v>10024</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
-      <c r="M47" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="O47" s="1"/>
+      <c r="N47" s="6" t="s">
+        <v>201</v>
+      </c>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-      <c r="S47" s="1"/>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:19 16373:16384">
+      <c r="R47" s="1"/>
+      <c r="T47" s="1"/>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:20 16374:16384">
       <c r="A48" s="1" t="s">
         <v>0</v>
       </c>
@@ -4251,7 +4412,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4263,29 +4424,29 @@
         <v>10034</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
-      <c r="M48" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="N48" s="1"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="O48" s="1"/>
+      <c r="P48" s="6"/>
       <c r="Q48" s="1"/>
-      <c r="S48" s="1"/>
-      <c r="XES48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="T48" s="1"/>
       <c r="XET48" s="1"/>
       <c r="XEU48" s="1"/>
       <c r="XEV48" s="1"/>
@@ -4298,7 +4459,7 @@
       <c r="XFC48" s="1"/>
       <c r="XFD48" s="1"/>
     </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:20 16374:16384">
       <c r="C49" s="1"/>
       <c r="D49" s="2"/>
       <c r="E49" s="1"/>
@@ -4311,11 +4472,11 @@
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
-      <c r="O49" s="6"/>
-      <c r="P49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="6"/>
       <c r="Q49" s="1"/>
-      <c r="S49" s="1"/>
-      <c r="XES49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="T49" s="1"/>
       <c r="XET49" s="1"/>
       <c r="XEU49" s="1"/>
       <c r="XEV49" s="1"/>
@@ -4328,13 +4489,13 @@
       <c r="XFC49" s="1"/>
       <c r="XFD49" s="1"/>
     </row>
-    <row r="50" customHeight="1" spans="3:19 16373:16384">
-      <c r="O50" s="1"/>
+    <row r="50" customHeight="1" spans="3:20 16374:16384">
       <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
-      <c r="S50" s="1"/>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+      <c r="R50" s="1"/>
+      <c r="T50" s="1"/>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:20 16374:16384">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -4346,11 +4507,11 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="P51" s="6"/>
       <c r="Q51" s="1"/>
-      <c r="S51" s="1"/>
-      <c r="XES51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="T51" s="1"/>
       <c r="XET51" s="1"/>
       <c r="XEU51" s="1"/>
       <c r="XEV51" s="1"/>
@@ -4363,42 +4524,42 @@
       <c r="XFC51" s="1"/>
       <c r="XFD51" s="1"/>
     </row>
-    <row r="52" customHeight="1" spans="3:19 16373:16384">
-      <c r="O52" s="6"/>
-      <c r="P52" s="1"/>
+    <row r="52" customHeight="1" spans="3:20 16374:16384">
+      <c r="P52" s="6"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="3:19 16373:16384">
-      <c r="Q53" s="1"/>
-      <c r="S53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="3:19 16373:16384">
-      <c r="Q54" s="1"/>
-      <c r="S54" s="1"/>
-    </row>
-    <row r="55" customHeight="1" spans="3:19 16373:16384">
-      <c r="O55" s="1"/>
-      <c r="Q55" s="1"/>
+      <c r="T52" s="1"/>
+    </row>
+    <row r="53" customHeight="1" spans="3:20 16374:16384">
+      <c r="R53" s="1"/>
+      <c r="T53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="3:20 16374:16384">
+      <c r="R54" s="1"/>
+      <c r="T54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="3:20 16374:16384">
+      <c r="P55" s="1"/>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
-    </row>
-    <row r="56" customHeight="1" spans="3:19 16373:16384">
-      <c r="Q56" s="1"/>
-      <c r="S56" s="1"/>
-    </row>
-    <row r="57" customHeight="1" spans="3:19 16373:16384">
-      <c r="Q57" s="1"/>
-      <c r="S57" s="1"/>
-    </row>
-    <row r="58" customHeight="1" spans="3:19 16373:16384">
-      <c r="Q58" s="1"/>
-    </row>
-    <row r="59" customHeight="1" spans="3:19 16373:16384">
-      <c r="Q59" s="1"/>
-    </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+      <c r="T55" s="1"/>
+    </row>
+    <row r="56" customHeight="1" spans="3:20 16374:16384">
+      <c r="R56" s="1"/>
+      <c r="T56" s="1"/>
+    </row>
+    <row r="57" customHeight="1" spans="3:20 16374:16384">
+      <c r="R57" s="1"/>
+      <c r="T57" s="1"/>
+    </row>
+    <row r="58" customHeight="1" spans="3:20 16374:16384">
+      <c r="R58" s="1"/>
+    </row>
+    <row r="59" customHeight="1" spans="3:20 16374:16384">
+      <c r="R59" s="1"/>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:20 16374:16384">
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -4410,7 +4571,7 @@
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
-      <c r="XES62" s="1"/>
+      <c r="N62" s="1"/>
       <c r="XET62" s="1"/>
       <c r="XEU62" s="1"/>
       <c r="XEV62" s="1"/>
@@ -4423,7 +4584,7 @@
       <c r="XFC62" s="1"/>
       <c r="XFD62" s="1"/>
     </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:20 16374:16384">
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -4435,7 +4596,7 @@
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
-      <c r="XES63" s="1"/>
+      <c r="N63" s="1"/>
       <c r="XET63" s="1"/>
       <c r="XEU63" s="1"/>
       <c r="XEV63" s="1"/>
@@ -4448,7 +4609,7 @@
       <c r="XFC63" s="1"/>
       <c r="XFD63" s="1"/>
     </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:19 16373:16384">
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:20 16374:16384">
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -4460,7 +4621,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
-      <c r="XES64" s="1"/>
+      <c r="N64" s="1"/>
       <c r="XET64" s="1"/>
       <c r="XEU64" s="1"/>
       <c r="XEV64" s="1"/>
@@ -4473,7 +4634,7 @@
       <c r="XFC64" s="1"/>
       <c r="XFD64" s="1"/>
     </row>
-    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="65" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -4485,7 +4646,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
-      <c r="XES65" s="1"/>
+      <c r="N65" s="1"/>
       <c r="XET65" s="1"/>
       <c r="XEU65" s="1"/>
       <c r="XEV65" s="1"/>
@@ -4498,7 +4659,7 @@
       <c r="XFC65" s="1"/>
       <c r="XFD65" s="1"/>
     </row>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -4510,7 +4671,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
-      <c r="XES66" s="1"/>
+      <c r="N66" s="1"/>
       <c r="XET66" s="1"/>
       <c r="XEU66" s="1"/>
       <c r="XEV66" s="1"/>
@@ -4523,7 +4684,7 @@
       <c r="XFC66" s="1"/>
       <c r="XFD66" s="1"/>
     </row>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -4535,7 +4696,7 @@
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
-      <c r="XES67" s="1"/>
+      <c r="N67" s="1"/>
       <c r="XET67" s="1"/>
       <c r="XEU67" s="1"/>
       <c r="XEV67" s="1"/>
@@ -4550,7 +4711,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3 M4 M5 L3:L5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -4572,27 +4733,29 @@
     <col min="7" max="9" width="12.25" style="1" customWidth="1"/>
     <col min="10" max="10" width="26" style="1" customWidth="1"/>
     <col min="11" max="11" width="17.1666666666667" style="1" customWidth="1"/>
-    <col min="12" max="13" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
-    <col min="15" max="16372" width="9" style="2"/>
-    <col min="16373" max="16384" width="9" style="1"/>
+    <col min="12" max="12" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="22.8333333333333" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.1666666666667" style="2" customWidth="1"/>
+    <col min="16" max="16373" width="9" style="2"/>
+    <col min="16374" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="N1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -4628,12 +4791,15 @@
       <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -4665,52 +4831,58 @@
       <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    </row>
+    <row r="6" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1">
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4722,24 +4894,26 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="XES6" s="1"/>
+        <v>206</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="XET6" s="1"/>
       <c r="XEU6" s="1"/>
       <c r="XEV6" s="1"/>
@@ -4752,14 +4926,14 @@
       <c r="XFC6" s="1"/>
       <c r="XFD6" s="1"/>
     </row>
-    <row r="7" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="7" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1">
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -4771,24 +4945,26 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="XES7" s="1"/>
+        <v>206</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="XET7" s="1"/>
       <c r="XEU7" s="1"/>
       <c r="XEV7" s="1"/>
@@ -4801,14 +4977,14 @@
       <c r="XFC7" s="1"/>
       <c r="XFD7" s="1"/>
     </row>
-    <row r="8" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="8" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1">
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -4820,24 +4996,26 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="XES8" s="1"/>
+        <v>206</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="XET8" s="1"/>
       <c r="XEU8" s="1"/>
       <c r="XEV8" s="1"/>
@@ -4850,14 +5028,14 @@
       <c r="XFC8" s="1"/>
       <c r="XFD8" s="1"/>
     </row>
-    <row r="9" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="9" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1">
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -4869,24 +5047,26 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L9" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="XES9" s="1"/>
+        <v>206</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="XET9" s="1"/>
       <c r="XEU9" s="1"/>
       <c r="XEV9" s="1"/>
@@ -4899,7 +5079,7 @@
       <c r="XFC9" s="1"/>
       <c r="XFD9" s="1"/>
     </row>
-    <row r="10" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="10" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -4910,7 +5090,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -4922,24 +5102,24 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="XES10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="XET10" s="1"/>
       <c r="XEU10" s="1"/>
       <c r="XEV10" s="1"/>
@@ -4952,7 +5132,7 @@
       <c r="XFC10" s="1"/>
       <c r="XFD10" s="1"/>
     </row>
-    <row r="11" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="11" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -4963,7 +5143,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -4975,24 +5155,24 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="XES11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="XET11" s="1"/>
       <c r="XEU11" s="1"/>
       <c r="XEV11" s="1"/>
@@ -5005,7 +5185,7 @@
       <c r="XFC11" s="1"/>
       <c r="XFD11" s="1"/>
     </row>
-    <row r="12" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="12" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -5016,7 +5196,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5028,24 +5208,24 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="XES12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="XET12" s="1"/>
       <c r="XEU12" s="1"/>
       <c r="XEV12" s="1"/>
@@ -5058,7 +5238,7 @@
       <c r="XFC12" s="1"/>
       <c r="XFD12" s="1"/>
     </row>
-    <row r="13" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="13" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -5069,7 +5249,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5081,24 +5261,24 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="XES13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="XET13" s="1"/>
       <c r="XEU13" s="1"/>
       <c r="XEV13" s="1"/>
@@ -5111,7 +5291,7 @@
       <c r="XFC13" s="1"/>
       <c r="XFD13" s="1"/>
     </row>
-    <row r="14" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="14" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -5122,7 +5302,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5134,24 +5314,24 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="XES14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="XET14" s="1"/>
       <c r="XEU14" s="1"/>
       <c r="XEV14" s="1"/>
@@ -5164,7 +5344,7 @@
       <c r="XFC14" s="1"/>
       <c r="XFD14" s="1"/>
     </row>
-    <row r="15" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="15" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -5177,7 +5357,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="XES15" s="1"/>
+      <c r="N15" s="1"/>
       <c r="XET15" s="1"/>
       <c r="XEU15" s="1"/>
       <c r="XEV15" s="1"/>
@@ -5190,12 +5370,12 @@
       <c r="XFC15" s="1"/>
       <c r="XFD15" s="1"/>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C16" s="1">
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5207,30 +5387,33 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
-      <c r="M16" s="6" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="M16" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C17" s="1">
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>205</v>
+        <v>224</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5242,30 +5425,33 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
-      <c r="M17" s="6" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="M17" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C18" s="1">
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5277,30 +5463,33 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
-      <c r="M18" s="6" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="M18" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C19" s="1">
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5312,30 +5501,33 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
-      <c r="M19" s="6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="M19" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C20" s="1">
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5347,30 +5539,33 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
-      <c r="M20" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="M20" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C21" s="1">
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5382,25 +5577,28 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
-      <c r="M21" s="6" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="M21" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -5411,7 +5609,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5423,29 +5621,32 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="M22" s="1" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N22" s="6" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="D23" s="6"/>
-      <c r="M23" s="6"/>
-    </row>
-    <row r="24" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -5456,7 +5657,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5468,25 +5669,25 @@
         <v>20011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="M24" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="XES24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="XET24" s="1"/>
       <c r="XEU24" s="1"/>
       <c r="XEV24" s="1"/>
@@ -5499,7 +5700,7 @@
       <c r="XFC24" s="1"/>
       <c r="XFD24" s="1"/>
     </row>
-    <row r="25" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="25" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -5510,7 +5711,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5522,25 +5723,25 @@
         <v>20021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="M25" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="N25" s="1"/>
-      <c r="XES25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="O25" s="1"/>
       <c r="XET25" s="1"/>
       <c r="XEU25" s="1"/>
       <c r="XEV25" s="1"/>
@@ -5553,7 +5754,7 @@
       <c r="XFC25" s="1"/>
       <c r="XFD25" s="1"/>
     </row>
-    <row r="26" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="26" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -5564,7 +5765,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5576,25 +5777,25 @@
         <v>20031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
-      <c r="M26" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="N26" s="1"/>
-      <c r="XES26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="O26" s="1"/>
       <c r="XET26" s="1"/>
       <c r="XEU26" s="1"/>
       <c r="XEV26" s="1"/>
@@ -5607,7 +5808,7 @@
       <c r="XFC26" s="1"/>
       <c r="XFD26" s="1"/>
     </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="27" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -5618,7 +5819,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5630,25 +5831,25 @@
         <v>20041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
-      <c r="M27" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="N27" s="1"/>
-      <c r="XES27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="O27" s="1"/>
       <c r="XET27" s="1"/>
       <c r="XEU27" s="1"/>
       <c r="XEV27" s="1"/>
@@ -5661,7 +5862,7 @@
       <c r="XFC27" s="1"/>
       <c r="XFD27" s="1"/>
     </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="28" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
@@ -5672,7 +5873,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -5684,25 +5885,25 @@
         <v>20051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
-      <c r="M28" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="N28" s="1"/>
-      <c r="XES28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="O28" s="1"/>
       <c r="XET28" s="1"/>
       <c r="XEU28" s="1"/>
       <c r="XEV28" s="1"/>
@@ -5715,7 +5916,7 @@
       <c r="XFC28" s="1"/>
       <c r="XFD28" s="1"/>
     </row>
-    <row r="29" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="29" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -5726,7 +5927,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>233</v>
+        <v>252</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -5738,25 +5939,25 @@
         <v>20061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
-      <c r="M29" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="N29" s="1"/>
-      <c r="XES29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="O29" s="1"/>
       <c r="XET29" s="1"/>
       <c r="XEU29" s="1"/>
       <c r="XEV29" s="1"/>
@@ -5769,7 +5970,7 @@
       <c r="XFC29" s="1"/>
       <c r="XFD29" s="1"/>
     </row>
-    <row r="30" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="30" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -5780,7 +5981,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -5792,25 +5993,25 @@
         <v>20071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
-      <c r="M30" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="N30" s="1"/>
-      <c r="XES30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="O30" s="1"/>
       <c r="XET30" s="1"/>
       <c r="XEU30" s="1"/>
       <c r="XEV30" s="1"/>
@@ -5823,7 +6024,7 @@
       <c r="XFC30" s="1"/>
       <c r="XFD30" s="1"/>
     </row>
-    <row r="31" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="31" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
@@ -5840,9 +6041,9 @@
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="1"/>
-      <c r="XES31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="1"/>
       <c r="XET31" s="1"/>
       <c r="XEU31" s="1"/>
       <c r="XEV31" s="1"/>
@@ -5855,7 +6056,7 @@
       <c r="XFC31" s="1"/>
       <c r="XFD31" s="1"/>
     </row>
-    <row r="32" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="32" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -5866,7 +6067,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -5878,25 +6079,25 @@
         <v>20012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
-      <c r="M32" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="N32" s="1"/>
-      <c r="XES32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="O32" s="1"/>
       <c r="XET32" s="1"/>
       <c r="XEU32" s="1"/>
       <c r="XEV32" s="1"/>
@@ -5909,7 +6110,7 @@
       <c r="XFC32" s="1"/>
       <c r="XFD32" s="1"/>
     </row>
-    <row r="33" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="33" customFormat="1" customHeight="1" spans="1:19 16374:16384">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -5920,7 +6121,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -5932,25 +6133,25 @@
         <v>20022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
-      <c r="M33" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="N33" s="1"/>
-      <c r="XES33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="O33" s="1"/>
       <c r="XET33" s="1"/>
       <c r="XEU33" s="1"/>
       <c r="XEV33" s="1"/>
@@ -5963,7 +6164,7 @@
       <c r="XFC33" s="1"/>
       <c r="XFD33" s="1"/>
     </row>
-    <row r="34" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="34" customFormat="1" customHeight="1" spans="1:19 16374:16384">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -5974,7 +6175,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>241</v>
+        <v>260</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -5986,25 +6187,25 @@
         <v>20032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
-      <c r="M34" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="XES34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="O34" s="1"/>
       <c r="XET34" s="1"/>
       <c r="XEU34" s="1"/>
       <c r="XEV34" s="1"/>
@@ -6017,7 +6218,7 @@
       <c r="XFC34" s="1"/>
       <c r="XFD34" s="1"/>
     </row>
-    <row r="35" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="35" customFormat="1" customHeight="1" spans="1:19 16374:16384">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -6028,7 +6229,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>243</v>
+        <v>262</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6040,25 +6241,25 @@
         <v>20052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
-      <c r="M35" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="N35" s="1"/>
-      <c r="XES35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="O35" s="1"/>
       <c r="XET35" s="1"/>
       <c r="XEU35" s="1"/>
       <c r="XEV35" s="1"/>
@@ -6071,7 +6272,7 @@
       <c r="XFC35" s="1"/>
       <c r="XFD35" s="1"/>
     </row>
-    <row r="36" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="36" customFormat="1" customHeight="1" spans="1:19 16374:16384">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
@@ -6082,7 +6283,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6094,25 +6295,25 @@
         <v>20072</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
-      <c r="M36" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="N36" s="1"/>
-      <c r="XES36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="O36" s="1"/>
       <c r="XET36" s="1"/>
       <c r="XEU36" s="1"/>
       <c r="XEV36" s="1"/>
@@ -6125,7 +6326,7 @@
       <c r="XFC36" s="1"/>
       <c r="XFD36" s="1"/>
     </row>
-    <row r="37" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="37" customFormat="1" customHeight="1" spans="1:19 16374:16384">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -6142,9 +6343,9 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="1"/>
-      <c r="XES37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="1"/>
       <c r="XET37" s="1"/>
       <c r="XEU37" s="1"/>
       <c r="XEV37" s="1"/>
@@ -6157,7 +6358,7 @@
       <c r="XFC37" s="1"/>
       <c r="XFD37" s="1"/>
     </row>
-    <row r="38" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="38" customFormat="1" customHeight="1" spans="1:19 16374:16384">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -6168,7 +6369,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6180,25 +6381,25 @@
         <v>20023</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
-      <c r="M38" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="XES38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="O38" s="1"/>
       <c r="XET38" s="1"/>
       <c r="XEU38" s="1"/>
       <c r="XEV38" s="1"/>
@@ -6211,7 +6412,7 @@
       <c r="XFC38" s="1"/>
       <c r="XFD38" s="1"/>
     </row>
-    <row r="39" s="2" customFormat="1" customHeight="1" spans="1:18 16373:16384">
+    <row r="39" s="2" customFormat="1" customHeight="1" spans="1:19 16374:16384">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -6222,7 +6423,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6234,25 +6435,25 @@
         <v>20043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
-      <c r="M39" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="N39" s="1"/>
-      <c r="XES39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="O39" s="1"/>
       <c r="XET39" s="1"/>
       <c r="XEU39" s="1"/>
       <c r="XEV39" s="1"/>
@@ -6265,7 +6466,7 @@
       <c r="XFC39" s="1"/>
       <c r="XFD39" s="1"/>
     </row>
-    <row r="40" customHeight="1" spans="1:18 16373:16384">
+    <row r="40" customHeight="1" spans="1:19 16374:16384">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -6276,7 +6477,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6288,30 +6489,30 @@
         <v>20073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
-      <c r="M40" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="N40" s="1"/>
+      <c r="N40" s="6" t="s">
+        <v>271</v>
+      </c>
       <c r="O40" s="1"/>
-      <c r="P40" s="6"/>
+      <c r="P40" s="1"/>
       <c r="Q40" s="6"/>
-      <c r="R40" s="1"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:18 16373:16384">
+      <c r="R40" s="6"/>
+      <c r="S40" s="1"/>
+    </row>
+    <row r="41" customHeight="1" spans="1:19 16374:16384">
       <c r="A41" s="1" t="s">
         <v>0</v>
       </c>
@@ -6319,14 +6520,14 @@
         <v>0</v>
       </c>
       <c r="D41" s="6"/>
-      <c r="M41" s="6"/>
-      <c r="N41" s="1"/>
+      <c r="N41" s="6"/>
       <c r="O41" s="1"/>
-      <c r="P41" s="6"/>
+      <c r="P41" s="1"/>
       <c r="Q41" s="6"/>
-      <c r="R41" s="1"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:18 16373:16384">
+      <c r="R41" s="6"/>
+      <c r="S41" s="1"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:19 16374:16384">
       <c r="A42" s="1" t="s">
         <v>0</v>
       </c>
@@ -6337,7 +6538,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6349,30 +6550,30 @@
         <v>20024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
-      <c r="M42" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="N42" s="1"/>
+      <c r="N42" s="6" t="s">
+        <v>273</v>
+      </c>
       <c r="O42" s="1"/>
-      <c r="P42" s="6"/>
+      <c r="P42" s="1"/>
       <c r="Q42" s="6"/>
-      <c r="R42" s="1"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:18 16373:16384">
+      <c r="R42" s="6"/>
+      <c r="S42" s="1"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:19 16374:16384">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -6383,7 +6584,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6395,65 +6596,65 @@
         <v>20034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
-      <c r="M43" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="N43" s="1"/>
+      <c r="N43" s="6" t="s">
+        <v>275</v>
+      </c>
       <c r="O43" s="1"/>
-      <c r="P43" s="6"/>
+      <c r="P43" s="1"/>
       <c r="Q43" s="6"/>
-      <c r="R43" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:18 16373:16384">
-      <c r="N44" s="1"/>
+      <c r="R43" s="6"/>
+      <c r="S43" s="1"/>
+    </row>
+    <row r="44" customHeight="1" spans="1:19 16374:16384">
       <c r="O44" s="1"/>
-      <c r="P44" s="6"/>
+      <c r="P44" s="1"/>
       <c r="Q44" s="6"/>
-      <c r="R44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="1:18 16373:16384">
-      <c r="N45" s="1"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="1:19 16374:16384">
       <c r="O45" s="1"/>
-      <c r="P45" s="6"/>
+      <c r="P45" s="1"/>
       <c r="Q45" s="6"/>
-      <c r="R45" s="1"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:18 16373:16384">
-      <c r="N46" s="1"/>
+      <c r="R45" s="6"/>
+      <c r="S45" s="1"/>
+    </row>
+    <row r="46" customHeight="1" spans="1:19 16374:16384">
       <c r="O46" s="1"/>
-      <c r="P46" s="6"/>
+      <c r="P46" s="1"/>
       <c r="Q46" s="6"/>
-      <c r="R46" s="1"/>
-    </row>
-    <row r="47" customHeight="1" spans="1:18 16373:16384">
-      <c r="N47" s="1"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="1"/>
+    </row>
+    <row r="47" customHeight="1" spans="1:19 16374:16384">
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="1"/>
-    </row>
-    <row r="48" customHeight="1" spans="1:18 16373:16384">
-      <c r="N48" s="1"/>
+      <c r="Q47" s="1"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="1"/>
+    </row>
+    <row r="48" customHeight="1" spans="1:19 16374:16384">
       <c r="O48" s="1"/>
-      <c r="P48" s="6"/>
+      <c r="P48" s="1"/>
       <c r="Q48" s="6"/>
-      <c r="R48" s="1"/>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+      <c r="R48" s="6"/>
+      <c r="S48" s="1"/>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:19 16374:16384">
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -6465,12 +6666,12 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
-      <c r="N49" s="2"/>
-      <c r="O49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="2"/>
       <c r="P49" s="1"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="1"/>
-      <c r="XES49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="6"/>
+      <c r="S49" s="1"/>
       <c r="XET49" s="1"/>
       <c r="XEU49" s="1"/>
       <c r="XEV49" s="1"/>
@@ -6483,7 +6684,7 @@
       <c r="XFC49" s="1"/>
       <c r="XFD49" s="1"/>
     </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:19 16374:16384">
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -6495,12 +6696,12 @@
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
-      <c r="N50" s="2"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="6"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="1"/>
       <c r="Q50" s="6"/>
-      <c r="R50" s="1"/>
-      <c r="XES50" s="1"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="1"/>
       <c r="XET50" s="1"/>
       <c r="XEU50" s="1"/>
       <c r="XEV50" s="1"/>
@@ -6513,7 +6714,7 @@
       <c r="XFC50" s="1"/>
       <c r="XFD50" s="1"/>
     </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:19 16374:16384">
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -6525,12 +6726,12 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="2"/>
       <c r="P51" s="1"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="1"/>
-      <c r="XES51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="6"/>
+      <c r="S51" s="1"/>
       <c r="XET51" s="1"/>
       <c r="XEU51" s="1"/>
       <c r="XEV51" s="1"/>
@@ -6543,7 +6744,7 @@
       <c r="XFC51" s="1"/>
       <c r="XFD51" s="1"/>
     </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:18 16373:16384">
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:19 16374:16384">
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -6555,12 +6756,12 @@
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
-      <c r="N52" s="2"/>
-      <c r="O52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="2"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
-      <c r="XES52" s="1"/>
+      <c r="S52" s="1"/>
       <c r="XET52" s="1"/>
       <c r="XEU52" s="1"/>
       <c r="XEV52" s="1"/>
@@ -6573,51 +6774,51 @@
       <c r="XFC52" s="1"/>
       <c r="XFD52" s="1"/>
     </row>
-    <row r="53" customHeight="1" spans="3:18 16373:16384">
-      <c r="O53" s="1"/>
+    <row r="53" customHeight="1" spans="3:19 16374:16384">
       <c r="P53" s="1"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="3:18 16373:16384">
-      <c r="O54" s="1"/>
+      <c r="Q53" s="1"/>
+      <c r="R53" s="6"/>
+      <c r="S53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="3:19 16374:16384">
       <c r="P54" s="1"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="1"/>
-    </row>
-    <row r="55" customHeight="1" spans="3:18 16373:16384">
-      <c r="O55" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="6"/>
+      <c r="S54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="3:19 16374:16384">
       <c r="P55" s="1"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="1"/>
-    </row>
-    <row r="56" customHeight="1" spans="3:18 16373:16384">
-      <c r="O56" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="6"/>
+      <c r="S55" s="1"/>
+    </row>
+    <row r="56" customHeight="1" spans="3:19 16374:16384">
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
       <c r="R56" s="1"/>
-    </row>
-    <row r="57" customHeight="1" spans="3:18 16373:16384">
-      <c r="O57" s="1"/>
+      <c r="S56" s="1"/>
+    </row>
+    <row r="57" customHeight="1" spans="3:19 16374:16384">
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
       <c r="R57" s="1"/>
-    </row>
-    <row r="58" customHeight="1" spans="3:18 16373:16384">
-      <c r="O58" s="1"/>
+      <c r="S57" s="1"/>
+    </row>
+    <row r="58" customHeight="1" spans="3:19 16374:16384">
       <c r="P58" s="1"/>
-      <c r="Q58" s="6"/>
-      <c r="R58" s="1"/>
-    </row>
-    <row r="59" customHeight="1" spans="3:18 16373:16384">
-      <c r="O59" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="1"/>
+    </row>
+    <row r="59" customHeight="1" spans="3:19 16374:16384">
       <c r="P59" s="1"/>
-      <c r="Q59" s="6"/>
-      <c r="R59" s="1"/>
+      <c r="Q59" s="1"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3 M4 M5 L3:L5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6639,27 +6840,29 @@
     <col min="7" max="7" width="12.25" style="1" customWidth="1"/>
     <col min="8" max="9" width="13.5" style="1" customWidth="1"/>
     <col min="10" max="10" width="19.5833333333333" style="1" customWidth="1"/>
-    <col min="11" max="13" width="15.9166666666667" style="1" customWidth="1"/>
-    <col min="14" max="14" width="18.1666666666667" style="2" customWidth="1"/>
-    <col min="15" max="16372" width="9" style="2"/>
-    <col min="16373" max="16384" width="9" style="1"/>
+    <col min="11" max="12" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.3333333333333" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.9166666666667" style="1" customWidth="1"/>
+    <col min="15" max="15" width="18.1666666666667" style="2" customWidth="1"/>
+    <col min="16" max="16373" width="9" style="2"/>
+    <col min="16374" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="N1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="N2" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -6695,12 +6898,15 @@
       <c r="M3" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N3" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -6732,50 +6938,56 @@
       <c r="M4" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:14">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C6" s="1">
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -6787,30 +6999,33 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>278</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C7" s="1">
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -6822,30 +7037,33 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>278</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C8" s="1">
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -6857,31 +7075,34 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="2"/>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>278</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C9" s="1">
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -6893,26 +7114,29 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L9" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9"/>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:14">
+        <v>278</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9"/>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -6923,7 +7147,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -6935,26 +7159,26 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10"/>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O10"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -6965,7 +7189,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -6977,26 +7201,26 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
@@ -7007,7 +7231,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7019,26 +7243,26 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
       </c>
-      <c r="M12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O12"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -7049,7 +7273,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7061,26 +7285,26 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
       </c>
-      <c r="M13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O13"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
@@ -7091,7 +7315,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7103,34 +7327,34 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
       </c>
-      <c r="M14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N14"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="N15"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O15"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C16" s="1">
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7142,30 +7366,33 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
-      <c r="M16" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="M16" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C17" s="1">
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7177,30 +7404,33 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
-      <c r="M17" s="6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="M17" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C18" s="1">
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7212,30 +7442,33 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
-      <c r="M18" s="6" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="M18" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C19" s="1">
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7247,30 +7480,33 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
-      <c r="M19" s="6" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="M19" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C20" s="1">
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7282,30 +7518,33 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
-      <c r="M20" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="M20" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C21" s="1">
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7317,25 +7556,28 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
-      <c r="M21" s="6" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="M21" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -7346,7 +7588,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7358,28 +7600,31 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
-      <c r="M22" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="N23"/>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="M22" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="O23"/>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A24" s="1" t="s">
         <v>0</v>
       </c>
@@ -7390,7 +7635,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7402,26 +7647,26 @@
         <v>30011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="N24" s="2"/>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N24" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -7432,7 +7677,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7444,26 +7689,26 @@
         <v>30021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
-      <c r="M25" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="N25" s="2"/>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N25" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -7474,7 +7719,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7486,26 +7731,26 @@
         <v>30031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
-      <c r="M26" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="N26" s="2"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N26" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A27" s="1" t="s">
         <v>0</v>
       </c>
@@ -7516,7 +7761,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7528,26 +7773,26 @@
         <v>30041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
-      <c r="M27" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="N27" s="2"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N27" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
@@ -7558,7 +7803,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7570,26 +7815,26 @@
         <v>30051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
-      <c r="M28" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="N28" s="2"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N28" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -7600,7 +7845,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7612,26 +7857,26 @@
         <v>30061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="N29" s="2"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N29" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A30" s="1" t="s">
         <v>0</v>
       </c>
@@ -7642,7 +7887,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7654,35 +7899,35 @@
         <v>30071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
-      <c r="M30" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="N30" s="2"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="N30" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A31" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N31" s="2"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="A32" s="1" t="s">
         <v>0</v>
       </c>
@@ -7693,7 +7938,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -7705,26 +7950,26 @@
         <v>30012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
-      <c r="M32" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="N32" s="2"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N32" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="O32" s="2"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -7735,7 +7980,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -7747,26 +7992,26 @@
         <v>30022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
-      <c r="M33" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="N33" s="2"/>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N33" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="O33" s="2"/>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -7777,7 +8022,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -7789,26 +8034,26 @@
         <v>30032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="N34" s="2"/>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N34" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="O34" s="2"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A35" s="1" t="s">
         <v>0</v>
       </c>
@@ -7819,7 +8064,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -7831,35 +8076,35 @@
         <v>30052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
-      <c r="M35" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="N35" s="2"/>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N35" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="O35" s="2"/>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A36" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="N36" s="2"/>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="O36" s="2"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
@@ -7870,7 +8115,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -7882,26 +8127,26 @@
         <v>30023</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
-      <c r="M37" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="N37" s="2"/>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N37" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="O37" s="2"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A38" s="1" t="s">
         <v>0</v>
       </c>
@@ -7912,7 +8157,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -7924,26 +8169,26 @@
         <v>30033</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N38" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -7954,7 +8199,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -7966,26 +8211,26 @@
         <v>30043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
-      <c r="M39" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="N39" s="2"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N39" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="O39" s="2"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A40" s="1" t="s">
         <v>0</v>
       </c>
@@ -7996,7 +8241,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8008,26 +8253,26 @@
         <v>30073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
-      <c r="M40" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="N40" s="2"/>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N40" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="O40" s="2"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A41" s="1" t="s">
         <v>0</v>
       </c>
@@ -8035,10 +8280,10 @@
         <v>0</v>
       </c>
       <c r="D41" s="2"/>
-      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="O41" s="2"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="A42" s="1" t="s">
         <v>0</v>
       </c>
@@ -8049,7 +8294,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8061,26 +8306,26 @@
         <v>30024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
-      <c r="M42" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="N42" s="2"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:14 16373:16384">
+      <c r="N42" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="O42" s="2"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:15 16374:16384">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -8091,7 +8336,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8103,25 +8348,25 @@
         <v>30034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
-      <c r="M43" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+      <c r="N43" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -8132,9 +8377,9 @@
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="6"/>
-      <c r="N44" s="1"/>
-      <c r="XES44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="1"/>
       <c r="XET44" s="1"/>
       <c r="XEU44" s="1"/>
       <c r="XEV44" s="1"/>
@@ -8147,7 +8392,7 @@
       <c r="XFC44" s="1"/>
       <c r="XFD44" s="1"/>
     </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -8160,7 +8405,7 @@
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
-      <c r="XES45" s="1"/>
+      <c r="O45" s="1"/>
       <c r="XET45" s="1"/>
       <c r="XEU45" s="1"/>
       <c r="XEV45" s="1"/>
@@ -8173,7 +8418,7 @@
       <c r="XFC45" s="1"/>
       <c r="XFD45" s="1"/>
     </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="1:14 16373:16384">
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -8185,7 +8430,7 @@
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
-      <c r="XES47" s="1"/>
+      <c r="N47" s="1"/>
       <c r="XET47" s="1"/>
       <c r="XEU47" s="1"/>
       <c r="XEV47" s="1"/>
@@ -8198,7 +8443,7 @@
       <c r="XFC47" s="1"/>
       <c r="XFD47" s="1"/>
     </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -8210,7 +8455,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
-      <c r="XES58" s="1"/>
+      <c r="N58" s="1"/>
       <c r="XET58" s="1"/>
       <c r="XEU58" s="1"/>
       <c r="XEV58" s="1"/>
@@ -8223,7 +8468,7 @@
       <c r="XFC58" s="1"/>
       <c r="XFD58" s="1"/>
     </row>
-    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="59" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -8235,7 +8480,7 @@
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
-      <c r="XES59" s="1"/>
+      <c r="N59" s="1"/>
       <c r="XET59" s="1"/>
       <c r="XEU59" s="1"/>
       <c r="XEV59" s="1"/>
@@ -8248,7 +8493,7 @@
       <c r="XFC59" s="1"/>
       <c r="XFD59" s="1"/>
     </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -8260,7 +8505,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
-      <c r="XES60" s="1"/>
+      <c r="N60" s="1"/>
       <c r="XET60" s="1"/>
       <c r="XEU60" s="1"/>
       <c r="XEV60" s="1"/>
@@ -8273,7 +8518,7 @@
       <c r="XFC60" s="1"/>
       <c r="XFD60" s="1"/>
     </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -8285,7 +8530,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
-      <c r="XES61" s="1"/>
+      <c r="N61" s="1"/>
       <c r="XET61" s="1"/>
       <c r="XEU61" s="1"/>
       <c r="XEV61" s="1"/>
@@ -8298,7 +8543,7 @@
       <c r="XFC61" s="1"/>
       <c r="XFD61" s="1"/>
     </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -8310,7 +8555,7 @@
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
-      <c r="XES62" s="1"/>
+      <c r="N62" s="1"/>
       <c r="XET62" s="1"/>
       <c r="XEU62" s="1"/>
       <c r="XEV62" s="1"/>
@@ -8323,7 +8568,7 @@
       <c r="XFC62" s="1"/>
       <c r="XFD62" s="1"/>
     </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:13 16373:16384">
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:14 16374:16384">
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -8335,7 +8580,7 @@
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
-      <c r="XES63" s="1"/>
+      <c r="N63" s="1"/>
       <c r="XET63" s="1"/>
       <c r="XEU63" s="1"/>
       <c r="XEV63" s="1"/>
@@ -8350,7 +8595,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3 M4 M5 L3:L5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="361">
   <si>
     <t>#</t>
   </si>
@@ -86,33 +86,36 @@
     <t>妙手扳指</t>
   </si>
   <si>
-    <t>85,3,95</t>
+    <t>85,1,95</t>
+  </si>
+  <si>
+    <t>20,1000,1</t>
+  </si>
+  <si>
+    <t>40000001,40000002,40000003</t>
+  </si>
+  <si>
+    <t>50,10,2</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive1</t>
+  </si>
+  <si>
+    <t>没有特殊效果</t>
+  </si>
+  <si>
+    <t>杀怪金币</t>
+  </si>
+  <si>
+    <t>修行符</t>
+  </si>
+  <si>
+    <t>86,2,95</t>
   </si>
   <si>
     <t>20,100,1</t>
   </si>
   <si>
-    <t>40000001,40000002,40000003</t>
-  </si>
-  <si>
-    <t>50,10,2</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive1</t>
-  </si>
-  <si>
-    <t>没有特殊效果</t>
-  </si>
-  <si>
-    <t>杀怪金币</t>
-  </si>
-  <si>
-    <t>修行符</t>
-  </si>
-  <si>
-    <t>86,3,95</t>
-  </si>
-  <si>
     <t>40000004,40000005,40000006</t>
   </si>
   <si>
@@ -125,10 +128,10 @@
     <t>摸金符</t>
   </si>
   <si>
-    <t>85,1003,95</t>
-  </si>
-  <si>
-    <t>40,1,1</t>
+    <t>85,1001,95</t>
+  </si>
+  <si>
+    <t>40,4,1</t>
   </si>
   <si>
     <t>40000007,40000008,40000009</t>
@@ -143,7 +146,10 @@
     <t>修行手册</t>
   </si>
   <si>
-    <t>86,1003,95</t>
+    <t>86,1002,95</t>
+  </si>
+  <si>
+    <t>40,2,1</t>
   </si>
   <si>
     <t>40000010,40000011,40000012</t>
@@ -155,297 +161,324 @@
     <t>铜钱袋</t>
   </si>
   <si>
-    <t>81,27,95</t>
+    <t>81,1001,95</t>
+  </si>
+  <si>
+    <t>3,6,1</t>
+  </si>
+  <si>
+    <t>150,18,6</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive5</t>
+  </si>
+  <si>
+    <t>金币加成</t>
+  </si>
+  <si>
+    <t>试炼卷轴</t>
+  </si>
+  <si>
+    <t>82,1002,95</t>
+  </si>
+  <si>
+    <t>3,3,1</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive6</t>
+  </si>
+  <si>
+    <t>经验加成</t>
+  </si>
+  <si>
+    <t>寻金符</t>
+  </si>
+  <si>
+    <t>83,1001,95</t>
+  </si>
+  <si>
+    <t>3,10,1</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive7</t>
+  </si>
+  <si>
+    <t>爆率加成</t>
+  </si>
+  <si>
+    <t>四叶草</t>
+  </si>
+  <si>
+    <t>84,1002,95</t>
+  </si>
+  <si>
+    <t>3,5,1</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive8</t>
+  </si>
+  <si>
+    <t>品质加成</t>
+  </si>
+  <si>
+    <t>宠物袋</t>
+  </si>
+  <si>
+    <t>2001,111,95</t>
+  </si>
+  <si>
+    <t>6,1,2</t>
+  </si>
+  <si>
+    <t>40000003,40000006,40000009</t>
+  </si>
+  <si>
+    <t>15,15,15</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive101</t>
+  </si>
+  <si>
+    <t>增加一个宠物备战位</t>
+  </si>
+  <si>
+    <t>技能手册</t>
+  </si>
+  <si>
+    <t>2002,113,95</t>
+  </si>
+  <si>
+    <t>3,1,2</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive102</t>
+  </si>
+  <si>
+    <t>增加一个技能出战栏位</t>
+  </si>
+  <si>
+    <t>增加一个技能出站栏位</t>
+  </si>
+  <si>
+    <t>传世勋章</t>
+  </si>
+  <si>
+    <t>2001,95</t>
+  </si>
+  <si>
+    <t>8,3</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive105</t>
+  </si>
+  <si>
+    <t>解锁传世高级挑战</t>
+  </si>
+  <si>
+    <t>传世印记</t>
+  </si>
+  <si>
+    <t>2002,95</t>
+  </si>
+  <si>
+    <t>4,3</t>
+  </si>
+  <si>
+    <t>40000012,40000015,40000018</t>
+  </si>
+  <si>
+    <t>30,30,30</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive106</t>
+  </si>
+  <si>
+    <t>解锁传世超级挑战</t>
+  </si>
+  <si>
+    <t>神灵印记</t>
+  </si>
+  <si>
+    <t>2001,114,95</t>
+  </si>
+  <si>
+    <t>10,1,3</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive103</t>
+  </si>
+  <si>
+    <t>技能词条套装所需数量-1</t>
+  </si>
+  <si>
+    <t>装备词条套装所需数量-1</t>
+  </si>
+  <si>
+    <t>勇气号角</t>
+  </si>
+  <si>
+    <t>5,3</t>
+  </si>
+  <si>
+    <t>Exclusive/Exclusive104</t>
+  </si>
+  <si>
+    <t>低概率刷新低于当前地图的区域boss</t>
+  </si>
+  <si>
+    <t>粗铁刀</t>
+  </si>
+  <si>
+    <t>4,1,95</t>
+  </si>
+  <si>
+    <t>100,1000,1</t>
+  </si>
+  <si>
+    <t>25,3,1</t>
+  </si>
+  <si>
+    <t>Bag/Equip/Box_Equip_1_1</t>
+  </si>
+  <si>
+    <t>物攻基础</t>
+  </si>
+  <si>
+    <t>粗铁剑</t>
+  </si>
+  <si>
+    <t>4,2,95</t>
+  </si>
+  <si>
+    <t>150,150,1</t>
+  </si>
+  <si>
+    <t>50,6,2</t>
+  </si>
+  <si>
+    <t>粗铁斧</t>
+  </si>
+  <si>
+    <t>200,2000,1</t>
+  </si>
+  <si>
+    <t>75,9,3</t>
+  </si>
+  <si>
+    <t>粗铁枪</t>
+  </si>
+  <si>
+    <t>250,250,1</t>
+  </si>
+  <si>
+    <t>100,12,4</t>
+  </si>
+  <si>
+    <t>黑铁指环</t>
+  </si>
+  <si>
+    <t>2,1004,95</t>
+  </si>
+  <si>
+    <t>100,5,1</t>
+  </si>
+  <si>
+    <t>40000001,40000003</t>
+  </si>
+  <si>
+    <t>100,1</t>
+  </si>
+  <si>
+    <t>物攻加成</t>
+  </si>
+  <si>
+    <t>黑铁头盔</t>
+  </si>
+  <si>
+    <t>1,1004,95</t>
+  </si>
+  <si>
+    <t>2000,5,1</t>
+  </si>
+  <si>
+    <t>40000004,40000005</t>
+  </si>
+  <si>
+    <t>古铜戒指</t>
+  </si>
+  <si>
+    <t>1003,1004,95</t>
+  </si>
+  <si>
+    <t>5,10,1</t>
+  </si>
+  <si>
+    <t>40000007,40000008</t>
+  </si>
+  <si>
+    <t>10,2</t>
+  </si>
+  <si>
+    <t>古铜项链</t>
+  </si>
+  <si>
+    <t>1002,1004,95</t>
+  </si>
+  <si>
+    <t>10,10,1</t>
+  </si>
+  <si>
+    <t>40000005,40000007</t>
+  </si>
+  <si>
+    <t>凌风长剑</t>
+  </si>
+  <si>
+    <t>1001,1004,95</t>
+  </si>
+  <si>
+    <t>20,10,1</t>
+  </si>
+  <si>
+    <t>40000008,40000009</t>
+  </si>
+  <si>
+    <t>物伤加成</t>
+  </si>
+  <si>
+    <t>法系技能全等级+1</t>
+  </si>
+  <si>
+    <t>法系技能攻速+5%</t>
+  </si>
+  <si>
+    <t>法系技能冷却+5%</t>
+  </si>
+  <si>
+    <t>基础心法·传承</t>
+  </si>
+  <si>
+    <t>1007,21001,95</t>
+  </si>
+  <si>
+    <t>2,1,1</t>
+  </si>
+  <si>
+    <t>ItemLogo/sb1</t>
+  </si>
+  <si>
+    <t>基础心法等级+1</t>
+  </si>
+  <si>
+    <t>流光剑诀·传承</t>
+  </si>
+  <si>
+    <t>1007,21002,95</t>
   </si>
   <si>
     <t>3,1,1</t>
   </si>
   <si>
-    <t>150,18,6</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive5</t>
-  </si>
-  <si>
-    <t>金币加成</t>
-  </si>
-  <si>
-    <t>试炼卷轴</t>
-  </si>
-  <si>
-    <t>82,27,95</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive6</t>
-  </si>
-  <si>
-    <t>经验加成</t>
-  </si>
-  <si>
-    <t>寻金符</t>
-  </si>
-  <si>
-    <t>83,27,95</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive7</t>
-  </si>
-  <si>
-    <t>爆率加成</t>
-  </si>
-  <si>
-    <t>四叶草</t>
-  </si>
-  <si>
-    <t>84,27,95</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive8</t>
-  </si>
-  <si>
-    <t>品质加成</t>
-  </si>
-  <si>
-    <t>宠物袋</t>
-  </si>
-  <si>
-    <t>2003,111,95</t>
-  </si>
-  <si>
-    <t>2,1,2</t>
-  </si>
-  <si>
-    <t>40000003,40000006,40000009</t>
-  </si>
-  <si>
-    <t>15,15,15</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive101</t>
-  </si>
-  <si>
-    <t>增加一个宠物备战位</t>
-  </si>
-  <si>
-    <t>技能手册</t>
-  </si>
-  <si>
-    <t>2003,113,95</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive102</t>
-  </si>
-  <si>
-    <t>增加一个技能出战栏位</t>
-  </si>
-  <si>
-    <t>增加一个技能出站栏位</t>
-  </si>
-  <si>
-    <t>神灵印记</t>
-  </si>
-  <si>
-    <t>2003,114,95</t>
-  </si>
-  <si>
-    <t>3,1,3</t>
-  </si>
-  <si>
-    <t>40000012,40000015,40000018</t>
-  </si>
-  <si>
-    <t>30,30,30</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive103</t>
-  </si>
-  <si>
-    <t>技能词条套装所需数量-1</t>
-  </si>
-  <si>
-    <t>装备词条套装所需数量-1</t>
-  </si>
-  <si>
-    <t>勇气号角</t>
-  </si>
-  <si>
-    <t>2003,95</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive104</t>
-  </si>
-  <si>
-    <t>低概率刷新低于当前地图的区域boss</t>
-  </si>
-  <si>
-    <t>传世勋章</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive105</t>
-  </si>
-  <si>
-    <t>解锁传世高级挑战</t>
-  </si>
-  <si>
-    <t>传世印记</t>
-  </si>
-  <si>
-    <t>Exclusive/Exclusive106</t>
-  </si>
-  <si>
-    <t>解锁传世超级挑战</t>
-  </si>
-  <si>
-    <t>粗铁刀</t>
-  </si>
-  <si>
-    <t>4,3,95</t>
-  </si>
-  <si>
-    <t>100,100,1</t>
-  </si>
-  <si>
-    <t>25,3,1</t>
-  </si>
-  <si>
-    <t>Bag/Equip/Box_Equip_1_1</t>
-  </si>
-  <si>
-    <t>物攻基础</t>
-  </si>
-  <si>
-    <t>粗铁剑</t>
-  </si>
-  <si>
-    <t>150,150,1</t>
-  </si>
-  <si>
-    <t>50,6,2</t>
-  </si>
-  <si>
-    <t>粗铁斧</t>
-  </si>
-  <si>
-    <t>200,200,1</t>
-  </si>
-  <si>
-    <t>75,9,3</t>
-  </si>
-  <si>
-    <t>粗铁枪</t>
-  </si>
-  <si>
-    <t>250,250,1</t>
-  </si>
-  <si>
-    <t>100,12,4</t>
-  </si>
-  <si>
-    <t>黑铁指环</t>
-  </si>
-  <si>
-    <t>2,1004,95</t>
-  </si>
-  <si>
-    <t>100,5,1</t>
-  </si>
-  <si>
-    <t>40000001,40000003</t>
-  </si>
-  <si>
-    <t>100,1</t>
-  </si>
-  <si>
-    <t>物攻加成</t>
-  </si>
-  <si>
-    <t>黑铁头盔</t>
-  </si>
-  <si>
-    <t>1,1004,95</t>
-  </si>
-  <si>
-    <t>2000,5,1</t>
-  </si>
-  <si>
-    <t>40000004,40000005</t>
-  </si>
-  <si>
-    <t>古铜戒指</t>
-  </si>
-  <si>
-    <t>1003,1004,95</t>
-  </si>
-  <si>
-    <t>5,10,1</t>
-  </si>
-  <si>
-    <t>40000007,40000008</t>
-  </si>
-  <si>
-    <t>10,2</t>
-  </si>
-  <si>
-    <t>古铜项链</t>
-  </si>
-  <si>
-    <t>1002,1004,95</t>
-  </si>
-  <si>
-    <t>10,10,1</t>
-  </si>
-  <si>
-    <t>40000005,40000007</t>
-  </si>
-  <si>
-    <t>凌风长剑</t>
-  </si>
-  <si>
-    <t>1001,1004,95</t>
-  </si>
-  <si>
-    <t>20,10,1</t>
-  </si>
-  <si>
-    <t>40000008,40000009</t>
-  </si>
-  <si>
-    <t>物伤加成</t>
-  </si>
-  <si>
-    <t>法系技能全等级+1</t>
-  </si>
-  <si>
-    <t>法系技能攻速+5%</t>
-  </si>
-  <si>
-    <t>法系技能冷却+5%</t>
-  </si>
-  <si>
-    <t>基础心法·传承</t>
-  </si>
-  <si>
-    <t>1007,21001,95</t>
-  </si>
-  <si>
-    <t>2,1,1</t>
-  </si>
-  <si>
-    <t>ItemLogo/sb1</t>
-  </si>
-  <si>
-    <t>基础心法等级+1</t>
-  </si>
-  <si>
-    <t>流光剑诀·传承</t>
-  </si>
-  <si>
-    <t>1007,21002,95</t>
-  </si>
-  <si>
     <t>流光剑诀等级+1</t>
   </si>
   <si>
@@ -647,7 +680,7 @@
     <t>乌木杖</t>
   </si>
   <si>
-    <t>5,3,95</t>
+    <t>5,1,95</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_2_1</t>
@@ -656,6 +689,9 @@
     <t>乌木戒</t>
   </si>
   <si>
+    <t>5,2,95</t>
+  </si>
+  <si>
     <t>乌木坠</t>
   </si>
   <si>
@@ -863,13 +899,16 @@
     <t>青竹剑</t>
   </si>
   <si>
-    <t>6,3,95</t>
+    <t>6,1,95</t>
   </si>
   <si>
     <t>Bag/Equip/Box_Equip_3_1</t>
   </si>
   <si>
     <t>青竹罗盘</t>
+  </si>
+  <si>
+    <t>6,2,95</t>
   </si>
   <si>
     <t>桃木剑</t>
@@ -2055,7 +2094,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2268,10 +2307,10 @@
         <v>26</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>21</v>
@@ -2280,13 +2319,13 @@
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -2294,7 +2333,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -2306,22 +2345,22 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -2335,7 +2374,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -2347,28 +2386,28 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -2376,7 +2415,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" s="1">
         <v>0</v>
@@ -2388,28 +2427,28 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>20</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L10" s="1">
         <v>3</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N10" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -2417,7 +2456,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="1">
         <v>0</v>
@@ -2429,28 +2468,28 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L11" s="1">
         <v>3</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -2458,7 +2497,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1">
         <v>0</v>
@@ -2470,28 +2509,28 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L12" s="1">
         <v>3</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -2499,7 +2538,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E13" s="1">
         <v>0</v>
@@ -2511,28 +2550,28 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L13" s="1">
         <v>3</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" customFormat="1" customHeight="1" spans="1:15">
@@ -2578,7 +2617,7 @@
         <v>101</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E24" s="1">
         <v>0</v>
@@ -2590,28 +2629,28 @@
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2619,7 +2658,7 @@
         <v>102</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E25" s="1">
         <v>0</v>
@@ -2631,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="J25" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I25" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>61</v>
-      </c>
       <c r="K25" s="10" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2660,7 +2699,7 @@
         <v>103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E26" s="1">
         <v>0</v>
@@ -2672,28 +2711,25 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="L26" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2701,7 +2737,7 @@
         <v>104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E27" s="1">
         <v>0</v>
@@ -2713,28 +2749,25 @@
         <v>0</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="L27" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2742,7 +2775,7 @@
         <v>105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E28" s="1">
         <v>0</v>
@@ -2754,25 +2787,28 @@
         <v>0</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="L28" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
@@ -2780,7 +2816,7 @@
         <v>106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="E29" s="1">
         <v>0</v>
@@ -2792,43 +2828,44 @@
         <v>0</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="L29" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1"/>
     <row r="31" s="1" customFormat="1" customHeight="1"/>
-    <row r="32" s="1" customFormat="1" customHeight="1"/>
-    <row r="33" s="1" customFormat="1" customHeight="1"/>
-    <row r="35" customHeight="1" spans="4:15">
-      <c r="O35" s="1"/>
-    </row>
-    <row r="36" customHeight="1" spans="4:15">
-      <c r="O36" s="1"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="4:15">
-      <c r="D39"/>
+    <row r="33" customHeight="1" spans="4:15">
+      <c r="O33" s="1"/>
+    </row>
+    <row r="34" customHeight="1" spans="4:15">
+      <c r="O34" s="1"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="4:15">
+      <c r="D37"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3 M4 M5 L3:L5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5 L3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -2997,7 +3034,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -3009,28 +3046,28 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>20</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3038,7 +3075,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3050,28 +3087,28 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3079,7 +3116,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -3091,28 +3128,28 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3120,7 +3157,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -3132,28 +3169,28 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3167,7 +3204,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3179,16 +3216,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -3197,7 +3234,7 @@
         <v>23</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3211,7 +3248,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3223,16 +3260,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -3241,7 +3278,7 @@
         <v>23</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3255,7 +3292,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3267,16 +3304,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -3285,7 +3322,7 @@
         <v>23</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3299,7 +3336,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3311,16 +3348,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -3329,7 +3366,7 @@
         <v>23</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3343,7 +3380,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3355,16 +3392,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -3373,7 +3410,7 @@
         <v>23</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
@@ -3385,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3397,7 +3434,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="N17" s="1" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3408,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
@@ -3417,7 +3454,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3429,25 +3466,25 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>20</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3455,7 +3492,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3467,25 +3504,25 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3493,7 +3530,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3505,25 +3542,25 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3531,7 +3568,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3543,25 +3580,25 @@
         <v>0</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="J23" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3569,7 +3606,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3581,25 +3618,25 @@
         <v>0</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3607,7 +3644,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3619,25 +3656,25 @@
         <v>0</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3651,7 +3688,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3663,25 +3700,25 @@
         <v>0</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
@@ -3697,7 +3734,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3709,22 +3746,22 @@
         <v>10011</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3738,7 +3775,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3750,22 +3787,22 @@
         <v>10021</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3779,7 +3816,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3791,22 +3828,22 @@
         <v>10031</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J31" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3820,7 +3857,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3832,22 +3869,22 @@
         <v>10041</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3861,7 +3898,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3873,22 +3910,22 @@
         <v>10051</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3902,7 +3939,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -3914,22 +3951,22 @@
         <v>10061</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3943,7 +3980,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -3955,22 +3992,22 @@
         <v>10071</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="S35" s="6"/>
     </row>
@@ -3996,7 +4033,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4008,22 +4045,22 @@
         <v>10012</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="S37" s="6"/>
     </row>
@@ -4038,7 +4075,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4050,22 +4087,22 @@
         <v>10022</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="S38" s="6"/>
     </row>
@@ -4080,7 +4117,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4092,22 +4129,22 @@
         <v>10032</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="1"/>
@@ -4124,7 +4161,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4136,22 +4173,22 @@
         <v>10042</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="1"/>
@@ -4168,7 +4205,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4180,22 +4217,22 @@
         <v>10052</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J41" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="P41" s="6"/>
       <c r="S41" s="6"/>
@@ -4211,7 +4248,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4223,22 +4260,22 @@
         <v>10072</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="1"/>
@@ -4267,7 +4304,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4279,22 +4316,22 @@
         <v>10023</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="1"/>
@@ -4311,7 +4348,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4323,22 +4360,22 @@
         <v>10073</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="1"/>
@@ -4367,7 +4404,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4379,22 +4416,22 @@
         <v>10024</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -4412,7 +4449,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4424,23 +4461,23 @@
         <v>10034</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J48" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="6" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="6"/>
@@ -4711,7 +4748,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3 M4 M5 L3:L5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5 L3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -4882,7 +4919,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4894,22 +4931,22 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>20</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
@@ -4933,7 +4970,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -4945,22 +4982,22 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -4984,7 +5021,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -4996,22 +5033,22 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -5035,7 +5072,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -5047,22 +5084,22 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
@@ -5090,7 +5127,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -5102,16 +5139,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -5143,7 +5180,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -5155,16 +5192,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -5196,7 +5233,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5208,16 +5245,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -5249,7 +5286,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5261,16 +5298,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -5302,7 +5339,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5314,16 +5351,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -5375,7 +5412,7 @@
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5387,25 +5424,25 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>20</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5413,7 +5450,7 @@
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5425,25 +5462,25 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5451,7 +5488,7 @@
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5463,25 +5500,25 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5489,7 +5526,7 @@
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5501,25 +5538,25 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5527,7 +5564,7 @@
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5539,25 +5576,25 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5565,7 +5602,7 @@
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5577,25 +5614,25 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5609,7 +5646,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5621,25 +5658,25 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5657,7 +5694,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5669,23 +5706,23 @@
         <v>20011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="6" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="O24" s="2"/>
       <c r="XET24" s="1"/>
@@ -5711,7 +5748,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5723,23 +5760,23 @@
         <v>20021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="6" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="O25" s="1"/>
       <c r="XET25" s="1"/>
@@ -5765,7 +5802,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5777,23 +5814,23 @@
         <v>20031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="6" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="O26" s="1"/>
       <c r="XET26" s="1"/>
@@ -5819,7 +5856,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5831,23 +5868,23 @@
         <v>20041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="6" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="O27" s="1"/>
       <c r="XET27" s="1"/>
@@ -5873,7 +5910,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -5885,23 +5922,23 @@
         <v>20051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="6" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="O28" s="1"/>
       <c r="XET28" s="1"/>
@@ -5927,7 +5964,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -5939,23 +5976,23 @@
         <v>20061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="6" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="O29" s="1"/>
       <c r="XET29" s="1"/>
@@ -5981,7 +6018,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -5993,23 +6030,23 @@
         <v>20071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="6" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="O30" s="1"/>
       <c r="XET30" s="1"/>
@@ -6067,7 +6104,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -6079,23 +6116,23 @@
         <v>20012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="6" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="O32" s="1"/>
       <c r="XET32" s="1"/>
@@ -6121,7 +6158,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -6133,23 +6170,23 @@
         <v>20022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="6" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="O33" s="1"/>
       <c r="XET33" s="1"/>
@@ -6175,7 +6212,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -6187,23 +6224,23 @@
         <v>20032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="6" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="O34" s="1"/>
       <c r="XET34" s="1"/>
@@ -6229,7 +6266,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6241,23 +6278,23 @@
         <v>20052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="6" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="O35" s="1"/>
       <c r="XET35" s="1"/>
@@ -6283,7 +6320,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6295,23 +6332,23 @@
         <v>20072</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J36" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="6" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="O36" s="1"/>
       <c r="XET36" s="1"/>
@@ -6369,7 +6406,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6381,23 +6418,23 @@
         <v>20023</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="6" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="O38" s="1"/>
       <c r="XET38" s="1"/>
@@ -6423,7 +6460,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6435,23 +6472,23 @@
         <v>20043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="6" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="O39" s="1"/>
       <c r="XET39" s="1"/>
@@ -6477,7 +6514,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6489,22 +6526,22 @@
         <v>20073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -6538,7 +6575,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6550,22 +6587,22 @@
         <v>20024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -6584,7 +6621,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6596,22 +6633,22 @@
         <v>20034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -6818,7 +6855,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3 M4 M5 L3:L5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5 L3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
@@ -6987,7 +7024,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -6999,22 +7036,22 @@
         <v>0</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>20</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
@@ -7025,7 +7062,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -7037,22 +7074,22 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -7063,7 +7100,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -7075,22 +7112,22 @@
         <v>0</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -7102,7 +7139,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -7114,22 +7151,22 @@
         <v>0</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
@@ -7147,7 +7184,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -7159,16 +7196,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -7189,7 +7226,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -7201,16 +7238,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -7231,7 +7268,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7243,16 +7280,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -7273,7 +7310,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7285,16 +7322,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -7315,7 +7352,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7327,16 +7364,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -7354,7 +7391,7 @@
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7366,25 +7403,25 @@
         <v>0</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>20</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7392,7 +7429,7 @@
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7404,25 +7441,25 @@
         <v>0</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>42</v>
+        <v>148</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7430,7 +7467,7 @@
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7442,25 +7479,25 @@
         <v>0</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J18" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7468,7 +7505,7 @@
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7480,25 +7517,25 @@
         <v>0</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="J19" s="10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7506,7 +7543,7 @@
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7518,25 +7555,25 @@
         <v>0</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J20" s="10" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7544,7 +7581,7 @@
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7556,25 +7593,25 @@
         <v>0</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="J21" s="10" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7588,7 +7625,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7600,25 +7637,25 @@
         <v>0</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="J22" s="10" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7635,7 +7672,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7647,22 +7684,22 @@
         <v>30011</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J24" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="O24" s="2"/>
     </row>
@@ -7677,7 +7714,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7689,22 +7726,22 @@
         <v>30021</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J25" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="O25" s="2"/>
     </row>
@@ -7719,7 +7756,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7731,22 +7768,22 @@
         <v>30031</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J26" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="O26" s="2"/>
     </row>
@@ -7761,7 +7798,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7773,22 +7810,22 @@
         <v>30041</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J27" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="O27" s="2"/>
     </row>
@@ -7803,7 +7840,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7815,22 +7852,22 @@
         <v>30051</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J28" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="O28" s="2"/>
     </row>
@@ -7845,7 +7882,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7857,22 +7894,22 @@
         <v>30061</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J29" s="10" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="O29" s="2"/>
     </row>
@@ -7887,7 +7924,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7899,22 +7936,22 @@
         <v>30071</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J30" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="O30" s="2"/>
     </row>
@@ -7938,7 +7975,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -7950,22 +7987,22 @@
         <v>30012</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J32" s="10" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="O32" s="2"/>
     </row>
@@ -7980,7 +8017,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -7992,22 +8029,22 @@
         <v>30022</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J33" s="10" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="O33" s="2"/>
     </row>
@@ -8022,7 +8059,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -8034,22 +8071,22 @@
         <v>30032</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J34" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="O34" s="2"/>
     </row>
@@ -8064,7 +8101,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -8076,22 +8113,22 @@
         <v>30052</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J35" s="10" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="O35" s="2"/>
     </row>
@@ -8115,7 +8152,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -8127,22 +8164,22 @@
         <v>30023</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J37" s="10" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="O37" s="2"/>
     </row>
@@ -8157,7 +8194,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -8169,22 +8206,22 @@
         <v>30033</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J38" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="O38" s="2"/>
     </row>
@@ -8199,7 +8236,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -8211,22 +8248,22 @@
         <v>30043</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J39" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="O39" s="2"/>
     </row>
@@ -8241,7 +8278,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8253,22 +8290,22 @@
         <v>30073</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J40" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="O40" s="2"/>
     </row>
@@ -8294,7 +8331,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8306,22 +8343,22 @@
         <v>30024</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="J42" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="O42" s="2"/>
     </row>
@@ -8336,7 +8373,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8348,22 +8385,22 @@
         <v>30034</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J43" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -8595,7 +8632,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3 M4 M5 L3:L5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5 L3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -30,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="363">
   <si>
     <t>#</t>
   </si>
@@ -324,6 +329,12 @@
   </si>
   <si>
     <t>低概率刷新低于当前地图的区域boss</t>
+  </si>
+  <si>
+    <t>龙胆枪</t>
+  </si>
+  <si>
+    <t>诸葛连弩</t>
   </si>
   <si>
     <t>粗铁刀</t>
@@ -1125,7 +1136,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1149,6 +1160,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF333333"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF05073B"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -1621,16 +1638,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1639,119 +1653,122 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1774,6 +1791,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2262,16 +2280,16 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="10" t="s">
+      <c r="I6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" s="11" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="1">
@@ -2303,16 +2321,16 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" s="11" t="s">
         <v>21</v>
       </c>
       <c r="L7" s="1">
@@ -2344,16 +2362,16 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="11" t="s">
         <v>35</v>
       </c>
       <c r="L8" s="1">
@@ -2385,16 +2403,16 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="11" t="s">
         <v>35</v>
       </c>
       <c r="L9" s="1">
@@ -2426,16 +2444,16 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="I10" s="10" t="s">
+      <c r="I10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" s="11" t="s">
         <v>45</v>
       </c>
       <c r="L10" s="1">
@@ -2467,16 +2485,16 @@
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="11" t="s">
         <v>45</v>
       </c>
       <c r="L11" s="1">
@@ -2508,16 +2526,16 @@
       <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="I12" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" s="11" t="s">
         <v>45</v>
       </c>
       <c r="L12" s="1">
@@ -2549,16 +2567,16 @@
       <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="I13" s="10" t="s">
+      <c r="I13" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="J13" s="10" t="s">
+      <c r="J13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="11" t="s">
         <v>45</v>
       </c>
       <c r="L13" s="1">
@@ -2591,28 +2609,28 @@
       <c r="N16" s="1"/>
       <c r="O16" s="2"/>
     </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="D17" s="5"/>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="D18" s="7"/>
     </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="D19" s="5"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="D20" s="9"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="D21" s="5"/>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="D22" s="7"/>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="D23" s="7"/>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C24" s="1">
         <v>101</v>
       </c>
@@ -2628,16 +2646,16 @@
       <c r="G24" s="1">
         <v>0</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="K24" s="11" t="s">
         <v>67</v>
       </c>
       <c r="L24" s="1">
@@ -2653,7 +2671,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C25" s="1">
         <v>102</v>
       </c>
@@ -2669,16 +2687,16 @@
       <c r="G25" s="1">
         <v>0</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="K25" s="10" t="s">
+      <c r="K25" s="11" t="s">
         <v>67</v>
       </c>
       <c r="L25" s="1">
@@ -2694,7 +2712,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C26" s="1">
         <v>103</v>
       </c>
@@ -2710,16 +2728,16 @@
       <c r="G26" s="1">
         <v>0</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="J26" s="10" t="s">
+      <c r="J26" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="K26" s="10" t="s">
+      <c r="K26" s="11" t="s">
         <v>67</v>
       </c>
       <c r="L26" s="1">
@@ -2732,7 +2750,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C27" s="1">
         <v>104</v>
       </c>
@@ -2748,16 +2766,16 @@
       <c r="G27" s="1">
         <v>0</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="K27" s="11" t="s">
         <v>85</v>
       </c>
       <c r="L27" s="1">
@@ -2770,7 +2788,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C28" s="1">
         <v>105</v>
       </c>
@@ -2786,16 +2804,16 @@
       <c r="G28" s="1">
         <v>0</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="J28" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="K28" s="10" t="s">
+      <c r="K28" s="11" t="s">
         <v>85</v>
       </c>
       <c r="L28" s="1">
@@ -2811,7 +2829,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="1:15">
       <c r="C29" s="1">
         <v>106</v>
       </c>
@@ -2827,16 +2845,16 @@
       <c r="G29" s="1">
         <v>0</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="K29" s="11" t="s">
         <v>85</v>
       </c>
       <c r="L29" s="1">
@@ -2852,8 +2870,28 @@
         <v>97</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1"/>
-    <row r="31" s="1" customFormat="1" customHeight="1"/>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>99</v>
+      </c>
+    </row>
     <row r="33" customHeight="1" spans="4:15">
       <c r="O33" s="1"/>
     </row>
@@ -3034,7 +3072,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -3045,29 +3083,29 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="J6" s="10" t="s">
+      <c r="H6" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="10" t="s">
-        <v>101</v>
+      <c r="K6" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3075,7 +3113,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3086,29 +3124,29 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="J7" s="10" t="s">
+      <c r="H7" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="10" t="s">
-        <v>107</v>
+      <c r="K7" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3116,7 +3154,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -3127,29 +3165,29 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J8" s="10" t="s">
+      <c r="H8" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="10" t="s">
-        <v>110</v>
+      <c r="K8" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3157,7 +3195,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -3168,29 +3206,29 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="10" t="s">
+      <c r="H9" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="10" t="s">
-        <v>113</v>
+      <c r="K9" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3204,7 +3242,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3215,17 +3253,17 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="J10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="I10" s="11" t="s">
         <v>118</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -3234,7 +3272,7 @@
         <v>23</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3248,7 +3286,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3259,17 +3297,17 @@
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="J11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="K11" s="10" t="s">
-        <v>118</v>
+      <c r="I11" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -3278,7 +3316,7 @@
         <v>23</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3292,7 +3330,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3303,17 +3341,17 @@
       <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="J12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="I12" s="11" t="s">
         <v>128</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -3322,7 +3360,7 @@
         <v>23</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3336,7 +3374,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3347,17 +3385,17 @@
       <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="K13" s="11" t="s">
         <v>130</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -3366,7 +3404,7 @@
         <v>23</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3380,7 +3418,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3391,17 +3429,17 @@
       <c r="G14" s="1">
         <v>0</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="J14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="K14" s="10" t="s">
-        <v>128</v>
+      <c r="I14" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -3410,7 +3448,7 @@
         <v>23</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
@@ -3422,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3434,7 +3472,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="N17" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3445,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
@@ -3454,7 +3492,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3465,26 +3503,26 @@
       <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="H20" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="J20" s="10" t="s">
+      <c r="H20" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="J20" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K20" s="10" t="s">
-        <v>113</v>
+      <c r="K20" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3492,7 +3530,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3503,26 +3541,26 @@
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="J21" s="10" t="s">
+      <c r="H21" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K21" s="10" t="s">
-        <v>113</v>
+      <c r="K21" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3530,7 +3568,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3541,26 +3579,26 @@
       <c r="G22" s="1">
         <v>0</v>
       </c>
-      <c r="H22" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="J22" s="10" t="s">
+      <c r="H22" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J22" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K22" s="10" t="s">
-        <v>113</v>
+      <c r="K22" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3568,7 +3606,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3579,26 +3617,26 @@
       <c r="G23" s="1">
         <v>0</v>
       </c>
-      <c r="H23" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="J23" s="10" t="s">
+      <c r="H23" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="J23" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K23" s="10" t="s">
-        <v>113</v>
+      <c r="K23" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3606,7 +3644,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3617,26 +3655,26 @@
       <c r="G24" s="1">
         <v>0</v>
       </c>
-      <c r="H24" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="J24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="K24" s="10" t="s">
-        <v>113</v>
+      <c r="I24" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3644,7 +3682,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3655,26 +3693,26 @@
       <c r="G25" s="1">
         <v>0</v>
       </c>
-      <c r="H25" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J25" s="10" t="s">
+      <c r="H25" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="K25" s="10" t="s">
-        <v>113</v>
+      <c r="I25" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3688,7 +3726,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3699,26 +3737,26 @@
       <c r="G26" s="1">
         <v>0</v>
       </c>
-      <c r="H26" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>113</v>
+      <c r="H26" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
@@ -3734,7 +3772,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3745,23 +3783,23 @@
       <c r="G29" s="1">
         <v>10011</v>
       </c>
-      <c r="H29" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J29" s="10" t="s">
+      <c r="H29" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="I29" s="11" t="s">
         <v>176</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3775,7 +3813,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3786,23 +3824,23 @@
       <c r="G30" s="1">
         <v>10021</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K30" s="10" t="s">
+      <c r="H30" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>176</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3816,7 +3854,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3827,23 +3865,23 @@
       <c r="G31" s="1">
         <v>10031</v>
       </c>
-      <c r="H31" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K31" s="10" t="s">
-        <v>176</v>
+      <c r="H31" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3857,7 +3895,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3868,23 +3906,23 @@
       <c r="G32" s="1">
         <v>10041</v>
       </c>
-      <c r="H32" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>186</v>
+      <c r="H32" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3898,7 +3936,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3909,23 +3947,23 @@
       <c r="G33" s="1">
         <v>10051</v>
       </c>
-      <c r="H33" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>186</v>
+      <c r="H33" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3939,7 +3977,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -3950,23 +3988,23 @@
       <c r="G34" s="1">
         <v>10061</v>
       </c>
-      <c r="H34" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K34" s="10" t="s">
-        <v>186</v>
+      <c r="H34" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3980,7 +4018,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -3991,23 +4029,23 @@
       <c r="G35" s="1">
         <v>10071</v>
       </c>
-      <c r="H35" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>193</v>
+      <c r="H35" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="S35" s="6"/>
     </row>
@@ -4033,7 +4071,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4044,23 +4082,23 @@
       <c r="G37" s="1">
         <v>10012</v>
       </c>
-      <c r="H37" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K37" s="10" t="s">
-        <v>193</v>
+      <c r="H37" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="K37" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="S37" s="6"/>
     </row>
@@ -4075,7 +4113,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4086,23 +4124,23 @@
       <c r="G38" s="1">
         <v>10022</v>
       </c>
-      <c r="H38" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="K38" s="10" t="s">
-        <v>193</v>
+      <c r="H38" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K38" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="S38" s="6"/>
     </row>
@@ -4117,7 +4155,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4128,23 +4166,23 @@
       <c r="G39" s="1">
         <v>10032</v>
       </c>
-      <c r="H39" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J39" s="10" t="s">
+      <c r="H39" s="11" t="s">
         <v>175</v>
       </c>
+      <c r="I39" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>177</v>
+      </c>
       <c r="K39" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="1"/>
@@ -4161,7 +4199,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4172,23 +4210,23 @@
       <c r="G40" s="1">
         <v>10042</v>
       </c>
-      <c r="H40" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J40" s="10" t="s">
-        <v>175</v>
+      <c r="H40" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="1"/>
@@ -4205,7 +4243,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4216,23 +4254,23 @@
       <c r="G41" s="1">
         <v>10052</v>
       </c>
-      <c r="H41" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I41" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J41" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K41" s="10" t="s">
-        <v>186</v>
+      <c r="H41" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P41" s="6"/>
       <c r="S41" s="6"/>
@@ -4248,7 +4286,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4259,23 +4297,23 @@
       <c r="G42" s="1">
         <v>10072</v>
       </c>
-      <c r="H42" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J42" s="10" t="s">
-        <v>175</v>
+      <c r="H42" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="1"/>
@@ -4304,7 +4342,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4315,23 +4353,23 @@
       <c r="G44" s="1">
         <v>10023</v>
       </c>
-      <c r="H44" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J44" s="10" t="s">
+      <c r="H44" s="11" t="s">
         <v>175</v>
       </c>
+      <c r="I44" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>177</v>
+      </c>
       <c r="K44" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="1"/>
@@ -4348,7 +4386,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4359,23 +4397,23 @@
       <c r="G45" s="1">
         <v>10073</v>
       </c>
-      <c r="H45" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I45" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J45" s="10" t="s">
-        <v>175</v>
+      <c r="H45" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="1"/>
@@ -4404,7 +4442,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4415,23 +4453,23 @@
       <c r="G47" s="1">
         <v>10024</v>
       </c>
-      <c r="H47" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J47" s="10" t="s">
-        <v>175</v>
+      <c r="H47" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J47" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -4449,7 +4487,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4460,24 +4498,24 @@
       <c r="G48" s="1">
         <v>10034</v>
       </c>
-      <c r="H48" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>175</v>
+      <c r="H48" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J48" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="6"/>
@@ -4919,7 +4957,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4930,23 +4968,23 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="J6" s="10" t="s">
+      <c r="H6" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="10" t="s">
-        <v>101</v>
+      <c r="K6" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
@@ -4970,7 +5008,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -4981,23 +5019,23 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="J7" s="10" t="s">
+      <c r="H7" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="10" t="s">
-        <v>107</v>
+      <c r="K7" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -5021,7 +5059,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -5032,23 +5070,23 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>216</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J8" s="10" t="s">
+      <c r="H8" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="10" t="s">
-        <v>110</v>
+      <c r="K8" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -5072,7 +5110,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -5083,23 +5121,23 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="10" t="s">
+      <c r="H9" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="10" t="s">
-        <v>113</v>
+      <c r="K9" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
@@ -5127,7 +5165,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -5138,17 +5176,17 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K10" s="10" t="s">
+      <c r="H10" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>118</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -5180,7 +5218,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -5191,17 +5229,17 @@
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>225</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>118</v>
+      <c r="H11" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -5233,7 +5271,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5244,17 +5282,17 @@
       <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K12" s="10" t="s">
+      <c r="H12" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="I12" s="11" t="s">
         <v>128</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -5286,7 +5324,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5297,17 +5335,17 @@
       <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>229</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>128</v>
+      <c r="H13" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -5339,7 +5377,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5350,17 +5388,17 @@
       <c r="G14" s="1">
         <v>0</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>231</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>128</v>
+      <c r="H14" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -5412,7 +5450,7 @@
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5423,26 +5461,26 @@
       <c r="G16" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>233</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="J16" s="10" t="s">
+      <c r="H16" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="10" t="s">
-        <v>113</v>
+      <c r="K16" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5450,7 +5488,7 @@
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5461,26 +5499,26 @@
       <c r="G17" s="1">
         <v>0</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>237</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="J17" s="10" t="s">
+      <c r="H17" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="10" t="s">
-        <v>113</v>
+      <c r="K17" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5488,7 +5526,7 @@
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5499,26 +5537,26 @@
       <c r="G18" s="1">
         <v>0</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="J18" s="10" t="s">
+      <c r="H18" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K18" s="10" t="s">
-        <v>113</v>
+      <c r="K18" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5526,7 +5564,7 @@
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5537,26 +5575,26 @@
       <c r="G19" s="1">
         <v>0</v>
       </c>
-      <c r="H19" s="10" t="s">
-        <v>243</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="J19" s="10" t="s">
+      <c r="H19" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="J19" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K19" s="10" t="s">
-        <v>113</v>
+      <c r="K19" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5564,7 +5602,7 @@
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5575,26 +5613,26 @@
       <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="H20" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>113</v>
+      <c r="H20" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5602,7 +5640,7 @@
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5613,26 +5651,26 @@
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>113</v>
+      <c r="H21" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5646,7 +5684,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5657,26 +5695,26 @@
       <c r="G22" s="1">
         <v>0</v>
       </c>
-      <c r="H22" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>113</v>
+      <c r="H22" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5694,7 +5732,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5705,24 +5743,24 @@
       <c r="G24" s="1">
         <v>20011</v>
       </c>
-      <c r="H24" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="I24" s="11" t="s">
         <v>176</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O24" s="2"/>
       <c r="XET24" s="1"/>
@@ -5748,7 +5786,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5759,24 +5797,24 @@
       <c r="G25" s="1">
         <v>20021</v>
       </c>
-      <c r="H25" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K25" s="10" t="s">
+      <c r="H25" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I25" s="11" t="s">
         <v>176</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O25" s="1"/>
       <c r="XET25" s="1"/>
@@ -5802,7 +5840,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5813,24 +5851,24 @@
       <c r="G26" s="1">
         <v>20031</v>
       </c>
-      <c r="H26" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>176</v>
+      <c r="H26" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O26" s="1"/>
       <c r="XET26" s="1"/>
@@ -5856,7 +5894,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5867,24 +5905,24 @@
       <c r="G27" s="1">
         <v>20041</v>
       </c>
-      <c r="H27" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>186</v>
+      <c r="H27" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O27" s="1"/>
       <c r="XET27" s="1"/>
@@ -5910,7 +5948,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -5921,24 +5959,24 @@
       <c r="G28" s="1">
         <v>20051</v>
       </c>
-      <c r="H28" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>186</v>
+      <c r="H28" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O28" s="1"/>
       <c r="XET28" s="1"/>
@@ -5964,7 +6002,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -5975,24 +6013,24 @@
       <c r="G29" s="1">
         <v>20061</v>
       </c>
-      <c r="H29" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>186</v>
+      <c r="H29" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O29" s="1"/>
       <c r="XET29" s="1"/>
@@ -6018,7 +6056,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -6029,24 +6067,24 @@
       <c r="G30" s="1">
         <v>20071</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>193</v>
+      <c r="H30" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O30" s="1"/>
       <c r="XET30" s="1"/>
@@ -6104,7 +6142,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -6115,24 +6153,24 @@
       <c r="G32" s="1">
         <v>20012</v>
       </c>
-      <c r="H32" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>193</v>
+      <c r="H32" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O32" s="1"/>
       <c r="XET32" s="1"/>
@@ -6158,7 +6196,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -6169,24 +6207,24 @@
       <c r="G33" s="1">
         <v>20022</v>
       </c>
-      <c r="H33" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>193</v>
+      <c r="H33" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O33" s="1"/>
       <c r="XET33" s="1"/>
@@ -6212,7 +6250,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -6223,24 +6261,24 @@
       <c r="G34" s="1">
         <v>20032</v>
       </c>
-      <c r="H34" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J34" s="10" t="s">
+      <c r="H34" s="11" t="s">
         <v>175</v>
       </c>
+      <c r="I34" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>177</v>
+      </c>
       <c r="K34" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="O34" s="1"/>
       <c r="XET34" s="1"/>
@@ -6266,7 +6304,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6277,24 +6315,24 @@
       <c r="G35" s="1">
         <v>20052</v>
       </c>
-      <c r="H35" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K35" s="10" t="s">
-        <v>186</v>
+      <c r="H35" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K35" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O35" s="1"/>
       <c r="XET35" s="1"/>
@@ -6320,7 +6358,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6331,24 +6369,24 @@
       <c r="G36" s="1">
         <v>20072</v>
       </c>
-      <c r="H36" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>175</v>
+      <c r="H36" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O36" s="1"/>
       <c r="XET36" s="1"/>
@@ -6406,7 +6444,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6417,24 +6455,24 @@
       <c r="G38" s="1">
         <v>20023</v>
       </c>
-      <c r="H38" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>175</v>
+      <c r="H38" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="O38" s="1"/>
       <c r="XET38" s="1"/>
@@ -6460,7 +6498,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6471,24 +6509,24 @@
       <c r="G39" s="1">
         <v>20043</v>
       </c>
-      <c r="H39" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>175</v>
+      <c r="H39" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="O39" s="1"/>
       <c r="XET39" s="1"/>
@@ -6514,7 +6552,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6525,23 +6563,23 @@
       <c r="G40" s="1">
         <v>20073</v>
       </c>
-      <c r="H40" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J40" s="10" t="s">
-        <v>175</v>
+      <c r="H40" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -6575,7 +6613,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6586,23 +6624,23 @@
       <c r="G42" s="1">
         <v>20024</v>
       </c>
-      <c r="H42" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J42" s="10" t="s">
-        <v>175</v>
+      <c r="H42" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -6621,7 +6659,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6632,23 +6670,23 @@
       <c r="G43" s="1">
         <v>20034</v>
       </c>
-      <c r="H43" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>175</v>
+      <c r="H43" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -7024,7 +7062,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -7035,23 +7073,23 @@
       <c r="G6" s="1">
         <v>0</v>
       </c>
-      <c r="H6" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="J6" s="10" t="s">
+      <c r="H6" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="10" t="s">
-        <v>101</v>
+      <c r="K6" s="11" t="s">
+        <v>103</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
@@ -7062,7 +7100,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -7073,23 +7111,23 @@
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="J7" s="10" t="s">
+      <c r="H7" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="10" t="s">
-        <v>107</v>
+      <c r="K7" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -7100,7 +7138,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -7111,23 +7149,23 @@
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J8" s="10" t="s">
+      <c r="H8" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K8" s="10" t="s">
-        <v>110</v>
+      <c r="K8" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -7139,7 +7177,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -7150,23 +7188,23 @@
       <c r="G9" s="1">
         <v>0</v>
       </c>
-      <c r="H9" s="10" t="s">
-        <v>292</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="10" t="s">
+      <c r="H9" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="10" t="s">
-        <v>113</v>
+      <c r="K9" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
@@ -7184,7 +7222,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -7195,17 +7233,17 @@
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K10" s="10" t="s">
+      <c r="H10" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>118</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -7226,7 +7264,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -7237,17 +7275,17 @@
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>118</v>
+      <c r="H11" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>120</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -7268,7 +7306,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7279,17 +7317,17 @@
       <c r="G12" s="1">
         <v>0</v>
       </c>
-      <c r="H12" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K12" s="10" t="s">
+      <c r="H12" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="I12" s="11" t="s">
         <v>128</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -7310,7 +7348,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7321,17 +7359,17 @@
       <c r="G13" s="1">
         <v>0</v>
       </c>
-      <c r="H13" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="I13" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K13" s="10" t="s">
-        <v>128</v>
+      <c r="H13" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -7352,7 +7390,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7363,17 +7401,17 @@
       <c r="G14" s="1">
         <v>0</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="K14" s="10" t="s">
-        <v>128</v>
+      <c r="H14" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>130</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -7391,7 +7429,7 @@
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7402,26 +7440,26 @@
       <c r="G16" s="1">
         <v>0</v>
       </c>
-      <c r="H16" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="J16" s="10" t="s">
+      <c r="H16" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="J16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="10" t="s">
-        <v>113</v>
+      <c r="K16" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7429,7 +7467,7 @@
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7440,26 +7478,26 @@
       <c r="G17" s="1">
         <v>0</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="J17" s="10" t="s">
+      <c r="H17" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="J17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="10" t="s">
-        <v>113</v>
+      <c r="K17" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7467,7 +7505,7 @@
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7478,26 +7516,26 @@
       <c r="G18" s="1">
         <v>0</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="J18" s="10" t="s">
+      <c r="H18" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="J18" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K18" s="10" t="s">
-        <v>113</v>
+      <c r="K18" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7505,7 +7543,7 @@
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7516,26 +7554,26 @@
       <c r="G19" s="1">
         <v>0</v>
       </c>
-      <c r="H19" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="J19" s="10" t="s">
+      <c r="H19" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="J19" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="K19" s="10" t="s">
-        <v>113</v>
+      <c r="K19" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7543,7 +7581,7 @@
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7554,26 +7592,26 @@
       <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="H20" s="10" t="s">
-        <v>319</v>
-      </c>
-      <c r="I20" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="K20" s="10" t="s">
-        <v>113</v>
+      <c r="H20" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7581,7 +7619,7 @@
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7592,26 +7630,26 @@
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="K21" s="10" t="s">
-        <v>113</v>
+      <c r="H21" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7625,7 +7663,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7636,26 +7674,26 @@
       <c r="G22" s="1">
         <v>0</v>
       </c>
-      <c r="H22" s="10" t="s">
-        <v>325</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="K22" s="10" t="s">
-        <v>113</v>
+      <c r="H22" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7672,7 +7710,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7683,23 +7721,23 @@
       <c r="G24" s="1">
         <v>30011</v>
       </c>
-      <c r="H24" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="I24" s="11" t="s">
         <v>176</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O24" s="2"/>
     </row>
@@ -7714,7 +7752,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7725,23 +7763,23 @@
       <c r="G25" s="1">
         <v>30021</v>
       </c>
-      <c r="H25" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I25" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J25" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K25" s="10" t="s">
+      <c r="H25" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I25" s="11" t="s">
         <v>176</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O25" s="2"/>
     </row>
@@ -7756,7 +7794,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7767,23 +7805,23 @@
       <c r="G26" s="1">
         <v>30031</v>
       </c>
-      <c r="H26" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K26" s="10" t="s">
-        <v>176</v>
+      <c r="H26" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>178</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O26" s="2"/>
     </row>
@@ -7798,7 +7836,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7809,23 +7847,23 @@
       <c r="G27" s="1">
         <v>30041</v>
       </c>
-      <c r="H27" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K27" s="10" t="s">
-        <v>186</v>
+      <c r="H27" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="O27" s="2"/>
     </row>
@@ -7840,7 +7878,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7851,23 +7889,23 @@
       <c r="G28" s="1">
         <v>30051</v>
       </c>
-      <c r="H28" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="K28" s="10" t="s">
-        <v>186</v>
+      <c r="H28" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O28" s="2"/>
     </row>
@@ -7882,7 +7920,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7893,23 +7931,23 @@
       <c r="G29" s="1">
         <v>30061</v>
       </c>
-      <c r="H29" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J29" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="K29" s="10" t="s">
-        <v>186</v>
+      <c r="H29" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>188</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O29" s="2"/>
     </row>
@@ -7924,7 +7962,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7935,23 +7973,23 @@
       <c r="G30" s="1">
         <v>30071</v>
       </c>
-      <c r="H30" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="K30" s="10" t="s">
-        <v>193</v>
+      <c r="H30" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O30" s="2"/>
     </row>
@@ -7975,7 +8013,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -7986,23 +8024,23 @@
       <c r="G32" s="1">
         <v>30012</v>
       </c>
-      <c r="H32" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="K32" s="10" t="s">
-        <v>193</v>
+      <c r="H32" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J32" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="K32" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O32" s="2"/>
     </row>
@@ -8017,7 +8055,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -8028,23 +8066,23 @@
       <c r="G33" s="1">
         <v>30022</v>
       </c>
-      <c r="H33" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="K33" s="10" t="s">
-        <v>193</v>
+      <c r="H33" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J33" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="K33" s="11" t="s">
+        <v>195</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O33" s="2"/>
     </row>
@@ -8059,7 +8097,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -8070,23 +8108,23 @@
       <c r="G34" s="1">
         <v>30032</v>
       </c>
-      <c r="H34" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J34" s="10" t="s">
+      <c r="H34" s="11" t="s">
         <v>175</v>
       </c>
+      <c r="I34" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>177</v>
+      </c>
       <c r="K34" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O34" s="2"/>
     </row>
@@ -8101,7 +8139,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -8112,23 +8150,23 @@
       <c r="G35" s="1">
         <v>30052</v>
       </c>
-      <c r="H35" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J35" s="10" t="s">
-        <v>117</v>
+      <c r="H35" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J35" s="11" t="s">
+        <v>119</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O35" s="2"/>
     </row>
@@ -8152,7 +8190,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -8163,23 +8201,23 @@
       <c r="G37" s="1">
         <v>30023</v>
       </c>
-      <c r="H37" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>136</v>
+      <c r="H37" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J37" s="11" t="s">
+        <v>138</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="O37" s="2"/>
     </row>
@@ -8194,7 +8232,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -8205,23 +8243,23 @@
       <c r="G38" s="1">
         <v>30033</v>
       </c>
-      <c r="H38" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I38" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>175</v>
+      <c r="H38" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J38" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="O38" s="2"/>
     </row>
@@ -8236,7 +8274,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -8247,23 +8285,23 @@
       <c r="G39" s="1">
         <v>30043</v>
       </c>
-      <c r="H39" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>175</v>
+      <c r="H39" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O39" s="2"/>
     </row>
@@ -8278,7 +8316,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8289,23 +8327,23 @@
       <c r="G40" s="1">
         <v>30073</v>
       </c>
-      <c r="H40" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="I40" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J40" s="10" t="s">
+      <c r="H40" s="11" t="s">
         <v>175</v>
       </c>
+      <c r="I40" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>177</v>
+      </c>
       <c r="K40" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O40" s="2"/>
     </row>
@@ -8331,7 +8369,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8342,23 +8380,23 @@
       <c r="G42" s="1">
         <v>30024</v>
       </c>
-      <c r="H42" s="10" t="s">
-        <v>179</v>
-      </c>
-      <c r="I42" s="10" t="s">
-        <v>174</v>
-      </c>
-      <c r="J42" s="10" t="s">
-        <v>175</v>
+      <c r="H42" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J42" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O42" s="2"/>
     </row>
@@ -8373,7 +8411,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8384,23 +8422,23 @@
       <c r="G43" s="1">
         <v>30034</v>
       </c>
-      <c r="H43" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>183</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>175</v>
+      <c r="H43" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>177</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="364">
   <si>
     <t>#</t>
   </si>
@@ -323,6 +323,9 @@
   </si>
   <si>
     <t>5,3</t>
+  </si>
+  <si>
+    <t>40000006,40000009,40000012</t>
   </si>
   <si>
     <t>Exclusive/Exclusive104</t>
@@ -2123,7 +2126,7 @@
     <col min="10" max="10" width="24.5833333333333" style="1" customWidth="1"/>
     <col min="11" max="11" width="15.9166666666667" style="1" customWidth="1"/>
     <col min="12" max="12" width="12.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.3333333333333" style="1" customWidth="1"/>
     <col min="14" max="14" width="29" style="1" customWidth="1"/>
     <col min="15" max="15" width="18.1666666666667" style="2" customWidth="1"/>
     <col min="16" max="16373" width="9" style="2"/>
@@ -2852,22 +2855,22 @@
         <v>95</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L29" s="1">
         <v>6</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -2878,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -2889,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" customHeight="1" spans="4:15">
@@ -3072,7 +3075,7 @@
         <v>1001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -3084,28 +3087,28 @@
         <v>0</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3113,7 +3116,7 @@
         <v>1002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -3125,28 +3128,28 @@
         <v>0</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3154,7 +3157,7 @@
         <v>1003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -3166,28 +3169,28 @@
         <v>0</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3195,7 +3198,7 @@
         <v>1004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -3207,28 +3210,28 @@
         <v>0</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>40</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3242,7 +3245,7 @@
         <v>1005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -3254,16 +3257,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -3272,7 +3275,7 @@
         <v>23</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3286,7 +3289,7 @@
         <v>1006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -3298,16 +3301,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -3316,7 +3319,7 @@
         <v>23</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3330,7 +3333,7 @@
         <v>1007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -3342,16 +3345,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -3360,7 +3363,7 @@
         <v>23</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3374,7 +3377,7 @@
         <v>1008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -3386,16 +3389,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -3404,7 +3407,7 @@
         <v>23</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -3418,7 +3421,7 @@
         <v>1009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -3430,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -3448,7 +3451,7 @@
         <v>23</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
@@ -3460,7 +3463,7 @@
         <v>0</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3472,7 +3475,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="N17" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3483,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
@@ -3492,7 +3495,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3504,25 +3507,25 @@
         <v>0</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>20</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3530,7 +3533,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3542,25 +3545,25 @@
         <v>0</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>28</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3568,7 +3571,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3580,25 +3583,25 @@
         <v>0</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3606,7 +3609,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3618,25 +3621,25 @@
         <v>0</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>40</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L23" s="1">
         <v>5</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3644,7 +3647,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3656,25 +3659,25 @@
         <v>0</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3682,7 +3685,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3694,25 +3697,25 @@
         <v>0</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3726,7 +3729,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3738,25 +3741,25 @@
         <v>0</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
@@ -3772,7 +3775,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3784,22 +3787,22 @@
         <v>10011</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3813,7 +3816,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3825,22 +3828,22 @@
         <v>10021</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3854,7 +3857,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3866,22 +3869,22 @@
         <v>10031</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3895,7 +3898,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3907,22 +3910,22 @@
         <v>10041</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3936,7 +3939,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3948,22 +3951,22 @@
         <v>10051</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3977,7 +3980,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -3989,22 +3992,22 @@
         <v>10061</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -4018,7 +4021,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -4030,22 +4033,22 @@
         <v>10071</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="S35" s="6"/>
     </row>
@@ -4071,7 +4074,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4083,22 +4086,22 @@
         <v>10012</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="S37" s="6"/>
     </row>
@@ -4113,7 +4116,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4125,22 +4128,22 @@
         <v>10022</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="S38" s="6"/>
     </row>
@@ -4155,7 +4158,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4167,22 +4170,22 @@
         <v>10032</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="1"/>
@@ -4199,7 +4202,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4211,22 +4214,22 @@
         <v>10042</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="1"/>
@@ -4243,7 +4246,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4255,22 +4258,22 @@
         <v>10052</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P41" s="6"/>
       <c r="S41" s="6"/>
@@ -4286,7 +4289,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4298,22 +4301,22 @@
         <v>10072</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="1"/>
@@ -4342,7 +4345,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4354,22 +4357,22 @@
         <v>10023</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="1"/>
@@ -4386,7 +4389,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4398,22 +4401,22 @@
         <v>10073</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="1"/>
@@ -4442,7 +4445,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4454,22 +4457,22 @@
         <v>10024</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -4487,7 +4490,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4499,23 +4502,23 @@
         <v>10034</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="6"/>
@@ -4957,7 +4960,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4969,22 +4972,22 @@
         <v>0</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
@@ -5008,7 +5011,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -5020,22 +5023,22 @@
         <v>0</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -5059,7 +5062,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -5071,22 +5074,22 @@
         <v>0</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -5110,7 +5113,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -5122,22 +5125,22 @@
         <v>0</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>40</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
@@ -5165,7 +5168,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -5177,16 +5180,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -5218,7 +5221,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -5230,16 +5233,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -5271,7 +5274,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5283,16 +5286,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -5324,7 +5327,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5336,16 +5339,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -5377,7 +5380,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5389,16 +5392,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -5450,7 +5453,7 @@
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5462,25 +5465,25 @@
         <v>0</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>20</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5488,7 +5491,7 @@
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5500,25 +5503,25 @@
         <v>0</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>28</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5526,7 +5529,7 @@
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5538,25 +5541,25 @@
         <v>0</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5564,7 +5567,7 @@
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5576,25 +5579,25 @@
         <v>0</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>40</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5602,7 +5605,7 @@
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5614,25 +5617,25 @@
         <v>0</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5640,7 +5643,7 @@
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5652,25 +5655,25 @@
         <v>0</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5684,7 +5687,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5696,25 +5699,25 @@
         <v>0</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5732,7 +5735,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5744,23 +5747,23 @@
         <v>20011</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O24" s="2"/>
       <c r="XET24" s="1"/>
@@ -5786,7 +5789,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5798,23 +5801,23 @@
         <v>20021</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O25" s="1"/>
       <c r="XET25" s="1"/>
@@ -5840,7 +5843,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5852,23 +5855,23 @@
         <v>20031</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O26" s="1"/>
       <c r="XET26" s="1"/>
@@ -5894,7 +5897,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5906,23 +5909,23 @@
         <v>20041</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O27" s="1"/>
       <c r="XET27" s="1"/>
@@ -5948,7 +5951,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -5960,23 +5963,23 @@
         <v>20051</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="O28" s="1"/>
       <c r="XET28" s="1"/>
@@ -6002,7 +6005,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -6014,23 +6017,23 @@
         <v>20061</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O29" s="1"/>
       <c r="XET29" s="1"/>
@@ -6056,7 +6059,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -6068,23 +6071,23 @@
         <v>20071</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O30" s="1"/>
       <c r="XET30" s="1"/>
@@ -6142,7 +6145,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -6154,23 +6157,23 @@
         <v>20012</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="O32" s="1"/>
       <c r="XET32" s="1"/>
@@ -6196,7 +6199,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -6208,23 +6211,23 @@
         <v>20022</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="O33" s="1"/>
       <c r="XET33" s="1"/>
@@ -6250,7 +6253,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -6262,23 +6265,23 @@
         <v>20032</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O34" s="1"/>
       <c r="XET34" s="1"/>
@@ -6304,7 +6307,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6316,23 +6319,23 @@
         <v>20052</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O35" s="1"/>
       <c r="XET35" s="1"/>
@@ -6358,7 +6361,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6370,23 +6373,23 @@
         <v>20072</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O36" s="1"/>
       <c r="XET36" s="1"/>
@@ -6444,7 +6447,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6456,23 +6459,23 @@
         <v>20023</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O38" s="1"/>
       <c r="XET38" s="1"/>
@@ -6498,7 +6501,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6510,23 +6513,23 @@
         <v>20043</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O39" s="1"/>
       <c r="XET39" s="1"/>
@@ -6552,7 +6555,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6564,22 +6567,22 @@
         <v>20073</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -6613,7 +6616,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6625,22 +6628,22 @@
         <v>20024</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -6659,7 +6662,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6671,22 +6674,22 @@
         <v>20034</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -7062,7 +7065,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -7074,22 +7077,22 @@
         <v>0</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" s="1">
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
@@ -7100,7 +7103,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -7112,22 +7115,22 @@
         <v>0</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J7" s="11" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L7" s="1">
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -7138,7 +7141,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -7150,22 +7153,22 @@
         <v>0</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L8" s="1">
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -7177,7 +7180,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -7189,22 +7192,22 @@
         <v>0</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J9" s="11" t="s">
         <v>40</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L9" s="1">
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
@@ -7222,7 +7225,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -7234,16 +7237,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L10" s="1">
         <v>4</v>
@@ -7264,7 +7267,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -7276,16 +7279,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L11" s="1">
         <v>4</v>
@@ -7306,7 +7309,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7318,16 +7321,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L12" s="1">
         <v>5</v>
@@ -7348,7 +7351,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7360,16 +7363,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L13" s="1">
         <v>5</v>
@@ -7390,7 +7393,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7402,16 +7405,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L14" s="1">
         <v>5</v>
@@ -7429,7 +7432,7 @@
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7441,25 +7444,25 @@
         <v>0</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>20</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L16" s="1">
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7467,7 +7470,7 @@
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7479,25 +7482,25 @@
         <v>0</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>28</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L17" s="1">
         <v>5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7505,7 +7508,7 @@
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7517,25 +7520,25 @@
         <v>0</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>34</v>
       </c>
       <c r="K18" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L18" s="1">
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7543,7 +7546,7 @@
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7555,25 +7558,25 @@
         <v>0</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>40</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L19" s="1">
         <v>5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7581,7 +7584,7 @@
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7593,25 +7596,25 @@
         <v>0</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K20" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L20" s="1">
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7619,7 +7622,7 @@
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7631,25 +7634,25 @@
         <v>0</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K21" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L21" s="1">
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7663,7 +7666,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7675,25 +7678,25 @@
         <v>0</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K22" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L22" s="1">
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7710,7 +7713,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7722,22 +7725,22 @@
         <v>30011</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K24" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O24" s="2"/>
     </row>
@@ -7752,7 +7755,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7764,22 +7767,22 @@
         <v>30021</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="O25" s="2"/>
     </row>
@@ -7794,7 +7797,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7806,22 +7809,22 @@
         <v>30031</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O26" s="2"/>
     </row>
@@ -7836,7 +7839,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7848,22 +7851,22 @@
         <v>30041</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O27" s="2"/>
     </row>
@@ -7878,7 +7881,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7890,22 +7893,22 @@
         <v>30051</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O28" s="2"/>
     </row>
@@ -7920,7 +7923,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7932,22 +7935,22 @@
         <v>30061</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O29" s="2"/>
     </row>
@@ -7962,7 +7965,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7974,22 +7977,22 @@
         <v>30071</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O30" s="2"/>
     </row>
@@ -8013,7 +8016,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -8025,22 +8028,22 @@
         <v>30012</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O32" s="2"/>
     </row>
@@ -8055,7 +8058,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -8067,22 +8070,22 @@
         <v>30022</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O33" s="2"/>
     </row>
@@ -8097,7 +8100,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -8109,22 +8112,22 @@
         <v>30032</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O34" s="2"/>
     </row>
@@ -8139,7 +8142,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -8151,22 +8154,22 @@
         <v>30052</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O35" s="2"/>
     </row>
@@ -8190,7 +8193,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -8202,22 +8205,22 @@
         <v>30023</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O37" s="2"/>
     </row>
@@ -8232,7 +8235,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -8244,22 +8247,22 @@
         <v>30033</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O38" s="2"/>
     </row>
@@ -8274,7 +8277,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -8286,22 +8289,22 @@
         <v>30043</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O39" s="2"/>
     </row>
@@ -8316,7 +8319,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8328,22 +8331,22 @@
         <v>30073</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O40" s="2"/>
     </row>
@@ -8369,7 +8372,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8381,22 +8384,22 @@
         <v>30024</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O42" s="2"/>
     </row>
@@ -8411,7 +8414,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8423,22 +8426,22 @@
         <v>30034</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1069" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="364">
   <si>
     <t>#</t>
   </si>
@@ -3719,12 +3719,6 @@
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
-      <c r="A26" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C26" s="1">
         <v>1107</v>
       </c>
@@ -5677,12 +5671,6 @@
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C22" s="1">
         <v>2107</v>
       </c>
@@ -7656,12 +7644,6 @@
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A22" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C22" s="1">
         <v>3107</v>
       </c>

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="374">
   <si>
     <t>#</t>
   </si>
@@ -460,9 +460,6 @@
     <t>物伤加成</t>
   </si>
   <si>
-    <t>法系技能全等级+1</t>
-  </si>
-  <si>
     <t>法系技能攻速+5%</t>
   </si>
   <si>
@@ -691,6 +688,21 @@
     <t>月华剑阵·疾风</t>
   </si>
   <si>
+    <t>圣战之刃</t>
+  </si>
+  <si>
+    <t>1004,1007,95</t>
+  </si>
+  <si>
+    <t>20,10,3</t>
+  </si>
+  <si>
+    <t>40000021,40000024,40000027</t>
+  </si>
+  <si>
+    <t>解锁神器圣战之刃</t>
+  </si>
+  <si>
     <t>乌木杖</t>
   </si>
   <si>
@@ -910,6 +922,15 @@
     <t>火狱阵法·疾风</t>
   </si>
   <si>
+    <t>法神之杖</t>
+  </si>
+  <si>
+    <t>1005,1008,95</t>
+  </si>
+  <si>
+    <t>解锁神器法神之杖</t>
+  </si>
+  <si>
     <t>青竹剑</t>
   </si>
   <si>
@@ -1127,6 +1148,15 @@
   </si>
   <si>
     <t>毒咒术·疾风</t>
+  </si>
+  <si>
+    <t>道尊之剑</t>
+  </si>
+  <si>
+    <t>1006,1009,95</t>
+  </si>
+  <si>
+    <t>解锁神器道尊之剑</t>
   </si>
 </sst>
 </file>
@@ -3455,17 +3485,6 @@
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1"/>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:15">
-      <c r="A16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
         <v>0</v>
@@ -3475,7 +3494,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="N17" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3486,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1"/>
@@ -3495,7 +3514,7 @@
         <v>1101</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -3507,10 +3526,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="I20" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>146</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>20</v>
@@ -3522,10 +3541,10 @@
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N20" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3533,7 +3552,7 @@
         <v>1102</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -3545,10 +3564,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>150</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>151</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>28</v>
@@ -3560,10 +3579,10 @@
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3571,7 +3590,7 @@
         <v>1103</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -3583,10 +3602,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>154</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>155</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>34</v>
@@ -3598,10 +3617,10 @@
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3609,7 +3628,7 @@
         <v>1104</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -3621,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="I23" s="11" t="s">
         <v>158</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>159</v>
       </c>
       <c r="J23" s="11" t="s">
         <v>40</v>
@@ -3636,10 +3655,10 @@
         <v>5</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3647,7 +3666,7 @@
         <v>1105</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -3659,13 +3678,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="J24" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>164</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>116</v>
@@ -3674,10 +3693,10 @@
         <v>5</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3685,7 +3704,7 @@
         <v>1106</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E25" s="1">
         <v>1</v>
@@ -3697,13 +3716,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="I25" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="J25" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="J25" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>116</v>
@@ -3712,10 +3731,10 @@
         <v>5</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3723,7 +3742,7 @@
         <v>1107</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -3735,13 +3754,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I26" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J26" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>173</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>116</v>
@@ -3750,10 +3769,10 @@
         <v>5</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1"/>
@@ -3769,7 +3788,7 @@
         <v>1101</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -3781,22 +3800,22 @@
         <v>10011</v>
       </c>
       <c r="H29" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="J29" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="K29" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="K29" s="11" t="s">
-        <v>179</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3810,7 +3829,7 @@
         <v>1102</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -3822,22 +3841,22 @@
         <v>10021</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>126</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3851,7 +3870,7 @@
         <v>1103</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -3863,22 +3882,22 @@
         <v>10031</v>
       </c>
       <c r="H31" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I31" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="I31" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>130</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L31" s="1">
         <v>5</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="1:14">
@@ -3892,7 +3911,7 @@
         <v>1104</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -3904,22 +3923,22 @@
         <v>10041</v>
       </c>
       <c r="H32" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I32" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="I32" s="11" t="s">
-        <v>177</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>120</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L32" s="1">
         <v>5</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3933,7 +3952,7 @@
         <v>1105</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3945,22 +3964,22 @@
         <v>10051</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>120</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L33" s="1">
         <v>5</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -3974,7 +3993,7 @@
         <v>1106</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -3986,22 +4005,22 @@
         <v>10061</v>
       </c>
       <c r="H34" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I34" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="I34" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="J34" s="11" t="s">
         <v>126</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L34" s="1">
         <v>5</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="1:20 16374:16384">
@@ -4015,7 +4034,7 @@
         <v>1107</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -4027,22 +4046,22 @@
         <v>10071</v>
       </c>
       <c r="H35" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I35" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="I35" s="11" t="s">
-        <v>177</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>130</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="S35" s="6"/>
     </row>
@@ -4068,7 +4087,7 @@
         <v>1201</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -4080,22 +4099,22 @@
         <v>10012</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>135</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="S37" s="6"/>
     </row>
@@ -4110,7 +4129,7 @@
         <v>1202</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -4122,22 +4141,22 @@
         <v>10022</v>
       </c>
       <c r="H38" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I38" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="I38" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>139</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="S38" s="6"/>
     </row>
@@ -4152,7 +4171,7 @@
         <v>1203</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -4164,22 +4183,22 @@
         <v>10032</v>
       </c>
       <c r="H39" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I39" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="I39" s="11" t="s">
+      <c r="J39" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J39" s="11" t="s">
+      <c r="K39" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P39" s="6"/>
       <c r="Q39" s="1"/>
@@ -4196,7 +4215,7 @@
         <v>1204</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -4208,22 +4227,22 @@
         <v>10042</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I40" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J40" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J40" s="11" t="s">
+      <c r="K40" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P40" s="6"/>
       <c r="Q40" s="1"/>
@@ -4240,7 +4259,7 @@
         <v>1205</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E41" s="1">
         <v>1</v>
@@ -4252,22 +4271,22 @@
         <v>10052</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J41" s="11" t="s">
         <v>120</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L41" s="1">
         <v>5</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P41" s="6"/>
       <c r="S41" s="6"/>
@@ -4283,7 +4302,7 @@
         <v>1207</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -4295,22 +4314,22 @@
         <v>10072</v>
       </c>
       <c r="H42" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I42" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I42" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="J42" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L42" s="1">
         <v>6</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P42" s="6"/>
       <c r="Q42" s="1"/>
@@ -4339,7 +4358,7 @@
         <v>1302</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -4351,22 +4370,22 @@
         <v>10023</v>
       </c>
       <c r="H44" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I44" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="I44" s="11" t="s">
+      <c r="J44" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J44" s="11" t="s">
+      <c r="K44" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L44" s="1">
         <v>6</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P44" s="6"/>
       <c r="Q44" s="1"/>
@@ -4383,7 +4402,7 @@
         <v>1307</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E45" s="1">
         <v>1</v>
@@ -4395,22 +4414,22 @@
         <v>10073</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I45" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J45" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J45" s="11" t="s">
+      <c r="K45" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L45" s="1">
         <v>7</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P45" s="6"/>
       <c r="Q45" s="1"/>
@@ -4439,7 +4458,7 @@
         <v>1402</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -4451,22 +4470,22 @@
         <v>10024</v>
       </c>
       <c r="H47" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I47" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I47" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="J47" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L47" s="1">
         <v>7</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -4484,7 +4503,7 @@
         <v>1403</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -4496,23 +4515,23 @@
         <v>10034</v>
       </c>
       <c r="H48" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I48" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I48" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="J48" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K48" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L48" s="1">
         <v>7</v>
       </c>
       <c r="M48" s="1"/>
       <c r="N48" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O48" s="1"/>
       <c r="P48" s="6"/>
@@ -4561,11 +4580,43 @@
       <c r="XFC49" s="1"/>
       <c r="XFD49" s="1"/>
     </row>
-    <row r="50" customHeight="1" spans="3:20 16374:16384">
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-      <c r="T50" s="1"/>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:20 16374:16384">
+      <c r="C50" s="1">
+        <v>1201</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1">
+        <v>0</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L50" s="1">
+        <v>7</v>
+      </c>
+      <c r="M50" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:20 16374:16384">
       <c r="C51" s="1"/>
@@ -4954,7 +5005,7 @@
         <v>2001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -4966,7 +5017,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>103</v>
@@ -4981,7 +5032,7 @@
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
@@ -5005,7 +5056,7 @@
         <v>2002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="E7" s="1">
         <v>2</v>
@@ -5017,7 +5068,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>109</v>
@@ -5032,7 +5083,7 @@
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -5056,7 +5107,7 @@
         <v>2003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E8" s="1">
         <v>2</v>
@@ -5068,7 +5119,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>112</v>
@@ -5083,7 +5134,7 @@
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -5107,7 +5158,7 @@
         <v>2004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -5119,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>115</v>
@@ -5134,7 +5185,7 @@
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
@@ -5162,7 +5213,7 @@
         <v>2005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="E10" s="1">
         <v>2</v>
@@ -5174,7 +5225,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>119</v>
@@ -5215,7 +5266,7 @@
         <v>2006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E11" s="1">
         <v>2</v>
@@ -5227,7 +5278,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>125</v>
@@ -5268,7 +5319,7 @@
         <v>2007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -5280,7 +5331,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>129</v>
@@ -5321,7 +5372,7 @@
         <v>2008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E13" s="1">
         <v>2</v>
@@ -5333,7 +5384,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>134</v>
@@ -5374,7 +5425,7 @@
         <v>2009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E14" s="1">
         <v>2</v>
@@ -5386,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>138</v>
@@ -5447,7 +5498,7 @@
         <v>2101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E16" s="1">
         <v>2</v>
@@ -5459,10 +5510,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>20</v>
@@ -5474,10 +5525,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5485,7 +5536,7 @@
         <v>2102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E17" s="1">
         <v>2</v>
@@ -5497,10 +5548,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>28</v>
@@ -5512,10 +5563,10 @@
         <v>5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5523,7 +5574,7 @@
         <v>2103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -5535,10 +5586,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>34</v>
@@ -5550,10 +5601,10 @@
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5561,7 +5612,7 @@
         <v>2104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="E19" s="1">
         <v>2</v>
@@ -5573,10 +5624,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>40</v>
@@ -5588,10 +5639,10 @@
         <v>5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5599,7 +5650,7 @@
         <v>2105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="E20" s="1">
         <v>2</v>
@@ -5611,13 +5662,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I20" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="J20" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>164</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>116</v>
@@ -5626,10 +5677,10 @@
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5637,7 +5688,7 @@
         <v>2106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
@@ -5649,13 +5700,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I21" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>116</v>
@@ -5664,10 +5715,10 @@
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5675,7 +5726,7 @@
         <v>2107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="E22" s="1">
         <v>2</v>
@@ -5687,13 +5738,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="I22" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J22" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>173</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>116</v>
@@ -5702,10 +5753,10 @@
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -5723,7 +5774,7 @@
         <v>2101</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -5735,23 +5786,23 @@
         <v>20011</v>
       </c>
       <c r="H24" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I24" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="J24" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="K24" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>179</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="O24" s="2"/>
       <c r="XET24" s="1"/>
@@ -5777,7 +5828,7 @@
         <v>2102</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="E25" s="1">
         <v>2</v>
@@ -5789,23 +5840,23 @@
         <v>20021</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>126</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="O25" s="1"/>
       <c r="XET25" s="1"/>
@@ -5831,7 +5882,7 @@
         <v>2103</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E26" s="1">
         <v>2</v>
@@ -5843,23 +5894,23 @@
         <v>20031</v>
       </c>
       <c r="H26" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I26" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>130</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="O26" s="1"/>
       <c r="XET26" s="1"/>
@@ -5885,7 +5936,7 @@
         <v>2104</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -5897,23 +5948,23 @@
         <v>20041</v>
       </c>
       <c r="H27" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I27" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>177</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>120</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="O27" s="1"/>
       <c r="XET27" s="1"/>
@@ -5939,7 +5990,7 @@
         <v>2105</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E28" s="1">
         <v>2</v>
@@ -5951,23 +6002,23 @@
         <v>20051</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>120</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="O28" s="1"/>
       <c r="XET28" s="1"/>
@@ -5993,7 +6044,7 @@
         <v>2106</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -6005,23 +6056,23 @@
         <v>20061</v>
       </c>
       <c r="H29" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>126</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="O29" s="1"/>
       <c r="XET29" s="1"/>
@@ -6047,7 +6098,7 @@
         <v>2107</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -6059,23 +6110,23 @@
         <v>20071</v>
       </c>
       <c r="H30" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>177</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>130</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="O30" s="1"/>
       <c r="XET30" s="1"/>
@@ -6133,7 +6184,7 @@
         <v>2201</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E32" s="1">
         <v>2</v>
@@ -6145,23 +6196,23 @@
         <v>20012</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>135</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="O32" s="1"/>
       <c r="XET32" s="1"/>
@@ -6187,7 +6238,7 @@
         <v>2202</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -6199,23 +6250,23 @@
         <v>20022</v>
       </c>
       <c r="H33" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>139</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="6" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="O33" s="1"/>
       <c r="XET33" s="1"/>
@@ -6241,7 +6292,7 @@
         <v>2203</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E34" s="1">
         <v>2</v>
@@ -6253,23 +6304,23 @@
         <v>20032</v>
       </c>
       <c r="H34" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I34" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="J34" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J34" s="11" t="s">
+      <c r="K34" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="6" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="O34" s="1"/>
       <c r="XET34" s="1"/>
@@ -6295,7 +6346,7 @@
         <v>2205</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="E35" s="1">
         <v>2</v>
@@ -6307,23 +6358,23 @@
         <v>20052</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>120</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="6" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="O35" s="1"/>
       <c r="XET35" s="1"/>
@@ -6349,7 +6400,7 @@
         <v>2207</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -6361,23 +6412,23 @@
         <v>20072</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I36" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J36" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J36" s="11" t="s">
+      <c r="K36" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L36" s="1">
         <v>6</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="6" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="O36" s="1"/>
       <c r="XET36" s="1"/>
@@ -6435,7 +6486,7 @@
         <v>2302</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="E38" s="1">
         <v>2</v>
@@ -6447,23 +6498,23 @@
         <v>20023</v>
       </c>
       <c r="H38" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I38" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I38" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="J38" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K38" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="6" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="O38" s="1"/>
       <c r="XET38" s="1"/>
@@ -6489,7 +6540,7 @@
         <v>2304</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -6501,23 +6552,23 @@
         <v>20043</v>
       </c>
       <c r="H39" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I39" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I39" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="J39" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="6" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="O39" s="1"/>
       <c r="XET39" s="1"/>
@@ -6543,7 +6594,7 @@
         <v>2307</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="E40" s="1">
         <v>2</v>
@@ -6555,22 +6606,22 @@
         <v>20073</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I40" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J40" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J40" s="11" t="s">
+      <c r="K40" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L40" s="1">
         <v>7</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
@@ -6604,7 +6655,7 @@
         <v>2402</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E42" s="1">
         <v>2</v>
@@ -6616,22 +6667,22 @@
         <v>20024</v>
       </c>
       <c r="H42" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I42" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I42" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="J42" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K42" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -6650,7 +6701,7 @@
         <v>2403</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E43" s="1">
         <v>2</v>
@@ -6662,22 +6713,22 @@
         <v>20034</v>
       </c>
       <c r="H43" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I43" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I43" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="J43" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
@@ -6692,12 +6743,43 @@
       <c r="R44" s="6"/>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" customHeight="1" spans="1:19 16374:16384">
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="1"/>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:19 16374:16384">
+      <c r="C45" s="1">
+        <v>2201</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E45" s="1">
+        <v>2</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L45" s="1">
+        <v>7</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="46" customHeight="1" spans="1:19 16374:16384">
       <c r="O46" s="1"/>
@@ -7053,7 +7135,7 @@
         <v>3001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="E6" s="1">
         <v>3</v>
@@ -7065,7 +7147,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>103</v>
@@ -7080,7 +7162,7 @@
         <v>3</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="N6" s="1" t="s">
         <v>23</v>
@@ -7091,7 +7173,7 @@
         <v>3002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -7103,7 +7185,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>109</v>
@@ -7118,7 +7200,7 @@
         <v>3</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="N7" s="1" t="s">
         <v>23</v>
@@ -7129,7 +7211,7 @@
         <v>3003</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="E8" s="1">
         <v>3</v>
@@ -7141,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>112</v>
@@ -7156,7 +7238,7 @@
         <v>3</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="N8" s="1" t="s">
         <v>23</v>
@@ -7168,7 +7250,7 @@
         <v>3004</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="E9" s="1">
         <v>3</v>
@@ -7180,7 +7262,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="I9" s="11" t="s">
         <v>115</v>
@@ -7195,7 +7277,7 @@
         <v>3</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>23</v>
@@ -7213,7 +7295,7 @@
         <v>3005</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -7225,7 +7307,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="I10" s="11" t="s">
         <v>119</v>
@@ -7255,7 +7337,7 @@
         <v>3006</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E11" s="1">
         <v>3</v>
@@ -7267,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="I11" s="11" t="s">
         <v>125</v>
@@ -7297,7 +7379,7 @@
         <v>3007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="E12" s="1">
         <v>3</v>
@@ -7309,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>129</v>
@@ -7339,7 +7421,7 @@
         <v>3008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -7351,7 +7433,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="I13" s="11" t="s">
         <v>134</v>
@@ -7381,7 +7463,7 @@
         <v>3009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="E14" s="1">
         <v>3</v>
@@ -7393,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>138</v>
@@ -7420,7 +7502,7 @@
         <v>3101</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -7432,10 +7514,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>20</v>
@@ -7447,10 +7529,10 @@
         <v>5</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7458,7 +7540,7 @@
         <v>3102</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="E17" s="1">
         <v>3</v>
@@ -7470,10 +7552,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J17" s="11" t="s">
         <v>28</v>
@@ -7485,10 +7567,10 @@
         <v>5</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7496,7 +7578,7 @@
         <v>3103</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="E18" s="1">
         <v>3</v>
@@ -7508,10 +7590,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>34</v>
@@ -7523,10 +7605,10 @@
         <v>5</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7534,7 +7616,7 @@
         <v>3104</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -7546,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J19" s="11" t="s">
         <v>40</v>
@@ -7561,10 +7643,10 @@
         <v>5</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7572,7 +7654,7 @@
         <v>3105</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="E20" s="1">
         <v>3</v>
@@ -7584,13 +7666,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="I20" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="J20" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>164</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>116</v>
@@ -7599,10 +7681,10 @@
         <v>5</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7610,7 +7692,7 @@
         <v>3106</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="E21" s="1">
         <v>3</v>
@@ -7622,13 +7704,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="I21" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="J21" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>116</v>
@@ -7637,10 +7719,10 @@
         <v>5</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7648,7 +7730,7 @@
         <v>3107</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
@@ -7660,13 +7742,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="I22" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="J22" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>173</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>116</v>
@@ -7675,10 +7757,10 @@
         <v>5</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="1:15">
@@ -7695,7 +7777,7 @@
         <v>3101</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -7707,22 +7789,22 @@
         <v>30011</v>
       </c>
       <c r="H24" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I24" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="J24" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="K24" s="11" t="s">
         <v>178</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>179</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="O24" s="2"/>
     </row>
@@ -7737,7 +7819,7 @@
         <v>3102</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -7749,22 +7831,22 @@
         <v>30021</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J25" s="11" t="s">
         <v>126</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L25" s="1">
         <v>5</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="O25" s="2"/>
     </row>
@@ -7779,7 +7861,7 @@
         <v>3103</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="E26" s="1">
         <v>3</v>
@@ -7791,22 +7873,22 @@
         <v>30031</v>
       </c>
       <c r="H26" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I26" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="J26" s="11" t="s">
         <v>130</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L26" s="1">
         <v>5</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="O26" s="2"/>
     </row>
@@ -7821,7 +7903,7 @@
         <v>3104</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="E27" s="1">
         <v>3</v>
@@ -7833,22 +7915,22 @@
         <v>30041</v>
       </c>
       <c r="H27" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I27" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="I27" s="11" t="s">
-        <v>177</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>120</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L27" s="1">
         <v>5</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="O27" s="2"/>
     </row>
@@ -7863,7 +7945,7 @@
         <v>3105</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -7875,22 +7957,22 @@
         <v>30051</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J28" s="11" t="s">
         <v>120</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L28" s="1">
         <v>5</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="O28" s="2"/>
     </row>
@@ -7905,7 +7987,7 @@
         <v>3106</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="E29" s="1">
         <v>3</v>
@@ -7917,22 +7999,22 @@
         <v>30061</v>
       </c>
       <c r="H29" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="I29" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>126</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L29" s="1">
         <v>5</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="O29" s="2"/>
     </row>
@@ -7947,7 +8029,7 @@
         <v>3107</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="E30" s="1">
         <v>3</v>
@@ -7959,22 +8041,22 @@
         <v>30071</v>
       </c>
       <c r="H30" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I30" s="11" t="s">
         <v>176</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>177</v>
       </c>
       <c r="J30" s="11" t="s">
         <v>130</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L30" s="1">
         <v>5</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="O30" s="2"/>
     </row>
@@ -7998,7 +8080,7 @@
         <v>3201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E32" s="1">
         <v>3</v>
@@ -8010,22 +8092,22 @@
         <v>30012</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>135</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L32" s="1">
         <v>6</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="O32" s="2"/>
     </row>
@@ -8040,7 +8122,7 @@
         <v>3202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="E33" s="1">
         <v>3</v>
@@ -8052,22 +8134,22 @@
         <v>30022</v>
       </c>
       <c r="H33" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I33" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="I33" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>139</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L33" s="1">
         <v>6</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="O33" s="2"/>
     </row>
@@ -8082,7 +8164,7 @@
         <v>3203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -8094,22 +8176,22 @@
         <v>30032</v>
       </c>
       <c r="H34" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I34" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="J34" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J34" s="11" t="s">
+      <c r="K34" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L34" s="1">
         <v>6</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="O34" s="2"/>
     </row>
@@ -8124,7 +8206,7 @@
         <v>3205</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="E35" s="1">
         <v>3</v>
@@ -8136,22 +8218,22 @@
         <v>30052</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J35" s="11" t="s">
         <v>120</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L35" s="1">
         <v>5</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="O35" s="2"/>
     </row>
@@ -8175,7 +8257,7 @@
         <v>3302</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -8187,22 +8269,22 @@
         <v>30023</v>
       </c>
       <c r="H37" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I37" s="11" t="s">
         <v>185</v>
-      </c>
-      <c r="I37" s="11" t="s">
-        <v>186</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>139</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="L37" s="1">
         <v>6</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="O37" s="2"/>
     </row>
@@ -8217,7 +8299,7 @@
         <v>3303</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="E38" s="1">
         <v>3</v>
@@ -8229,22 +8311,22 @@
         <v>30033</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I38" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J38" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J38" s="11" t="s">
+      <c r="K38" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L38" s="1">
         <v>6</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="O38" s="2"/>
     </row>
@@ -8259,7 +8341,7 @@
         <v>3304</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E39" s="1">
         <v>3</v>
@@ -8271,22 +8353,22 @@
         <v>30043</v>
       </c>
       <c r="H39" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I39" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I39" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="J39" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L39" s="1">
         <v>6</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O39" s="2"/>
     </row>
@@ -8301,7 +8383,7 @@
         <v>3307</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -8313,22 +8395,22 @@
         <v>30073</v>
       </c>
       <c r="H40" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="I40" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="I40" s="11" t="s">
+      <c r="J40" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J40" s="11" t="s">
+      <c r="K40" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="O40" s="2"/>
     </row>
@@ -8354,7 +8436,7 @@
         <v>3402</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="E42" s="1">
         <v>3</v>
@@ -8366,22 +8448,22 @@
         <v>30024</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I42" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="J42" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="J42" s="11" t="s">
+      <c r="K42" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L42" s="1">
         <v>7</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="O42" s="2"/>
     </row>
@@ -8396,7 +8478,7 @@
         <v>3403</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="E43" s="1">
         <v>3</v>
@@ -8408,22 +8490,22 @@
         <v>30034</v>
       </c>
       <c r="H43" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="I43" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="I43" s="11" t="s">
-        <v>186</v>
-      </c>
       <c r="J43" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="K43" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="L43" s="1">
         <v>7</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
@@ -8452,31 +8534,43 @@
       <c r="XFC44" s="1"/>
       <c r="XFD44" s="1"/>
     </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="XET45" s="1"/>
-      <c r="XEU45" s="1"/>
-      <c r="XEV45" s="1"/>
-      <c r="XEW45" s="1"/>
-      <c r="XEX45" s="1"/>
-      <c r="XEY45" s="1"/>
-      <c r="XEZ45" s="1"/>
-      <c r="XFA45" s="1"/>
-      <c r="XFB45" s="1"/>
-      <c r="XFC45" s="1"/>
-      <c r="XFD45" s="1"/>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:15 16374:16384">
+      <c r="C45" s="1">
+        <v>3201</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="E45" s="1">
+        <v>3</v>
+      </c>
+      <c r="F45" s="1">
+        <v>0</v>
+      </c>
+      <c r="G45" s="1">
+        <v>0</v>
+      </c>
+      <c r="H45" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="J45" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L45" s="1">
+        <v>7</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="1:15 16374:16384">
       <c r="C47" s="1"/>

--- a/Excel/ExclusiveConfig.xlsx
+++ b/Excel/ExclusiveConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="通用" sheetId="2" r:id="rId1"/>
@@ -6775,7 +6775,7 @@
         <v>7</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>105</v>
+        <v>224</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>297</v>
@@ -8566,7 +8566,7 @@
         <v>7</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>105</v>
+        <v>300</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>373</v>
